--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F63463-A7D9-4FB5-9031-BA3BD9F65957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FF41B7-6BFC-4F98-AB21-F2AEED868480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1461">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5466,6 +5466,406 @@
   </si>
   <si>
     <t>texture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remarkable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enormous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archaeologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neither</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perspective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cetacean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunlight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>destructive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plankton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nearby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>press</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neanderthal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distinction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>French</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ideal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>behind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foreign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enjoy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>furthermore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>independence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>technical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artificial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precede</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guild</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decoration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>originate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radiation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>massive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fundamental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>height</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>butterfly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asteroid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunnnel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apartment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>him</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>export</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secondary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pottery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chimpanzee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occupy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harvest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Australian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conclusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dominant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tuna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restrict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distribution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>movie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>projection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stretch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>requirement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>majority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pastoralism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reliable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frequency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geologic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pleistocene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enhance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accompany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interpret</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snowfall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>musician</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critical</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5938,7 +6338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N859"/>
+  <dimension ref="A1:N914"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -13328,6 +13728,581 @@
         <v>1360</v>
       </c>
     </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A860" s="4">
+        <v>1500</v>
+      </c>
+      <c r="B860" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C860" s="3" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A861" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B861" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C861" s="3" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A862" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B862" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C862" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A863" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B863" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C863" s="3" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A864" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B864" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C864" s="3" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A865" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B865" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C865" s="3" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A866" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B866" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C866" s="3" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A867" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B867" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C867" s="3" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A868" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B868" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C868" s="3" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A869" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B869" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C869" s="3" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A870" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B870" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C870" s="3" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A871" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B871" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C871" s="3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A872" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B872" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C872" s="3" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A873" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B873" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C873" s="3" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A874" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B874" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C874" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A875" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B875" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C875" s="3" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A876" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C876" s="3" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A877" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B877" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C877" s="3" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A878" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B878" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C878" s="3" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A879" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B879" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C879" s="3" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A880" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B880" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C880" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A881" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B881" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C881" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A882" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B882" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C882" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A883" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B883" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C883" s="3" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A884" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B884" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C884" s="3" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A885" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B885" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C885" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A886" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B886" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C886" s="3" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A887" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B887" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C887" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A888" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B888" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C888" s="3" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A889" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B889" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C889" s="3" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A890" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B890" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C890" s="3" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A891" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B891" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C891" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A892" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B892" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C892" s="3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A893" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B893" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C893" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A894" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B894" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C894" s="3" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A895" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B895" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C895" s="3" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A896" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B896" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C896" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A897" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B897" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C897" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A898" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B898" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C898" s="3" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A899" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B899" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C899" s="3" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A900" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B900" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C900" s="3" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A901" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B901" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C901" s="3" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A902" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B902" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C902" s="3" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A903" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B903" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C903" s="3" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A904" s="3">
+        <v>1500</v>
+      </c>
+      <c r="B904" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C904" s="3" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A905" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A906" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A907" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A908" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A909" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A910" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A911" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A912" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A913" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A914" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>1460</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FF41B7-6BFC-4F98-AB21-F2AEED868480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D845CAEB-365A-4DEC-B564-11399E8CE12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1561">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5866,6 +5866,406 @@
   </si>
   <si>
     <t>critical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Netherlands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pollutant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>branch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seawater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicago</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>health</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decorate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>combination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>active</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>send</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boston</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opportunist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dependent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>balance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pollution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drought</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reflective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accumulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alaska</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>context</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perfect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>millennium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>somewhat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>China</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>favorable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>risk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antarctica</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kinetoscope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>representative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enlarge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abandon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhibition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>myth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dramatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>promise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wooden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>composer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glaciation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transfer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prediction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stencil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distinctive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>France</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toxic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herbivore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cross</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tornado</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metallic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shallow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6338,7 +6738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N914"/>
+  <dimension ref="A1:N967"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -14303,6 +14703,571 @@
         <v>1460</v>
       </c>
     </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A915" s="4">
+        <v>1600</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A916" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A917" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A918" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B918" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A919" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B919" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A920" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C920" s="3" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A921" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B921" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C921" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A922" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B922" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C922" s="3" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A923" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B923" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C923" s="3" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A924" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B924" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A925" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B925" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A926" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B926" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A927" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A928" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B928" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A929" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B929" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A930" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B930" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A931" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A932" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A933" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B933" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A934" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B934" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A935" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B935" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A936" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B936" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A937" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B937" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A938" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B938" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C938" s="3" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A939" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B939" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C939" s="3" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A940" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B940" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C940" s="3" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A941" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B941" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C941" s="3" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A942" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B942" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C942" s="3" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A943" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B943" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C943" s="3" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A944" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B944" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C944" s="3" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A945" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B945" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C945" s="3" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A946" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B946" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C946" s="3" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A947" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B947" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C947" s="3" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A948" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B948" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C948" s="3" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A949" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B949" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A950" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B950" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C950" s="3" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A951" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B951" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C951" s="3" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A952" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B952" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C952" s="3" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A953" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B953" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C953" s="3" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A954" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B954" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C954" s="3" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A955" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B955" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C955" s="3" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A956" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B956" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C956" s="3" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A957" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B957" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C957" s="3" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A958" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B958" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C958" s="3" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A959" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B959" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C959" s="3" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A960" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B960" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C960" s="3" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A961" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B961" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C961" s="3" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A962" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C962" s="3" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A963" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C963" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A964" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C964" s="3" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A965" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C965" s="3" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A966" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C966" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A967" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>1560</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D845CAEB-365A-4DEC-B564-11399E8CE12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422C0B5D-7DCD-4A9E-B7AD-CF4828880673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="1661">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6266,6 +6266,406 @@
   </si>
   <si>
     <t>shallow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surplus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>possibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>novel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afford</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southeast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>northwest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lung</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temperate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>widespread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isotope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nevertheless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wheat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parlor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tendency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flourish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evolutionary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turbine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>highland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>communicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comparative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>newly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indirect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>destruction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>customer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suddenly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multiple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vitamin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vegetable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conclude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rough</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corridor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>challenger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fragment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occasionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>component</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprehension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physiological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ceremony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>altitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microscopic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>schedule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>former</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>career</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inventor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atmospheric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>province</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>introduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squirrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x-ray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tulip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pueblo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pebble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obvious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limestone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sumerian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gazelle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Columbia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evaporation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archaeology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dweller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>possess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elsewhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasonal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6738,7 +7138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N967"/>
+  <dimension ref="A1:N1023"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -15268,6 +15668,586 @@
         <v>1560</v>
       </c>
     </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A968" s="4">
+        <v>1700</v>
+      </c>
+      <c r="B968" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C968" s="3" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A969" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B969" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C969" s="3" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A970" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B970" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A971" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B971" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C971" s="3" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A972" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B972" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C972" s="3" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A973" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B973" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C973" s="3" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A974" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B974" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C974" s="3" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A975" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B975" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C975" s="3" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A976" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B976" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C976" s="3" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A977" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B977" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C977" s="3" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A978" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B978" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C978" s="3" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A979" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B979" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C979" s="3" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A980" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B980" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C980" s="3" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A981" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B981" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C981" s="3" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A982" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B982" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C982" s="3" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A983" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B983" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C983" s="3" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A984" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B984" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A985" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B985" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C985" s="3" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A986" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B986" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C986" s="3" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A987" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B987" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C987" s="3" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A988" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B988" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C988" s="3" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A989" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B989" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C989" s="3" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A990" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B990" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C990" s="3" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A991" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B991" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C991" s="3" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A992" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B992" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C992" s="3" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A993" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B993" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A994" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B994" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C994" s="3" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A995" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B995" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C995" s="3" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A996" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B996" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A997" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B997" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A998" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B998" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A999" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B999" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1000" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1000" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1001" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1001" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1002" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1002" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1003" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1003" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1004" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1004" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1005" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1005" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C1005" s="3" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1006" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1006" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1007" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1007" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1008" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1008" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1009" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1009" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1010" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1010" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1011" s="3">
+        <v>1700</v>
+      </c>
+      <c r="B1011" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1012" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1013" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1014" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1015" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1016" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1017" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1018" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1019" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1020" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1021" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1022" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1023" s="3">
+        <v>1700</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>1658</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422C0B5D-7DCD-4A9E-B7AD-CF4828880673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63089323-0EAE-45BE-A442-5CE567A7AEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="1661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1761">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6666,6 +6666,406 @@
   </si>
   <si>
     <t>seasonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assemble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>college</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>definition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>border</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>household</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sandstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sweden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speech</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crisis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>literary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pioneer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criticize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>originally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salinity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>room</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dynasty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>livestock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drama</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colonist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>algae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lowland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>otherwise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>round</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vertebrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sixteenth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smooth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scheme</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bright</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthropologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discipline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opposite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oyster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volcano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>love</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steady</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>full</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>universal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>union</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>terrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wildebeest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resistance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>candidate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>museum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hormone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>countryside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thereby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>track</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>porcelain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pellet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spectrum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mesozoic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rigid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Denmark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>functional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cultivation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impossible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domestic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emphasis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colonize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flipper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peninsula</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7138,7 +7538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1023"/>
+  <dimension ref="A1:N1073"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -16248,6 +16648,556 @@
         <v>1658</v>
       </c>
     </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1024" s="4">
+        <v>1800</v>
+      </c>
+      <c r="B1024" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1025" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1025" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1026" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1026" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1027" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1027" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1028" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1028" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1029" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1029" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1030" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1030" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1031" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1031" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1032" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1032" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1033" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1033" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1034" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1034" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1035" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1035" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1036" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1036" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1037" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1037" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1038" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1038" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1039" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1039" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1040" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1040" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1041" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1041" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1042" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1042" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1043" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1043" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1044" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1044" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1045" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1045" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1046" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1046" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1047" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1047" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1048" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1048" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1049" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1049" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1050" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1050" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1051" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1051" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1052" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1052" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1053" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1053" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1054" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1055" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1056" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1057" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1058" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1059" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1060" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1060" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1061" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1061" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1062" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1063" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1063" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1064" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1065" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1066" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1067" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1068" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1069" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1070" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1071" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1072" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1073" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>1760</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63089323-0EAE-45BE-A442-5CE567A7AEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ED96EC-1AC1-48B8-936E-5C3A1602DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1860">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7066,6 +7066,402 @@
   </si>
   <si>
     <t>peninsula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>droplet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paleontologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apprentice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grandma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>justify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cereal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feeling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fossilizzation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consistent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>policy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greece</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>screen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freezing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mislead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice-free</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aurora</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zebra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whatever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scandinavian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paris</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long-term</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fracture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investigator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interpretation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transformation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calculate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>establishment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canopy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consumption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reservoir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumstance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>severe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satellite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trouble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>architect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhibitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undergo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fragile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>responsibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exaggerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyscraper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>win</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluctuation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>partner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>argument</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>furniture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>systematic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maker</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7538,7 +7934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1073"/>
+  <dimension ref="A1:N1123"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -17198,6 +17594,556 @@
         <v>1760</v>
       </c>
     </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1074" s="4">
+        <v>1900</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1075" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1076" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1077" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1078" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1079" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1080" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1081" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1082" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1083" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1084" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1085" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1086" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1087" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1088" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1089" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1090" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C1090" s="3" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1091" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1091" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C1091" s="3" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1092" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1092" s="3" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1093" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1093" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C1093" s="3" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1094" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1095" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1096" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1096" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1097" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1098" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1098" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1099" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1099" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1101" s="3" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1102" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1103" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1103" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1104" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1104" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1105" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1106" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1106" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1107" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1108" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1108" s="3" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1109" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1110" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1111" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1112" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1113" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1114" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1115" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1115" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1116" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1117" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1118" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1118" s="3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1119" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1120" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1121" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1122" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1122" s="3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1123" s="3">
+        <v>1900</v>
+      </c>
+      <c r="B1123" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C1123" s="3" t="s">
+        <v>1858</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ED96EC-1AC1-48B8-936E-5C3A1602DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D59F1CB-4300-42DA-83C6-F1BA323946E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="1960">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7462,6 +7462,406 @@
   </si>
   <si>
     <t>maker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reservation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perceive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convince</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nervous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>challenge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hyper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eliminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warren</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resident</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linguistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cucumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elaborate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mystery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sustain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>latitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clothe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>news</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>organ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earthenware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wagon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>achiecement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inhabit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>federal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>govern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>philosophy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offspring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hawaii</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pigeon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>your</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>territory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gulf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calcium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vital</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poetry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entrance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chemistry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oppose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portrait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scatter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>islander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recognition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proxy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neolithic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voyage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Texas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rank</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7934,7 +8334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1123"/>
+  <dimension ref="A1:N1187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -18144,6 +18544,626 @@
         <v>1858</v>
       </c>
     </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1124" s="4">
+        <v>2000</v>
+      </c>
+      <c r="B1124" s="3" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1125" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1125" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1126" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1126" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1127" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1127" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C1127" s="3" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1128" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1128" s="3" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1128" s="3" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1129" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1129" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C1129" s="3" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1130" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1130" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1130" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1131" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1131" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1131" s="3" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1132" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1132" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C1132" s="3" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1133" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1133" s="3" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C1133" s="3" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1134" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1134" s="3" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C1134" s="3" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1135" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1135" s="3" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C1135" s="3" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1136" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1136" s="3" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1136" s="3" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1137" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1137" s="3" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C1137" s="3" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1138" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1138" s="3" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C1138" s="3" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1139" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1139" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C1139" s="3" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1140" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1140" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C1140" s="3" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1141" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1141" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C1141" s="3" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1142" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1142" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C1142" s="3" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1143" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1143" s="3" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C1143" s="3" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1144" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1144" s="3" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C1144" s="3" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1145" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1145" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C1145" s="3" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1146" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1146" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C1146" s="3" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1147" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1147" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1147" s="3" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1148" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1148" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C1148" s="3" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1149" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1149" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C1149" s="3" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1150" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1150" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C1150" s="3" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1151" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1151" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1151" s="3" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1152" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1152" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C1152" s="3" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1153" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1153" s="3" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C1153" s="3" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1154" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1154" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C1154" s="3" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1155" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1155" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C1155" s="3" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1156" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1156" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C1156" s="3" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1157" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1157" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1157" s="3" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1158" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1158" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C1158" s="3" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1159" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B1159" s="3" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1159" s="3" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1160" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1160" s="3" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1161" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1161" s="3" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1162" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1162" s="3" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1163" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1163" s="3" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1164" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1164" s="3" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1165" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1165" s="3" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1166" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1166" s="3" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1167" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1167" s="3" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1168" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1168" s="3" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1169" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1169" s="3" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1170" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1170" s="3" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1171" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1171" s="3" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1172" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1172" s="3" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1173" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1173" s="3" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1174" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1174" s="3" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1175" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1175" s="3" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1176" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1176" s="3" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1177" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1177" s="3" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1178" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1178" s="3" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1179" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1179" s="3" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1180" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1180" s="3" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1181" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1181" s="3" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1182" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1182" s="3" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1183" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1184" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1184" s="3" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1185" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1185" s="3" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1186" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1186" s="4" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1187" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C1187" s="3" t="s">
+        <v>1958</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D59F1CB-4300-42DA-83C6-F1BA323946E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DE59BC-ECC8-4C14-8C89-8BBFD137CF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="1960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="2060">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7862,6 +7862,406 @@
   </si>
   <si>
     <t>rank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concentrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>container</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ecology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>runoff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watercolor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>streamline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mantle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hungry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>episode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crossbill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emergence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrialize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hominid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cinema</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kittiwake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertainment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everything</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purchase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sanctuary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theatrical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profession</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theme</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gravel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commerce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aluminum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puzzle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>performer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dramatically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dependence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>struggle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>German</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irregular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>centimeter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colonization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fund</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>historian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>female</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retreat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invertebrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbiotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alternative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vertical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quarter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doubt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tennessee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>treat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>politician</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>politics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beauty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>format</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spanish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confirm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engraving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specimen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weigh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>encounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>costume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nouveau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>log</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glaze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>martian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>latter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8334,7 +8734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1187"/>
+  <dimension ref="A1:N1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -19164,6 +19564,591 @@
         <v>1958</v>
       </c>
     </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1188" s="4">
+        <v>2100</v>
+      </c>
+      <c r="B1188" s="3" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1188" s="3" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1189" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1189" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C1189" s="3" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1190" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1190" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1190" s="3" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1191" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1191" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C1191" s="3" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1192" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1192" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C1192" s="3" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1193" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1193" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1193" s="3" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1194" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1194" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1194" s="3" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1195" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1195" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C1195" s="3" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1196" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1196" s="3" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C1196" s="3" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1197" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1197" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C1197" s="3" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1198" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1198" s="3" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C1198" s="3" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1199" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1199" s="3" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C1199" s="3" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1200" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1200" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C1200" s="3" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1201" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1201" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C1201" s="3" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1202" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1202" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1202" s="3" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1203" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1203" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C1203" s="3" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1204" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1204" s="3" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C1204" s="3" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1205" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1205" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C1205" s="3" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1206" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1206" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1206" s="3" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1207" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1207" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C1207" s="3" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1208" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1208" s="3" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1208" s="3" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1209" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1209" s="3" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C1209" s="3" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1210" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1210" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C1210" s="3" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1211" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1211" s="3" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C1211" s="3" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1212" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1212" s="3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C1212" s="3" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1213" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1213" s="3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C1213" s="3" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1214" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1214" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1214" s="3" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1215" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1215" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1215" s="3" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1216" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1216" s="3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C1216" s="3" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1217" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1217" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C1217" s="3" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1218" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1218" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1218" s="3" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1219" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1219" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C1219" s="3" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1220" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1220" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1220" s="3" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1221" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1221" s="3" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C1221" s="3" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1222" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1222" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C1222" s="3" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1223" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1223" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C1223" s="3" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1224" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1224" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C1224" s="3" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1225" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1225" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C1225" s="3" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1226" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1226" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C1226" s="3" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1227" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1227" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C1227" s="3" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1228" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1228" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1228" s="3" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1229" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1229" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C1229" s="3" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1230" s="3">
+        <v>2100</v>
+      </c>
+      <c r="B1230" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C1230" s="3" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1231" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1231" s="3" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1232" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1232" s="3" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1233" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1233" s="3" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1234" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1234" s="3" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1235" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1235" s="3" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1236" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1237" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1237" s="3" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1238" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1239" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1239" s="3" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1240" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1240" s="3" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1241" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1241" s="3" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1242" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1242" s="3" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1243" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1243" s="3" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1244" s="3">
+        <v>2100</v>
+      </c>
+      <c r="C1244" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DE59BC-ECC8-4C14-8C89-8BBFD137CF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923F21CB-A713-493C-8886-28E83D1C7192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="2060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="2160">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -8262,6 +8262,405 @@
   </si>
   <si>
     <t>latter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occurrence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anything</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prevail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reliance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roof</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercantile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fossilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cylinder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>countercurrent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potter</t>
+  </si>
+  <si>
+    <t>aesthetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neighborhood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hemisphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excavate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reclamation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ensure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incorporate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aboriginal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>automatically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>version</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drawing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>income</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freedom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mississippi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cartoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>separation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recharge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motivation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penetrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nerve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engrave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disadvantage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constitute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graham</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turnpike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>load</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mixture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expressive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>row</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discourage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tremendous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>astronomer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Erie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inhibit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yucatan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alkali</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complexity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedimentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accelerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>window</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>representation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enclose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluctuate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>furnace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reptile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>popularity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>institution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbolic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>religion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conserve</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8734,7 +9133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1244"/>
+  <dimension ref="A1:N1310"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -20149,8 +20548,639 @@
         <v>2057</v>
       </c>
     </row>
+    <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1245" s="4">
+        <v>2200</v>
+      </c>
+      <c r="B1245" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C1245" s="3" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1246" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1246" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1246" s="3" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1247" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1247" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C1247" s="3" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1248" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1248" s="3" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C1248" s="3" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1249" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1249" s="3" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1249" s="3" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1250" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1250" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C1250" s="3" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1251" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1251" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1251" s="3" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1252" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1252" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C1252" s="3" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1253" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1253" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C1253" s="3" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1254" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1254" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C1254" s="3" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1255" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1255" s="3" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C1255" s="3" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1256" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1256" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C1256" s="3" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1257" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1257" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C1257" s="3" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1258" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1258" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1258" s="3" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1259" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1259" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C1259" s="3" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1260" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1260" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C1260" s="3" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1261" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1261" s="3" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C1261" s="3" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1262" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1262" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C1262" s="3" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1263" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1263" s="3" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1263" s="3" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1264" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1264" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C1264" s="3" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1265" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1265" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C1265" s="3" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1266" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1266" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C1266" s="3" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1267" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1267" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C1267" s="3" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1268" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1268" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C1268" s="3" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1269" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1269" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C1269" s="3" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1270" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1270" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C1270" s="3" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1271" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1271" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1271" s="3" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1272" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1272" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1272" s="3" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1273" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1273" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1273" s="3" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1274" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1274" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C1274" s="3" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1275" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1275" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1275" s="3" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1276" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1276" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C1276" s="3" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1277" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1277" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C1277" s="3" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1278" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B1278" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C1278" s="4" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1279" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1279" s="3" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1280" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1280" s="3" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1281" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1281" s="3" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1282" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1282" s="3" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1283" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1283" s="3" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1284" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1284" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1285" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1285" s="3" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1286" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1286" s="3" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1287" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1287" s="3" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1288" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1288" s="3" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1289" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1289" s="3" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1290" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1290" s="3" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1291" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1291" s="3" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1292" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1292" s="3" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1293" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1293" s="3" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1294" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1294" s="3" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1295" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1295" s="3" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1296" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1296" s="3" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1297" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1297" s="3" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1298" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1298" s="3" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1299" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1299" s="3" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1300" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1300" s="3" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1301" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1301" s="3" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1302" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1302" s="3" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1303" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1303" s="3" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1304" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1304" s="3" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1305" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1305" s="3" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1306" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1306" s="3" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1307" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1307" s="3" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1308" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1308" s="3" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1309" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1309" s="3" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1310" s="3">
+        <v>2200</v>
+      </c>
+      <c r="C1310" s="3" t="s">
+        <v>2155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923F21CB-A713-493C-8886-28E83D1C7192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F9EDFD-4181-46DE-AB21-6D77411A84F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="2160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="2259">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -8661,6 +8661,402 @@
   </si>
   <si>
     <t>conserve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traffic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harvard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Himalaya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>digest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>application</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gravity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explorer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>educate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sudden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>present-day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precipitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lewis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oceanic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>award</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comfortable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>publisher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>touch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>administration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>durable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undertake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assumption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ohio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exceed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>switch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southwestern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infantile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crucial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amnesia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nutritional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taste</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contradict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verbal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supplement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delivery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>span</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comparable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satisfy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>panel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>react</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freshwater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>official</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>save</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crustal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>threat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carbohydrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>periodical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strengthen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quartz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sociologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leadership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>King</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colleague</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indo-european</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seafloor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bronze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>found</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instruction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>partially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Germany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beautiful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vehivcle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marsh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrigue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artwork</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9133,7 +9529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1310"/>
+  <dimension ref="A1:N1365"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -21178,6 +21574,581 @@
         <v>2155</v>
       </c>
     </row>
+    <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1311" s="4">
+        <v>2300</v>
+      </c>
+      <c r="B1311" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C1311" s="3" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1312" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1312" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C1312" s="3" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1313" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1313" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C1313" s="3" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1314" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1314" s="3" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C1314" s="3" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1315" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1315" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C1315" s="3" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1316" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1316" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C1316" s="3" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1317" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1317" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C1317" s="3" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1318" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1318" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C1318" s="3" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1319" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1319" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C1319" s="3" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1320" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1320" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C1320" s="3" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1321" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1321" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1321" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1322" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1322" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C1322" s="3" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1323" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1323" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C1323" s="3" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1324" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1324" s="3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C1324" s="3" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1325" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1325" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C1325" s="3" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1326" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1326" s="3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C1326" s="3" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1327" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1327" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C1327" s="3" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1328" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1328" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1328" s="3" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1329" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1329" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C1329" s="3" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1330" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1330" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C1330" s="3" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1331" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1331" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C1331" s="3" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1332" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1332" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C1332" s="3" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1333" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1333" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C1333" s="3" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1334" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1334" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C1334" s="3" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1335" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1335" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C1335" s="3" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1336" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1336" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C1336" s="3" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1337" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1337" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C1337" s="3" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1338" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1338" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C1338" s="3" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1339" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1339" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C1339" s="3" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1340" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1340" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C1340" s="3" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1341" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1341" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C1341" s="3" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1342" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1342" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C1342" s="3" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1343" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1343" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C1343" s="3" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1344" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1344" s="3" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C1344" s="3" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1345" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1345" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C1345" s="3" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1346" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1346" s="3" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C1346" s="3" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1347" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1347" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C1347" s="3" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1348" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1348" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C1348" s="3" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1349" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1349" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C1349" s="3" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1350" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1350" s="3" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C1350" s="3" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1351" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1351" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C1351" s="3" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1352" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1352" s="3" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C1352" s="3" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1353" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1353" s="3" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C1353" s="3" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1354" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1354" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C1354" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1355" s="3">
+        <v>2300</v>
+      </c>
+      <c r="B1355" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C1355" s="3" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1356" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1356" s="3" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1357" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1357" s="3" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1358" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1358" s="3" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1359" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1359" s="3" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1360" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1360" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1361" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1361" s="3" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1362" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1362" s="3" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1363" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1363" s="3" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1364" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1364" s="3" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1365" s="3">
+        <v>2300</v>
+      </c>
+      <c r="C1365" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F9EDFD-4181-46DE-AB21-6D77411A84F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8FF88-9358-4369-9A81-8014B6F0BE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="2259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="2359">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -9057,6 +9057,405 @@
   </si>
   <si>
     <t>artwork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tube</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiln</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awareness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>velocity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>academy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imprint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intellectual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iridium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mobility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strongly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>footprint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herself</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sponsor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calorie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpredictable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>automobile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enzyme</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>employee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irrigate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dozen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retrieve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>printer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surveyor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worldwide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nuclear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nutrition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>larva</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sharp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peasant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palstic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accumulator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chief</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beneficial</t>
+  </si>
+  <si>
+    <t>lip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fertilizer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rainwater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epoch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foundation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evident</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>race</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barren</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prosperity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lava</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descriptive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruminant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stoneware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mirror</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>norm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nitinol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9529,7 +9928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1365"/>
+  <dimension ref="A1:N1438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -22149,6 +22548,671 @@
         <v>2257</v>
       </c>
     </row>
+    <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1366" s="4">
+        <v>2400</v>
+      </c>
+      <c r="B1366" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C1366" s="3" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1367" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1367" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C1367" s="3" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1368" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1368" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C1368" s="3" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1369" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1369" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C1369" s="3" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1370" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1370" s="3" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1370" s="3" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1371" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1371" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C1371" s="3" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1372" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1372" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C1372" s="3" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1373" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1373" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C1373" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1374" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1374" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C1374" s="3" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1375" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1375" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C1375" s="3" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1376" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1376" s="3" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C1376" s="3" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1377" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1377" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C1377" s="3" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1378" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1378" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C1378" s="3" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1379" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1379" s="3" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C1379" s="3" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1380" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1380" s="3" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C1380" s="3" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1381" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1381" s="3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C1381" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1382" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1382" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C1382" s="3" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1383" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1383" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C1383" s="3" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1384" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1384" s="3" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C1384" s="3" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1385" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1385" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C1385" s="3" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1386" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1386" s="3" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C1386" s="3" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1387" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1387" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C1387" s="3" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1388" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1388" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1388" s="3" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1389" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1389" s="3" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C1389" s="3" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1390" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1390" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C1390" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1391" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1391" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C1391" s="3" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1392" s="3">
+        <v>2400</v>
+      </c>
+      <c r="B1392" s="3" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C1392" s="3" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1393" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1393" s="3" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1394" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1394" s="3" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1395" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1395" s="3" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1396" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1396" s="3" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1397" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1397" s="3" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1398" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1398" s="3" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1399" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1399" s="3" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1400" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1400" s="3" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1401" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1401" s="3" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1402" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1402" s="3" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1403" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1403" s="3" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1404" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1404" s="3" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1405" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1405" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1406" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1406" s="3" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1407" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1407" s="3" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1408" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1408" s="3" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1409" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1409" s="3" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1410" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1410" s="3" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1411" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1411" s="3" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1412" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1412" s="3" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1413" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1413" s="3" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1414" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1414" s="3" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1415" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1415" s="3" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1416" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1416" s="3" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1417" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1417" s="3" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1418" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1418" s="3" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1419" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1419" s="3" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1420" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1420" s="3" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1421" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1421" s="3" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1422" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1422" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1423" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1423" s="4" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1424" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1424" s="3" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1425" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1425" s="3" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1426" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1426" s="3" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1427" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1427" s="3" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1428" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1428" s="3" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1429" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1429" s="3" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1430" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1430" s="3" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1431" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1431" s="3" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1432" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1432" s="3" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1433" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1433" s="3" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1434" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1434" s="3" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1435" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1435" s="3" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1436" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1436" s="3" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1437" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1437" s="3" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1438" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C1438" s="3" t="s">
+        <v>2357</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8FF88-9358-4369-9A81-8014B6F0BE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B958E1-06E7-439A-A01F-2C44945A984F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="2458">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -9456,6 +9456,402 @@
   </si>
   <si>
     <t>client</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potentially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fertile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>background</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>facilitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flexible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precisely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>egalitarian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shelve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>judge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>progressive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjacent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfortunately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>downward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warbler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specialization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>media</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workweek</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extensively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nutritious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>throw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eka-aluminum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mammoth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tellurium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hopewell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>facility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>percentage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>butter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evaluate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occupation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fauna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diacharge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indicator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steamboat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>highten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archaeopteryx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disclaimer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desirable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carbonate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southeastern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scarce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obviously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Missouri</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>department</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>senate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mobile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pearl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>westward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>being</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forecast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excellent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conceal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naturalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stomach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sloth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interfere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perceptual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plentiful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>childhood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proterozoic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>falcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orchid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>semiarid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>renaissance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maintenance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sibling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regardless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>click</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kestrel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9928,7 +10324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1438"/>
+  <dimension ref="A1:N1508"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -23213,6 +23609,656 @@
         <v>2357</v>
       </c>
     </row>
+    <row r="1439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1439" s="4">
+        <v>2500</v>
+      </c>
+      <c r="B1439" s="3" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C1439" s="3" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1440" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1440" s="3" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C1440" s="3" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1441" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1441" s="3" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C1441" s="3" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1442" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1442" s="3" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1442" s="3" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1443" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1443" s="3" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C1443" s="3" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1444" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1444" s="3" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C1444" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1445" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1445" s="3" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C1445" s="3" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1446" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1446" s="3" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C1446" s="3" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1447" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1447" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C1447" s="3" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1448" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1448" s="3" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C1448" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1449" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1449" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C1449" s="3" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1450" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1450" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C1450" s="3" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1451" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1451" s="3" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C1451" s="3" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1452" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1452" s="3" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C1452" s="3" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1453" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1453" s="3" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C1453" s="3" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1454" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1454" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C1454" s="3" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1455" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1455" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="C1455" s="3" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1456" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1456" s="3" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C1456" s="3" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1457" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1457" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C1457" s="3" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1458" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1458" s="3" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C1458" s="3" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1459" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1459" s="3" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C1459" s="3" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1460" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1460" s="3" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C1460" s="3" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1461" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1461" s="3" t="s">
+        <v>2429</v>
+      </c>
+      <c r="C1461" s="3" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1462" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1462" s="3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C1462" s="3" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1463" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1463" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C1463" s="3" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1464" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1464" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C1464" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1465" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1465" s="3" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C1465" s="3" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1466" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1466" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C1466" s="3" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1467" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1467" s="3" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C1467" s="3" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1468" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B1468" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C1468" s="3" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1469" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1469" s="3" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1470" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1470" s="3" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1471" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1471" s="3" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1472" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1472" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1473" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1473" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1474" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1474" s="3" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1475" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1475" s="3" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1476" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1476" s="3" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1477" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1477" s="3" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1478" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1478" s="3" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1479" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1479" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1480" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1480" s="3" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1481" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1481" s="3" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1482" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1482" s="3" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1483" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1483" s="3" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1484" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1484" s="3" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1485" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1485" s="3" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1486" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1486" s="3" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1487" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1487" s="3" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1488" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1488" s="3" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1489" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1489" s="3" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1490" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1490" s="3" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1491" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1491" s="3" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1492" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1492" s="3" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1493" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1493" s="3" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1494" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1494" s="3" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1495" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1495" s="3" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1496" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1496" s="3" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1497" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1497" s="3" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1498" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1498" s="3" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1499" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1499" s="3" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1500" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1500" s="3" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1501" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1501" s="3" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1502" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1502" s="3" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1503" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1503" s="3" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1504" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1504" s="3" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1505" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1505" s="3" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1506" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1506" s="3" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1507" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1507" s="3" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1508" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C1508" s="3" t="s">
+        <v>2457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B958E1-06E7-439A-A01F-2C44945A984F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F709312-D687-4C6D-8AA6-2687013B7D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="2458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="2558">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -9852,6 +9852,406 @@
   </si>
   <si>
     <t>kestrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spontaneous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earthquake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cognitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maximum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spiral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relevant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>straight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elevation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sahara</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wavelength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passenger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>highway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>molt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>columbian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equivalent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graduate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everywhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>succeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commodity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>experimental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crystalline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thirty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revolutionary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luxury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scandinavia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dairy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substantial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>continually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warm-blooded</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calcite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orchestra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>me</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intermediate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proponent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>partnership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>republican</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ichthyosaur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>India</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>niche</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magazine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tribal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storytelling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>district</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stationary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>measurement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pleasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snowflake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swallow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insufficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telephone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pterosaur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fifteen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squeeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>populate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gallery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>porous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disturb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harbor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long-distance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protein</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inexpensive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equatorial</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10324,7 +10724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1508"/>
+  <dimension ref="A1:N1579"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -24259,6 +24659,661 @@
         <v>2457</v>
       </c>
     </row>
+    <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1509" s="4">
+        <v>2600</v>
+      </c>
+      <c r="B1509" s="3" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C1509" s="3" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1510" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1510" s="3" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C1510" s="3" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1511" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1511" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C1511" s="3" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1512" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1512" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C1512" s="3" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1513" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1513" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C1513" s="3" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1514" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1514" s="3" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C1514" s="3" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1515" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1515" s="3" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C1515" s="3" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1516" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1516" s="3" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C1516" s="3" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1517" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1517" s="3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C1517" s="3" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1518" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1518" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C1518" s="3" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1519" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1519" s="3" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C1519" s="3" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1520" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1520" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C1520" s="3" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1521" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1521" s="3" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C1521" s="3" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1522" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1522" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C1522" s="3" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1523" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1523" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C1523" s="3" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1524" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1524" s="3" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C1524" s="3" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1525" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1525" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="C1525" s="3" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1526" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1526" s="3" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C1526" s="3" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1527" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1527" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C1527" s="3" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1528" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1528" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="C1528" s="3" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1529" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1529" s="3" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C1529" s="3" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1530" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1530" s="3" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C1530" s="3" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1531" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1531" s="3" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C1531" s="3" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1532" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1532" s="3" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C1532" s="3" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1533" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1533" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C1533" s="3" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1534" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1534" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C1534" s="3" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1535" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1535" s="3" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C1535" s="3" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1536" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1536" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C1536" s="3" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1537" s="3">
+        <v>2600</v>
+      </c>
+      <c r="B1537" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C1537" s="3" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1538" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1538" s="3" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1539" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1539" s="3" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1540" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1540" s="3" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1541" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1541" s="3" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1542" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1542" s="3" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1543" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1543" s="3" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1544" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1544" s="3" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1545" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1545" s="3" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1546" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1546" s="3" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1547" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1547" s="3" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1548" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1548" s="3" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1549" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1549" s="3" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1550" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1550" s="3" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1551" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1551" s="3" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1552" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1552" s="3" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1553" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1553" s="3" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1554" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1554" s="3" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1555" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1555" s="3" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1556" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1556" s="3" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1557" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1557" s="3" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1558" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1558" s="3" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1559" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1559" s="3" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1560" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1560" s="3" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1561" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1561" s="3" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1562" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1562" s="3" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1563" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1563" s="3" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1564" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1564" s="3" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1565" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1565" s="3" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1566" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1566" s="3" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1567" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1567" s="3" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1568" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1568" s="3" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1569" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1569" s="3" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1570" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1570" s="3" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1571" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1571" s="3" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1572" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1572" s="3" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1573" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1573" s="3" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1574" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1574" s="3" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1575" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1575" s="3" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1576" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1576" s="3" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1577" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1577" s="3" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1578" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1578" s="3" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1579" s="3">
+        <v>2600</v>
+      </c>
+      <c r="C1579" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F709312-D687-4C6D-8AA6-2687013B7D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E843C312-9BFF-4CF3-AF0D-486DE30F1F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="2558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="2657">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -10252,6 +10252,402 @@
   </si>
   <si>
     <t>equatorial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiredness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hollow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illuminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>influential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>behave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everyday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>review</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iodine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypothalamus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tablet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>songbird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cliff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>else</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interplay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>topi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stiff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>terminal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ceremonial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piston</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tolerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virtue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icebox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tropic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nestle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tactic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contaminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Japanese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accomplish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>properly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kohoutek</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disagreement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entrepreneur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingredient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prominent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fashion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alarm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>husband</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proceed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coordinate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substitute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meaningful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agrarian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>margin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airplane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>letter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contrary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adequate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>starling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>correspond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fifteenth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humidity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>additive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peripheral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Egypt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steadily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>odor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>three-dimensional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conquer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loyalty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unexpected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exchanger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strictly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychodynamic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lighthouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innovative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expectation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10724,7 +11120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1579"/>
+  <dimension ref="A1:N1655"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -25314,6 +25710,686 @@
         <v>2557</v>
       </c>
     </row>
+    <row r="1580" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1580" s="4">
+        <v>2700</v>
+      </c>
+      <c r="B1580" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C1580" s="3" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1581" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1581" s="3" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C1581" s="3" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1582" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1582" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C1582" s="3" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1583" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1583" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C1583" s="3" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1584" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1584" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C1584" s="3" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1585" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1585" s="3" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C1585" s="3" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1586" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1586" s="3" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C1586" s="3" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1587" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1587" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C1587" s="3" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1588" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1588" s="3" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C1588" s="3" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1589" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1589" s="3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1589" s="3" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1590" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1590" s="3" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C1590" s="3" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1591" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1591" s="3" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C1591" s="3" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1592" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1592" s="3" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C1592" s="3" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1593" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1593" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C1593" s="3" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1594" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1594" s="3" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C1594" s="3" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1595" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1595" s="3" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C1595" s="3" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1596" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1596" s="3" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C1596" s="3" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1597" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1597" s="3" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C1597" s="3" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1598" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1598" s="3" t="s">
+        <v>2629</v>
+      </c>
+      <c r="C1598" s="3" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1599" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1599" s="3" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C1599" s="3" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1600" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1600" s="3" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C1600" s="3" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1601" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1601" s="3" t="s">
+        <v>2649</v>
+      </c>
+      <c r="C1601" s="3" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1602" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1602" s="3" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C1602" s="3" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1603" s="3">
+        <v>2700</v>
+      </c>
+      <c r="B1603" s="3" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C1603" s="3" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1604" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1604" s="3" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1605" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1605" s="3" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1606" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1606" s="3" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1607" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1607" s="3" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1608" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1608" s="3" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1609" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1609" s="3" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1610" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1610" s="3" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1611" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1611" s="3" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1612" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1612" s="3" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1613" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1613" s="3" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1614" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1614" s="3" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1615" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1615" s="3" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1616" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1616" s="3" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1617" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1617" s="3" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1618" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1618" s="3" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1619" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1619" s="3" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1620" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1620" s="3" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1621" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1621" s="3" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1622" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1622" s="3" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1623" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1623" s="3" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1624" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1624" s="3" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1625" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1625" s="3" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1626" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1626" s="3" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1627" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1627" s="3" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1628" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1628" s="3" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1629" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1629" s="3" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1630" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1630" s="3" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1631" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1631" s="3" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1632" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1632" s="3" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1633" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1633" s="3" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1634" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1634" s="3" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1635" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1635" s="3" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1636" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1636" s="3" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1637" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1637" s="3" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1638" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1638" s="3" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1639" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1639" s="3" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1640" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1640" s="3" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1641" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1641" s="3" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1642" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1642" s="3" t="s">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1643" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1643" s="3" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1644" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1644" s="3" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1645" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1645" s="4" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1646" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1646" s="3" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1647" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1647" s="3" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1648" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1648" s="3" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1649" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1649" s="3" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1650" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1650" s="3" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1651" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1651" s="3" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1652" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1652" s="3" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1653" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1653" s="3" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1654" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1654" s="3" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1655" s="3">
+        <v>2700</v>
+      </c>
+      <c r="C1655" s="3" t="s">
+        <v>2655</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E843C312-9BFF-4CF3-AF0D-486DE30F1F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2966B9-60D6-496F-B715-E51799E2D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="2657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="2756">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -10648,6 +10648,402 @@
   </si>
   <si>
     <t>expectation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disperse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>management</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gallium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>life-forms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eggshell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pigment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silversmith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>darkness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sodium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ready</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hispanic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instinct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reformer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minimize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mississippian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>browse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southwest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>injury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meeting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>address</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saturate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>terrace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secret</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-being</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inclusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cadmium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>designate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abstract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assessment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dominace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horticulture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constitution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifestyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispersal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>residential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indiana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mild</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tectonic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adulthood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consciously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advocate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sixteen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supernatural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomadism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catastrophe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selenium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ballet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unhappy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bantu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inadequate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strategy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geothermal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reclaim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restoration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eddy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wherever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legislation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telecommuting</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11120,7 +11516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1655"/>
+  <dimension ref="A1:N1722"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -26390,6 +26786,641 @@
         <v>2655</v>
       </c>
     </row>
+    <row r="1656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1656" s="4">
+        <v>2800</v>
+      </c>
+      <c r="B1656" s="3" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C1656" s="3" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1657" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1657" s="3" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C1657" s="3" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1658" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1658" s="3" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C1658" s="3" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1659" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1659" s="3" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C1659" s="3" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1660" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1660" s="3" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C1660" s="3" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1661" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1661" s="3" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C1661" s="3" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1662" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1662" s="3" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C1662" s="3" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1663" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1663" s="3" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C1663" s="3" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1664" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1664" s="3" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C1664" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1665" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1665" s="3" t="s">
+        <v>2682</v>
+      </c>
+      <c r="C1665" s="3" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1666" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1666" s="3" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C1666" s="3" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1667" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1667" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C1667" s="3" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1668" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1668" s="3" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C1668" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1669" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1669" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C1669" s="3" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1670" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1670" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C1670" s="3" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1671" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1671" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C1671" s="3" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1672" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1672" s="3" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C1672" s="3" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1673" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1673" s="3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C1673" s="3" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1674" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1674" s="3" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C1674" s="3" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1675" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1675" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C1675" s="3" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1676" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1676" s="3" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C1676" s="3" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1677" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1677" s="3" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C1677" s="3" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1678" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1678" s="3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1678" s="3" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1679" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1679" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1679" s="3" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1680" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1680" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1680" s="3" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1681" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1681" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C1681" s="3" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1682" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1682" s="3" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C1682" s="3" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1683" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1683" s="3" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1683" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1684" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1684" s="3" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C1684" s="3" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1685" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1685" s="3" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C1685" s="3" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1686" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1686" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C1686" s="3" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1687" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1687" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C1687" s="3" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1688" s="3">
+        <v>2800</v>
+      </c>
+      <c r="B1688" s="3" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C1688" s="3" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1689" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1689" s="3" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1690" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1690" s="3" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1691" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1691" s="3" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1692" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1692" s="3" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1693" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1693" s="3" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1694" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1694" s="3" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1695" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1695" s="3" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1696" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1696" s="3" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1697" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1697" s="3" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1698" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1698" s="3" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1699" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1699" s="3" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1700" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1700" s="3" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1701" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1701" s="3" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1702" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1702" s="3" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1703" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1703" s="3" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1704" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1704" s="3" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1705" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1705" s="3" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1706" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1706" s="3" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1707" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1707" s="3" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1708" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1708" s="3" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1709" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1709" s="3" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1710" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1710" s="3" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1711" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1711" s="3" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1712" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1712" s="3" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1713" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1713" s="3" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1714" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1714" s="3" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1715" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1715" s="3" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1716" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1716" s="3" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1717" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1717" s="3" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1718" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1718" s="3" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1719" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1719" s="3" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1720" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1720" s="3" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1721" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1721" s="3" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1722" s="3">
+        <v>2800</v>
+      </c>
+      <c r="C1722" s="3" t="s">
+        <v>2755</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2966B9-60D6-496F-B715-E51799E2D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640B86F2-4129-47F9-BE77-4E4090551A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="2756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2863" uniqueCount="2855">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -11044,6 +11044,402 @@
   </si>
   <si>
     <t>telecommuting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crowd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presumably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metabolism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transplant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geographical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pride</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refrigerator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reserve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>court</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>short-lived</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superorganism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calculation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criterion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harlem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orleans</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orientation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inevitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>controversial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geographic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>projector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peepshow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anemone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handedness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>billfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>identical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mutual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regularity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minimum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figurine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polygon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypothesize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depletion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>request</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conservation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ammonia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beringia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedimentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rectangular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>questionnaire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asphalt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evergreen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lizard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornament</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illumination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>healthy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simplify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advertiser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neonate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caterpillar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drainage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criticism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antarctic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zinc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vulnerable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proposal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wartime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Euphrates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gypsum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>objective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspiration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meltwater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trillion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isolation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frontality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tasmania</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abroad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burgess</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11516,7 +11912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1722"/>
+  <dimension ref="A1:N1795"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -27421,6 +27817,671 @@
         <v>2755</v>
       </c>
     </row>
+    <row r="1723" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1723" s="4">
+        <v>2900</v>
+      </c>
+      <c r="B1723" s="3" t="s">
+        <v>2756</v>
+      </c>
+      <c r="C1723" s="3" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1724" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1724" s="3" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C1724" s="3" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1725" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1725" s="3" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C1725" s="3" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1726" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1726" s="3" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C1726" s="3" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1727" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1727" s="3" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C1727" s="3" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1728" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1728" s="3" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C1728" s="3" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1729" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1729" s="3" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C1729" s="3" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1730" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1730" s="3" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C1730" s="3" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1731" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1731" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C1731" s="3" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1732" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1732" s="3" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C1732" s="3" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1733" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1733" s="3" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C1733" s="3" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1734" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1734" s="3" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C1734" s="3" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1735" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1735" s="3" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C1735" s="3" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1736" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1736" s="3" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C1736" s="3" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1737" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1737" s="3" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C1737" s="3" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1738" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1738" s="3" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C1738" s="3" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1739" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1739" s="3" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C1739" s="3" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1740" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1740" s="3" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C1740" s="3" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1741" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1741" s="3" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C1741" s="3" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1742" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1742" s="3" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C1742" s="3" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1743" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1743" s="3" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C1743" s="3" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1744" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1744" s="3" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C1744" s="3" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1745" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1745" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C1745" s="3" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1746" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1746" s="3" t="s">
+        <v>2830</v>
+      </c>
+      <c r="C1746" s="3" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1747" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1747" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="C1747" s="3" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1748" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1748" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C1748" s="3" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1749" s="3">
+        <v>2900</v>
+      </c>
+      <c r="B1749" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C1749" s="3" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1750" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1750" s="3" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1751" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1751" s="3" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1752" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1752" s="3" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1753" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1753" s="3" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1754" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1754" s="3" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1755" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1755" s="3" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1756" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1756" s="3" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1757" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1757" s="3" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1758" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1758" s="3" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1759" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1759" s="3" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1760" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1760" s="3" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1761" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1761" s="3" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1762" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1762" s="3" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1763" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1763" s="3" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1764" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1764" s="3" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1765" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1765" s="3" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1766" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1766" s="3" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1767" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1767" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1768" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1768" s="3" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1769" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1769" s="3" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1770" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1770" s="3" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1771" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1771" s="3" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1772" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1772" s="3" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1773" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1773" s="3" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1774" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1774" s="3" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1775" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1775" s="3" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1776" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1776" s="3" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1777" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1777" s="3" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1778" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1778" s="3" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1779" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1779" s="3" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1780" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1780" s="3" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1781" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1781" s="3" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1782" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1782" s="3" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1783" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1783" s="3" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1784" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1784" s="3" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1785" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1785" s="3" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1786" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1786" s="3" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1787" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1787" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1788" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1788" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1789" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1789" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1790" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1790" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1791" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1791" s="3" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1792" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1792" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1793" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1793" s="3" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1794" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1794" s="3" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1795" s="3">
+        <v>2900</v>
+      </c>
+      <c r="C1795" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640B86F2-4129-47F9-BE77-4E4090551A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C7E577-4418-41C3-AE97-073C5B832742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2863" uniqueCount="2855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2877">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -11440,6 +11440,94 @@
   </si>
   <si>
     <t>burgess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alternate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guarantee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manganese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ultimately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>igneous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zealand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gaseous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enrich</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metropolis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>botanical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lomas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>safe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confederacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>so-called</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11912,7 +12000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1795"/>
+  <dimension ref="A1:N1812"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -28482,6 +28570,160 @@
         <v>2854</v>
       </c>
     </row>
+    <row r="1796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1796" s="4">
+        <v>3000</v>
+      </c>
+      <c r="B1796" s="3" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C1796" s="3" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1797" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B1797" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C1797" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1798" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B1798" s="3" t="s">
+        <v>2866</v>
+      </c>
+      <c r="C1798" s="3" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1799" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B1799" s="3" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C1799" s="3" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1800" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B1800" s="3" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C1800" s="3" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1801" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B1801" s="3" t="s">
+        <v>2873</v>
+      </c>
+      <c r="C1801" s="3" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1802" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1802" s="3" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1803" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1803" s="3" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1804" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1804" s="3" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1805" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1805" s="3" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1806" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1806" s="3" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1807" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1807" s="3" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1808" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1808" s="3" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1809" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1809" s="3" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1810" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1810" s="3" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1811" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1811" s="3" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1812" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C1812" s="3" t="s">
+        <v>2325</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C7E577-4418-41C3-AE97-073C5B832742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA345185-03D0-4C22-8BD4-030D758C24B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2986" uniqueCount="2977">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -11528,6 +11528,406 @@
   </si>
   <si>
     <t>spite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fulfill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narrative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reasonable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consideration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wilderness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woodcut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extraordinary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>putrefy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resistant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peculiar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preparation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regiment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>procedure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conquest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workshop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replacement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wonder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toddler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opponent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carrier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soda</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproductive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>troop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abigail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>small-scale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>educational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zigzag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>argon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genetically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shortage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>himself</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occasion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symptom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>render</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>robin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tourist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marseille</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vigorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elliptical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worksheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadcast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seabed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multipfy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angiosperm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inclination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circadian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seaway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>congress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oversea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>honor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frighten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>library</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decomposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>door</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>observer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caledonian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volunteer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wetland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harsh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fabric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soften</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synthetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exposure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chondrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>digestive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>northeast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constituent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sketch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embryo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allende</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metropolitan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notably</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12000,7 +12400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1812"/>
+  <dimension ref="A1:N1885"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -28724,6 +29124,671 @@
         <v>2325</v>
       </c>
     </row>
+    <row r="1813" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1813" s="4">
+        <v>3100</v>
+      </c>
+      <c r="B1813" s="3" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C1813" s="3" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1814" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1814" s="3" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C1814" s="3" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1815" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1815" s="3" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C1815" s="3" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1816" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1816" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="C1816" s="3" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1817" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1817" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C1817" s="3" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1818" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1818" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="C1818" s="3" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1819" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1819" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C1819" s="3" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1820" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1820" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C1820" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1821" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1821" s="3" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C1821" s="3" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1822" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1822" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C1822" s="3" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1823" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1823" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C1823" s="3" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1824" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1824" s="3" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1824" s="3" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1825" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1825" s="3" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C1825" s="3" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1826" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1826" s="3" t="s">
+        <v>2924</v>
+      </c>
+      <c r="C1826" s="3" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1827" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1827" s="3" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1827" s="3" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1828" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1828" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C1828" s="3" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1829" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1829" s="3" t="s">
+        <v>2942</v>
+      </c>
+      <c r="C1829" s="3" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1830" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1830" s="3" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C1830" s="3" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1831" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1831" s="3" t="s">
+        <v>2946</v>
+      </c>
+      <c r="C1831" s="3" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1832" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1832" s="3" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C1832" s="3" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1833" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1833" s="3" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C1833" s="3" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1834" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1834" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="C1834" s="3" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1835" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1835" s="3" t="s">
+        <v>2953</v>
+      </c>
+      <c r="C1835" s="3" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1836" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1836" s="3" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C1836" s="3" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1837" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1837" s="3" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C1837" s="3" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1838" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1838" s="3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="C1838" s="3" t="s">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1839" s="3">
+        <v>3100</v>
+      </c>
+      <c r="B1839" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="C1839" s="3" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1840" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1840" s="3" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1841" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1841" s="3" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1842" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1842" s="3" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1843" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1843" s="3" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1844" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1844" s="3" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1845" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1845" s="3" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1846" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1846" s="3" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1847" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1847" s="3" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1848" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1848" s="3" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1849" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1849" s="3" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1850" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1850" s="3" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1851" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1851" s="3" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1852" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1852" s="3" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1853" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1853" s="3" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1854" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1854" s="3" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1855" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1855" s="3" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1856" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1856" s="3" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1857" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1857" s="3" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1858" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1858" s="3" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1859" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1859" s="3" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1860" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1860" s="3" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1861" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1861" s="3" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1862" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1862" s="3" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1863" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1863" s="3" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1864" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1864" s="3" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1865" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1865" s="3" t="s">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1866" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1866" s="3" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1867" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1867" s="3" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1868" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1868" s="3" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1869" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1869" s="3" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1870" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1870" s="3" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1871" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1871" s="3" t="s">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1872" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1872" s="3" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1873" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1873" s="3" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1874" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1874" s="3" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1875" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1875" s="3" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1876" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1876" s="3" t="s">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1877" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1877" s="3" t="s">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1878" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1878" s="3" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1879" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1879" s="3" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1880" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1880" s="3" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1881" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1881" s="3" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1882" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1882" s="3" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1883" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1883" s="3" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1884" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1884" s="3" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1885" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C1885" s="3" t="s">
+        <v>2976</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA345185-03D0-4C22-8BD4-030D758C24B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D031F-C285-4072-8EB4-86E8492A0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2986" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="3076">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -11928,6 +11928,402 @@
   </si>
   <si>
     <t>notably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonetheless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinterland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oregon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>couple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>willing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steppe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noticeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spirit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lunar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presidency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viewer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>academic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtractive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motivate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ubdoubtedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>granite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quilt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>campaign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mandan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invisible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dwell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moderate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>territorial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predominate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chiefly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>champion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>craftspeople</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>likewise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intelligence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>single-celled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unskilled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>progressively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thickness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graphic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>termite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analogy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consciousness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reindeer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oxide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kingdom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seldom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recovery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>father</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voyager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonograph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accustom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eurasia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>literally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Italian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>railway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobalt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accident</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tongue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncommon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simplification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chemically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peculiarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncertain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intricate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coarse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feedback</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Norway</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12400,7 +12796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1885"/>
+  <dimension ref="A1:N1959"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -29789,6 +30185,676 @@
         <v>2976</v>
       </c>
     </row>
+    <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1886" s="4">
+        <v>3200</v>
+      </c>
+      <c r="B1886" s="3" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C1886" s="3" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1887" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1887" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C1887" s="3" t="s">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1888" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1888" s="3" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C1888" s="3" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1889" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1889" s="3" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1889" s="3" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1890" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1890" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C1890" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1891" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1891" s="3" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C1891" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1892" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1892" s="3" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C1892" s="3" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1893" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1893" s="3" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C1893" s="3" t="s">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1894" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1894" s="3" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C1894" s="3" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1895" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1895" s="3" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C1895" s="3" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1896" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1896" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="C1896" s="3" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1897" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1897" s="3" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C1897" s="3" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1898" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1898" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C1898" s="3" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1899" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1899" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C1899" s="3" t="s">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1900" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1900" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C1900" s="3" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1901" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1901" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C1901" s="3" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1902" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1902" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C1902" s="3" t="s">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1903" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1903" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="C1903" s="3" t="s">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1904" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1904" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C1904" s="3" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1905" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1905" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C1905" s="3" t="s">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1906" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1906" s="3" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C1906" s="3" t="s">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1907" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1907" s="3" t="s">
+        <v>3059</v>
+      </c>
+      <c r="C1907" s="3" t="s">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1908" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1908" s="3" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1908" s="3" t="s">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1909" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1909" s="3" t="s">
+        <v>3067</v>
+      </c>
+      <c r="C1909" s="3" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1910" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1910" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1910" s="3" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1911" s="3">
+        <v>3200</v>
+      </c>
+      <c r="B1911" s="3" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C1911" s="3" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1912" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1912" s="3" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1913" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1913" s="3" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1914" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1914" s="3" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1915" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1915" s="3" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1916" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1916" s="3" t="s">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1917" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1917" s="3" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1918" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1918" s="3" t="s">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1919" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1919" s="3" t="s">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1920" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1920" s="3" t="s">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1921" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1921" s="3" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1922" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1922" s="3" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1923" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1923" s="3" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1924" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1924" s="3" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1925" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1925" s="3" t="s">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1926" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1926" s="3" t="s">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1927" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1927" s="3" t="s">
+        <v>3028</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1928" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1928" s="3" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1929" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1929" s="3" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1930" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1930" s="3" t="s">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1931" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1931" s="3" t="s">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1932" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1932" s="3" t="s">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1933" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1933" s="3" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1934" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1934" s="3" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1935" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1935" s="3" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1936" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1936" s="3" t="s">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1937" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1937" s="3" t="s">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1938" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1938" s="3" t="s">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1939" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1939" s="3" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1940" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1940" s="3" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1941" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1941" s="3" t="s">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1942" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1942" s="3" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1943" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1943" s="3" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1944" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1944" s="3" t="s">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1945" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1945" s="3" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1946" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1946" s="3" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1947" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1947" s="3" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1948" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1948" s="3" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1949" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1949" s="3" t="s">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1950" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1950" s="3" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1951" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1951" s="3" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1952" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1952" s="3" t="s">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1953" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1953" s="3" t="s">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1954" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1954" s="3" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1955" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1955" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1956" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1956" s="3" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1957" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1957" s="3" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1958" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1958" s="3" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1959" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C1959" s="3" t="s">
+        <v>3075</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D031F-C285-4072-8EB4-86E8492A0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27623BC1-36AF-4D57-8516-D65D17FDB0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="3076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="3176">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -12324,6 +12324,406 @@
   </si>
   <si>
     <t>Norway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encouragement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bombard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>praise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>editor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soluble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oceania</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>election</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backbone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chemist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trample</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mountainous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potassium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cascade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reconstruction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accordingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locomotive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predominant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saturn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>groove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journeyman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long-lasting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chondrule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accessible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>demension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bacterial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medicine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incubation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>northeastern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excavation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mutualism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>left-handed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>probe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capillary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>behavioral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pleasant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsequently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blacksmith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electronic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>besides</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>platform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surrounding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tobacco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agreement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>costly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>director</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repeatedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tentacle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fertility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simplicity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>annually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enthusiasm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagecoach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investigate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excessive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjustment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figurative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inscription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appalachian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>declaration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>markedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overcast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noisy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>muscular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remarkably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>team</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surpass</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12796,7 +13196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N1959"/>
+  <dimension ref="A1:N2031"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -30855,6 +31255,666 @@
         <v>3075</v>
       </c>
     </row>
+    <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1960" s="4">
+        <v>3300</v>
+      </c>
+      <c r="B1960" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C1960" s="3" t="s">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1961" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1961" s="3" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C1961" s="3" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1962" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1962" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1962" s="3" t="s">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1963" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1963" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C1963" s="3" t="s">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1964" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1964" s="3" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C1964" s="3" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1965" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1965" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1965" s="3" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1966" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1966" s="3" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C1966" s="3" t="s">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1967" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1967" s="3" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C1967" s="3" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1968" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1968" s="3" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C1968" s="3" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1969" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1969" s="3" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1969" s="3" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1970" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1970" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C1970" s="3" t="s">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1971" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1971" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1971" s="3" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1972" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1972" s="3" t="s">
+        <v>3122</v>
+      </c>
+      <c r="C1972" s="3" t="s">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1973" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1973" s="3" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1973" s="3" t="s">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1974" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1974" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1974" s="3" t="s">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1975" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1975" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1975" s="3" t="s">
+        <v>3098</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1976" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1976" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1976" s="3" t="s">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1977" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1977" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="C1977" s="3" t="s">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1978" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1978" s="3" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1978" s="3" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1979" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1979" s="3" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1979" s="3" t="s">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1980" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1980" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="C1980" s="3" t="s">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1981" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1981" s="3" t="s">
+        <v>3146</v>
+      </c>
+      <c r="C1981" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1982" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1982" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1982" s="3" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1983" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1983" s="3" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C1983" s="3" t="s">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1984" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1984" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1984" s="3" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1985" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1985" s="3" t="s">
+        <v>3166</v>
+      </c>
+      <c r="C1985" s="3" t="s">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1986" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1986" s="3" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C1986" s="3" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1987" s="3">
+        <v>3300</v>
+      </c>
+      <c r="B1987" s="3" t="s">
+        <v>3174</v>
+      </c>
+      <c r="C1987" s="3" t="s">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1988" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1988" s="3" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1989" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1989" s="3" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1990" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1990" s="3" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1991" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1991" s="3" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1992" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1992" s="3" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1993" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1993" s="3" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1994" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1994" s="3" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1995" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1995" s="3" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1996" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1996" s="3" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1997" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1997" s="3" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1998" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1998" s="3" t="s">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1999" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C1999" s="3" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2000" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2000" s="3" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2001" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2001" s="3" t="s">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2002" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2002" s="3" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2003" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2003" s="3" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2004" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2004" s="3" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2005" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2005" s="3" t="s">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2006" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2006" s="3" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2007" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2007" s="3" t="s">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2008" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2008" s="3" t="s">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2009" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2009" s="3" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2010" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2010" s="3" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2011" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2011" s="3" t="s">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2012" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2012" s="3" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2013" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2013" s="3" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2014" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2014" s="3" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2015" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2015" s="3" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2016" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2016" s="3" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2017" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2017" s="3" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2018" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2018" s="3" t="s">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2019" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2019" s="3" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2020" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2020" s="3" t="s">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2021" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2021" s="3" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2022" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2022" s="3" t="s">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2023" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2023" s="3" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2024" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2024" s="3" t="s">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2025" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2025" s="3" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2026" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2026" s="3" t="s">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2027" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2027" s="3" t="s">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2028" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2028" s="3" t="s">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2029" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2029" s="3" t="s">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2030" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2030" s="3" t="s">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2031" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C2031" s="3" t="s">
+        <v>3175</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27623BC1-36AF-4D57-8516-D65D17FDB0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD69F205-3FB5-4C79-BB87-26C60042DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="3176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3286" uniqueCount="3275">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -12724,6 +12724,402 @@
   </si>
   <si>
     <t>surpass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>institute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>versus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predecessor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flora</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pollinator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descendant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>somehow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>efficiently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tightly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medieval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jewelry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>differently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>church</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>putt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reshape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metabolic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>methane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fundamentally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unprecedented</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conservative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>identity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expenditure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cohesive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>practivally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forerunner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alertness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invasion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recurrence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hawk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moraine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sandy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jurassic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>literacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prosper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traditionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intelligent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analogous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavendish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>council</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exogenous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>informative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ooze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>educator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>republic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dwarf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choreographer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marriage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>severely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>propagate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>environmentalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outstanding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endogenous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horseshoe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>probability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specifically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>susceptible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>envision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capsize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elicit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>financier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obscure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turbulent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simultaneously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rodent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seafarer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uneven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repudiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faunal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nighttime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pry</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13196,7 +13592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2031"/>
+  <dimension ref="A1:N2109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -31915,6 +32311,696 @@
         <v>3175</v>
       </c>
     </row>
+    <row r="2032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2032" s="4">
+        <v>3400</v>
+      </c>
+      <c r="B2032" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="C2032" s="3" t="s">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2033" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2033" s="3" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C2033" s="3" t="s">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2034" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2034" s="3" t="s">
+        <v>3190</v>
+      </c>
+      <c r="C2034" s="3" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2035" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2035" s="3" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C2035" s="3" t="s">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2036" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2036" s="3" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C2036" s="3" t="s">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2037" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2037" s="3" t="s">
+        <v>3216</v>
+      </c>
+      <c r="C2037" s="3" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2038" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2038" s="3" t="s">
+        <v>3218</v>
+      </c>
+      <c r="C2038" s="3" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2039" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2039" s="3" t="s">
+        <v>3222</v>
+      </c>
+      <c r="C2039" s="3" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2040" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2040" s="3" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C2040" s="3" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2041" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2041" s="3" t="s">
+        <v>3226</v>
+      </c>
+      <c r="C2041" s="3" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2042" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2042" s="3" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C2042" s="3" t="s">
+        <v>3187</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2043" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2043" s="3" t="s">
+        <v>3230</v>
+      </c>
+      <c r="C2043" s="3" t="s">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2044" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2044" s="3" t="s">
+        <v>3235</v>
+      </c>
+      <c r="C2044" s="3" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2045" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2045" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C2045" s="3" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2046" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2046" s="3" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C2046" s="3" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2047" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2047" s="3" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C2047" s="3" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2048" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2048" s="3" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C2048" s="3" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2049" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2049" s="3" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C2049" s="3" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2050" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2050" s="3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="C2050" s="3" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2051" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2051" s="3" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C2051" s="3" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2052" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2052" s="3" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C2052" s="3" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2053" s="3">
+        <v>3400</v>
+      </c>
+      <c r="B2053" s="3" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C2053" s="3" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2054" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2054" s="3" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2055" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2055" s="3" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2056" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2056" s="3" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2057" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2057" s="3" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2058" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2058" s="3" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2059" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2059" s="3" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2060" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2060" s="3" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2061" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2061" s="3" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2062" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2062" s="3" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2063" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2063" s="3" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2064" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2064" s="3" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2065" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2065" s="3" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2066" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2066" s="3" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2067" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2067" s="3" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2068" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2068" s="3" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2069" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2069" s="3" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2070" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2070" s="3" t="s">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2071" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2071" s="3" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2072" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2072" s="3" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2073" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2073" s="3" t="s">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2074" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2074" s="3" t="s">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2075" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2075" s="3" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2076" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2076" s="3" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2077" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2077" s="3" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2078" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2078" s="3" t="s">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2079" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2079" s="3" t="s">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2080" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2080" s="3" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2081" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2081" s="3" t="s">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2082" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2082" s="3" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2083" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2083" s="3" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2084" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2084" s="3" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2085" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2085" s="3" t="s">
+        <v>3243</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2086" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2086" s="3" t="s">
+        <v>3245</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2087" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2087" s="3" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2088" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2088" s="3" t="s">
+        <v>3248</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2089" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2089" s="3" t="s">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2090" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2090" s="3" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2091" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2091" s="3" t="s">
+        <v>3253</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2092" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2092" s="3" t="s">
+        <v>3254</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2093" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2093" s="3" t="s">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2094" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2094" s="3" t="s">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2095" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2095" s="3" t="s">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2096" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2096" s="3" t="s">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2097" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2097" s="3" t="s">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2098" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2098" s="3" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2099" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2099" s="3" t="s">
+        <v>3262</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2100" s="3" t="s">
+        <v>3263</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2101" s="3" t="s">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2102" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2102" s="3" t="s">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2103" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2103" s="3" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2104" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2104" s="3" t="s">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2105" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2105" s="3" t="s">
+        <v>3268</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2106" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2106" s="3" t="s">
+        <v>3269</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2107" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2107" s="3" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2108" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2108" s="3" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2109" s="3">
+        <v>3400</v>
+      </c>
+      <c r="C2109" s="3" t="s">
+        <v>3274</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD69F205-3FB5-4C79-BB87-26C60042DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C776D6EE-9BBF-42C5-A888-C764AF2E1D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3286" uniqueCount="3275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="3375">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -13120,6 +13120,406 @@
   </si>
   <si>
     <t>pry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enterprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>designer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>karst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interstellar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scratch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gibraltar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caravan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microorganism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>probable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compromise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inequality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sailor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intervention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immobile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calendar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predominantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disgust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persistent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prestige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fashionable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vaudeville</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncertainty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carnivore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>civilian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hunger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>publication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prolong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plaster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sadness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tundra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>localize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dependable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anomaly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>displace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gravitational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pronounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abundantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liberate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pollute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cuneiform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gamma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nebula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>security</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parasitic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>documentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lithosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>richness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sulfate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wildlife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steamship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lithospheric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disturbance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anywhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>April</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incomplete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lecture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tolerance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hostile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triangle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unchanging</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cargo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13592,7 +13992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2109"/>
+  <dimension ref="A1:N2172"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -33001,6 +33401,621 @@
         <v>3274</v>
       </c>
     </row>
+    <row r="2110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2110" s="4">
+        <v>3500</v>
+      </c>
+      <c r="B2110" s="3" t="s">
+        <v>3279</v>
+      </c>
+      <c r="C2110" s="3" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2111" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2111" s="3" t="s">
+        <v>3281</v>
+      </c>
+      <c r="C2111" s="3" t="s">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2112" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2112" s="3" t="s">
+        <v>3282</v>
+      </c>
+      <c r="C2112" s="3" t="s">
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2113" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2113" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="C2113" s="3" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2114" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2114" s="3" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C2114" s="3" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2115" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2115" s="3" t="s">
+        <v>3289</v>
+      </c>
+      <c r="C2115" s="3" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2116" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2116" s="3" t="s">
+        <v>3296</v>
+      </c>
+      <c r="C2116" s="3" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2117" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2117" s="3" t="s">
+        <v>3301</v>
+      </c>
+      <c r="C2117" s="3" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2118" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2118" s="3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="C2118" s="3" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2119" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2119" s="3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="C2119" s="3" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2120" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2120" s="3" t="s">
+        <v>3307</v>
+      </c>
+      <c r="C2120" s="3" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2121" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2121" s="3" t="s">
+        <v>3308</v>
+      </c>
+      <c r="C2121" s="3" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2122" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2122" s="3" t="s">
+        <v>3310</v>
+      </c>
+      <c r="C2122" s="3" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2123" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2123" s="3" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C2123" s="3" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2124" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>3314</v>
+      </c>
+      <c r="C2124" s="3" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2125" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2125" s="3" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C2125" s="3" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2126" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2126" s="3" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C2126" s="3" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2127" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2127" s="3" t="s">
+        <v>3325</v>
+      </c>
+      <c r="C2127" s="3" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2128" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2128" s="3" t="s">
+        <v>3326</v>
+      </c>
+      <c r="C2128" s="3" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2129" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2129" s="3" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C2129" s="3" t="s">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2130" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2130" s="3" t="s">
+        <v>3330</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2131" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2131" s="3" t="s">
+        <v>3333</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>3306</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2132" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2132" s="3" t="s">
+        <v>3335</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>3309</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2133" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2133" s="3" t="s">
+        <v>3337</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2134" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2134" s="3" t="s">
+        <v>3339</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2135" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2135" s="3" t="s">
+        <v>3349</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2136" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2136" s="3" t="s">
+        <v>3352</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2137" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2137" s="3" t="s">
+        <v>3354</v>
+      </c>
+      <c r="C2137" s="3" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2138" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2138" s="3" t="s">
+        <v>3357</v>
+      </c>
+      <c r="C2138" s="3" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2139" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2139" s="3" t="s">
+        <v>3358</v>
+      </c>
+      <c r="C2139" s="3" t="s">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2140" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2140" s="3" t="s">
+        <v>3359</v>
+      </c>
+      <c r="C2140" s="3" t="s">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2141" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2141" s="3" t="s">
+        <v>3360</v>
+      </c>
+      <c r="C2141" s="3" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2142" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2142" s="3" t="s">
+        <v>3365</v>
+      </c>
+      <c r="C2142" s="3" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2143" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2143" s="3" t="s">
+        <v>3366</v>
+      </c>
+      <c r="C2143" s="3" t="s">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2144" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2144" s="3" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C2144" s="3" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2145" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2145" s="3" t="s">
+        <v>3370</v>
+      </c>
+      <c r="C2145" s="3" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2146" s="3">
+        <v>3500</v>
+      </c>
+      <c r="B2146" s="3" t="s">
+        <v>3373</v>
+      </c>
+      <c r="C2146" s="3" t="s">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2147" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2147" s="3" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2148" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2148" s="3" t="s">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2149" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2149" s="3" t="s">
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2150" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2150" s="3" t="s">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2151" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2151" s="4" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2152" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2153" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2154" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2155" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2156" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2157" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2158" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>3348</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2159" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2160" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2161" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2162" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2163" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2163" s="3" t="s">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2164" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2164" s="3" t="s">
+        <v>3361</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2165" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2165" s="3" t="s">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2166" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2166" s="3" t="s">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2167" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2167" s="3" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2168" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2168" s="3" t="s">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2169" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2169" s="3" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2170" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2170" s="3" t="s">
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2171" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2171" s="3" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2172" s="3">
+        <v>3500</v>
+      </c>
+      <c r="C2172" s="3" t="s">
+        <v>3374</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C776D6EE-9BBF-42C5-A888-C764AF2E1D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF861438-018B-486C-A0B5-F953A40674D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="3375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3486" uniqueCount="3475">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -13520,6 +13520,406 @@
   </si>
   <si>
     <t>cargo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reconstruct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conventionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rainy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>judgment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nickel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Georgia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ourselves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pasture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overwhelm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prolific</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liberty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>millimeter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>molecular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exterior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antiquity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adobe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absorption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensitivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>studio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inevitably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fifity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utilitarian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoroughly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stunt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accomplishment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>routine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nourish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ultraviolet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pyramid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cannonball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transitional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amplification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsurface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>philosopher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>semiskilled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mackerel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>witness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>midwest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scrub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>textbook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sharply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunrise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mutoscope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summarize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numerical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dynamic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>punishment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tehnic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cottonwood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theorist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>web</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pursue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resilience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outbreak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mutually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>driver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bladder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advancement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dedicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thirteen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respiration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheaply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>safety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quiet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corona</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>therapy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressionist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incentive</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13992,7 +14392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2172"/>
+  <dimension ref="A1:N2247"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -34016,6 +34416,681 @@
         <v>3374</v>
       </c>
     </row>
+    <row r="2173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2173" s="4">
+        <v>3600</v>
+      </c>
+      <c r="B2173" s="3" t="s">
+        <v>3377</v>
+      </c>
+      <c r="C2173" s="3" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2174" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2174" s="3" t="s">
+        <v>3380</v>
+      </c>
+      <c r="C2174" s="3" t="s">
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2175" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2175" s="3" t="s">
+        <v>3381</v>
+      </c>
+      <c r="C2175" s="3" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2176" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2176" s="3" t="s">
+        <v>3384</v>
+      </c>
+      <c r="C2176" s="3" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2177" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2177" s="3" t="s">
+        <v>3399</v>
+      </c>
+      <c r="C2177" s="3" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2178" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2178" s="3" t="s">
+        <v>3404</v>
+      </c>
+      <c r="C2178" s="3" t="s">
+        <v>3383</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2179" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2179" s="3" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C2179" s="3" t="s">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2180" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2180" s="3" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C2180" s="3" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2181" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2181" s="3" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C2181" s="3" t="s">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2182" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2182" s="3" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C2182" s="3" t="s">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2183" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2183" s="3" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C2183" s="3" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2184" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2184" s="3" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C2184" s="3" t="s">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2185" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2185" s="3" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C2185" s="3" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2186" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2186" s="3" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C2186" s="3" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2187" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2187" s="3" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C2187" s="3" t="s">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2188" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2188" s="3" t="s">
+        <v>3445</v>
+      </c>
+      <c r="C2188" s="3" t="s">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2189" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2189" s="3" t="s">
+        <v>3450</v>
+      </c>
+      <c r="C2189" s="4" t="s">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2190" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2190" s="3" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C2190" s="3" t="s">
+        <v>3396</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2191" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2191" s="3" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C2191" s="3" t="s">
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2192" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2192" s="3" t="s">
+        <v>3456</v>
+      </c>
+      <c r="C2192" s="3" t="s">
+        <v>3398</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2193" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2193" s="3" t="s">
+        <v>3462</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2194" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>3464</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2195" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2196" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2196" s="3" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>3403</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2197" s="3">
+        <v>3600</v>
+      </c>
+      <c r="B2197" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>3405</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2198" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2199" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2200" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2201" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2202" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2203" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2204" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>3417</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2205" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2205" s="3" t="s">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2206" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2206" s="3" t="s">
+        <v>3419</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2207" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2207" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2208" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2208" s="3" t="s">
+        <v>3421</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2209" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2209" s="3" t="s">
+        <v>3422</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2210" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2210" s="3" t="s">
+        <v>3423</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2211" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2211" s="3" t="s">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2212" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2212" s="3" t="s">
+        <v>3426</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2213" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2213" s="3" t="s">
+        <v>3428</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2214" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2214" s="3" t="s">
+        <v>3429</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2215" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2215" s="3" t="s">
+        <v>3431</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2216" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2216" s="3" t="s">
+        <v>3433</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2217" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2217" s="3" t="s">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2218" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2218" s="3" t="s">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2219" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2219" s="3" t="s">
+        <v>3436</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2220" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2220" s="3" t="s">
+        <v>3437</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2221" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2221" s="3" t="s">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2222" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2222" s="3" t="s">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2223" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2223" s="3" t="s">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2224" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2224" s="3" t="s">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2225" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2225" s="3" t="s">
+        <v>3442</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2226" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2226" s="3" t="s">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2227" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2227" s="3" t="s">
+        <v>3444</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2228" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2228" s="3" t="s">
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2229" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2229" s="3" t="s">
+        <v>3447</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2230" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2230" s="3" t="s">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2231" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2231" s="3" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2232" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2232" s="3" t="s">
+        <v>3451</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2233" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2233" s="3" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2234" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2234" s="3" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2235" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2235" s="3" t="s">
+        <v>3457</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2236" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2236" s="3" t="s">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2237" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2237" s="3" t="s">
+        <v>3459</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2238" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2238" s="3" t="s">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2239" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2239" s="3" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2240" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2240" s="3" t="s">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2241" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2241" s="3" t="s">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2242" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2242" s="3" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2243" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2243" s="3" t="s">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2244" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2244" s="3" t="s">
+        <v>3471</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2245" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2245" s="3" t="s">
+        <v>3472</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2246" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2246" s="3" t="s">
+        <v>3473</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2247" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C2247" s="3" t="s">
+        <v>3474</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF861438-018B-486C-A0B5-F953A40674D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769B058C-C68F-4C4D-AE84-244DE47EDD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3486" uniqueCount="3475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3586" uniqueCount="3575">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -13920,6 +13920,406 @@
   </si>
   <si>
     <t>incentive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pilot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disposal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spectacle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>latent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silica</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deaf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bureau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hunter-gatherer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rudimentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>involvement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>otter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>let</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illustration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shatter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>makeup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anticipate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vaild</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>borrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indoor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grassland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deciduous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>large-scale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fifth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tethys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decipher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorough</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dislike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfamiliar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shortly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>raven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pamphlet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swarm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commuter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>movable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alloy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>astronomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conversion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negotiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tidal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eusocial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gardening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deeoen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oliver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canvas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ideology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turkey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solitary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unstable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reheat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>via</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>financially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diversification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outwork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eohippus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conductor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nutritionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mythical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handcraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endanger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sweep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>porosity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windmill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>understory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shaman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -14392,7 +14792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2247"/>
+  <dimension ref="A1:N2324"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -35091,6 +35491,691 @@
         <v>3474</v>
       </c>
     </row>
+    <row r="2248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2248" s="4">
+        <v>3700</v>
+      </c>
+      <c r="B2248" s="3" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C2248" s="3" t="s">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2249" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2249" s="3" t="s">
+        <v>3489</v>
+      </c>
+      <c r="C2249" s="3" t="s">
+        <v>3476</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2250" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2250" s="3" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C2250" s="3" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2251" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2251" s="3" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C2251" s="3" t="s">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2252" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2252" s="3" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C2252" s="3" t="s">
+        <v>3479</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2253" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2253" s="3" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C2253" s="3" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2254" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2254" s="3" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C2254" s="3" t="s">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2255" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2255" s="3" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C2255" s="3" t="s">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2256" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2256" s="3" t="s">
+        <v>3515</v>
+      </c>
+      <c r="C2256" s="3" t="s">
+        <v>3483</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2257" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2257" s="3" t="s">
+        <v>3516</v>
+      </c>
+      <c r="C2257" s="3" t="s">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2258" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2258" s="3" t="s">
+        <v>3525</v>
+      </c>
+      <c r="C2258" s="3" t="s">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2259" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2259" s="3" t="s">
+        <v>3526</v>
+      </c>
+      <c r="C2259" s="3" t="s">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2260" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2260" s="3" t="s">
+        <v>3529</v>
+      </c>
+      <c r="C2260" s="3" t="s">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2261" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2261" s="3" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C2261" s="3" t="s">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2262" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2262" s="3" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C2262" s="3" t="s">
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2263" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2263" s="3" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C2263" s="3" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2264" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2264" s="3" t="s">
+        <v>3540</v>
+      </c>
+      <c r="C2264" s="3" t="s">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2265" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2265" s="3" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C2265" s="3" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2266" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2266" s="3" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C2266" s="3" t="s">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2267" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2267" s="3" t="s">
+        <v>3560</v>
+      </c>
+      <c r="C2267" s="3" t="s">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2268" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2268" s="3" t="s">
+        <v>3561</v>
+      </c>
+      <c r="C2268" s="3" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2269" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2269" s="3" t="s">
+        <v>3562</v>
+      </c>
+      <c r="C2269" s="3" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2270" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B2270" s="3" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C2270" s="3" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2271" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2271" s="3" t="s">
+        <v>3503</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2272" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2272" s="3" t="s">
+        <v>3506</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2273" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2273" s="3" t="s">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2274" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2274" s="3" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2275" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2275" s="3" t="s">
+        <v>3509</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2276" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2276" s="3" t="s">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2277" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2277" s="3" t="s">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2278" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2278" s="3" t="s">
+        <v>3512</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2279" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2279" s="3" t="s">
+        <v>3513</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2280" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2280" s="3" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2281" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2281" s="3" t="s">
+        <v>3518</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2282" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2282" s="3" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2283" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2283" s="3" t="s">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2284" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2284" s="3" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2285" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2285" s="3" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2286" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2286" s="3" t="s">
+        <v>3523</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2287" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2287" s="3" t="s">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2288" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2288" s="3" t="s">
+        <v>3527</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2289" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2289" s="3" t="s">
+        <v>3528</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2290" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2290" s="3" t="s">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2291" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2291" s="3" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2292" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2292" s="3" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2293" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2293" s="3" t="s">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2294" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2294" s="3" t="s">
+        <v>3535</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2295" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2295" s="3" t="s">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2296" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2296" s="3" t="s">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2297" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2297" s="3" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2298" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2298" s="3" t="s">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2299" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2299" s="3" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2300" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2300" s="4" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2301" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2301" s="3" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2302" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2302" s="3" t="s">
+        <v>3548</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2303" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2303" s="3" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2304" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2304" s="3" t="s">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2305" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2305" s="3" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2306" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2306" s="3" t="s">
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2307" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2307" s="3" t="s">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2308" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2308" s="3" t="s">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2309" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2309" s="3" t="s">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2310" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2310" s="3" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2311" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2311" s="3" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2312" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2312" s="3" t="s">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2313" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2313" s="3" t="s">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2314" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2314" s="3" t="s">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2315" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2315" s="3" t="s">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2316" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2316" s="3" t="s">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2317" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2317" s="3" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2318" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2318" s="3" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2319" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2319" s="3" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2320" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2320" s="3" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2321" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2321" s="3" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2322" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2322" s="3" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2323" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2323" s="3" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2324" s="3">
+        <v>3700</v>
+      </c>
+      <c r="C2324" s="3" t="s">
+        <v>3574</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769B058C-C68F-4C4D-AE84-244DE47EDD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDD1F00-2F99-4BCB-913F-09DD340E2841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3586" uniqueCount="3575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="3775">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -14320,6 +14320,806 @@
   </si>
   <si>
     <t>shaman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stylize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autonomous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pipeline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>renew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dandelion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monopoly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>membership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homogeneous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substantially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>internally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poorly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>popularly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devoid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manifest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guinea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mistake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinpoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relief</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rancher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mosaic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maturation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recruitment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preschooler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>practitioner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cold-blooded</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photosynthesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diffuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flagellum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cloth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collapse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phytoremediation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mustard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chlorosis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-known</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>daylight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piecework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingenuity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>efficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polynesian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inaccurate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eighteen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monument</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garrison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>starve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>employment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crevice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>port</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scavenger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antibiotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cohesion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fungal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interconnect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synthesize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnetosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chisel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disguise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vein</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bloodhound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>informal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ambitious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>measurable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stroke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enforce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tannin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disagree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tourism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ownership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prehistory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>centralize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silicon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consistently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cajun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrinsically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gratify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ledge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cowboy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maritime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vastly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bicycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fascinate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shellfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inferior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agriculturalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooperate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adorn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pakistan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhetorical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inferential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>partial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysterious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>planetarium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aristocratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parrot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conductance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>filter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rainforest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endocrine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hemlock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>determination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quotation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>professor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fine-grained</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shuttle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>necessity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reasonably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ceiling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commensalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parasitism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outdoor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blanket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modernize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boredom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>somewhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>happiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>currency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>county</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>correspondence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confidence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low-quality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coverage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>botany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seemingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feminist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transmit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warrior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gentle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleepy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weakness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outgoing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>combat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispute</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -14792,12 +15592,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2324"/>
+  <dimension ref="A1:N2475"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="18.25" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -36176,6 +36976,1364 @@
         <v>3574</v>
       </c>
     </row>
+    <row r="2325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2325" s="4">
+        <v>3800</v>
+      </c>
+      <c r="B2325" s="3" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C2325" s="3" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2326" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2326" s="3" t="s">
+        <v>3582</v>
+      </c>
+      <c r="C2326" s="3" t="s">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2327" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2327" s="3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="C2327" s="3" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2328" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2328" s="3" t="s">
+        <v>3596</v>
+      </c>
+      <c r="C2328" s="3" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2329" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2329" s="3" t="s">
+        <v>3605</v>
+      </c>
+      <c r="C2329" s="3" t="s">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2330" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2330" s="3" t="s">
+        <v>3608</v>
+      </c>
+      <c r="C2330" s="3" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2331" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2331" s="3" t="s">
+        <v>3609</v>
+      </c>
+      <c r="C2331" s="3" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2332" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2332" s="3" t="s">
+        <v>3614</v>
+      </c>
+      <c r="C2332" s="3" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2333" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2333" s="3" t="s">
+        <v>3619</v>
+      </c>
+      <c r="C2333" s="3" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2334" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2334" s="3" t="s">
+        <v>3620</v>
+      </c>
+      <c r="C2334" s="3" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2335" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2335" s="3" t="s">
+        <v>3621</v>
+      </c>
+      <c r="C2335" s="3" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2336" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2336" s="3" t="s">
+        <v>3622</v>
+      </c>
+      <c r="C2336" s="3" t="s">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2337" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2337" s="3" t="s">
+        <v>3623</v>
+      </c>
+      <c r="C2337" s="3" t="s">
+        <v>3589</v>
+      </c>
+      <c r="I2337" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2338" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2338" s="3" t="s">
+        <v>3630</v>
+      </c>
+      <c r="C2338" s="3" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2339" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2339" s="3" t="s">
+        <v>3637</v>
+      </c>
+      <c r="C2339" s="3" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2340" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2340" s="3" t="s">
+        <v>3640</v>
+      </c>
+      <c r="C2340" s="3" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2341" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2341" s="3" t="s">
+        <v>3645</v>
+      </c>
+      <c r="C2341" s="3" t="s">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2342" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2342" s="3" t="s">
+        <v>3658</v>
+      </c>
+      <c r="C2342" s="3" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2343" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2343" s="3" t="s">
+        <v>3660</v>
+      </c>
+      <c r="C2343" s="3" t="s">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2344" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2344" s="3" t="s">
+        <v>3663</v>
+      </c>
+      <c r="C2344" s="3" t="s">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2345" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2345" s="3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="C2345" s="3" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2346" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2346" s="3" t="s">
+        <v>3667</v>
+      </c>
+      <c r="C2346" s="3" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2347" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2347" s="3" t="s">
+        <v>3669</v>
+      </c>
+      <c r="C2347" s="3" t="s">
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2348" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2348" s="3" t="s">
+        <v>3670</v>
+      </c>
+      <c r="C2348" s="3" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2349" s="3">
+        <v>3800</v>
+      </c>
+      <c r="B2349" s="3" t="s">
+        <v>3671</v>
+      </c>
+      <c r="C2349" s="3" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2350" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2350" s="3" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2351" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2351" s="3" t="s">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2352" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2352" s="3" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2353" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2353" s="3" t="s">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2354" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2354" s="3" t="s">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2355" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2355" s="3" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2356" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2356" s="3" t="s">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2357" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2357" s="3" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2358" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2358" s="3" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2359" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2359" s="3" t="s">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2360" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2360" s="3" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2361" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2361" s="3" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2362" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2362" s="3" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2363" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2363" s="4" t="s">
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2364" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2364" s="3" t="s">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2365" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2365" s="3" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2366" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2366" s="3" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2367" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2367" s="3" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2368" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2368" s="3" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2369" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2369" s="3" t="s">
+        <v>3633</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2370" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2370" s="3" t="s">
+        <v>3634</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2371" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2371" s="3" t="s">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2372" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2372" s="3" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2373" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2373" s="3" t="s">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2374" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2374" s="3" t="s">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2375" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2375" s="3" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2376" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2376" s="3" t="s">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2377" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2377" s="3" t="s">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2378" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2378" s="3" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2379" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2379" s="3" t="s">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2380" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2380" s="3" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2381" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2381" s="3" t="s">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2382" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2382" s="3" t="s">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2383" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2383" s="3" t="s">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2384" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2384" s="3" t="s">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2385" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2385" s="3" t="s">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2386" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2386" s="3" t="s">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2387" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2387" s="3" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2388" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2388" s="3" t="s">
+        <v>3655</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2389" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2389" s="3" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2390" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2390" s="3" t="s">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2391" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2391" s="3" t="s">
+        <v>3659</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2392" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2392" s="3" t="s">
+        <v>3661</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2393" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2393" s="3" t="s">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2394" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2394" s="3" t="s">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2395" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2395" s="3" t="s">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2396" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2396" s="3" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2397" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2397" s="3" t="s">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2398" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2398" s="3" t="s">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2399" s="3">
+        <v>3800</v>
+      </c>
+      <c r="C2399" s="3" t="s">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2400" s="4">
+        <v>3900</v>
+      </c>
+      <c r="B2400" s="3" t="s">
+        <v>3676</v>
+      </c>
+      <c r="C2400" s="3" t="s">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2401" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2401" s="3" t="s">
+        <v>3682</v>
+      </c>
+      <c r="C2401" s="3" t="s">
+        <v>3677</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2402" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2402" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="C2402" s="3" t="s">
+        <v>3678</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2403" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2403" s="3" t="s">
+        <v>3696</v>
+      </c>
+      <c r="C2403" s="3" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2404" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2404" s="3" t="s">
+        <v>3698</v>
+      </c>
+      <c r="C2404" s="3" t="s">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2405" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2405" s="3" t="s">
+        <v>3702</v>
+      </c>
+      <c r="C2405" s="3" t="s">
+        <v>3681</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2406" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2406" s="3" t="s">
+        <v>3703</v>
+      </c>
+      <c r="C2406" s="3" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2407" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2407" s="3" t="s">
+        <v>3716</v>
+      </c>
+      <c r="C2407" s="3" t="s">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2408" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2408" s="3" t="s">
+        <v>3718</v>
+      </c>
+      <c r="C2408" s="3" t="s">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2409" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2409" s="3" t="s">
+        <v>3719</v>
+      </c>
+      <c r="C2409" s="3" t="s">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2410" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2410" s="3" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C2410" s="3" t="s">
+        <v>3687</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2411" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2411" s="3" t="s">
+        <v>3734</v>
+      </c>
+      <c r="C2411" s="3" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2412" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2412" s="3" t="s">
+        <v>3740</v>
+      </c>
+      <c r="C2412" s="3" t="s">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2413" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2413" s="3" t="s">
+        <v>3741</v>
+      </c>
+      <c r="C2413" s="3" t="s">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2414" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2414" s="3" t="s">
+        <v>3743</v>
+      </c>
+      <c r="C2414" s="3" t="s">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2415" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2415" s="3" t="s">
+        <v>3747</v>
+      </c>
+      <c r="C2415" s="3" t="s">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2416" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2416" s="3" t="s">
+        <v>3751</v>
+      </c>
+      <c r="C2416" s="3" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2417" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2417" s="3" t="s">
+        <v>3752</v>
+      </c>
+      <c r="C2417" s="3" t="s">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2418" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2418" s="3" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C2418" s="3" t="s">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2419" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2419" s="3" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C2419" s="3" t="s">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2420" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2420" s="3" t="s">
+        <v>3768</v>
+      </c>
+      <c r="C2420" s="3" t="s">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2421" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2421" s="3" t="s">
+        <v>3770</v>
+      </c>
+      <c r="C2421" s="3" t="s">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2422" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2422" s="3" t="s">
+        <v>3771</v>
+      </c>
+      <c r="C2422" s="3" t="s">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2423" s="3">
+        <v>3900</v>
+      </c>
+      <c r="B2423" s="3" t="s">
+        <v>3772</v>
+      </c>
+      <c r="C2423" s="3" t="s">
+        <v>3705</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2424" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2424" s="3" t="s">
+        <v>3706</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2425" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2425" s="3" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2426" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2426" s="3" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2427" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2427" s="3" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2428" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2428" s="3" t="s">
+        <v>3710</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2429" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2429" s="3" t="s">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2430" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2430" s="3" t="s">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2431" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2431" s="3" t="s">
+        <v>3713</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2432" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2432" s="3" t="s">
+        <v>3714</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2433" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2433" s="3" t="s">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2434" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2434" s="3" t="s">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2435" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2435" s="3" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2436" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2436" s="3" t="s">
+        <v>3721</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2437" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2437" s="3" t="s">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2438" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2438" s="3" t="s">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2439" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2439" s="3" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2440" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2440" s="3" t="s">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2441" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2441" s="3" t="s">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2442" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2442" s="3" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2443" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2443" s="3" t="s">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2444" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2444" s="3" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2445" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2445" s="3" t="s">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2446" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2446" s="3" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2447" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2447" s="3" t="s">
+        <v>3733</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2448" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2448" s="3" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2449" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2449" s="3" t="s">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2450" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2450" s="3" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2451" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2451" s="3" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2452" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2452" s="3" t="s">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2453" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2453" s="3" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2454" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2454" s="3" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2455" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2455" s="3" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2456" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2456" s="3" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2457" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2457" s="3" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2458" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2458" s="3" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2459" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2459" s="3" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2460" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2460" s="3" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2461" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2461" s="3" t="s">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2462" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2462" s="3" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2463" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2463" s="3" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2464" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2464" s="3" t="s">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2465" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2465" s="3" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2466" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2466" s="3" t="s">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2467" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2467" s="3" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2468" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2468" s="3" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2469" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2469" s="3" t="s">
+        <v>3763</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2470" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2470" s="3" t="s">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2471" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2471" s="3" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2472" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2472" s="3" t="s">
+        <v>3766</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2473" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2473" s="3" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2474" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2474" s="3" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2475" s="3">
+        <v>3900</v>
+      </c>
+      <c r="C2475" s="3" t="s">
+        <v>3774</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDD1F00-2F99-4BCB-913F-09DD340E2841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C53B20-F621-47F4-B819-E7B691697066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="3775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="3875">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -15120,6 +15120,406 @@
   </si>
   <si>
     <t>dispute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baltic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>male</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prevalent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nest-building</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recruit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hereditary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterpart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consensus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sugar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ethic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>individualistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stylistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eka</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cabin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convenient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fine-art</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exaggeration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hamper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpleasant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>softwood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arsenic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reptilian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overirrigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conclusive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>honeybee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satiric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>starvation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spruce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprehend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diffusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>differentiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whenever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stiffen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fetus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feeder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reminder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foodstuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shepherd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>informant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allocate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cedar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vanish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coexist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>migrant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aviation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frontal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hexagonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sizable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decompose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mineralization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>krypton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diminish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>residual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chlorophyll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xenon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penicillin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homestead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prestigious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frustration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>servant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imitative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lesson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incubate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hectare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commitee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chocolate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loosely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linsey-woolsey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enthusiastic</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15592,7 +15992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2475"/>
+  <dimension ref="A1:N2555"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -38334,6 +38734,706 @@
         <v>3774</v>
       </c>
     </row>
+    <row r="2476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2476" s="4">
+        <v>4000</v>
+      </c>
+      <c r="B2476" s="3" t="s">
+        <v>3776</v>
+      </c>
+      <c r="C2476" s="3" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2477" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2477" s="3" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C2477" s="3" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2478" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2478" s="3" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C2478" s="3" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2479" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2479" s="3" t="s">
+        <v>3790</v>
+      </c>
+      <c r="C2479" s="3" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2480" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2480" s="3" t="s">
+        <v>3795</v>
+      </c>
+      <c r="C2480" s="3" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2481" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2481" s="3" t="s">
+        <v>3800</v>
+      </c>
+      <c r="C2481" s="3" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2482" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2482" s="3" t="s">
+        <v>3812</v>
+      </c>
+      <c r="C2482" s="3" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2483" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2483" s="3" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C2483" s="3" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2484" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2484" s="3" t="s">
+        <v>3823</v>
+      </c>
+      <c r="C2484" s="3" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2485" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2485" s="3" t="s">
+        <v>3825</v>
+      </c>
+      <c r="C2485" s="3" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2486" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2486" s="3" t="s">
+        <v>3827</v>
+      </c>
+      <c r="C2486" s="3" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2487" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2487" s="3" t="s">
+        <v>3828</v>
+      </c>
+      <c r="C2487" s="3" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2488" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2488" s="3" t="s">
+        <v>3841</v>
+      </c>
+      <c r="C2488" s="3" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2489" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2489" s="3" t="s">
+        <v>3845</v>
+      </c>
+      <c r="C2489" s="3" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2490" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2490" s="3" t="s">
+        <v>3863</v>
+      </c>
+      <c r="C2490" s="3" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2491" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2491" s="3" t="s">
+        <v>3867</v>
+      </c>
+      <c r="C2491" s="3" t="s">
+        <v>3794</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2492" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2492" s="3" t="s">
+        <v>3868</v>
+      </c>
+      <c r="C2492" s="3" t="s">
+        <v>3796</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2493" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2493" s="3" t="s">
+        <v>3870</v>
+      </c>
+      <c r="C2493" s="3" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2494" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2494" s="3" t="s">
+        <v>3873</v>
+      </c>
+      <c r="C2494" s="3" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2495" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B2495" s="3" t="s">
+        <v>3874</v>
+      </c>
+      <c r="C2495" s="3" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2496" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2496" s="3" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2497" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2497" s="3" t="s">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2498" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2498" s="3" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2499" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2499" s="3" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2500" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2500" s="3" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2501" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2501" s="3" t="s">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2502" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2502" s="3" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2503" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2503" s="3" t="s">
+        <v>3808</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2504" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2504" s="3" t="s">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2505" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2505" s="3" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2506" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2506" s="3" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2507" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2507" s="3" t="s">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2508" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2508" s="3" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2509" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2509" s="3" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2510" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2510" s="3" t="s">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2511" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2511" s="3" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2512" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2512" s="3" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2513" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2513" s="3" t="s">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2514" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2514" s="3" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2515" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2515" s="3" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2516" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2516" s="3" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2517" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2517" s="3" t="s">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2518" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2518" s="3" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2519" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2519" s="3" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2520" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2520" s="3" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2521" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2521" s="3" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2522" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2522" s="3" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2523" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2523" s="3" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2524" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2524" s="3" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2525" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2525" s="3" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2526" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2526" s="3" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2527" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2527" s="3" t="s">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2528" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2528" s="3" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2529" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2529" s="3" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2530" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2530" s="3" t="s">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2531" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2531" s="3" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2532" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2532" s="3" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2533" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2533" s="3" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2534" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2534" s="3" t="s">
+        <v>3847</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2535" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2535" s="3" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2536" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2536" s="3" t="s">
+        <v>3849</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2537" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2537" s="3" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2538" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2538" s="3" t="s">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2539" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2539" s="3" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2540" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2540" s="3" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2541" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2541" s="3" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2542" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2542" s="3" t="s">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2543" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2543" s="3" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2544" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2544" s="3" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2545" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2545" s="3" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2546" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2546" s="3" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2547" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2547" s="3" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2548" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2548" s="3" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2549" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2549" s="3" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2550" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2550" s="3" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2551" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2551" s="3" t="s">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2552" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2552" s="3" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2553" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2553" s="3" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2554" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2554" s="3" t="s">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2555" s="3">
+        <v>4000</v>
+      </c>
+      <c r="C2555" s="3" t="s">
+        <v>3872</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C53B20-F621-47F4-B819-E7B691697066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4996786-D2B7-4EE6-BA04-BCCB72EDE54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="3875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="3974">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -15520,6 +15520,402 @@
   </si>
   <si>
     <t>enthusiastic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proof</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infrastructure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>novelist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peruvian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>osprey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scotland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underneath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pillar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>someone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kneel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evaluation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huckleberry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>darken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>historically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disorient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthocyanin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acidic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anyone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fingerboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watercraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buildup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varnish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbiosis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presidential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sponge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Russia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>powder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>organizational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abruptly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>administrative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypothetical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pastoral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overtime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interglacial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bias</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ahead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detractor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timescale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>far-reaching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>left-hand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>middle-class</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sailfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marlin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swordfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>renewal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eurasian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tolerant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortunate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buoyant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kinship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>helpful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domestication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replenish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fellowship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutelage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freudian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pent-up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>controversy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blubber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basalt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photographer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Berlin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opaque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vigorously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brightly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underlies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telecommunication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constructive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>habituation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generalization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shock</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15992,7 +16388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2555"/>
+  <dimension ref="A1:N2630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -39434,6 +39830,681 @@
         <v>3872</v>
       </c>
     </row>
+    <row r="2556" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2556" s="4">
+        <v>4100</v>
+      </c>
+      <c r="B2556" s="3" t="s">
+        <v>3879</v>
+      </c>
+      <c r="C2556" s="3" t="s">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2557" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2557" s="3" t="s">
+        <v>3884</v>
+      </c>
+      <c r="C2557" s="3" t="s">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2558" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2558" s="3" t="s">
+        <v>3885</v>
+      </c>
+      <c r="C2558" s="3" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2559" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2559" s="3" t="s">
+        <v>3893</v>
+      </c>
+      <c r="C2559" s="3" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2560" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2560" s="3" t="s">
+        <v>3898</v>
+      </c>
+      <c r="C2560" s="3" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2561" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2561" s="3" t="s">
+        <v>3900</v>
+      </c>
+      <c r="C2561" s="3" t="s">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2562" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2562" s="3" t="s">
+        <v>3901</v>
+      </c>
+      <c r="C2562" s="3" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2563" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2563" s="3" t="s">
+        <v>3902</v>
+      </c>
+      <c r="C2563" s="3" t="s">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2564" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2564" s="3" t="s">
+        <v>3908</v>
+      </c>
+      <c r="C2564" s="3" t="s">
+        <v>3886</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2565" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2565" s="3" t="s">
+        <v>3911</v>
+      </c>
+      <c r="C2565" s="3" t="s">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2566" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2566" s="3" t="s">
+        <v>3915</v>
+      </c>
+      <c r="C2566" s="3" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2567" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2567" s="3" t="s">
+        <v>3918</v>
+      </c>
+      <c r="C2567" s="3" t="s">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2568" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2568" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="C2568" s="3" t="s">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2569" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2569" s="3" t="s">
+        <v>3923</v>
+      </c>
+      <c r="C2569" s="3" t="s">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2570" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2570" s="3" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C2570" s="3" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2571" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2571" s="3" t="s">
+        <v>3928</v>
+      </c>
+      <c r="C2571" s="3" t="s">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2572" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2572" s="3" t="s">
+        <v>3933</v>
+      </c>
+      <c r="C2572" s="3" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2573" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2573" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2573" s="3" t="s">
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2574" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2574" s="3" t="s">
+        <v>3939</v>
+      </c>
+      <c r="C2574" s="3" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2575" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2575" s="3" t="s">
+        <v>3942</v>
+      </c>
+      <c r="C2575" s="3" t="s">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2576" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2576" s="3" t="s">
+        <v>3944</v>
+      </c>
+      <c r="C2576" s="3" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2577" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2577" s="3" t="s">
+        <v>3958</v>
+      </c>
+      <c r="C2577" s="3" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2578" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2578" s="3" t="s">
+        <v>3960</v>
+      </c>
+      <c r="C2578" s="3" t="s">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2579" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2579" s="3" t="s">
+        <v>3965</v>
+      </c>
+      <c r="C2579" s="3" t="s">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2580" s="3">
+        <v>4100</v>
+      </c>
+      <c r="B2580" s="3" t="s">
+        <v>3969</v>
+      </c>
+      <c r="C2580" s="3" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2581" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2581" s="3" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2582" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2582" s="3" t="s">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2583" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2583" s="3" t="s">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2584" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2584" s="3" t="s">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2585" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2585" s="3" t="s">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2586" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2586" s="3" t="s">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2587" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2587" s="3" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2588" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2588" s="3" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2589" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2589" s="4" t="s">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2590" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2590" s="3" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2591" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2591" s="3" t="s">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2592" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2592" s="3" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2593" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2593" s="3" t="s">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2594" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2594" s="3" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2595" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2595" s="3" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2596" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2596" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2597" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2597" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2598" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2598" s="3" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2599" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2599" s="3" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2600" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2600" s="3" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2601" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2601" s="3" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2602" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2602" s="3" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2603" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2603" s="3" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2604" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2604" s="3" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2605" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2605" s="3" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2606" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2606" s="3" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2607" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2607" s="3" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2608" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2608" s="3" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2609" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2609" s="3" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2610" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2610" s="3" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2611" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2611" s="3" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2612" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2612" s="3" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2613" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2613" s="3" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2614" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2614" s="3" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2615" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2615" s="3" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2616" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2616" s="3" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2617" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2617" s="3" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2618" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2618" s="3" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2619" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2619" s="3" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2620" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2620" s="3" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2621" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2621" s="3" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2622" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2622" s="3" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2623" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2623" s="3" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2624" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2624" s="3" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2625" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2625" s="3" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2626" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2626" s="3" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2627" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2627" s="3" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2628" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2628" s="3" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2629" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2629" s="3" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2630" s="3">
+        <v>4100</v>
+      </c>
+      <c r="C2630" s="3" t="s">
+        <v>3973</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4996786-D2B7-4EE6-BA04-BCCB72EDE54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960ED794-994E-4497-9C19-96F1851F76D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="3974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="4074">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -15916,6 +15916,406 @@
   </si>
   <si>
     <t>shock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permanence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>briefly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precipitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scottish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Norwegian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joiner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repetition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patronage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bacterium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shaft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mexican</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crumple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>developmental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>await</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warmth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>newborn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alien</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shapbook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manhattan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satisfactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devastate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Holland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prospect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arcade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deterioration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pursuit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metallurgy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taxes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solidify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>belt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meticulously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>configuration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unaided</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perplex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unnecessary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outermost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legendary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>haul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>congressional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abstraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>December</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overlap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>width</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camouflage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prairie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triumph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cylindrical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reinforce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>son</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stimulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hibernate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auxiliary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>athlete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulit-in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>close-up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kettle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaboration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16388,7 +16788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2630"/>
+  <dimension ref="A1:N2704"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -40505,6 +40905,676 @@
         <v>3973</v>
       </c>
     </row>
+    <row r="2631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2631" s="4">
+        <v>4200</v>
+      </c>
+      <c r="B2631" s="3" t="s">
+        <v>3976</v>
+      </c>
+      <c r="C2631" s="3" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2632" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2632" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="C2632" s="3" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2633" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2633" s="4" t="s">
+        <v>3985</v>
+      </c>
+      <c r="C2633" s="3" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2634" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2634" s="3" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C2634" s="3" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2635" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2635" s="3" t="s">
+        <v>3995</v>
+      </c>
+      <c r="C2635" s="3" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2636" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2636" s="3" t="s">
+        <v>3996</v>
+      </c>
+      <c r="C2636" s="3" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2637" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2637" s="3" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C2637" s="3" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2638" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2638" s="3" t="s">
+        <v>4001</v>
+      </c>
+      <c r="C2638" s="3" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2639" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2639" s="3" t="s">
+        <v>4004</v>
+      </c>
+      <c r="C2639" s="3" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2640" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2640" s="3" t="s">
+        <v>4006</v>
+      </c>
+      <c r="C2640" s="3" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2641" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2641" s="3" t="s">
+        <v>4007</v>
+      </c>
+      <c r="C2641" s="3" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2642" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2642" s="3" t="s">
+        <v>4008</v>
+      </c>
+      <c r="C2642" s="3" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2643" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2643" s="3" t="s">
+        <v>4009</v>
+      </c>
+      <c r="C2643" s="3" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2644" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2644" s="3" t="s">
+        <v>4011</v>
+      </c>
+      <c r="C2644" s="3" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2645" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2645" s="3" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C2645" s="3" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2646" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2646" s="3" t="s">
+        <v>4027</v>
+      </c>
+      <c r="C2646" s="3" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2647" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2647" s="3" t="s">
+        <v>4041</v>
+      </c>
+      <c r="C2647" s="3" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2648" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2648" s="3" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C2648" s="3" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2649" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2649" s="3" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C2649" s="3" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2650" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2650" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="C2650" s="3" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2651" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2651" s="3" t="s">
+        <v>4052</v>
+      </c>
+      <c r="C2651" s="3" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2652" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2652" s="3" t="s">
+        <v>4062</v>
+      </c>
+      <c r="C2652" s="3" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2653" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2653" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="C2653" s="3" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2654" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2654" s="3" t="s">
+        <v>4070</v>
+      </c>
+      <c r="C2654" s="3" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2655" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2655" s="3" t="s">
+        <v>4072</v>
+      </c>
+      <c r="C2655" s="3" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2656" s="3">
+        <v>4200</v>
+      </c>
+      <c r="B2656" s="3" t="s">
+        <v>4073</v>
+      </c>
+      <c r="C2656" s="3" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2657" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2657" s="3" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2658" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2658" s="3" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2659" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2659" s="3" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2660" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2660" s="3" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2661" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2661" s="3" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2662" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2662" s="3" t="s">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2663" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2663" s="3" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2664" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2664" s="3" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2665" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2665" s="3" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2666" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2666" s="4" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2667" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2667" s="3" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2668" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2668" s="3" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2669" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2669" s="3" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2670" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2670" s="3" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2671" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2671" s="3" t="s">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2672" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2672" s="3" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2673" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2673" s="3" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2674" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2674" s="3" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2675" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2675" s="3" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2676" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2676" s="3" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2677" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2677" s="3" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2678" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2678" s="3" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2679" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2679" s="3" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2680" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2680" s="3" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2681" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2681" s="3" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2682" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2682" s="3" t="s">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2683" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2683" s="3" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2684" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2684" s="3" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2685" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2685" s="3" t="s">
+        <v>4047</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2686" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2686" s="3" t="s">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2687" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2687" s="3" t="s">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2688" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2688" s="3" t="s">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2689" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2689" s="3" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2690" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2690" s="3" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2691" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2691" s="3" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2692" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2692" s="3" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2693" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2693" s="3" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2694" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2694" s="4" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2695" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2695" s="3" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2696" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2696" s="3" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2697" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2697" s="3" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2698" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2698" s="3" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2699" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2699" s="3" t="s">
+        <v>4064</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2700" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2700" s="3" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2701" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2701" s="3" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2702" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2702" s="3" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2703" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2703" s="3" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2704" s="3">
+        <v>4200</v>
+      </c>
+      <c r="C2704" s="3" t="s">
+        <v>4071</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960ED794-994E-4497-9C19-96F1851F76D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2323558-DEEF-4C04-A386-B7640A6A558D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="4074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="4174">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -16316,6 +16316,406 @@
   </si>
   <si>
     <t>collaboration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterpower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pollen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dealer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firmly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relieve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defensive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equilibrium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbolize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exocrine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>definite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foemerly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cosmos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overlie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shorten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detectable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accommodate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toolmaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>printmaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>populous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wallpaper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reputation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gasoline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>igloo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>edition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inefficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geographer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>willow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>continuity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteoric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recipient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Michigan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>favorite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anxious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adoption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instruct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>god</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>girl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exceptionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fieldstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imperial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defenseless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>furnish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lumiere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accompaniment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repetitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>individualism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Russian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>krill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coastline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unevenly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drapery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordinarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>headquarter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radiocarbon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relocate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enormously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saltwater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deglaciation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wax</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16788,7 +17188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2704"/>
+  <dimension ref="A1:N2786"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -41575,6 +41975,716 @@
         <v>4071</v>
       </c>
     </row>
+    <row r="2705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2705" s="4">
+        <v>4300</v>
+      </c>
+      <c r="B2705" s="3" t="s">
+        <v>4074</v>
+      </c>
+      <c r="C2705" s="3" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2706" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2706" s="3" t="s">
+        <v>4090</v>
+      </c>
+      <c r="C2706" s="3" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2707" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2707" s="3" t="s">
+        <v>4091</v>
+      </c>
+      <c r="C2707" s="3" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2708" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2708" s="3" t="s">
+        <v>4092</v>
+      </c>
+      <c r="C2708" s="3" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2709" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2709" s="3" t="s">
+        <v>4102</v>
+      </c>
+      <c r="C2709" s="3" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2710" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2710" s="3" t="s">
+        <v>4105</v>
+      </c>
+      <c r="C2710" s="3" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2711" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2711" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C2711" s="3" t="s">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2712" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2712" s="3" t="s">
+        <v>4119</v>
+      </c>
+      <c r="C2712" s="3" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2713" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2713" s="3" t="s">
+        <v>4122</v>
+      </c>
+      <c r="C2713" s="3" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2714" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2714" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="C2714" s="3" t="s">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2715" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2715" s="3" t="s">
+        <v>4129</v>
+      </c>
+      <c r="C2715" s="3" t="s">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2716" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2716" s="3" t="s">
+        <v>4130</v>
+      </c>
+      <c r="C2716" s="3" t="s">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2717" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2717" s="3" t="s">
+        <v>4131</v>
+      </c>
+      <c r="C2717" s="3" t="s">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2718" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2718" s="3" t="s">
+        <v>4149</v>
+      </c>
+      <c r="C2718" s="3" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2719" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2719" s="3" t="s">
+        <v>4152</v>
+      </c>
+      <c r="C2719" s="3" t="s">
+        <v>4089</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2720" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2720" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="C2720" s="3" t="s">
+        <v>4093</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2721" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2721" s="3" t="s">
+        <v>4162</v>
+      </c>
+      <c r="C2721" s="3" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2722" s="3">
+        <v>4300</v>
+      </c>
+      <c r="B2722" s="3" t="s">
+        <v>4167</v>
+      </c>
+      <c r="C2722" s="3" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2723" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2723" s="3" t="s">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2724" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2724" s="3" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2725" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2725" s="3" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2726" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2726" s="3" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2727" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2727" s="3" t="s">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2728" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2728" s="3" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2729" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2729" s="3" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2730" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2730" s="3" t="s">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2731" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2731" s="3" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2732" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2732" s="3" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2733" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2733" s="3" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2734" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2734" s="3" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2735" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2735" s="3" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2736" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2736" s="3" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2737" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2737" s="3" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2738" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2738" s="3" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2739" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2739" s="3" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2740" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2740" s="3" t="s">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2741" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2741" s="3" t="s">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2742" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2742" s="3" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2743" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2743" s="3" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2744" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2744" s="3" t="s">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2745" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2745" s="3" t="s">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2746" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2746" s="3" t="s">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2747" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2747" s="3" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2748" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2748" s="3" t="s">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2749" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2749" s="3" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2750" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2750" s="3" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2751" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2751" s="3" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2752" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2752" s="3" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2753" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2753" s="3" t="s">
+        <v>4135</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2754" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2754" s="3" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2755" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2755" s="3" t="s">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2756" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2756" s="3" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2757" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2757" s="3" t="s">
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2758" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2758" s="3" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2759" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2759" s="3" t="s">
+        <v>4141</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2760" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2760" s="3" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2761" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2761" s="3" t="s">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2762" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2762" s="3" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2763" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2763" s="3" t="s">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2764" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2764" s="3" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2765" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2765" s="3" t="s">
+        <v>4147</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2766" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2766" s="3" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2767" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2767" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2768" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2768" s="3" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2769" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2769" s="3" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2770" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2770" s="3" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2771" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2771" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2772" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2772" s="3" t="s">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2773" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2773" s="3" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2774" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2774" s="3" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2775" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2775" s="3" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2776" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2776" s="3" t="s">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2777" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2777" s="3" t="s">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2778" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2778" s="3" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2779" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2779" s="3" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2780" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2780" s="3" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2781" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2781" s="3" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2782" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2782" s="3" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2783" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2783" s="3" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2784" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2784" s="3" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2785" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2785" s="3" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2786" s="3">
+        <v>4300</v>
+      </c>
+      <c r="C2786" s="3" t="s">
+        <v>4173</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2323558-DEEF-4C04-A386-B7640A6A558D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A9E26-D919-411B-ADA4-0DBAD1BD7AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="4174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4286" uniqueCount="4274">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -16716,6 +16716,406 @@
   </si>
   <si>
     <t>wax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neglect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pangaea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fahrenheit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>midcontinent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emperor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mainstay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>connecticut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wholly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brilliance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhinoceros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>externally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plumb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lessen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superintendent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friendly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wasteful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foraminifera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aborigine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sttest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggressiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vague</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lawlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oppositely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anecdotal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disorder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>right-hand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synchronization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biographer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creativity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joint-stock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curriculum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anglo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hampshire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worthwhile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instinctive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>signaler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turbulence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paradigm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penchant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sinkhole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neptune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cyanide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revolve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdraw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supplant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harpsichord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long-range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peaceful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tempt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revitalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spiritual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fictional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heterogeneous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diversion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protrude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recrystallize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nevada</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amusement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monetary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legislature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baboon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wedge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overgraze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blowhole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magenta</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17188,7 +17588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2786"/>
+  <dimension ref="A1:N2874"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -42685,6 +43085,746 @@
         <v>4173</v>
       </c>
     </row>
+    <row r="2787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2787" s="4">
+        <v>4400</v>
+      </c>
+      <c r="B2787" s="3" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C2787" s="3" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2788" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2788" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C2788" s="3" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2789" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2789" s="3" t="s">
+        <v>4191</v>
+      </c>
+      <c r="C2789" s="3" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2790" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2790" s="3" t="s">
+        <v>4195</v>
+      </c>
+      <c r="C2790" s="3" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2791" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2791" s="3" t="s">
+        <v>4196</v>
+      </c>
+      <c r="C2791" s="3" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2792" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2792" s="3" t="s">
+        <v>4198</v>
+      </c>
+      <c r="C2792" s="3" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2793" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2793" s="3" t="s">
+        <v>4215</v>
+      </c>
+      <c r="C2793" s="3" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2794" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2794" s="3" t="s">
+        <v>4228</v>
+      </c>
+      <c r="C2794" s="3" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2795" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2795" s="3" t="s">
+        <v>4239</v>
+      </c>
+      <c r="C2795" s="3" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2796" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2796" s="3" t="s">
+        <v>4240</v>
+      </c>
+      <c r="C2796" s="3" t="s">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2797" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2797" s="3" t="s">
+        <v>4242</v>
+      </c>
+      <c r="C2797" s="3" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2798" s="3">
+        <v>4400</v>
+      </c>
+      <c r="B2798" s="3" t="s">
+        <v>4246</v>
+      </c>
+      <c r="C2798" s="3" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2799" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2799" s="3" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2800" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2800" s="3" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2801" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2801" s="3" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2802" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2802" s="3" t="s">
+        <v>4192</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2803" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2803" s="3" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2804" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2804" s="3" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2805" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2805" s="3" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2806" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2806" s="3" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2807" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2807" s="3" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2808" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2808" s="3" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2809" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2809" s="3" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2810" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2810" s="3" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2811" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2811" s="3" t="s">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2812" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2812" s="3" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2813" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2813" s="3" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2814" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2814" s="3" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2815" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2815" s="3" t="s">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2816" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2816" s="3" t="s">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2817" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2817" s="3" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2818" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2818" s="3" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2819" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2819" s="3" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2820" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2820" s="3" t="s">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2821" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2821" s="3" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2822" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2822" s="3" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2823" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2823" s="3" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2824" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2824" s="3" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2825" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2825" s="3" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2826" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2826" s="3" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2827" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2827" s="3" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2828" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2828" s="3" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2829" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2829" s="3" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2830" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2830" s="3" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2831" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2831" s="3" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2832" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2832" s="3" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2833" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2833" s="3" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2834" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2834" s="3" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2835" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2835" s="3" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2836" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2836" s="3" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2837" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2837" s="3" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2838" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2838" s="3" t="s">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2839" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2839" s="3" t="s">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2840" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2840" s="3" t="s">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2841" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2841" s="3" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2842" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2842" s="3" t="s">
+        <v>4237</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2843" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2843" s="3" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2844" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2844" s="3" t="s">
+        <v>4241</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2845" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2845" s="3" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2846" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2846" s="3" t="s">
+        <v>4244</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2847" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2847" s="3" t="s">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2848" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2848" s="3" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2849" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2849" s="3" t="s">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2850" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2850" s="3" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2851" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2851" s="3" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2852" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2852" s="3" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2853" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2853" s="3" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2854" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2854" s="3" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2855" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2855" s="3" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2856" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2856" s="3" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2857" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2857" s="3" t="s">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2858" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2858" s="3" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2859" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2859" s="3" t="s">
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2860" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2860" s="3" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2861" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2861" s="3" t="s">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2862" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2862" s="3" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2863" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2863" s="3" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2864" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2864" s="3" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2865" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2865" s="3" t="s">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2866" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2866" s="3" t="s">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2867" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2867" s="3" t="s">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2868" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2868" s="3" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2869" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2869" s="3" t="s">
+        <v>4268</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2870" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2870" s="3" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2871" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2871" s="3" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2872" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2872" s="3" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2873" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2873" s="3" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2874" s="3">
+        <v>4400</v>
+      </c>
+      <c r="C2874" s="3" t="s">
+        <v>4273</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A9E26-D919-411B-ADA4-0DBAD1BD7AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B2AC40-9C5A-4750-9432-54E9EF83CA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4286" uniqueCount="4274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4386" uniqueCount="4374">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -17116,6 +17116,406 @@
   </si>
   <si>
     <t>magenta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>valse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rebellion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discoverer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charcoal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conifer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>botanist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narrator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inca</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woolen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>void</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dictate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incursion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sweet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advantageous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliberate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>socially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inventory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drastic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>daguerreotype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>staple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fatty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mainland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spinal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clockwise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feasible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distrust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>by-product</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-governing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incredible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-pressure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minuscule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>envelop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortunately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dormant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coppersmith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrinsic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potato</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clarify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extermination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suburbanization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>succulent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>micron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>publicize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catastrophic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fodder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photoflash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substantiated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cramp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reversal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virtuosity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leafy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perishable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Israel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retrieval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domelike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>savannah</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacuum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elliot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arthropod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>departure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>momentum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spearhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unjust</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17588,7 +17988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2874"/>
+  <dimension ref="A1:N2959"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -43825,6 +44225,731 @@
         <v>4273</v>
       </c>
     </row>
+    <row r="2875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2875" s="4">
+        <v>4500</v>
+      </c>
+      <c r="B2875" s="3" t="s">
+        <v>4276</v>
+      </c>
+      <c r="C2875" s="3" t="s">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2876" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2876" s="3" t="s">
+        <v>4285</v>
+      </c>
+      <c r="C2876" s="3" t="s">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2877" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2877" s="3" t="s">
+        <v>4286</v>
+      </c>
+      <c r="C2877" s="3" t="s">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2878" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2878" s="3" t="s">
+        <v>4289</v>
+      </c>
+      <c r="C2878" s="3" t="s">
+        <v>4278</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2879" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2879" s="3" t="s">
+        <v>4290</v>
+      </c>
+      <c r="C2879" s="3" t="s">
+        <v>4279</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2880" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2880" s="3" t="s">
+        <v>4291</v>
+      </c>
+      <c r="C2880" s="3" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2881" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2881" s="3" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C2881" s="3" t="s">
+        <v>4281</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2882" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2882" s="3" t="s">
+        <v>4295</v>
+      </c>
+      <c r="C2882" s="3" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2883" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2883" s="3" t="s">
+        <v>4297</v>
+      </c>
+      <c r="C2883" s="3" t="s">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2884" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2884" s="3" t="s">
+        <v>4299</v>
+      </c>
+      <c r="C2884" s="3" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2885" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2885" s="3" t="s">
+        <v>4306</v>
+      </c>
+      <c r="C2885" s="3" t="s">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2886" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2886" s="3" t="s">
+        <v>4328</v>
+      </c>
+      <c r="C2886" s="3" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2887" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2887" s="3" t="s">
+        <v>4346</v>
+      </c>
+      <c r="C2887" s="3" t="s">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2888" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2888" s="3" t="s">
+        <v>4361</v>
+      </c>
+      <c r="C2888" s="3" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2889" s="3">
+        <v>4500</v>
+      </c>
+      <c r="B2889" s="3" t="s">
+        <v>4363</v>
+      </c>
+      <c r="C2889" s="3" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2890" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2890" s="3" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2891" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2891" s="3" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2892" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2892" s="3" t="s">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2893" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2893" s="3" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2894" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2894" s="3" t="s">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2895" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2895" s="3" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2896" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2896" s="3" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2897" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2897" s="3" t="s">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2898" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2898" s="3" t="s">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2899" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2899" s="3" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2900" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2900" s="3" t="s">
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2901" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2901" s="3" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2902" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2902" s="3" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2903" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2903" s="3" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2904" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2904" s="3" t="s">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2905" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2905" s="3" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2906" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2906" s="3" t="s">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2907" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2907" s="3" t="s">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2908" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2908" s="3" t="s">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2909" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2909" s="3" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2910" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2910" s="3" t="s">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2911" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2911" s="3" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2912" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2912" s="3" t="s">
+        <v>4322</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2913" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2913" s="3" t="s">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2914" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2914" s="3" t="s">
+        <v>4324</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2915" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2915" s="3" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2916" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2916" s="3" t="s">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2917" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2917" s="3" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2918" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2918" s="3" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2919" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2919" s="3" t="s">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2920" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2920" s="3" t="s">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2921" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2921" s="3" t="s">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2922" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2922" s="3" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2923" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2923" s="3" t="s">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2924" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2924" s="3" t="s">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2925" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2925" s="3" t="s">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2926" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2926" s="3" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2927" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2927" s="3" t="s">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2928" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2928" s="3" t="s">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2929" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2929" s="3" t="s">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2930" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2930" s="3" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2931" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2931" s="3" t="s">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2932" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2932" s="3" t="s">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2933" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2933" s="3" t="s">
+        <v>4344</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2934" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2934" s="3" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2935" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2935" s="3" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2936" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2936" s="3" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2937" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2937" s="3" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2938" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2938" s="3" t="s">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2939" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2939" s="3" t="s">
+        <v>4351</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2940" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2940" s="3" t="s">
+        <v>4352</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2941" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2941" s="3" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2942" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2942" s="3" t="s">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2943" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2943" s="3" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2944" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2944" s="3" t="s">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2945" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2945" s="3" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2946" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2946" s="3" t="s">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2947" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2947" s="3" t="s">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2948" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2948" s="3" t="s">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2949" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2949" s="3" t="s">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2950" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2950" s="3" t="s">
+        <v>4364</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2951" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2951" s="3" t="s">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2952" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2952" s="3" t="s">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2953" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2953" s="3" t="s">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2954" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2954" s="3" t="s">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2955" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2955" s="3" t="s">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2956" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2956" s="3" t="s">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2957" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2957" s="4" t="s">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2958" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2958" s="3" t="s">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2959" s="3">
+        <v>4500</v>
+      </c>
+      <c r="C2959" s="3" t="s">
+        <v>4373</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B2AC40-9C5A-4750-9432-54E9EF83CA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3BCAB-A0EF-4B67-B902-3641897CC313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4386" uniqueCount="4374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4486" uniqueCount="4474">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -17516,6 +17516,405 @@
   </si>
   <si>
     <t>unjust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrialism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>part-time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>environmentally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swirl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bluefin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radiant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sociobiology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ideological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solidarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>providence</t>
+  </si>
+  <si>
+    <t>catharsis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contradictory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chloride</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archaic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aristocrat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consolidate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absolute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soviet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humanity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>budget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnesium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engulf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frigid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grandiose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>citizenship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>despondent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>identifiable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cellular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>universality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>widen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressionism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moderately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbolism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unreliable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfortunate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weekly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compensation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aerodynamic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>command</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arbitrary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pianist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliberately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>craftsmanship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affinity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diagonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhaust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resemblance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nontraditional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disprove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skeptical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plenty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appropriately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emotionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freshly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unbelievable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simultaneous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>induce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woodworker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conversation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>translate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>possession</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invariably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Babylonian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urbanization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sulfur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stripe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ought</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volatile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>densely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biography</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17988,7 +18387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N2959"/>
+  <dimension ref="A1:N3043"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -44950,6 +45349,726 @@
         <v>4373</v>
       </c>
     </row>
+    <row r="2960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2960" s="4">
+        <v>4600</v>
+      </c>
+      <c r="B2960" s="3" t="s">
+        <v>4375</v>
+      </c>
+      <c r="C2960" s="3" t="s">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2961" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2961" s="3" t="s">
+        <v>4376</v>
+      </c>
+      <c r="C2961" s="3" t="s">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2962" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2962" s="3" t="s">
+        <v>4400</v>
+      </c>
+      <c r="C2962" s="3" t="s">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2963" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2963" s="3" t="s">
+        <v>4422</v>
+      </c>
+      <c r="C2963" s="3" t="s">
+        <v>4379</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2964" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2964" s="3" t="s">
+        <v>4425</v>
+      </c>
+      <c r="C2964" s="3" t="s">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2965" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2965" s="3" t="s">
+        <v>4427</v>
+      </c>
+      <c r="C2965" s="3" t="s">
+        <v>4381</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2966" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2966" s="3" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C2966" s="3" t="s">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2967" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2967" s="3" t="s">
+        <v>4431</v>
+      </c>
+      <c r="C2967" s="3" t="s">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2968" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2968" s="3" t="s">
+        <v>4438</v>
+      </c>
+      <c r="C2968" s="3" t="s">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2969" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2969" s="3" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C2969" s="3" t="s">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="2970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2970" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2970" s="3" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C2970" s="3" t="s">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="2971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2971" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2971" s="3" t="s">
+        <v>4458</v>
+      </c>
+      <c r="C2971" s="3" t="s">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="2972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2972" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2972" s="3" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C2972" s="3" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="2973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2973" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2973" s="3" t="s">
+        <v>4462</v>
+      </c>
+      <c r="C2973" s="3" t="s">
+        <v>4389</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2974" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2974" s="3" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C2974" s="3" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2975" s="3">
+        <v>4600</v>
+      </c>
+      <c r="B2975" s="3" t="s">
+        <v>4473</v>
+      </c>
+      <c r="C2975" s="3" t="s">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2976" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2976" s="3" t="s">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2977" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2977" s="3" t="s">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2978" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2978" s="3" t="s">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2979" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2979" s="3" t="s">
+        <v>4395</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2980" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2980" s="3" t="s">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2981" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2981" s="3" t="s">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2982" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2982" s="3" t="s">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2983" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2983" s="3" t="s">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2984" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2984" s="3" t="s">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2985" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2985" s="3" t="s">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2986" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2986" s="3" t="s">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2987" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2987" s="3" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2988" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2988" s="3" t="s">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2989" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2989" s="3" t="s">
+        <v>4406</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2990" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2990" s="3" t="s">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2991" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2991" s="3" t="s">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2992" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2992" s="3" t="s">
+        <v>4409</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2993" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2993" s="3" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2994" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2994" s="3" t="s">
+        <v>4411</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2995" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2995" s="3" t="s">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2996" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2996" s="3" t="s">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2997" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2997" s="3" t="s">
+        <v>4414</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2998" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2998" s="3" t="s">
+        <v>4415</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2999" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C2999" s="3" t="s">
+        <v>4416</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3000" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3000" s="3" t="s">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3001" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3001" s="3" t="s">
+        <v>4418</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3002" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3002" s="3" t="s">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="3003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3003" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3003" s="3" t="s">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="3004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3004" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3004" s="3" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="3005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3005" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3005" s="3" t="s">
+        <v>4423</v>
+      </c>
+    </row>
+    <row r="3006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3006" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3006" s="3" t="s">
+        <v>4424</v>
+      </c>
+    </row>
+    <row r="3007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3007" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3007" s="3" t="s">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3008" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3008" s="3" t="s">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3009" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3009" s="3" t="s">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="3010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3010" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3010" s="3" t="s">
+        <v>4432</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3011" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3011" s="3" t="s">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3012" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3012" s="3" t="s">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3013" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3013" s="3" t="s">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3014" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3014" s="3" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3015" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3015" s="3" t="s">
+        <v>4437</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3016" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3016" s="3" t="s">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3017" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3017" s="3" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3018" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3018" s="3" t="s">
+        <v>4441</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3019" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3019" s="3" t="s">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3020" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3020" s="3" t="s">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3021" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3021" s="3" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3022" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3022" s="3" t="s">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3023" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3023" s="3" t="s">
+        <v>4446</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3024" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3024" s="3" t="s">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3025" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3025" s="3" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3026" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3026" s="3" t="s">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3027" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3027" s="3" t="s">
+        <v>4451</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3028" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3028" s="3" t="s">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3029" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3029" s="3" t="s">
+        <v>4453</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3030" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3030" s="3" t="s">
+        <v>4454</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3031" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3031" s="3" t="s">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3032" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3032" s="3" t="s">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3033" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3033" s="3" t="s">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3034" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3034" s="3" t="s">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3035" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3035" s="3" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3036" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3036" s="3" t="s">
+        <v>4465</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3037" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3037" s="3" t="s">
+        <v>4466</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3038" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3038" s="3" t="s">
+        <v>4467</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3039" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3039" s="3" t="s">
+        <v>4468</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3040" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3040" s="3" t="s">
+        <v>4469</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3041" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3041" s="3" t="s">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3042" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3042" s="3" t="s">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3043" s="3">
+        <v>4600</v>
+      </c>
+      <c r="C3043" s="3" t="s">
+        <v>4472</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3BCAB-A0EF-4B67-B902-3641897CC313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9098153-C808-42FE-B70E-9A0B213D9EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4486" uniqueCount="4474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="4573">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -17915,6 +17918,402 @@
   </si>
   <si>
     <t>biography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inscribe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intercity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alongside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uplift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>officially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sacrifice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thunderstorm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>astronomical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-sufficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peregrine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tapestry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>influx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sculptural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>announce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leisure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>essence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landmass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrimp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornamentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undesirable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>globe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grasshopper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elegant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-sufficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shiny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glassmaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spectacularly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submerge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>terminology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unclear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unimportant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ubiquitous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>demise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conspicuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deadly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomadic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seashore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonhuman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cottage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fairground</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lengthen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>candle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kilogram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naturalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telegraph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kitchen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maturity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>honest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firewood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>granular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preindustrial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quarry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amendment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overtake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impurity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formidable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acceptable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glasslike</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18387,7 +18786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3043"/>
+  <dimension ref="A1:N3124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -46069,6 +46468,711 @@
         <v>4472</v>
       </c>
     </row>
+    <row r="3044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3044" s="4">
+        <v>4700</v>
+      </c>
+      <c r="B3044" s="3" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C3044" s="3" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3045" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3045" s="3" t="s">
+        <v>4481</v>
+      </c>
+      <c r="C3045" s="3" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3046" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3046" s="3" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C3046" s="3" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3047" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3047" s="3" t="s">
+        <v>4492</v>
+      </c>
+      <c r="C3047" s="3" t="s">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3048" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3048" s="3" t="s">
+        <v>4505</v>
+      </c>
+      <c r="C3048" s="3" t="s">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3049" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3049" s="3" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C3049" s="3" t="s">
+        <v>4479</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3050" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3050" s="3" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C3050" s="3" t="s">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3051" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3051" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C3051" s="4" t="s">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3052" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3052" s="3" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C3052" s="3" t="s">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3053" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3053" s="3" t="s">
+        <v>4525</v>
+      </c>
+      <c r="C3053" s="3" t="s">
+        <v>4485</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3054" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3054" s="3" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C3054" s="3" t="s">
+        <v>4487</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3055" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3055" s="3" t="s">
+        <v>4533</v>
+      </c>
+      <c r="C3055" s="3" t="s">
+        <v>4488</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3056" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3056" s="3" t="s">
+        <v>4539</v>
+      </c>
+      <c r="C3056" s="3" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3057" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3057" s="3" t="s">
+        <v>4542</v>
+      </c>
+      <c r="C3057" s="3" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3058" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3058" s="3" t="s">
+        <v>4546</v>
+      </c>
+      <c r="C3058" s="3" t="s">
+        <v>4491</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3059" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3059" s="3" t="s">
+        <v>4547</v>
+      </c>
+      <c r="C3059" s="3" t="s">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3060" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3060" s="3" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C3060" s="3" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3061" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3061" s="3" t="s">
+        <v>4556</v>
+      </c>
+      <c r="C3061" s="3" t="s">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3062" s="3">
+        <v>4700</v>
+      </c>
+      <c r="B3062" s="3" t="s">
+        <v>4564</v>
+      </c>
+      <c r="C3062" s="3" t="s">
+        <v>4496</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3063" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3063" s="3" t="s">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3064" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3064" s="3" t="s">
+        <v>4498</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3065" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3065" s="3" t="s">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3066" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3066" s="3" t="s">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3067" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3067" s="3" t="s">
+        <v>4501</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3068" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3068" s="3" t="s">
+        <v>4502</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3069" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3069" s="3" t="s">
+        <v>4503</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3070" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3070" s="3" t="s">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3071" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3071" s="3" t="s">
+        <v>4507</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3072" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3072" s="3" t="s">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3073" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3073" s="3" t="s">
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3074" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3074" s="3" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3075" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3075" s="3" t="s">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3076" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3076" s="3" t="s">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3077" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3077" s="3" t="s">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3078" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3078" s="3" t="s">
+        <v>4515</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3079" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3079" s="3" t="s">
+        <v>4516</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3080" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3080" s="3" t="s">
+        <v>4517</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3081" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3081" s="3" t="s">
+        <v>4519</v>
+      </c>
+    </row>
+    <row r="3082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3082" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3082" s="3" t="s">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="3083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3083" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3083" s="3" t="s">
+        <v>4521</v>
+      </c>
+    </row>
+    <row r="3084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3084" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3084" s="3" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="3085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3085" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3085" s="3" t="s">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="3086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3086" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3086" s="3" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="3087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3087" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3087" s="3" t="s">
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="3088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3088" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3088" s="3" t="s">
+        <v>4528</v>
+      </c>
+    </row>
+    <row r="3089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3089" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3089" s="3" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="3090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3090" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3090" s="3" t="s">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="3091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3091" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3091" s="3" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="3092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3092" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3092" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="3093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3093" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3093" s="3" t="s">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="3094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3094" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3094" s="3" t="s">
+        <v>4535</v>
+      </c>
+    </row>
+    <row r="3095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3095" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3095" s="3" t="s">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="3096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3096" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3096" s="3" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="3097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3097" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3097" s="3" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="3098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3098" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3098" s="3" t="s">
+        <v>4540</v>
+      </c>
+    </row>
+    <row r="3099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3099" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3099" s="3" t="s">
+        <v>4541</v>
+      </c>
+    </row>
+    <row r="3100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3100" s="3" t="s">
+        <v>4543</v>
+      </c>
+    </row>
+    <row r="3101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3101" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3101" s="3" t="s">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="3102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3102" s="3" t="s">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="3103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3103" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3103" s="3" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="3104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3104" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3104" s="3" t="s">
+        <v>4549</v>
+      </c>
+    </row>
+    <row r="3105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3105" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3105" s="3" t="s">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="3106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3106" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3106" s="3" t="s">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="3107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3107" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3107" s="3" t="s">
+        <v>4552</v>
+      </c>
+    </row>
+    <row r="3108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3108" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3108" s="3" t="s">
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="3109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3109" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3109" s="3" t="s">
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="3110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3110" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3110" s="3" t="s">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="3111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3111" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3111" s="3" t="s">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="3112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3112" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3112" s="3" t="s">
+        <v>4559</v>
+      </c>
+    </row>
+    <row r="3113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3113" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3113" s="3" t="s">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="3114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3114" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3114" s="3" t="s">
+        <v>4561</v>
+      </c>
+    </row>
+    <row r="3115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3115" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3115" s="3" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="3116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3116" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3116" s="3" t="s">
+        <v>4563</v>
+      </c>
+    </row>
+    <row r="3117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3117" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3117" s="3" t="s">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="3118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3118" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3118" s="3" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="3119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3119" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3119" s="3" t="s">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="3120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3120" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3120" s="3" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="3121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3121" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3121" s="3" t="s">
+        <v>4569</v>
+      </c>
+    </row>
+    <row r="3122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3122" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3122" s="3" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="3123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3123" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3123" s="3" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="3124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3124" s="3">
+        <v>4700</v>
+      </c>
+      <c r="C3124" s="3" t="s">
+        <v>4572</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9098153-C808-42FE-B70E-9A0B213D9EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F665BF37-0508-49DF-B0F6-3594CEC66E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="4573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4686" uniqueCount="4672">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -18314,6 +18314,402 @@
   </si>
   <si>
     <t>glasslike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>translucent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>topsoil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interrelationship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pocket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hillside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subscribe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>happy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>litter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outsider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aragonite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convenience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modern-day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>promotion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unaltered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>directional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romantic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>treeless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recorder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noticeably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plunge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eradicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caste</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inherit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gosling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rattle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>residence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antecedent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long-standing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disloyalty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>certainty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nystatin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prodigious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gatherer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoemaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electrically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprawl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>petal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>technologicallly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proportionately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>germanium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>likelihood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>threshold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sparse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mass-produce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statuary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farsighted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fatten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crawl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cautious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expanse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wonderful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sanskrit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orbital</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confront</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sideways</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hyksos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arduous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boulder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bathhouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dilute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>principally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imbalance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ionize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immigration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vivid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>necessitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hollywood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poverty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blossom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>demographic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accidentally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shipbuilding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sweat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empirical</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18786,7 +19182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3124"/>
+  <dimension ref="A1:N3206"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -47173,6 +47569,716 @@
         <v>4572</v>
       </c>
     </row>
+    <row r="3125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3125" s="4">
+        <v>4800</v>
+      </c>
+      <c r="B3125" s="3" t="s">
+        <v>4577</v>
+      </c>
+      <c r="C3125" s="3" t="s">
+        <v>4573</v>
+      </c>
+    </row>
+    <row r="3126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3126" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3126" s="3" t="s">
+        <v>4579</v>
+      </c>
+      <c r="C3126" s="3" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="3127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3127" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3127" s="3" t="s">
+        <v>4580</v>
+      </c>
+      <c r="C3127" s="3" t="s">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="3128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3128" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3128" s="3" t="s">
+        <v>4581</v>
+      </c>
+      <c r="C3128" s="3" t="s">
+        <v>4576</v>
+      </c>
+    </row>
+    <row r="3129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3129" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3129" s="3" t="s">
+        <v>4583</v>
+      </c>
+      <c r="C3129" s="3" t="s">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="3130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3130" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3130" s="3" t="s">
+        <v>4584</v>
+      </c>
+      <c r="C3130" s="3" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3131" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3131" s="3" t="s">
+        <v>4594</v>
+      </c>
+      <c r="C3131" s="3" t="s">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="3132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3132" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3132" s="3" t="s">
+        <v>4596</v>
+      </c>
+      <c r="C3132" s="3" t="s">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3133" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3133" s="3" t="s">
+        <v>4597</v>
+      </c>
+      <c r="C3133" s="3" t="s">
+        <v>4587</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3134" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3134" s="3" t="s">
+        <v>4598</v>
+      </c>
+      <c r="C3134" s="3" t="s">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3135" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3135" s="3" t="s">
+        <v>4621</v>
+      </c>
+      <c r="C3135" s="3" t="s">
+        <v>4589</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3136" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3136" s="3" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C3136" s="3" t="s">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3137" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3137" s="3" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C3137" s="3" t="s">
+        <v>4591</v>
+      </c>
+    </row>
+    <row r="3138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3138" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3138" s="3" t="s">
+        <v>4646</v>
+      </c>
+      <c r="C3138" s="3" t="s">
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3139" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3139" s="3" t="s">
+        <v>4654</v>
+      </c>
+      <c r="C3139" s="3" t="s">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3140" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3140" s="3" t="s">
+        <v>4663</v>
+      </c>
+      <c r="C3140" s="3" t="s">
+        <v>4595</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3141" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3141" s="3" t="s">
+        <v>4664</v>
+      </c>
+      <c r="C3141" s="3" t="s">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3142" s="3">
+        <v>4800</v>
+      </c>
+      <c r="B3142" s="3" t="s">
+        <v>4668</v>
+      </c>
+      <c r="C3142" s="3" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="3143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3143" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3143" s="3" t="s">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="3144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3144" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3144" s="3" t="s">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="3145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3145" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3145" s="3" t="s">
+        <v>4603</v>
+      </c>
+    </row>
+    <row r="3146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3146" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3146" s="3" t="s">
+        <v>4604</v>
+      </c>
+    </row>
+    <row r="3147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3147" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3147" s="3" t="s">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="3148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3148" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3148" s="3" t="s">
+        <v>4606</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3149" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3149" s="3" t="s">
+        <v>4607</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3150" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3150" s="3" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3151" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3151" s="3" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="3152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3152" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3152" s="3" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="3153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3153" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3153" s="3" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="3154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3154" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3154" s="3" t="s">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="3155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3155" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3155" s="3" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="3156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3156" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3156" s="3" t="s">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="3157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3157" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3157" s="3" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3158" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3158" s="3" t="s">
+        <v>4616</v>
+      </c>
+    </row>
+    <row r="3159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3159" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3159" s="3" t="s">
+        <v>4617</v>
+      </c>
+    </row>
+    <row r="3160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3160" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3160" s="3" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="3161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3161" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3161" s="3" t="s">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="3162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3162" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3162" s="3" t="s">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="3163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3163" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3163" s="3" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="3164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3164" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3164" s="3" t="s">
+        <v>4623</v>
+      </c>
+    </row>
+    <row r="3165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3165" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3165" s="3" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="3166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3166" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3166" s="3" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="3167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3167" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3167" s="3" t="s">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="3168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3168" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3168" s="3" t="s">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="3169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3169" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3169" s="3" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="3170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3170" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3170" s="3" t="s">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="3171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3171" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3171" s="3" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="3172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3172" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3172" s="3" t="s">
+        <v>4631</v>
+      </c>
+    </row>
+    <row r="3173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3173" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3173" s="3" t="s">
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="3174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3174" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3174" s="3" t="s">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="3175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3175" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3175" s="3" t="s">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="3176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3176" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3176" s="3" t="s">
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="3177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3177" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3177" s="3" t="s">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="3178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3178" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3178" s="3" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="3179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3179" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3179" s="3" t="s">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="3180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3180" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3180" s="3" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="3181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3181" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3181" s="3" t="s">
+        <v>4641</v>
+      </c>
+    </row>
+    <row r="3182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3182" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3182" s="3" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="3183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3183" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3183" s="3" t="s">
+        <v>4644</v>
+      </c>
+    </row>
+    <row r="3184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3184" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3184" s="3" t="s">
+        <v>4645</v>
+      </c>
+    </row>
+    <row r="3185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3185" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3185" s="3" t="s">
+        <v>4647</v>
+      </c>
+    </row>
+    <row r="3186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3186" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3186" s="3" t="s">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="3187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3187" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3187" s="3" t="s">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="3188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3188" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3188" s="3" t="s">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="3189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3189" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3189" s="3" t="s">
+        <v>4651</v>
+      </c>
+    </row>
+    <row r="3190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3190" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3190" s="3" t="s">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="3191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3191" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3191" s="3" t="s">
+        <v>4653</v>
+      </c>
+    </row>
+    <row r="3192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3192" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3192" s="3" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="3193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3193" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3193" s="3" t="s">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="3194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3194" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3194" s="3" t="s">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="3195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3195" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3195" s="3" t="s">
+        <v>4657</v>
+      </c>
+    </row>
+    <row r="3196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3196" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3196" s="3" t="s">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="3197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3197" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3197" s="3" t="s">
+        <v>4659</v>
+      </c>
+    </row>
+    <row r="3198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3198" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3198" s="3" t="s">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="3199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3199" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3199" s="3" t="s">
+        <v>4661</v>
+      </c>
+    </row>
+    <row r="3200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3200" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3200" s="3" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="3201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3201" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3201" s="3" t="s">
+        <v>4665</v>
+      </c>
+    </row>
+    <row r="3202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3202" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3202" s="3" t="s">
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="3203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3203" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3203" s="3" t="s">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="3204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3204" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3204" s="3" t="s">
+        <v>4669</v>
+      </c>
+    </row>
+    <row r="3205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3205" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3205" s="3" t="s">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="3206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3206" s="3">
+        <v>4800</v>
+      </c>
+      <c r="C3206" s="3" t="s">
+        <v>4671</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F665BF37-0508-49DF-B0F6-3594CEC66E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97C5F95-67F1-4428-B447-E6405B3800FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4686" uniqueCount="4672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="4770">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -18710,6 +18710,397 @@
   </si>
   <si>
     <t>empirical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mediate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bloodstream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reelection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dwelling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foremost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>midair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crocodile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sister</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intefration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usefulness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>olfactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cranial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prerequisite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occupational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eclipse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliberation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flagpole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypersensitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unavoidable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lucky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upcoming</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>February</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friendship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pathogen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>memorable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auditory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tertiary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submarine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>questionable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lnuit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alga</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respectively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feldspar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drought-resistant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fatal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romanticism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needlework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>short-term</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingenious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>framework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meantime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caribou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attentive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifelong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>August</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motionless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>renewable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amatrur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tangle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornamental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>connective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meaningless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capitalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>estate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cenotes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mesquite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whistle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seeding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constrict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electromagnetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Virginian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dryness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rodeo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endurance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mussel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cyan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jungle</t>
+  </si>
+  <si>
+    <t>angry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scarcely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herald</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mismatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stitch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspicious</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19182,7 +19573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3206"/>
+  <dimension ref="A1:N3291"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -48279,6 +48670,731 @@
         <v>4671</v>
       </c>
     </row>
+    <row r="3207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3207" s="4">
+        <v>4900</v>
+      </c>
+      <c r="B3207" s="3" t="s">
+        <v>4680</v>
+      </c>
+      <c r="C3207" s="3" t="s">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="3208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3208" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3208" s="3" t="s">
+        <v>4696</v>
+      </c>
+      <c r="C3208" s="3" t="s">
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="3209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3209" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3209" s="3" t="s">
+        <v>4698</v>
+      </c>
+      <c r="C3209" s="3" t="s">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="3210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3210" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3210" s="3" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C3210" s="3" t="s">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="3211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3211" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3211" s="3" t="s">
+        <v>4702</v>
+      </c>
+      <c r="C3211" s="3" t="s">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="3212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3212" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3212" s="3" t="s">
+        <v>4709</v>
+      </c>
+      <c r="C3212" s="3" t="s">
+        <v>4677</v>
+      </c>
+    </row>
+    <row r="3213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3213" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3213" s="3" t="s">
+        <v>4722</v>
+      </c>
+      <c r="C3213" s="3" t="s">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="3214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3214" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3214" s="3" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C3214" s="3" t="s">
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="3215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3215" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3215" s="3" t="s">
+        <v>4725</v>
+      </c>
+      <c r="C3215" s="3" t="s">
+        <v>4681</v>
+      </c>
+    </row>
+    <row r="3216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3216" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3216" s="3" t="s">
+        <v>4730</v>
+      </c>
+      <c r="C3216" s="3" t="s">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="3217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3217" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3217" s="3" t="s">
+        <v>4731</v>
+      </c>
+      <c r="C3217" s="3" t="s">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="3218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3218" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3218" s="3" t="s">
+        <v>4740</v>
+      </c>
+      <c r="C3218" s="3" t="s">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="3219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3219" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3219" s="3" t="s">
+        <v>4746</v>
+      </c>
+      <c r="C3219" s="3" t="s">
+        <v>4685</v>
+      </c>
+    </row>
+    <row r="3220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3220" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3220" s="3" t="s">
+        <v>4747</v>
+      </c>
+      <c r="C3220" s="3" t="s">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="3221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3221" s="3">
+        <v>4900</v>
+      </c>
+      <c r="B3221" s="3" t="s">
+        <v>4762</v>
+      </c>
+      <c r="C3221" s="3" t="s">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="3222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3222" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3222" s="3" t="s">
+        <v>4688</v>
+      </c>
+    </row>
+    <row r="3223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3223" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3223" s="3" t="s">
+        <v>4689</v>
+      </c>
+    </row>
+    <row r="3224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3224" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3224" s="3" t="s">
+        <v>4690</v>
+      </c>
+    </row>
+    <row r="3225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3225" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3225" s="3" t="s">
+        <v>4691</v>
+      </c>
+    </row>
+    <row r="3226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3226" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3226" s="3" t="s">
+        <v>4692</v>
+      </c>
+    </row>
+    <row r="3227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3227" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3227" s="3" t="s">
+        <v>4693</v>
+      </c>
+    </row>
+    <row r="3228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3228" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3228" s="3" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="3229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3229" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3229" s="3" t="s">
+        <v>4695</v>
+      </c>
+    </row>
+    <row r="3230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3230" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3230" s="3" t="s">
+        <v>4697</v>
+      </c>
+    </row>
+    <row r="3231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3231" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3231" s="3" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="3232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3232" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3232" s="3" t="s">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="3233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3233" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3233" s="3" t="s">
+        <v>4703</v>
+      </c>
+    </row>
+    <row r="3234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3234" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3234" s="3" t="s">
+        <v>4704</v>
+      </c>
+    </row>
+    <row r="3235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3235" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3235" s="3" t="s">
+        <v>4705</v>
+      </c>
+    </row>
+    <row r="3236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3236" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3236" s="3" t="s">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="3237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3237" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3237" s="3" t="s">
+        <v>4707</v>
+      </c>
+    </row>
+    <row r="3238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3238" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3238" s="3" t="s">
+        <v>4708</v>
+      </c>
+    </row>
+    <row r="3239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3239" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3239" s="3" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="3240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3240" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3240" s="3" t="s">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="3241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3241" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3241" s="3" t="s">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="3242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3242" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3242" s="3" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="3243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3243" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3243" s="3" t="s">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="3244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3244" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3244" s="3" t="s">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="3245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3245" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3245" s="3" t="s">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="3246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3246" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3246" s="3" t="s">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="3247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3247" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3247" s="3" t="s">
+        <v>4718</v>
+      </c>
+    </row>
+    <row r="3248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3248" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3248" s="3" t="s">
+        <v>4719</v>
+      </c>
+    </row>
+    <row r="3249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3249" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3249" s="3" t="s">
+        <v>4720</v>
+      </c>
+    </row>
+    <row r="3250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3250" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3250" s="3" t="s">
+        <v>4721</v>
+      </c>
+    </row>
+    <row r="3251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3251" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3251" s="3" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="3252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3252" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3252" s="3" t="s">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="3253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3253" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3253" s="3" t="s">
+        <v>4727</v>
+      </c>
+    </row>
+    <row r="3254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3254" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3254" s="3" t="s">
+        <v>4728</v>
+      </c>
+    </row>
+    <row r="3255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3255" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3255" s="3" t="s">
+        <v>4729</v>
+      </c>
+    </row>
+    <row r="3256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3256" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3256" s="3" t="s">
+        <v>4732</v>
+      </c>
+    </row>
+    <row r="3257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3257" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3257" s="3" t="s">
+        <v>4733</v>
+      </c>
+    </row>
+    <row r="3258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3258" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3258" s="3" t="s">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="3259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3259" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3259" s="3" t="s">
+        <v>4735</v>
+      </c>
+    </row>
+    <row r="3260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3260" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3260" s="3" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="3261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3261" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3261" s="3" t="s">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="3262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3262" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3262" s="3" t="s">
+        <v>4737</v>
+      </c>
+    </row>
+    <row r="3263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3263" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3263" s="3" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="3264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3264" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3264" s="3" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="3265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3265" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3265" s="3" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="3266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3266" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3266" s="4" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="3267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3267" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3267" s="3" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="3268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3268" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3268" s="3" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="3269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3269" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3269" s="3" t="s">
+        <v>4745</v>
+      </c>
+    </row>
+    <row r="3270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3270" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3270" s="3" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="3271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3271" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3271" s="3" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="3272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3272" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3272" s="3" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="3273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3273" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3273" s="3" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="3274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3274" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3274" s="3" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="3275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3275" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3275" s="3" t="s">
+        <v>4753</v>
+      </c>
+    </row>
+    <row r="3276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3276" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3276" s="3" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="3277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3277" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3277" s="3" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="3278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3278" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3278" s="3" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="3279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3279" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3279" s="3" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="3280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3280" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3280" s="3" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="3281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3281" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3281" s="3" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="3282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3282" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3282" s="3" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="3283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3283" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3283" s="3" t="s">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="3284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3284" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3284" s="3" t="s">
+        <v>4505</v>
+      </c>
+    </row>
+    <row r="3285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3285" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3285" s="3" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="3286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3286" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3286" s="3" t="s">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="3287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3287" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3287" s="3" t="s">
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="3288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3288" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3288" s="3" t="s">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="3289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3289" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3289" s="3" t="s">
+        <v>4767</v>
+      </c>
+    </row>
+    <row r="3290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3290" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3290" s="3" t="s">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="3291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3291" s="3">
+        <v>4900</v>
+      </c>
+      <c r="C3291" s="3" t="s">
+        <v>4769</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97C5F95-67F1-4428-B447-E6405B3800FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC4EEA7-698E-4DDE-8030-2EAFE5B7A7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="4770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4886" uniqueCount="4870">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -19101,6 +19101,406 @@
   </si>
   <si>
     <t>suspicious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monarch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chaos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prizefight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inactivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confident</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shipment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unprotected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lobe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plummet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firearm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>communal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linguist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cortex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>objectively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chilly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artifact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statesman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corporation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expertise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coincide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>originator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pacifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asymmetrical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lady</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantifiable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humanness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>companion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinniped</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>companionship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archaeocyte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incidental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intruder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conjunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intentionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impractical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhetoric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immaturity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>understandable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faculty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divorce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>daytime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overcrowd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marvelous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foolish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opportunistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naïve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merchandise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lapis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakthrough</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compositional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>youngster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ideologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interpersonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lazuli</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electronically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sewage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>municipal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refreeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydrologic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dietary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydropower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>granule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>further</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recreational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insecure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumvent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chunk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>staff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>achondrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19573,7 +19973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3291"/>
+  <dimension ref="A1:N3379"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -49395,6 +49795,746 @@
         <v>4769</v>
       </c>
     </row>
+    <row r="3292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3292" s="4">
+        <v>5000</v>
+      </c>
+      <c r="B3292" s="3" t="s">
+        <v>4779</v>
+      </c>
+      <c r="C3292" s="3" t="s">
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="3293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3293" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3293" s="3" t="s">
+        <v>4789</v>
+      </c>
+      <c r="C3293" s="3" t="s">
+        <v>4771</v>
+      </c>
+    </row>
+    <row r="3294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3294" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3294" s="3" t="s">
+        <v>4801</v>
+      </c>
+      <c r="C3294" s="3" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="3295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3295" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3295" s="3" t="s">
+        <v>4806</v>
+      </c>
+      <c r="C3295" s="3" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="3296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3296" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3296" s="3" t="s">
+        <v>4810</v>
+      </c>
+      <c r="C3296" s="3" t="s">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="3297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3297" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3297" s="3" t="s">
+        <v>4812</v>
+      </c>
+      <c r="C3297" s="3" t="s">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="3298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3298" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3298" s="3" t="s">
+        <v>4823</v>
+      </c>
+      <c r="C3298" s="3" t="s">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="3299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3299" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3299" s="3" t="s">
+        <v>4828</v>
+      </c>
+      <c r="C3299" s="3" t="s">
+        <v>4777</v>
+      </c>
+    </row>
+    <row r="3300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3300" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3300" s="3" t="s">
+        <v>4832</v>
+      </c>
+      <c r="C3300" s="3" t="s">
+        <v>4778</v>
+      </c>
+    </row>
+    <row r="3301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3301" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3301" s="3" t="s">
+        <v>4844</v>
+      </c>
+      <c r="C3301" s="3" t="s">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="3302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3302" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3302" s="3" t="s">
+        <v>4867</v>
+      </c>
+      <c r="C3302" s="3" t="s">
+        <v>4781</v>
+      </c>
+    </row>
+    <row r="3303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3303" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B3303" s="3" t="s">
+        <v>4869</v>
+      </c>
+      <c r="C3303" s="3" t="s">
+        <v>4782</v>
+      </c>
+    </row>
+    <row r="3304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3304" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3304" s="3" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="3305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3305" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3305" s="3" t="s">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="3306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3306" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3306" s="3" t="s">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="3307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3307" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3307" s="3" t="s">
+        <v>4786</v>
+      </c>
+    </row>
+    <row r="3308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3308" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3308" s="3" t="s">
+        <v>4787</v>
+      </c>
+    </row>
+    <row r="3309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3309" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3309" s="3" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="3310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3310" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3310" s="3" t="s">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="3311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3311" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3311" s="3" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="3312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3312" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3312" s="3" t="s">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="3313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3313" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3313" s="3" t="s">
+        <v>4793</v>
+      </c>
+    </row>
+    <row r="3314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3314" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3314" s="3" t="s">
+        <v>4794</v>
+      </c>
+    </row>
+    <row r="3315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3315" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3315" s="3" t="s">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="3316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3316" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3316" s="3" t="s">
+        <v>4796</v>
+      </c>
+    </row>
+    <row r="3317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3317" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3317" s="3" t="s">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="3318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3318" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3318" s="3" t="s">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="3319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3319" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3319" s="3" t="s">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="3320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3320" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3320" s="3" t="s">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="3321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3321" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3321" s="3" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="3322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3322" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3322" s="3" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="3323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3323" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3323" s="3" t="s">
+        <v>4804</v>
+      </c>
+    </row>
+    <row r="3324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3324" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3324" s="3" t="s">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="3325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3325" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3325" s="3" t="s">
+        <v>4807</v>
+      </c>
+    </row>
+    <row r="3326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3326" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3326" s="3" t="s">
+        <v>4808</v>
+      </c>
+    </row>
+    <row r="3327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3327" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3327" s="3" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="3328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3328" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3328" s="3" t="s">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="3329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3329" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3329" s="3" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="3330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3330" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3330" s="3" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="3331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3331" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3331" s="3" t="s">
+        <v>4815</v>
+      </c>
+    </row>
+    <row r="3332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3332" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3332" s="3" t="s">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="3333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3333" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3333" s="3" t="s">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="3334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3334" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3334" s="3" t="s">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="3335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3335" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3335" s="3" t="s">
+        <v>4819</v>
+      </c>
+    </row>
+    <row r="3336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3336" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3336" s="3" t="s">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="3337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3337" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3337" s="3" t="s">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3338" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3338" s="3" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="3339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3339" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3339" s="3" t="s">
+        <v>4824</v>
+      </c>
+    </row>
+    <row r="3340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3340" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3340" s="3" t="s">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="3341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3341" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3341" s="3" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="3342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3342" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3342" s="3" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="3343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3343" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3343" s="3" t="s">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="3344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3344" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3344" s="3" t="s">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="3345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3345" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3345" s="3" t="s">
+        <v>4831</v>
+      </c>
+    </row>
+    <row r="3346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3346" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3346" s="3" t="s">
+        <v>4833</v>
+      </c>
+    </row>
+    <row r="3347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3347" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3347" s="3" t="s">
+        <v>4834</v>
+      </c>
+    </row>
+    <row r="3348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3348" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3348" s="3" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="3349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3349" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3349" s="3" t="s">
+        <v>4836</v>
+      </c>
+    </row>
+    <row r="3350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3350" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3350" s="3" t="s">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="3351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3351" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3351" s="3" t="s">
+        <v>4838</v>
+      </c>
+    </row>
+    <row r="3352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3352" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3352" s="3" t="s">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="3353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3353" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3353" s="3" t="s">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="3354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3354" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3354" s="3" t="s">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="3355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3355" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3355" s="3" t="s">
+        <v>4842</v>
+      </c>
+    </row>
+    <row r="3356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3356" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3356" s="3" t="s">
+        <v>4843</v>
+      </c>
+    </row>
+    <row r="3357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3357" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3357" s="3" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="3358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3358" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3358" s="3" t="s">
+        <v>4846</v>
+      </c>
+    </row>
+    <row r="3359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3359" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3359" s="3" t="s">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="3360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3360" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3360" s="3" t="s">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="3361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3361" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3361" s="3" t="s">
+        <v>4849</v>
+      </c>
+    </row>
+    <row r="3362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3362" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3362" s="3" t="s">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="3363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3363" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3363" s="3" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="3364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3364" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3364" s="3" t="s">
+        <v>4852</v>
+      </c>
+    </row>
+    <row r="3365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3365" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3365" s="3" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="3366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3366" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3366" s="3" t="s">
+        <v>4854</v>
+      </c>
+    </row>
+    <row r="3367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3367" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3367" s="3" t="s">
+        <v>4855</v>
+      </c>
+    </row>
+    <row r="3368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3368" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3368" s="3" t="s">
+        <v>4856</v>
+      </c>
+    </row>
+    <row r="3369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3369" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3369" s="3" t="s">
+        <v>4857</v>
+      </c>
+    </row>
+    <row r="3370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3370" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3370" s="3" t="s">
+        <v>4858</v>
+      </c>
+    </row>
+    <row r="3371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3371" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3371" s="3" t="s">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="3372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3372" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3372" s="3" t="s">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="3373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3373" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3373" s="3" t="s">
+        <v>4861</v>
+      </c>
+    </row>
+    <row r="3374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3374" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3374" s="3" t="s">
+        <v>4862</v>
+      </c>
+    </row>
+    <row r="3375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3375" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3375" s="3" t="s">
+        <v>4863</v>
+      </c>
+    </row>
+    <row r="3376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3376" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3376" s="3" t="s">
+        <v>4864</v>
+      </c>
+    </row>
+    <row r="3377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3377" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3377" s="3" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="3378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3378" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3378" s="3" t="s">
+        <v>4866</v>
+      </c>
+    </row>
+    <row r="3379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3379" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3379" s="3" t="s">
+        <v>4868</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC4EEA7-698E-4DDE-8030-2EAFE5B7A7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656FBA06-426C-4EB9-B910-30862E8777E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4886" uniqueCount="4870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="4969">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -19501,6 +19501,402 @@
   </si>
   <si>
     <t>asset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flutter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pitch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multiplicity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laissez-faire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figuratively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undermine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greener</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entrepreneurial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foliage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-assertion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supreme</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maximize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bushman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marshy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anxiety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retirement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sympathetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manifestation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excitement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>porcupine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amaze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keyboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>experimentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>percussion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plausible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crisscross</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radiator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>myriad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>three-toed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clavichord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trilobite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>converter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>layout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>claw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sierra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legitimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horse-drawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>octopus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpredictability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minimalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storefront</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>makeshift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cactus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solemn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>labor-saving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>improvise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ascend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>showman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appointment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lawyer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alaskan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctrine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immeasurably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ambition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perpetuate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterlife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humanitarian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoemaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prairies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handicraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airstream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whoever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsafe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashbulb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bovine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoughtful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icicle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unbroken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>funnel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastidious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overshadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inhospitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artistically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quincy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afternoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rumen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19973,7 +20369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3379"/>
+  <dimension ref="A1:N3461"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -50535,6 +50931,713 @@
         <v>4868</v>
       </c>
     </row>
+    <row r="3380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3380" s="4">
+        <v>5100</v>
+      </c>
+      <c r="B3380" s="3" t="s">
+        <v>4876</v>
+      </c>
+      <c r="C3380" s="3" t="s">
+        <v>4870</v>
+      </c>
+    </row>
+    <row r="3381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3381" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3381" s="3" t="s">
+        <v>4877</v>
+      </c>
+      <c r="C3381" s="3" t="s">
+        <v>4871</v>
+      </c>
+    </row>
+    <row r="3382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3382" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3382" s="3" t="s">
+        <v>4884</v>
+      </c>
+      <c r="C3382" s="3" t="s">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="3383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3383" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3383" s="3" t="s">
+        <v>4887</v>
+      </c>
+      <c r="C3383" s="3" t="s">
+        <v>4873</v>
+      </c>
+    </row>
+    <row r="3384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3384" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3384" s="3" t="s">
+        <v>4889</v>
+      </c>
+      <c r="C3384" s="3" t="s">
+        <v>4874</v>
+      </c>
+    </row>
+    <row r="3385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3385" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3385" s="3" t="s">
+        <v>4890</v>
+      </c>
+      <c r="C3385" s="3" t="s">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="3386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3386" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3386" s="3" t="s">
+        <v>4893</v>
+      </c>
+      <c r="C3386" s="3" t="s">
+        <v>4878</v>
+      </c>
+    </row>
+    <row r="3387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3387" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3387" s="3" t="s">
+        <v>4897</v>
+      </c>
+      <c r="C3387" s="3" t="s">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="3388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3388" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3388" s="3" t="s">
+        <v>4911</v>
+      </c>
+      <c r="C3388" s="3" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="3389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3389" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3389" s="3" t="s">
+        <v>4916</v>
+      </c>
+      <c r="C3389" s="3" t="s">
+        <v>4881</v>
+      </c>
+    </row>
+    <row r="3390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3390" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3390" s="3" t="s">
+        <v>4922</v>
+      </c>
+      <c r="C3390" s="3" t="s">
+        <v>4882</v>
+      </c>
+    </row>
+    <row r="3391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3391" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3391" s="3" t="s">
+        <v>4935</v>
+      </c>
+      <c r="C3391" s="3" t="s">
+        <v>4883</v>
+      </c>
+    </row>
+    <row r="3392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3392" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3392" s="3" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C3392" s="3" t="s">
+        <v>4885</v>
+      </c>
+    </row>
+    <row r="3393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3393" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3393" s="3" t="s">
+        <v>4951</v>
+      </c>
+      <c r="C3393" s="3" t="s">
+        <v>4886</v>
+      </c>
+    </row>
+    <row r="3394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3394" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3394" s="3" t="s">
+        <v>4952</v>
+      </c>
+      <c r="C3394" s="3" t="s">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="3395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3395" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3395" s="3" t="s">
+        <v>4955</v>
+      </c>
+      <c r="C3395" s="3" t="s">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="3396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3396" s="3">
+        <v>5100</v>
+      </c>
+      <c r="B3396" s="3" t="s">
+        <v>4967</v>
+      </c>
+      <c r="C3396" s="3" t="s">
+        <v>4892</v>
+      </c>
+    </row>
+    <row r="3397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3397" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3397" s="3" t="s">
+        <v>4894</v>
+      </c>
+    </row>
+    <row r="3398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3398" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3398" s="3" t="s">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="3399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3399" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3399" s="3" t="s">
+        <v>4896</v>
+      </c>
+    </row>
+    <row r="3400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3400" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3400" s="3" t="s">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="3401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3401" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3401" s="3" t="s">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="3402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3402" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3402" s="3" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="3403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3403" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3403" s="3" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="3404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3404" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3404" s="3" t="s">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="3405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3405" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3405" s="3" t="s">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="3406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3406" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3406" s="3" t="s">
+        <v>4904</v>
+      </c>
+    </row>
+    <row r="3407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3407" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3407" s="3" t="s">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="3408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3408" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3408" s="3" t="s">
+        <v>4906</v>
+      </c>
+    </row>
+    <row r="3409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3409" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3409" s="3" t="s">
+        <v>4907</v>
+      </c>
+    </row>
+    <row r="3410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3410" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3410" s="3" t="s">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="3411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3411" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3411" s="3" t="s">
+        <v>4909</v>
+      </c>
+    </row>
+    <row r="3412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3412" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3412" s="3" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="3413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3413" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3413" s="3" t="s">
+        <v>4912</v>
+      </c>
+    </row>
+    <row r="3414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3414" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3414" s="3" t="s">
+        <v>4913</v>
+      </c>
+    </row>
+    <row r="3415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3415" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3415" s="3" t="s">
+        <v>4914</v>
+      </c>
+    </row>
+    <row r="3416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3416" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3416" s="3" t="s">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="3417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3417" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3417" s="3" t="s">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="3418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3418" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3418" s="3" t="s">
+        <v>4918</v>
+      </c>
+    </row>
+    <row r="3419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3419" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3419" s="3" t="s">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="3420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3420" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3420" s="3" t="s">
+        <v>4920</v>
+      </c>
+    </row>
+    <row r="3421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3421" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3421" s="3" t="s">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="3422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3422" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3422" s="3" t="s">
+        <v>4923</v>
+      </c>
+    </row>
+    <row r="3423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3423" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3423" s="3" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="3424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3424" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3424" s="3" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="3425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3425" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3425" s="3" t="s">
+        <v>4926</v>
+      </c>
+    </row>
+    <row r="3426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3426" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3426" s="3" t="s">
+        <v>4927</v>
+      </c>
+    </row>
+    <row r="3427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3427" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3427" s="3" t="s">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="3428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3428" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3428" s="3" t="s">
+        <v>4929</v>
+      </c>
+    </row>
+    <row r="3429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3429" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3429" s="3" t="s">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="3430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3430" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3430" s="3" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="3431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3431" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3431" s="3" t="s">
+        <v>4932</v>
+      </c>
+    </row>
+    <row r="3432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3432" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3432" s="3" t="s">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="3433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3433" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3433" s="3" t="s">
+        <v>4934</v>
+      </c>
+    </row>
+    <row r="3434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3434" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3434" s="3" t="s">
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="3435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3435" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3435" s="3" t="s">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="3436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3436" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3436" s="3" t="s">
+        <v>4938</v>
+      </c>
+    </row>
+    <row r="3437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3437" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3437" s="3" t="s">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="3438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3438" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3438" s="3" t="s">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="3439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3439" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3439" s="3" t="s">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="3440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3440" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3440" s="3" t="s">
+        <v>4943</v>
+      </c>
+    </row>
+    <row r="3441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3441" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3441" s="3" t="s">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="3442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3442" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3442" s="3" t="s">
+        <v>4945</v>
+      </c>
+    </row>
+    <row r="3443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3443" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3443" s="3" t="s">
+        <v>4946</v>
+      </c>
+    </row>
+    <row r="3444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3444" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3444" s="3" t="s">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="3445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3445" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3445" s="3" t="s">
+        <v>4948</v>
+      </c>
+    </row>
+    <row r="3446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3446" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3446" s="3" t="s">
+        <v>4949</v>
+      </c>
+    </row>
+    <row r="3447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3447" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3447" s="3" t="s">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="3448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3448" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3448" s="3" t="s">
+        <v>4953</v>
+      </c>
+    </row>
+    <row r="3449" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3449" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3449" s="3" t="s">
+        <v>4954</v>
+      </c>
+    </row>
+    <row r="3450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3450" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3450" s="3" t="s">
+        <v>4956</v>
+      </c>
+    </row>
+    <row r="3451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3451" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3451" s="3" t="s">
+        <v>4957</v>
+      </c>
+    </row>
+    <row r="3452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3452" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3452" s="3" t="s">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="3453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3453" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3453" s="3" t="s">
+        <v>4959</v>
+      </c>
+    </row>
+    <row r="3454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3454" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3454" s="3" t="s">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="3455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3455" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3455" s="3" t="s">
+        <v>4961</v>
+      </c>
+    </row>
+    <row r="3456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3456" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3456" s="3" t="s">
+        <v>4962</v>
+      </c>
+    </row>
+    <row r="3457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3457" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3457" s="3" t="s">
+        <v>4963</v>
+      </c>
+    </row>
+    <row r="3458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3458" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3458" s="3" t="s">
+        <v>4964</v>
+      </c>
+    </row>
+    <row r="3459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3459" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3459" s="3" t="s">
+        <v>4965</v>
+      </c>
+    </row>
+    <row r="3460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3460" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3460" s="3" t="s">
+        <v>4966</v>
+      </c>
+    </row>
+    <row r="3461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3461" s="3">
+        <v>5100</v>
+      </c>
+      <c r="C3461" s="3" t="s">
+        <v>4968</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656FBA06-426C-4EB9-B910-30862E8777E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B3086-BFC0-44F9-B3DA-F8645B4D6E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="4969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5085" uniqueCount="5069">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -19897,6 +19897,406 @@
   </si>
   <si>
     <t>rumen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aristocracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadleaf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pierce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bluish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autobiographical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parisian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>halfway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fabricate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embrace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postwar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>license</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whichever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsession</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scurry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtropical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comfort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vancouver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>megawatt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cellar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arboreal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multicellular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spontaneously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repertoire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swimmer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eagerly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protectionist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>husbandry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vascular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>built-up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glassy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trunk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unavailable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sulfuric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>latest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redefine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low-lying</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greenhouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instinctively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>universally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matrix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graduation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huddle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bloom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epitome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subspecies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scrap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>propel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlimited</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respondent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portrayal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>declare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curtain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hexagon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undisturbed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ascent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talbot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>causal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metalworker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sinuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>floral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grasp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incongruous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overlook</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20369,7 +20769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3461"/>
+  <dimension ref="A1:N3548"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -51638,6 +52038,741 @@
         <v>4968</v>
       </c>
     </row>
+    <row r="3462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3462" s="4">
+        <v>5200</v>
+      </c>
+      <c r="B3462" s="3" t="s">
+        <v>4970</v>
+      </c>
+      <c r="C3462" s="3" t="s">
+        <v>4969</v>
+      </c>
+    </row>
+    <row r="3463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3463" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3463" s="3" t="s">
+        <v>4981</v>
+      </c>
+      <c r="C3463" s="3" t="s">
+        <v>4971</v>
+      </c>
+    </row>
+    <row r="3464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3464" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3464" s="3" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C3464" s="3" t="s">
+        <v>4972</v>
+      </c>
+    </row>
+    <row r="3465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3465" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3465" s="3" t="s">
+        <v>4986</v>
+      </c>
+      <c r="C3465" s="3" t="s">
+        <v>4973</v>
+      </c>
+    </row>
+    <row r="3466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3466" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3466" s="3" t="s">
+        <v>4994</v>
+      </c>
+      <c r="C3466" s="3" t="s">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="3467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3467" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3467" s="3" t="s">
+        <v>4999</v>
+      </c>
+      <c r="C3467" s="3" t="s">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="3468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3468" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3468" s="3" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C3468" s="3" t="s">
+        <v>4976</v>
+      </c>
+    </row>
+    <row r="3469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3469" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3469" s="3" t="s">
+        <v>5021</v>
+      </c>
+      <c r="C3469" s="3" t="s">
+        <v>4977</v>
+      </c>
+    </row>
+    <row r="3470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3470" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3470" s="3" t="s">
+        <v>5024</v>
+      </c>
+      <c r="C3470" s="3" t="s">
+        <v>4978</v>
+      </c>
+    </row>
+    <row r="3471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3471" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3471" s="3" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C3471" s="3" t="s">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="3472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3472" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3472" s="3" t="s">
+        <v>5031</v>
+      </c>
+      <c r="C3472" s="3" t="s">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="3473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3473" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3473" s="3" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C3473" s="3" t="s">
+        <v>4982</v>
+      </c>
+    </row>
+    <row r="3474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3474" s="3">
+        <v>5200</v>
+      </c>
+      <c r="B3474" s="3" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C3474" s="3" t="s">
+        <v>4983</v>
+      </c>
+    </row>
+    <row r="3475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3475" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3475" s="3" t="s">
+        <v>4984</v>
+      </c>
+    </row>
+    <row r="3476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3476" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3476" s="3" t="s">
+        <v>4987</v>
+      </c>
+    </row>
+    <row r="3477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3477" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3477" s="3" t="s">
+        <v>4988</v>
+      </c>
+    </row>
+    <row r="3478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3478" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3478" s="3" t="s">
+        <v>4989</v>
+      </c>
+    </row>
+    <row r="3479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3479" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3479" s="3" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="3480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3480" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3480" s="3" t="s">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="3481" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3481" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3481" s="3" t="s">
+        <v>4992</v>
+      </c>
+    </row>
+    <row r="3482" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3482" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3482" s="3" t="s">
+        <v>4993</v>
+      </c>
+    </row>
+    <row r="3483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3483" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3483" s="3" t="s">
+        <v>4995</v>
+      </c>
+    </row>
+    <row r="3484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3484" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3484" s="3" t="s">
+        <v>4996</v>
+      </c>
+    </row>
+    <row r="3485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3485" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3485" s="3" t="s">
+        <v>4997</v>
+      </c>
+    </row>
+    <row r="3486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3486" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3486" s="3" t="s">
+        <v>4998</v>
+      </c>
+    </row>
+    <row r="3487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3487" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3487" s="3" t="s">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3488" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3488" s="3" t="s">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="3489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3489" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3489" s="3" t="s">
+        <v>5002</v>
+      </c>
+    </row>
+    <row r="3490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3490" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3490" s="3" t="s">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="3491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3491" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3491" s="3" t="s">
+        <v>5004</v>
+      </c>
+    </row>
+    <row r="3492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3492" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3492" s="3" t="s">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="3493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3493" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3493" s="3" t="s">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="3494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3494" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3494" s="3" t="s">
+        <v>5007</v>
+      </c>
+    </row>
+    <row r="3495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3495" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3495" s="3" t="s">
+        <v>5008</v>
+      </c>
+    </row>
+    <row r="3496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3496" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3496" s="3" t="s">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="3497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3497" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3497" s="3" t="s">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="3498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3498" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3498" s="3" t="s">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="3499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3499" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3499" s="3" t="s">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="3500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3500" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3500" s="3" t="s">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="3501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3501" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3501" s="3" t="s">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="3502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3502" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3502" s="3" t="s">
+        <v>5016</v>
+      </c>
+    </row>
+    <row r="3503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3503" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3503" s="3" t="s">
+        <v>5017</v>
+      </c>
+    </row>
+    <row r="3504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3504" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3504" s="3" t="s">
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="3505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3505" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3505" s="3" t="s">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="3506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3506" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3506" s="3" t="s">
+        <v>5020</v>
+      </c>
+    </row>
+    <row r="3507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3507" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3507" s="3" t="s">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="3508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3508" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3508" s="3" t="s">
+        <v>5023</v>
+      </c>
+    </row>
+    <row r="3509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3509" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3509" s="3" t="s">
+        <v>5026</v>
+      </c>
+    </row>
+    <row r="3510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3510" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3510" s="3" t="s">
+        <v>5027</v>
+      </c>
+    </row>
+    <row r="3511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3511" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3511" s="3" t="s">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="3512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3512" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3512" s="3" t="s">
+        <v>5029</v>
+      </c>
+    </row>
+    <row r="3513" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3513" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3513" s="3" t="s">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="3514" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3514" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3514" s="3" t="s">
+        <v>5032</v>
+      </c>
+    </row>
+    <row r="3515" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3515" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3515" s="3" t="s">
+        <v>5033</v>
+      </c>
+    </row>
+    <row r="3516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3516" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3516" s="3" t="s">
+        <v>5035</v>
+      </c>
+    </row>
+    <row r="3517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3517" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3517" s="3" t="s">
+        <v>5036</v>
+      </c>
+    </row>
+    <row r="3518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3518" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3518" s="3" t="s">
+        <v>5037</v>
+      </c>
+    </row>
+    <row r="3519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3519" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3519" s="3" t="s">
+        <v>5038</v>
+      </c>
+    </row>
+    <row r="3520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3520" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3520" s="3" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="3521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3521" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3521" s="3" t="s">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="3522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3522" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3522" s="3" t="s">
+        <v>5042</v>
+      </c>
+    </row>
+    <row r="3523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3523" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3523" s="3" t="s">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="3524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3524" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3524" s="3" t="s">
+        <v>5044</v>
+      </c>
+    </row>
+    <row r="3525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3525" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3525" s="3" t="s">
+        <v>5045</v>
+      </c>
+    </row>
+    <row r="3526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3526" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3526" s="3" t="s">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="3527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3527" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3527" s="3" t="s">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="3528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3528" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3528" s="3" t="s">
+        <v>5048</v>
+      </c>
+    </row>
+    <row r="3529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3529" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3529" s="3" t="s">
+        <v>5049</v>
+      </c>
+    </row>
+    <row r="3530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3530" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3530" s="3" t="s">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="3531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3531" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3531" s="3" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="3532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3532" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3532" s="3" t="s">
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="3533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3533" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3533" s="3" t="s">
+        <v>5053</v>
+      </c>
+    </row>
+    <row r="3534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3534" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3534" s="3" t="s">
+        <v>5054</v>
+      </c>
+    </row>
+    <row r="3535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3535" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3535" s="3" t="s">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="3536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3536" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3536" s="3" t="s">
+        <v>5056</v>
+      </c>
+    </row>
+    <row r="3537" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3537" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3537" s="4" t="s">
+        <v>5057</v>
+      </c>
+    </row>
+    <row r="3538" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3538" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3538" s="3" t="s">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="3539" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3539" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3539" s="3" t="s">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="3540" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3540" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3540" s="3" t="s">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="3541" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3541" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3541" s="3" t="s">
+        <v>5061</v>
+      </c>
+    </row>
+    <row r="3542" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3542" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3542" s="3" t="s">
+        <v>5062</v>
+      </c>
+    </row>
+    <row r="3543" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3543" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3543" s="3" t="s">
+        <v>5063</v>
+      </c>
+    </row>
+    <row r="3544" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3544" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3544" s="3" t="s">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="3545" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3545" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3545" s="3" t="s">
+        <v>5065</v>
+      </c>
+    </row>
+    <row r="3546" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3546" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3546" s="3" t="s">
+        <v>5066</v>
+      </c>
+    </row>
+    <row r="3547" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3547" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3547" s="3" t="s">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="3548" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3548" s="3">
+        <v>5200</v>
+      </c>
+      <c r="C3548" s="3" t="s">
+        <v>5068</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B3086-BFC0-44F9-B3DA-F8645B4D6E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EA8988-BB17-4A8D-885A-2F876A310B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5085" uniqueCount="5069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5185" uniqueCount="5169">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -20297,6 +20297,406 @@
   </si>
   <si>
     <t>overlook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herbaceous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primordial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oversee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phosphorus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unearned</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infrequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acclaim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>translation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yarn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plasma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>London</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>originality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ford</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mortise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microbial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intervene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ironwork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unearth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microbiologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>situate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mallet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alcohol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guncotton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>approval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fathom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accidental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disastrous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>execute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supersonic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examplify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sixth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pantomime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alligator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>continuum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transparent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conscious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spherical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fairy-tale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Japan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microwave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adversely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indirectly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domesticate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>philosophical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deceive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aesthetically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthropology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>functionalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>continuation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydrodynamic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoreline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disproportionate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tanker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lament</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>systematically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curiosity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ancestral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eligible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absolutely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>best-known</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>senator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marvel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afraid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>estuary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seismic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdrawal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ember</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>launch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sorghum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paleoecologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fan-shaped</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regulatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isotopic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>captain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ultimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>omit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>applicable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snowstorm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>macdonald</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>locomotion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20769,7 +21169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3548"/>
+  <dimension ref="A1:N3631"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -52773,6 +53173,721 @@
         <v>5068</v>
       </c>
     </row>
+    <row r="3549" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3549" s="4">
+        <v>5300</v>
+      </c>
+      <c r="B3549" s="3" t="s">
+        <v>5084</v>
+      </c>
+      <c r="C3549" s="3" t="s">
+        <v>5069</v>
+      </c>
+    </row>
+    <row r="3550" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3550" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3550" s="3" t="s">
+        <v>5087</v>
+      </c>
+      <c r="C3550" s="3" t="s">
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="3551" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3551" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3551" s="3" t="s">
+        <v>5091</v>
+      </c>
+      <c r="C3551" s="3" t="s">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="3552" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3552" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3552" s="3" t="s">
+        <v>5092</v>
+      </c>
+      <c r="C3552" s="3" t="s">
+        <v>5072</v>
+      </c>
+    </row>
+    <row r="3553" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3553" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3553" s="3" t="s">
+        <v>5100</v>
+      </c>
+      <c r="C3553" s="3" t="s">
+        <v>5073</v>
+      </c>
+    </row>
+    <row r="3554" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3554" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3554" s="3" t="s">
+        <v>5102</v>
+      </c>
+      <c r="C3554" s="3" t="s">
+        <v>5074</v>
+      </c>
+    </row>
+    <row r="3555" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3555" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3555" s="3" t="s">
+        <v>5106</v>
+      </c>
+      <c r="C3555" s="3" t="s">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="3556" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3556" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3556" s="3" t="s">
+        <v>5109</v>
+      </c>
+      <c r="C3556" s="3" t="s">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="3557" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3557" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3557" s="3" t="s">
+        <v>5110</v>
+      </c>
+      <c r="C3557" s="3" t="s">
+        <v>5077</v>
+      </c>
+    </row>
+    <row r="3558" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3558" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3558" s="3" t="s">
+        <v>5115</v>
+      </c>
+      <c r="C3558" s="3" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="3559" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3559" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3559" s="3" t="s">
+        <v>5119</v>
+      </c>
+      <c r="C3559" s="3" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="3560" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3560" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3560" s="3" t="s">
+        <v>5129</v>
+      </c>
+      <c r="C3560" s="3" t="s">
+        <v>5080</v>
+      </c>
+    </row>
+    <row r="3561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3561" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3561" s="3" t="s">
+        <v>5146</v>
+      </c>
+      <c r="C3561" s="3" t="s">
+        <v>5081</v>
+      </c>
+    </row>
+    <row r="3562" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3562" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3562" s="3" t="s">
+        <v>5147</v>
+      </c>
+      <c r="C3562" s="3" t="s">
+        <v>5082</v>
+      </c>
+    </row>
+    <row r="3563" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3563" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3563" s="3" t="s">
+        <v>5148</v>
+      </c>
+      <c r="C3563" s="3" t="s">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="3564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3564" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3564" s="3" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C3564" s="3" t="s">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="3565" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3565" s="3">
+        <v>5300</v>
+      </c>
+      <c r="B3565" s="3" t="s">
+        <v>5163</v>
+      </c>
+      <c r="C3565" s="3" t="s">
+        <v>5086</v>
+      </c>
+    </row>
+    <row r="3566" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3566" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3566" s="3" t="s">
+        <v>5088</v>
+      </c>
+    </row>
+    <row r="3567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3567" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3567" s="3" t="s">
+        <v>5089</v>
+      </c>
+    </row>
+    <row r="3568" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3568" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3568" s="3" t="s">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="3569" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3569" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3569" s="3" t="s">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="3570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3570" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3570" s="3" t="s">
+        <v>5094</v>
+      </c>
+    </row>
+    <row r="3571" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3571" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3571" s="3" t="s">
+        <v>5095</v>
+      </c>
+    </row>
+    <row r="3572" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3572" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3572" s="3" t="s">
+        <v>5096</v>
+      </c>
+    </row>
+    <row r="3573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3573" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3573" s="3" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="3574" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3574" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3574" s="3" t="s">
+        <v>5098</v>
+      </c>
+    </row>
+    <row r="3575" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3575" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3575" s="3" t="s">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="3576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3576" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3576" s="3" t="s">
+        <v>5101</v>
+      </c>
+    </row>
+    <row r="3577" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3577" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3577" s="3" t="s">
+        <v>5103</v>
+      </c>
+    </row>
+    <row r="3578" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3578" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3578" s="3" t="s">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="3579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3579" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3579" s="3" t="s">
+        <v>5105</v>
+      </c>
+    </row>
+    <row r="3580" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3580" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3580" s="3" t="s">
+        <v>5107</v>
+      </c>
+    </row>
+    <row r="3581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3581" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3581" s="3" t="s">
+        <v>5108</v>
+      </c>
+    </row>
+    <row r="3582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3582" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3582" s="3" t="s">
+        <v>5111</v>
+      </c>
+    </row>
+    <row r="3583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3583" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3583" s="3" t="s">
+        <v>5112</v>
+      </c>
+    </row>
+    <row r="3584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3584" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3584" s="3" t="s">
+        <v>5113</v>
+      </c>
+    </row>
+    <row r="3585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3585" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3585" s="3" t="s">
+        <v>5114</v>
+      </c>
+    </row>
+    <row r="3586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3586" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3586" s="3" t="s">
+        <v>5116</v>
+      </c>
+    </row>
+    <row r="3587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3587" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3587" s="3" t="s">
+        <v>5117</v>
+      </c>
+    </row>
+    <row r="3588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3588" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3588" s="3" t="s">
+        <v>5118</v>
+      </c>
+    </row>
+    <row r="3589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3589" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3589" s="3" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="3590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3590" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3590" s="3" t="s">
+        <v>5121</v>
+      </c>
+    </row>
+    <row r="3591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3591" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3591" s="3" t="s">
+        <v>5122</v>
+      </c>
+    </row>
+    <row r="3592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3592" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3592" s="3" t="s">
+        <v>5123</v>
+      </c>
+    </row>
+    <row r="3593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3593" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3593" s="3" t="s">
+        <v>5124</v>
+      </c>
+    </row>
+    <row r="3594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3594" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3594" s="3" t="s">
+        <v>5125</v>
+      </c>
+    </row>
+    <row r="3595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3595" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3595" s="3" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="3596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3596" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3596" s="3" t="s">
+        <v>5127</v>
+      </c>
+    </row>
+    <row r="3597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3597" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3597" s="3" t="s">
+        <v>5128</v>
+      </c>
+    </row>
+    <row r="3598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3598" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3598" s="3" t="s">
+        <v>5130</v>
+      </c>
+    </row>
+    <row r="3599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3599" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3599" s="3" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="3600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3600" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3600" s="3" t="s">
+        <v>5132</v>
+      </c>
+    </row>
+    <row r="3601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3601" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3601" s="3" t="s">
+        <v>5133</v>
+      </c>
+    </row>
+    <row r="3602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3602" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3602" s="3" t="s">
+        <v>5134</v>
+      </c>
+    </row>
+    <row r="3603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3603" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3603" s="3" t="s">
+        <v>5135</v>
+      </c>
+    </row>
+    <row r="3604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3604" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3604" s="3" t="s">
+        <v>5136</v>
+      </c>
+    </row>
+    <row r="3605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3605" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3605" s="3" t="s">
+        <v>5137</v>
+      </c>
+    </row>
+    <row r="3606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3606" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3606" s="3" t="s">
+        <v>5138</v>
+      </c>
+    </row>
+    <row r="3607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3607" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3607" s="4" t="s">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="3608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3608" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3608" s="3" t="s">
+        <v>5140</v>
+      </c>
+    </row>
+    <row r="3609" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3609" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3609" s="4" t="s">
+        <v>5141</v>
+      </c>
+    </row>
+    <row r="3610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3610" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3610" s="3" t="s">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="3611" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3611" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3611" s="3" t="s">
+        <v>5143</v>
+      </c>
+    </row>
+    <row r="3612" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3612" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3612" s="3" t="s">
+        <v>5144</v>
+      </c>
+    </row>
+    <row r="3613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3613" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3613" s="3" t="s">
+        <v>5145</v>
+      </c>
+    </row>
+    <row r="3614" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3614" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3614" s="3" t="s">
+        <v>5149</v>
+      </c>
+    </row>
+    <row r="3615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3615" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3615" s="3" t="s">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="3616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3616" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3616" s="3" t="s">
+        <v>5151</v>
+      </c>
+    </row>
+    <row r="3617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3617" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3617" s="3" t="s">
+        <v>5152</v>
+      </c>
+    </row>
+    <row r="3618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3618" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3618" s="3" t="s">
+        <v>5153</v>
+      </c>
+    </row>
+    <row r="3619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3619" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3619" s="3" t="s">
+        <v>5154</v>
+      </c>
+    </row>
+    <row r="3620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3620" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3620" s="3" t="s">
+        <v>5155</v>
+      </c>
+    </row>
+    <row r="3621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3621" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3621" s="3" t="s">
+        <v>5156</v>
+      </c>
+    </row>
+    <row r="3622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3622" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3622" s="3" t="s">
+        <v>5157</v>
+      </c>
+    </row>
+    <row r="3623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3623" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3623" s="3" t="s">
+        <v>5158</v>
+      </c>
+    </row>
+    <row r="3624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3624" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3624" s="3" t="s">
+        <v>5159</v>
+      </c>
+    </row>
+    <row r="3625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3625" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3625" s="3" t="s">
+        <v>5160</v>
+      </c>
+    </row>
+    <row r="3626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3626" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3626" s="3" t="s">
+        <v>5162</v>
+      </c>
+    </row>
+    <row r="3627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3627" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3627" s="3" t="s">
+        <v>5164</v>
+      </c>
+    </row>
+    <row r="3628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3628" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3628" s="3" t="s">
+        <v>5165</v>
+      </c>
+    </row>
+    <row r="3629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3629" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3629" s="3" t="s">
+        <v>5166</v>
+      </c>
+    </row>
+    <row r="3630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3630" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3630" s="3" t="s">
+        <v>5167</v>
+      </c>
+    </row>
+    <row r="3631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3631" s="3">
+        <v>5300</v>
+      </c>
+      <c r="C3631" s="3" t="s">
+        <v>5168</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EA8988-BB17-4A8D-885A-2F876A310B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A1C7A7-234E-41D6-8C8C-561FE8A7A308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5185" uniqueCount="5169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="5269">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -20697,6 +20697,406 @@
   </si>
   <si>
     <t>locomotion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persuasively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>livable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlying</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dollar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>privilege</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ethological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsistence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notwithstanding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autumn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impetus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sophistication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instructive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mundane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>raindrop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inflation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunflower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doorway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>injure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instigate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>January</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gateway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rigorously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onrushing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tricycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydrological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-velovity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foresee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignorance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constitutional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orogeny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>administrator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trainer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>befit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaborator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lodge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-tech</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>residency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cosmopolitan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaborative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>westerner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refrigerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clergy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brewster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>execution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tough</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lithograph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wholesale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adrift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mystical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coerce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eccentricity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distasteful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tragedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lantern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diagram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>durability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tabulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>please</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniquely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>birch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adaptability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caledonian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualitative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prohibitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prospector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contradiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auditorium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rote</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -21169,7 +21569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3631"/>
+  <dimension ref="A1:N3717"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -53888,6 +54288,736 @@
         <v>5168</v>
       </c>
     </row>
+    <row r="3632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3632" s="4">
+        <v>5400</v>
+      </c>
+      <c r="B3632" s="3" t="s">
+        <v>5171</v>
+      </c>
+      <c r="C3632" s="3" t="s">
+        <v>5169</v>
+      </c>
+    </row>
+    <row r="3633" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3633" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3633" s="3" t="s">
+        <v>5175</v>
+      </c>
+      <c r="C3633" s="3" t="s">
+        <v>5170</v>
+      </c>
+    </row>
+    <row r="3634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3634" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3634" s="3" t="s">
+        <v>5182</v>
+      </c>
+      <c r="C3634" s="3" t="s">
+        <v>5172</v>
+      </c>
+    </row>
+    <row r="3635" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3635" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3635" s="3" t="s">
+        <v>5191</v>
+      </c>
+      <c r="C3635" s="3" t="s">
+        <v>5173</v>
+      </c>
+    </row>
+    <row r="3636" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3636" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3636" s="3" t="s">
+        <v>5195</v>
+      </c>
+      <c r="C3636" s="3" t="s">
+        <v>5174</v>
+      </c>
+    </row>
+    <row r="3637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3637" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3637" s="3" t="s">
+        <v>5198</v>
+      </c>
+      <c r="C3637" s="3" t="s">
+        <v>5176</v>
+      </c>
+    </row>
+    <row r="3638" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3638" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3638" s="3" t="s">
+        <v>5199</v>
+      </c>
+      <c r="C3638" s="3" t="s">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="3639" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3639" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3639" s="3" t="s">
+        <v>5206</v>
+      </c>
+      <c r="C3639" s="3" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="3640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3640" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3640" s="3" t="s">
+        <v>5232</v>
+      </c>
+      <c r="C3640" s="3" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="3641" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3641" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3641" s="3" t="s">
+        <v>5247</v>
+      </c>
+      <c r="C3641" s="3" t="s">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="3642" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3642" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3642" s="3" t="s">
+        <v>5250</v>
+      </c>
+      <c r="C3642" s="3" t="s">
+        <v>5181</v>
+      </c>
+    </row>
+    <row r="3643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3643" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3643" s="3" t="s">
+        <v>5252</v>
+      </c>
+      <c r="C3643" s="3" t="s">
+        <v>5183</v>
+      </c>
+    </row>
+    <row r="3644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3644" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3644" s="3" t="s">
+        <v>5255</v>
+      </c>
+      <c r="C3644" s="3" t="s">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="3645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3645" s="3">
+        <v>5400</v>
+      </c>
+      <c r="B3645" s="3" t="s">
+        <v>5267</v>
+      </c>
+      <c r="C3645" s="3" t="s">
+        <v>5185</v>
+      </c>
+    </row>
+    <row r="3646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3646" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3646" s="3" t="s">
+        <v>5186</v>
+      </c>
+    </row>
+    <row r="3647" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3647" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3647" s="3" t="s">
+        <v>5187</v>
+      </c>
+    </row>
+    <row r="3648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3648" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3648" s="3" t="s">
+        <v>5188</v>
+      </c>
+    </row>
+    <row r="3649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3649" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3649" s="3" t="s">
+        <v>5189</v>
+      </c>
+    </row>
+    <row r="3650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3650" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3650" s="3" t="s">
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="3651" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3651" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3651" s="3" t="s">
+        <v>5192</v>
+      </c>
+    </row>
+    <row r="3652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3652" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3652" s="3" t="s">
+        <v>5193</v>
+      </c>
+    </row>
+    <row r="3653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3653" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3653" s="3" t="s">
+        <v>5194</v>
+      </c>
+    </row>
+    <row r="3654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3654" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3654" s="3" t="s">
+        <v>5196</v>
+      </c>
+    </row>
+    <row r="3655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3655" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3655" s="3" t="s">
+        <v>5197</v>
+      </c>
+    </row>
+    <row r="3656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3656" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3656" s="3" t="s">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="3657" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3657" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3657" s="3" t="s">
+        <v>5201</v>
+      </c>
+    </row>
+    <row r="3658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3658" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3658" s="3" t="s">
+        <v>5202</v>
+      </c>
+    </row>
+    <row r="3659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3659" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3659" s="3" t="s">
+        <v>5203</v>
+      </c>
+    </row>
+    <row r="3660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3660" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3660" s="3" t="s">
+        <v>5204</v>
+      </c>
+    </row>
+    <row r="3661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3661" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3661" s="3" t="s">
+        <v>5205</v>
+      </c>
+    </row>
+    <row r="3662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3662" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3662" s="3" t="s">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="3663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3663" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3663" s="3" t="s">
+        <v>5208</v>
+      </c>
+    </row>
+    <row r="3664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3664" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3664" s="3" t="s">
+        <v>5209</v>
+      </c>
+    </row>
+    <row r="3665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3665" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3665" s="3" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="3666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3666" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3666" s="3" t="s">
+        <v>5211</v>
+      </c>
+    </row>
+    <row r="3667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3667" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3667" s="3" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="3668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3668" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3668" s="3" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="3669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3669" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3669" s="3" t="s">
+        <v>5214</v>
+      </c>
+    </row>
+    <row r="3670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3670" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3670" s="3" t="s">
+        <v>5215</v>
+      </c>
+    </row>
+    <row r="3671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3671" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3671" s="3" t="s">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="3672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3672" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3672" s="3" t="s">
+        <v>5217</v>
+      </c>
+    </row>
+    <row r="3673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3673" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3673" s="3" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="3674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3674" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3674" s="3" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="3675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3675" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3675" s="3" t="s">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="3676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3676" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3676" s="3" t="s">
+        <v>5221</v>
+      </c>
+    </row>
+    <row r="3677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3677" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3677" s="3" t="s">
+        <v>5222</v>
+      </c>
+    </row>
+    <row r="3678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3678" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3678" s="3" t="s">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="3679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3679" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3679" s="3" t="s">
+        <v>5224</v>
+      </c>
+    </row>
+    <row r="3680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3680" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3680" s="3" t="s">
+        <v>5225</v>
+      </c>
+    </row>
+    <row r="3681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3681" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3681" s="3" t="s">
+        <v>5226</v>
+      </c>
+    </row>
+    <row r="3682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3682" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3682" s="3" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="3683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3683" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3683" s="3" t="s">
+        <v>5228</v>
+      </c>
+    </row>
+    <row r="3684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3684" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3684" s="3" t="s">
+        <v>5229</v>
+      </c>
+    </row>
+    <row r="3685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3685" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3685" s="3" t="s">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="3686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3686" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3686" s="3" t="s">
+        <v>5231</v>
+      </c>
+    </row>
+    <row r="3687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3687" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3687" s="3" t="s">
+        <v>5233</v>
+      </c>
+    </row>
+    <row r="3688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3688" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3688" s="3" t="s">
+        <v>5234</v>
+      </c>
+    </row>
+    <row r="3689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3689" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3689" s="3" t="s">
+        <v>5235</v>
+      </c>
+    </row>
+    <row r="3690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3690" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3690" s="3" t="s">
+        <v>5236</v>
+      </c>
+    </row>
+    <row r="3691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3691" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3691" s="3" t="s">
+        <v>5237</v>
+      </c>
+    </row>
+    <row r="3692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3692" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3692" s="3" t="s">
+        <v>5238</v>
+      </c>
+    </row>
+    <row r="3693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3693" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3693" s="3" t="s">
+        <v>5239</v>
+      </c>
+    </row>
+    <row r="3694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3694" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3694" s="3" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="3695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3695" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3695" s="3" t="s">
+        <v>5241</v>
+      </c>
+    </row>
+    <row r="3696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3696" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3696" s="3" t="s">
+        <v>5242</v>
+      </c>
+    </row>
+    <row r="3697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3697" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3697" s="3" t="s">
+        <v>5243</v>
+      </c>
+    </row>
+    <row r="3698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3698" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3698" s="3" t="s">
+        <v>5244</v>
+      </c>
+    </row>
+    <row r="3699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3699" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3699" s="3" t="s">
+        <v>5245</v>
+      </c>
+    </row>
+    <row r="3700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3700" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3700" s="3" t="s">
+        <v>5246</v>
+      </c>
+    </row>
+    <row r="3701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3701" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3701" s="3" t="s">
+        <v>5248</v>
+      </c>
+    </row>
+    <row r="3702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3702" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3702" s="3" t="s">
+        <v>5249</v>
+      </c>
+    </row>
+    <row r="3703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3703" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3703" s="3" t="s">
+        <v>5251</v>
+      </c>
+    </row>
+    <row r="3704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3704" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3704" s="3" t="s">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="3705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3705" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3705" s="3" t="s">
+        <v>5254</v>
+      </c>
+    </row>
+    <row r="3706" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3706" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3706" s="3" t="s">
+        <v>5256</v>
+      </c>
+    </row>
+    <row r="3707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3707" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3707" s="3" t="s">
+        <v>5257</v>
+      </c>
+    </row>
+    <row r="3708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3708" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3708" s="3" t="s">
+        <v>5258</v>
+      </c>
+    </row>
+    <row r="3709" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3709" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3709" s="3" t="s">
+        <v>5259</v>
+      </c>
+    </row>
+    <row r="3710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3710" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3710" s="3" t="s">
+        <v>5260</v>
+      </c>
+    </row>
+    <row r="3711" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3711" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3711" s="3" t="s">
+        <v>5261</v>
+      </c>
+    </row>
+    <row r="3712" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3712" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3712" s="3" t="s">
+        <v>5262</v>
+      </c>
+    </row>
+    <row r="3713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3713" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3713" s="3" t="s">
+        <v>5263</v>
+      </c>
+    </row>
+    <row r="3714" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3714" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3714" s="3" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="3715" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3715" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3715" s="3" t="s">
+        <v>5265</v>
+      </c>
+    </row>
+    <row r="3716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3716" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3716" s="3" t="s">
+        <v>5266</v>
+      </c>
+    </row>
+    <row r="3717" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3717" s="3">
+        <v>5400</v>
+      </c>
+      <c r="C3717" s="3" t="s">
+        <v>5268</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A1C7A7-234E-41D6-8C8C-561FE8A7A308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576151F9-44C5-4712-A0CE-F92E32D565A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="5269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5385" uniqueCount="5366">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -21097,6 +21097,394 @@
   </si>
   <si>
     <t>rote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battleship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skepticism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commandment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glimpse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preferable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delineate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rugged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>referent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inadequacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gypsy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outwash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crumble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissatisfaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basaltic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plateau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carbonic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lengthy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intersect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>masterpiece</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redwood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>connoisseur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accessory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seriousness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preferentially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquisition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>march</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sterile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seaweed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preschool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smelt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>streambed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luckily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drawback</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salinization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrinkage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detachment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oblige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inconclusive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innovator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pulverization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homemaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rebuild</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intestine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tavern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncompetitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenfold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>panic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aircraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desiccation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chimney</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mandarin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conceive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iroquois</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quietly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ectotherm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqueduct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meanwhile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ravage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>befriend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adaptable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>converge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phosphorescence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endeavor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervisor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portugal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>safely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invisibly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>levy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rye</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpopular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holocene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>astronaut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reuse</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -21569,7 +21957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3717"/>
+  <dimension ref="A1:N3811"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -55018,6 +55406,776 @@
         <v>5268</v>
       </c>
     </row>
+    <row r="3718" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3718" s="4">
+        <v>5500</v>
+      </c>
+      <c r="B3718" s="3" t="s">
+        <v>5299</v>
+      </c>
+      <c r="C3718" s="3" t="s">
+        <v>5269</v>
+      </c>
+    </row>
+    <row r="3719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3719" s="3">
+        <v>5500</v>
+      </c>
+      <c r="B3719" s="3" t="s">
+        <v>5321</v>
+      </c>
+      <c r="C3719" s="3" t="s">
+        <v>5270</v>
+      </c>
+    </row>
+    <row r="3720" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3720" s="3">
+        <v>5500</v>
+      </c>
+      <c r="B3720" s="3" t="s">
+        <v>5335</v>
+      </c>
+      <c r="C3720" s="3" t="s">
+        <v>5271</v>
+      </c>
+    </row>
+    <row r="3721" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3721" s="3">
+        <v>5500</v>
+      </c>
+      <c r="B3721" s="3" t="s">
+        <v>5336</v>
+      </c>
+      <c r="C3721" s="3" t="s">
+        <v>5272</v>
+      </c>
+    </row>
+    <row r="3722" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3722" s="3">
+        <v>5500</v>
+      </c>
+      <c r="B3722" s="3" t="s">
+        <v>5352</v>
+      </c>
+      <c r="C3722" s="3" t="s">
+        <v>5273</v>
+      </c>
+    </row>
+    <row r="3723" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3723" s="3">
+        <v>5500</v>
+      </c>
+      <c r="B3723" s="3" t="s">
+        <v>5365</v>
+      </c>
+      <c r="C3723" s="3" t="s">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3724" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3724" s="3" t="s">
+        <v>5275</v>
+      </c>
+    </row>
+    <row r="3725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3725" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3725" s="3" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="3726" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3726" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3726" s="3" t="s">
+        <v>5277</v>
+      </c>
+    </row>
+    <row r="3727" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3727" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3727" s="3" t="s">
+        <v>5278</v>
+      </c>
+    </row>
+    <row r="3728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3728" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3728" s="3" t="s">
+        <v>5279</v>
+      </c>
+    </row>
+    <row r="3729" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3729" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3729" s="3" t="s">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="3730" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3730" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3730" s="3" t="s">
+        <v>5281</v>
+      </c>
+    </row>
+    <row r="3731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3731" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3731" s="3" t="s">
+        <v>5282</v>
+      </c>
+    </row>
+    <row r="3732" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3732" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3732" s="3" t="s">
+        <v>5283</v>
+      </c>
+    </row>
+    <row r="3733" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3733" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3733" s="3" t="s">
+        <v>5284</v>
+      </c>
+    </row>
+    <row r="3734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3734" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3734" s="3" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="3735" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3735" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3735" s="3" t="s">
+        <v>5286</v>
+      </c>
+    </row>
+    <row r="3736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3736" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3736" s="3" t="s">
+        <v>5287</v>
+      </c>
+    </row>
+    <row r="3737" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3737" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3737" s="3" t="s">
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="3738" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3738" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3738" s="3" t="s">
+        <v>5289</v>
+      </c>
+    </row>
+    <row r="3739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3739" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3739" s="3" t="s">
+        <v>5290</v>
+      </c>
+    </row>
+    <row r="3740" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3740" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3740" s="3" t="s">
+        <v>5291</v>
+      </c>
+    </row>
+    <row r="3741" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3741" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3741" s="3" t="s">
+        <v>5292</v>
+      </c>
+    </row>
+    <row r="3742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3742" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3742" s="3" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="3743" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3743" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3743" s="3" t="s">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="3744" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3744" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3744" s="3" t="s">
+        <v>5295</v>
+      </c>
+    </row>
+    <row r="3745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3745" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3745" s="3" t="s">
+        <v>5296</v>
+      </c>
+    </row>
+    <row r="3746" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3746" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3746" s="3" t="s">
+        <v>5297</v>
+      </c>
+    </row>
+    <row r="3747" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3747" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3747" s="3" t="s">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="3748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3748" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3748" s="3" t="s">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="3749" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3749" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3749" s="3" t="s">
+        <v>5301</v>
+      </c>
+    </row>
+    <row r="3750" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3750" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3750" s="3" t="s">
+        <v>5302</v>
+      </c>
+    </row>
+    <row r="3751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3751" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3751" s="3" t="s">
+        <v>5303</v>
+      </c>
+    </row>
+    <row r="3752" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3752" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3752" s="3" t="s">
+        <v>5304</v>
+      </c>
+    </row>
+    <row r="3753" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3753" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3753" s="3" t="s">
+        <v>5305</v>
+      </c>
+    </row>
+    <row r="3754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3754" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3754" s="3" t="s">
+        <v>5306</v>
+      </c>
+    </row>
+    <row r="3755" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3755" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3755" s="3" t="s">
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="3756" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3756" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3756" s="3" t="s">
+        <v>5308</v>
+      </c>
+    </row>
+    <row r="3757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3757" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3757" s="3" t="s">
+        <v>5309</v>
+      </c>
+    </row>
+    <row r="3758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3758" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3758" s="3" t="s">
+        <v>5310</v>
+      </c>
+    </row>
+    <row r="3759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3759" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3759" s="3" t="s">
+        <v>5311</v>
+      </c>
+    </row>
+    <row r="3760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3760" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3760" s="3" t="s">
+        <v>5312</v>
+      </c>
+    </row>
+    <row r="3761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3761" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3761" s="3" t="s">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="3762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3762" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3762" s="3" t="s">
+        <v>5314</v>
+      </c>
+    </row>
+    <row r="3763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3763" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3763" s="3" t="s">
+        <v>5315</v>
+      </c>
+    </row>
+    <row r="3764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3764" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3764" s="3" t="s">
+        <v>5316</v>
+      </c>
+    </row>
+    <row r="3765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3765" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3765" s="3" t="s">
+        <v>5317</v>
+      </c>
+    </row>
+    <row r="3766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3766" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3766" s="3" t="s">
+        <v>5318</v>
+      </c>
+    </row>
+    <row r="3767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3767" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3767" s="3" t="s">
+        <v>5319</v>
+      </c>
+    </row>
+    <row r="3768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3768" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3768" s="3" t="s">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="3769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3769" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3769" s="3" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="3770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3770" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3770" s="3" t="s">
+        <v>5322</v>
+      </c>
+    </row>
+    <row r="3771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3771" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3771" s="3" t="s">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="3772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3772" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3772" s="3" t="s">
+        <v>5324</v>
+      </c>
+    </row>
+    <row r="3773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3773" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3773" s="3" t="s">
+        <v>5325</v>
+      </c>
+    </row>
+    <row r="3774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3774" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3774" s="3" t="s">
+        <v>5326</v>
+      </c>
+    </row>
+    <row r="3775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3775" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3775" s="3" t="s">
+        <v>5327</v>
+      </c>
+    </row>
+    <row r="3776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3776" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3776" s="3" t="s">
+        <v>5328</v>
+      </c>
+    </row>
+    <row r="3777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3777" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3777" s="3" t="s">
+        <v>5329</v>
+      </c>
+    </row>
+    <row r="3778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3778" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3778" s="3" t="s">
+        <v>5330</v>
+      </c>
+    </row>
+    <row r="3779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3779" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3779" s="3" t="s">
+        <v>5331</v>
+      </c>
+    </row>
+    <row r="3780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3780" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3780" s="3" t="s">
+        <v>5332</v>
+      </c>
+    </row>
+    <row r="3781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3781" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3781" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="3782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3782" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3782" s="3" t="s">
+        <v>5333</v>
+      </c>
+    </row>
+    <row r="3783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3783" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3783" s="3" t="s">
+        <v>5334</v>
+      </c>
+    </row>
+    <row r="3784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3784" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3784" s="3" t="s">
+        <v>5337</v>
+      </c>
+    </row>
+    <row r="3785" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3785" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3785" s="3" t="s">
+        <v>5338</v>
+      </c>
+    </row>
+    <row r="3786" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3786" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3786" s="3" t="s">
+        <v>5339</v>
+      </c>
+    </row>
+    <row r="3787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3787" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3787" s="3" t="s">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="3788" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3788" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3788" s="3" t="s">
+        <v>5341</v>
+      </c>
+    </row>
+    <row r="3789" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3789" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3789" s="3" t="s">
+        <v>5342</v>
+      </c>
+    </row>
+    <row r="3790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3790" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3790" s="3" t="s">
+        <v>5343</v>
+      </c>
+    </row>
+    <row r="3791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3791" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3791" s="3" t="s">
+        <v>5344</v>
+      </c>
+    </row>
+    <row r="3792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3792" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3792" s="3" t="s">
+        <v>5345</v>
+      </c>
+    </row>
+    <row r="3793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3793" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3793" s="3" t="s">
+        <v>5346</v>
+      </c>
+    </row>
+    <row r="3794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3794" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3794" s="3" t="s">
+        <v>5347</v>
+      </c>
+    </row>
+    <row r="3795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3795" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3795" s="3" t="s">
+        <v>5348</v>
+      </c>
+    </row>
+    <row r="3796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3796" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3796" s="3" t="s">
+        <v>5349</v>
+      </c>
+    </row>
+    <row r="3797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3797" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3797" s="3" t="s">
+        <v>5350</v>
+      </c>
+    </row>
+    <row r="3798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3798" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3798" s="3" t="s">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="3799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3799" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3799" s="3" t="s">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="3800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3800" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3800" s="3" t="s">
+        <v>5353</v>
+      </c>
+    </row>
+    <row r="3801" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3801" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3801" s="3" t="s">
+        <v>5354</v>
+      </c>
+    </row>
+    <row r="3802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3802" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3802" s="3" t="s">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="3803" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3803" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3803" s="3" t="s">
+        <v>5356</v>
+      </c>
+    </row>
+    <row r="3804" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3804" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3804" s="3" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="3805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3805" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3805" s="3" t="s">
+        <v>5358</v>
+      </c>
+    </row>
+    <row r="3806" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3806" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3806" s="3" t="s">
+        <v>5359</v>
+      </c>
+    </row>
+    <row r="3807" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3807" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3807" s="3" t="s">
+        <v>5360</v>
+      </c>
+    </row>
+    <row r="3808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3808" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3808" s="3" t="s">
+        <v>5361</v>
+      </c>
+    </row>
+    <row r="3809" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3809" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3809" s="3" t="s">
+        <v>5362</v>
+      </c>
+    </row>
+    <row r="3810" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3810" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3810" s="3" t="s">
+        <v>5363</v>
+      </c>
+    </row>
+    <row r="3811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3811" s="3">
+        <v>5500</v>
+      </c>
+      <c r="C3811" s="3" t="s">
+        <v>5364</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576151F9-44C5-4712-A0CE-F92E32D565A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860C8999-468A-420F-87A9-7FD6C3AE0A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5385" uniqueCount="5366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5486" uniqueCount="5466">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -21485,6 +21485,406 @@
   </si>
   <si>
     <t>reuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antagonism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rehabilitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canoe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dramatize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leisurely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minneapolis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ontario</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>June</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unobtainable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utterly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reddish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rejection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outweigh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chariot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>communicative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conversely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instrumentalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>racial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>platelet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ambient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubbly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metalwork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>correlation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devotion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulldozer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>politically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>centigrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alchemist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reelect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warehouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ensue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>historic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tapeworm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>languish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mythology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lateness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mythological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prototype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>newcomer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gravitas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foresightedness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prerecord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>half-day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brittle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inedible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swiftly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>risky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gibbon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>raccoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arousal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neurotransmitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avalanche</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyrocket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ibex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monkey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cessation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shovel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eccentric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steamer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentimental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iridescent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eocene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cushion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bowel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>technician</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maybe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snowdrift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seventy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleaner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accordion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>treatment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sanitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertainer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scrape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violently</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -21957,7 +22357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3811"/>
+  <dimension ref="A1:N3907"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -56176,6 +56576,789 @@
         <v>5364</v>
       </c>
     </row>
+    <row r="3812" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3812" s="4">
+        <v>5600</v>
+      </c>
+      <c r="B3812" s="3" t="s">
+        <v>5374</v>
+      </c>
+      <c r="C3812" s="3" t="s">
+        <v>5366</v>
+      </c>
+    </row>
+    <row r="3813" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3813" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3813" s="3" t="s">
+        <v>5377</v>
+      </c>
+      <c r="C3813" s="3" t="s">
+        <v>5367</v>
+      </c>
+    </row>
+    <row r="3814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3814" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3814" s="3" t="s">
+        <v>5384</v>
+      </c>
+      <c r="C3814" s="3" t="s">
+        <v>5368</v>
+      </c>
+    </row>
+    <row r="3815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3815" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3815" s="3" t="s">
+        <v>5398</v>
+      </c>
+      <c r="C3815" s="3" t="s">
+        <v>5369</v>
+      </c>
+    </row>
+    <row r="3816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3816" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3816" s="3" t="s">
+        <v>5413</v>
+      </c>
+      <c r="C3816" s="3" t="s">
+        <v>5370</v>
+      </c>
+    </row>
+    <row r="3817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3817" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3817" s="3" t="s">
+        <v>5417</v>
+      </c>
+      <c r="C3817" s="3" t="s">
+        <v>5371</v>
+      </c>
+    </row>
+    <row r="3818" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3818" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3818" s="3" t="s">
+        <v>5452</v>
+      </c>
+      <c r="C3818" s="3" t="s">
+        <v>5372</v>
+      </c>
+    </row>
+    <row r="3819" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3819" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3819" s="3" t="s">
+        <v>5454</v>
+      </c>
+      <c r="C3819" s="3" t="s">
+        <v>5373</v>
+      </c>
+    </row>
+    <row r="3820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3820" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3820" s="3" t="s">
+        <v>5455</v>
+      </c>
+      <c r="C3820" s="3" t="s">
+        <v>5375</v>
+      </c>
+    </row>
+    <row r="3821" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3821" s="3">
+        <v>5600</v>
+      </c>
+      <c r="B3821" s="3" t="s">
+        <v>5461</v>
+      </c>
+      <c r="C3821" s="3" t="s">
+        <v>5376</v>
+      </c>
+    </row>
+    <row r="3822" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3822" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3822" s="3" t="s">
+        <v>5378</v>
+      </c>
+    </row>
+    <row r="3823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3823" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3823" s="3" t="s">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="3824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3824" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3824" s="3" t="s">
+        <v>5380</v>
+      </c>
+    </row>
+    <row r="3825" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3825" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3825" s="3" t="s">
+        <v>5381</v>
+      </c>
+    </row>
+    <row r="3826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3826" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3826" s="3" t="s">
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="3827" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3827" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3827" s="3" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="3828" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3828" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3828" s="3" t="s">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="3829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3829" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3829" s="3" t="s">
+        <v>5386</v>
+      </c>
+    </row>
+    <row r="3830" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3830" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3830" s="3" t="s">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="3831" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3831" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3831" s="3" t="s">
+        <v>5388</v>
+      </c>
+    </row>
+    <row r="3832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3832" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3832" s="3" t="s">
+        <v>5389</v>
+      </c>
+    </row>
+    <row r="3833" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3833" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3833" s="3" t="s">
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="3834" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3834" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3834" s="3" t="s">
+        <v>5391</v>
+      </c>
+    </row>
+    <row r="3835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3835" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3835" s="3" t="s">
+        <v>5392</v>
+      </c>
+    </row>
+    <row r="3836" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3836" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3836" s="3" t="s">
+        <v>5393</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3837" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3837" s="3" t="s">
+        <v>5394</v>
+      </c>
+    </row>
+    <row r="3838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3838" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3838" s="3" t="s">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3839" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3839" s="3" t="s">
+        <v>5396</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3840" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3840" s="3" t="s">
+        <v>5397</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3841" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3841" s="3" t="s">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3842" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3842" s="3" t="s">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3843" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3843" s="3" t="s">
+        <v>5401</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3844" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3844" s="3" t="s">
+        <v>5402</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3845" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3845" s="3" t="s">
+        <v>5403</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3846" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3846" s="3" t="s">
+        <v>5404</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3847" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3847" s="3" t="s">
+        <v>5405</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3848" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3848" s="3" t="s">
+        <v>5406</v>
+      </c>
+    </row>
+    <row r="3849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3849" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3849" s="3" t="s">
+        <v>5407</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3850" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3850" s="3" t="s">
+        <v>5408</v>
+      </c>
+    </row>
+    <row r="3851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3851" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3851" s="3" t="s">
+        <v>5409</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3852" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3852" s="3" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="3853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3853" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3853" s="3" t="s">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3854" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3854" s="3" t="s">
+        <v>5411</v>
+      </c>
+    </row>
+    <row r="3855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3855" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3855" s="3" t="s">
+        <v>5412</v>
+      </c>
+    </row>
+    <row r="3856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3856" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3856" s="3" t="s">
+        <v>5414</v>
+      </c>
+    </row>
+    <row r="3857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3857" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3857" s="3" t="s">
+        <v>5415</v>
+      </c>
+    </row>
+    <row r="3858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3858" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3858" s="3" t="s">
+        <v>5416</v>
+      </c>
+    </row>
+    <row r="3859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3859" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3859" s="3" t="s">
+        <v>5418</v>
+      </c>
+    </row>
+    <row r="3860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3860" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3860" s="3" t="s">
+        <v>5419</v>
+      </c>
+    </row>
+    <row r="3861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3861" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3861" s="3" t="s">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="3862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3862" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3862" s="3" t="s">
+        <v>5421</v>
+      </c>
+    </row>
+    <row r="3863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3863" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3863" s="3" t="s">
+        <v>5422</v>
+      </c>
+    </row>
+    <row r="3864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3864" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3864" s="3" t="s">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="3865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3865" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3865" s="3" t="s">
+        <v>5424</v>
+      </c>
+    </row>
+    <row r="3866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3866" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3866" s="3" t="s">
+        <v>5425</v>
+      </c>
+    </row>
+    <row r="3867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3867" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3867" s="3" t="s">
+        <v>5426</v>
+      </c>
+    </row>
+    <row r="3868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3868" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3868" s="3" t="s">
+        <v>5427</v>
+      </c>
+    </row>
+    <row r="3869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3869" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3869" s="3" t="s">
+        <v>5428</v>
+      </c>
+    </row>
+    <row r="3870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3870" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3870" s="3" t="s">
+        <v>5429</v>
+      </c>
+    </row>
+    <row r="3871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3871" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3871" s="3" t="s">
+        <v>5430</v>
+      </c>
+    </row>
+    <row r="3872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3872" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3872" s="3" t="s">
+        <v>5431</v>
+      </c>
+    </row>
+    <row r="3873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3873" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3873" s="3" t="s">
+        <v>5432</v>
+      </c>
+    </row>
+    <row r="3874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3874" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3874" s="3" t="s">
+        <v>5433</v>
+      </c>
+    </row>
+    <row r="3875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3875" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3875" s="3" t="s">
+        <v>5434</v>
+      </c>
+    </row>
+    <row r="3876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3876" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3876" s="3" t="s">
+        <v>5435</v>
+      </c>
+    </row>
+    <row r="3877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3877" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3877" s="3" t="s">
+        <v>5436</v>
+      </c>
+    </row>
+    <row r="3878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3878" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3878" s="3" t="s">
+        <v>5437</v>
+      </c>
+    </row>
+    <row r="3879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3879" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3879" s="3" t="s">
+        <v>5438</v>
+      </c>
+    </row>
+    <row r="3880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3880" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3880" s="3" t="s">
+        <v>5439</v>
+      </c>
+    </row>
+    <row r="3881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3881" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3881" s="3" t="s">
+        <v>5440</v>
+      </c>
+    </row>
+    <row r="3882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3882" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3882" s="3" t="s">
+        <v>5441</v>
+      </c>
+    </row>
+    <row r="3883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3883" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3883" s="3" t="s">
+        <v>5442</v>
+      </c>
+    </row>
+    <row r="3884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3884" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3884" s="3" t="s">
+        <v>5443</v>
+      </c>
+    </row>
+    <row r="3885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3885" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3885" s="3" t="s">
+        <v>5444</v>
+      </c>
+    </row>
+    <row r="3886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3886" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3886" s="3" t="s">
+        <v>5445</v>
+      </c>
+    </row>
+    <row r="3887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3887" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3887" s="3" t="s">
+        <v>5446</v>
+      </c>
+    </row>
+    <row r="3888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3888" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3888" s="3" t="s">
+        <v>5447</v>
+      </c>
+    </row>
+    <row r="3889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3889" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3889" s="3" t="s">
+        <v>5448</v>
+      </c>
+    </row>
+    <row r="3890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3890" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3890" s="3" t="s">
+        <v>5449</v>
+      </c>
+    </row>
+    <row r="3891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3891" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3891" s="3" t="s">
+        <v>5450</v>
+      </c>
+    </row>
+    <row r="3892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3892" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3892" s="3" t="s">
+        <v>5451</v>
+      </c>
+    </row>
+    <row r="3893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3893" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3893" s="3" t="s">
+        <v>5453</v>
+      </c>
+    </row>
+    <row r="3894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3894" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3894" s="3" t="s">
+        <v>5456</v>
+      </c>
+    </row>
+    <row r="3895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3895" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3895" s="3" t="s">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3896" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3896" s="3" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="3897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3897" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3897" s="3" t="s">
+        <v>5459</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3898" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3898" s="3" t="s">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3899" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3899" s="3" t="s">
+        <v>5462</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3900" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3900" s="3" t="s">
+        <v>5463</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3901" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C3901" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3902" s="4">
+        <v>5700</v>
+      </c>
+      <c r="C3902" s="3" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3903" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3904" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3905" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="3906" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3906" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3907" s="3">
+        <v>5700</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860C8999-468A-420F-87A9-7FD6C3AE0A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC108F60-2CC5-4CA0-8AE6-B547AFE562C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5486" uniqueCount="5466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5586" uniqueCount="5566">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -21885,6 +21885,406 @@
   </si>
   <si>
     <t>violently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>masonry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flexibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obstruct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mediocre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tributary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choosy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distinguishable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absenteeism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pointillist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crudely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ride</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epistle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endotherms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disseminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>berg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corpus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unchangeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patriot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignorant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illusory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sparsely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>methyl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worshipper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watercourses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luxurious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receptacle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motorcycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recreation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chemurgy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imitator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>edifice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surmise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>life-size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disdain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisonous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anti</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>continuator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aviator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preposterous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtlety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suburb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>streetcar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oscillate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aptly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underfoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>developer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gourd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landowner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crossing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undisputed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maneuver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predictability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celsius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncomfortable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revitalization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redbud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullrush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homesteader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>valve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inaccessible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>draft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nodule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillfully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dormancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supposedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basketry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eukaryotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emulsion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condensation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rebound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indefinite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insignificant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handmade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iceland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incandescent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implicitly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fanciful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fixture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprecate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carriage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -22357,7 +22757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N3907"/>
+  <dimension ref="A1:N4011"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -57330,6 +57730,9 @@
       <c r="A3902" s="4">
         <v>5700</v>
       </c>
+      <c r="B3902" s="3" t="s">
+        <v>5477</v>
+      </c>
       <c r="C3902" s="3" t="s">
         <v>5465</v>
       </c>
@@ -57338,25 +57741,842 @@
       <c r="A3903" s="3">
         <v>5700</v>
       </c>
+      <c r="B3903" s="3" t="s">
+        <v>5483</v>
+      </c>
+      <c r="C3903" s="3" t="s">
+        <v>5466</v>
+      </c>
     </row>
     <row r="3904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3904" s="3">
         <v>5700</v>
       </c>
-    </row>
-    <row r="3905" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B3904" s="3" t="s">
+        <v>5491</v>
+      </c>
+      <c r="C3904" s="3" t="s">
+        <v>5467</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3905" s="3">
         <v>5700</v>
       </c>
-    </row>
-    <row r="3906" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B3905" s="3" t="s">
+        <v>5519</v>
+      </c>
+      <c r="C3905" s="3" t="s">
+        <v>5468</v>
+      </c>
+    </row>
+    <row r="3906" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3906" s="3">
         <v>5700</v>
       </c>
-    </row>
-    <row r="3907" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B3906" s="3" t="s">
+        <v>5520</v>
+      </c>
+      <c r="C3906" s="3" t="s">
+        <v>5469</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3907" s="3">
         <v>5700</v>
+      </c>
+      <c r="B3907" s="3" t="s">
+        <v>5529</v>
+      </c>
+      <c r="C3907" s="3" t="s">
+        <v>5470</v>
+      </c>
+    </row>
+    <row r="3908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3908" s="3">
+        <v>5700</v>
+      </c>
+      <c r="B3908" s="3" t="s">
+        <v>5547</v>
+      </c>
+      <c r="C3908" s="3" t="s">
+        <v>5471</v>
+      </c>
+    </row>
+    <row r="3909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3909" s="3">
+        <v>5700</v>
+      </c>
+      <c r="B3909" s="3" t="s">
+        <v>5562</v>
+      </c>
+      <c r="C3909" s="3" t="s">
+        <v>5472</v>
+      </c>
+    </row>
+    <row r="3910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3910" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3910" s="3" t="s">
+        <v>5473</v>
+      </c>
+    </row>
+    <row r="3911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3911" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3911" s="3" t="s">
+        <v>5474</v>
+      </c>
+    </row>
+    <row r="3912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3912" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3912" s="3" t="s">
+        <v>5475</v>
+      </c>
+    </row>
+    <row r="3913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3913" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3913" s="3" t="s">
+        <v>5476</v>
+      </c>
+    </row>
+    <row r="3914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3914" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3914" s="3" t="s">
+        <v>5478</v>
+      </c>
+    </row>
+    <row r="3915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3915" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3915" s="3" t="s">
+        <v>5479</v>
+      </c>
+    </row>
+    <row r="3916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3916" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3916" s="3" t="s">
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="3917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3917" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3917" s="3" t="s">
+        <v>5481</v>
+      </c>
+    </row>
+    <row r="3918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3918" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3918" s="3" t="s">
+        <v>5482</v>
+      </c>
+    </row>
+    <row r="3919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3919" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3919" s="3" t="s">
+        <v>5484</v>
+      </c>
+    </row>
+    <row r="3920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3920" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3920" s="3" t="s">
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="3921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3921" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3921" s="3" t="s">
+        <v>5486</v>
+      </c>
+    </row>
+    <row r="3922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3922" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3922" s="3" t="s">
+        <v>5487</v>
+      </c>
+    </row>
+    <row r="3923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3923" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3923" s="3" t="s">
+        <v>5488</v>
+      </c>
+    </row>
+    <row r="3924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3924" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3924" s="3" t="s">
+        <v>5489</v>
+      </c>
+    </row>
+    <row r="3925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3925" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3925" s="3" t="s">
+        <v>5490</v>
+      </c>
+    </row>
+    <row r="3926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3926" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3926" s="3" t="s">
+        <v>5492</v>
+      </c>
+    </row>
+    <row r="3927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3927" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3927" s="3" t="s">
+        <v>5493</v>
+      </c>
+    </row>
+    <row r="3928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3928" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3928" s="3" t="s">
+        <v>5494</v>
+      </c>
+    </row>
+    <row r="3929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3929" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3929" s="3" t="s">
+        <v>5495</v>
+      </c>
+    </row>
+    <row r="3930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3930" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3930" s="3" t="s">
+        <v>5496</v>
+      </c>
+    </row>
+    <row r="3931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3931" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3931" s="3" t="s">
+        <v>5497</v>
+      </c>
+    </row>
+    <row r="3932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3932" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3932" s="3" t="s">
+        <v>5498</v>
+      </c>
+    </row>
+    <row r="3933" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3933" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3933" s="3" t="s">
+        <v>5499</v>
+      </c>
+    </row>
+    <row r="3934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3934" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3934" s="3" t="s">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="3935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3935" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3935" s="3" t="s">
+        <v>5501</v>
+      </c>
+    </row>
+    <row r="3936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3936" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3936" s="3" t="s">
+        <v>5502</v>
+      </c>
+    </row>
+    <row r="3937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3937" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3937" s="3" t="s">
+        <v>5503</v>
+      </c>
+    </row>
+    <row r="3938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3938" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3938" s="3" t="s">
+        <v>5504</v>
+      </c>
+    </row>
+    <row r="3939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3939" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3939" s="3" t="s">
+        <v>5505</v>
+      </c>
+    </row>
+    <row r="3940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3940" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3940" s="3" t="s">
+        <v>5506</v>
+      </c>
+    </row>
+    <row r="3941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3941" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3941" s="3" t="s">
+        <v>5507</v>
+      </c>
+    </row>
+    <row r="3942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3942" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3942" s="3" t="s">
+        <v>5508</v>
+      </c>
+    </row>
+    <row r="3943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3943" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3943" s="3" t="s">
+        <v>5509</v>
+      </c>
+    </row>
+    <row r="3944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3944" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3944" s="3" t="s">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="3945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3945" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3945" s="3" t="s">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="3946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3946" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3946" s="3" t="s">
+        <v>5512</v>
+      </c>
+    </row>
+    <row r="3947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3947" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3947" s="3" t="s">
+        <v>5513</v>
+      </c>
+    </row>
+    <row r="3948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3948" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3948" s="3" t="s">
+        <v>5514</v>
+      </c>
+    </row>
+    <row r="3949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3949" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3949" s="3" t="s">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="3950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3950" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3950" s="3" t="s">
+        <v>5516</v>
+      </c>
+    </row>
+    <row r="3951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3951" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3951" s="3" t="s">
+        <v>5517</v>
+      </c>
+    </row>
+    <row r="3952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3952" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3952" s="3" t="s">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="3953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3953" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3953" s="3" t="s">
+        <v>5521</v>
+      </c>
+    </row>
+    <row r="3954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3954" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3954" s="3" t="s">
+        <v>5522</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3955" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3955" s="3" t="s">
+        <v>5523</v>
+      </c>
+    </row>
+    <row r="3956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3956" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3956" s="3" t="s">
+        <v>5524</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3957" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3957" s="3" t="s">
+        <v>5525</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3958" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3958" s="3" t="s">
+        <v>5526</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3959" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3959" s="3" t="s">
+        <v>5527</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3960" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3960" s="3" t="s">
+        <v>5528</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3961" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3961" s="3" t="s">
+        <v>5530</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3962" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3962" s="3" t="s">
+        <v>5531</v>
+      </c>
+    </row>
+    <row r="3963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3963" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3963" s="3" t="s">
+        <v>5532</v>
+      </c>
+    </row>
+    <row r="3964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3964" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3964" s="3" t="s">
+        <v>5533</v>
+      </c>
+    </row>
+    <row r="3965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3965" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3965" s="3" t="s">
+        <v>5534</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3966" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3966" s="3" t="s">
+        <v>5535</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3967" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3967" s="3" t="s">
+        <v>5536</v>
+      </c>
+    </row>
+    <row r="3968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3968" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3968" s="3" t="s">
+        <v>5537</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3969" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3969" s="3" t="s">
+        <v>5538</v>
+      </c>
+    </row>
+    <row r="3970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3970" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3970" s="3" t="s">
+        <v>5539</v>
+      </c>
+    </row>
+    <row r="3971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3971" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3971" s="3" t="s">
+        <v>5540</v>
+      </c>
+    </row>
+    <row r="3972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3972" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3972" s="3" t="s">
+        <v>5541</v>
+      </c>
+    </row>
+    <row r="3973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3973" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3973" s="3" t="s">
+        <v>5542</v>
+      </c>
+    </row>
+    <row r="3974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3974" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3974" s="3" t="s">
+        <v>5543</v>
+      </c>
+    </row>
+    <row r="3975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3975" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3975" s="3" t="s">
+        <v>5544</v>
+      </c>
+    </row>
+    <row r="3976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3976" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3976" s="3" t="s">
+        <v>5545</v>
+      </c>
+    </row>
+    <row r="3977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3977" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3977" s="3" t="s">
+        <v>5546</v>
+      </c>
+    </row>
+    <row r="3978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3978" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3978" s="3" t="s">
+        <v>5548</v>
+      </c>
+    </row>
+    <row r="3979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3979" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3979" s="3" t="s">
+        <v>5549</v>
+      </c>
+    </row>
+    <row r="3980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3980" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3980" s="3" t="s">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="3981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3981" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3981" s="3" t="s">
+        <v>5551</v>
+      </c>
+    </row>
+    <row r="3982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3982" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3982" s="3" t="s">
+        <v>5552</v>
+      </c>
+    </row>
+    <row r="3983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3983" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3983" s="3" t="s">
+        <v>5553</v>
+      </c>
+    </row>
+    <row r="3984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3984" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3984" s="3" t="s">
+        <v>5554</v>
+      </c>
+    </row>
+    <row r="3985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3985" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3985" s="3" t="s">
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="3986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3986" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3986" s="3" t="s">
+        <v>5556</v>
+      </c>
+    </row>
+    <row r="3987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3987" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3987" s="3" t="s">
+        <v>5557</v>
+      </c>
+    </row>
+    <row r="3988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3988" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3988" s="3" t="s">
+        <v>5558</v>
+      </c>
+    </row>
+    <row r="3989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3989" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3989" s="3" t="s">
+        <v>5559</v>
+      </c>
+    </row>
+    <row r="3990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3990" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3990" s="3" t="s">
+        <v>5560</v>
+      </c>
+    </row>
+    <row r="3991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3991" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3991" s="3" t="s">
+        <v>5561</v>
+      </c>
+    </row>
+    <row r="3992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3992" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3992" s="3" t="s">
+        <v>5563</v>
+      </c>
+    </row>
+    <row r="3993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3993" s="3">
+        <v>5700</v>
+      </c>
+      <c r="C3993" s="3" t="s">
+        <v>5564</v>
+      </c>
+    </row>
+    <row r="3994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3994" s="4">
+        <v>5800</v>
+      </c>
+      <c r="C3994" s="3" t="s">
+        <v>5565</v>
+      </c>
+    </row>
+    <row r="3995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3995" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="3996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3996" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="3997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3997" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="3998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3998" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="3999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3999" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4000" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4001" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4002" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4003" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4004" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4005" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4006" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4007" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4008" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4009" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4010" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4011" s="3">
+        <v>5800</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC108F60-2CC5-4CA0-8AE6-B547AFE562C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1E771-7D41-4E6C-B917-1A5C055BAF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5586" uniqueCount="5566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5686" uniqueCount="5666">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -22285,6 +22285,406 @@
   </si>
   <si>
     <t>carriage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worsen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portraitist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhythmical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploratory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coconut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visualize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bemoan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maroon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immunity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tariff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restriction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asthenosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>periphery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supercontinet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notorious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idiom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hieroglyphic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurricane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condenser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bilingual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abolish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>streptomycin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innermost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jellyfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagnant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumscribe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inactive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alkaloid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>televise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reciprocate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discourse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>labellum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fishery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>necrosis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eastward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encroach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syllable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tempera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dogwood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Switzerland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immigrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lighten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cripple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notoriously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plutonic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggravate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutralize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>memorial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappointment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>badly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corpse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attainment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>careless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>progression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oceanographer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legitimately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>estuarine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speciality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterfront</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carboniferous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>believable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regularize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>casual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skeletal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landmark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serpentine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tentatively</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -22757,7 +23157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4011"/>
+  <dimension ref="A1:N4091"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -58490,6 +58890,9 @@
       <c r="A3994" s="4">
         <v>5800</v>
       </c>
+      <c r="B3994" s="3" t="s">
+        <v>5583</v>
+      </c>
       <c r="C3994" s="3" t="s">
         <v>5565</v>
       </c>
@@ -58498,85 +58901,782 @@
       <c r="A3995" s="3">
         <v>5800</v>
       </c>
+      <c r="B3995" s="3" t="s">
+        <v>5585</v>
+      </c>
+      <c r="C3995" s="3" t="s">
+        <v>5566</v>
+      </c>
     </row>
     <row r="3996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3996" s="3">
         <v>5800</v>
       </c>
+      <c r="B3996" s="3" t="s">
+        <v>5607</v>
+      </c>
+      <c r="C3996" s="3" t="s">
+        <v>5567</v>
+      </c>
     </row>
     <row r="3997" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3997" s="3">
         <v>5800</v>
       </c>
+      <c r="B3997" s="3" t="s">
+        <v>5622</v>
+      </c>
+      <c r="C3997" s="3" t="s">
+        <v>5568</v>
+      </c>
     </row>
     <row r="3998" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3998" s="3">
         <v>5800</v>
       </c>
+      <c r="B3998" s="3" t="s">
+        <v>5630</v>
+      </c>
+      <c r="C3998" s="3" t="s">
+        <v>5569</v>
+      </c>
     </row>
     <row r="3999" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3999" s="3">
         <v>5800</v>
       </c>
+      <c r="B3999" s="3" t="s">
+        <v>5638</v>
+      </c>
+      <c r="C3999" s="3" t="s">
+        <v>5570</v>
+      </c>
     </row>
     <row r="4000" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4000" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4001" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4000" s="3" t="s">
+        <v>5640</v>
+      </c>
+      <c r="C4000" s="3" t="s">
+        <v>5571</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4001" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4002" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4001" s="3" t="s">
+        <v>5650</v>
+      </c>
+      <c r="C4001" s="3" t="s">
+        <v>5572</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4002" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4003" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4002" s="3" t="s">
+        <v>5655</v>
+      </c>
+      <c r="C4002" s="3" t="s">
+        <v>5573</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4003" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4004" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4003" s="3" t="s">
+        <v>5660</v>
+      </c>
+      <c r="C4003" s="3" t="s">
+        <v>5574</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4004" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4005" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4004" s="3" t="s">
+        <v>5575</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4005" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4006" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4005" s="3" t="s">
+        <v>5576</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4006" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4007" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4006" s="3" t="s">
+        <v>5577</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4007" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4008" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4007" s="3" t="s">
+        <v>5578</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4008" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4009" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4008" s="3" t="s">
+        <v>5579</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4009" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4010" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4009" s="3" t="s">
+        <v>5580</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4010" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="4011" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4010" s="3" t="s">
+        <v>5581</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4011" s="3">
         <v>5800</v>
+      </c>
+      <c r="C4011" s="3" t="s">
+        <v>5582</v>
+      </c>
+    </row>
+    <row r="4012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4012" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4012" s="3" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="4013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4013" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4013" s="3" t="s">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4014" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4014" s="3" t="s">
+        <v>5587</v>
+      </c>
+    </row>
+    <row r="4015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4015" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4015" s="3" t="s">
+        <v>5588</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4016" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4016" s="3" t="s">
+        <v>5589</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4017" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4017" s="3" t="s">
+        <v>5590</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4018" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4018" s="3" t="s">
+        <v>5591</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4019" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4019" s="3" t="s">
+        <v>5592</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4020" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4020" s="3" t="s">
+        <v>5593</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4021" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4021" s="3" t="s">
+        <v>5594</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4022" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4022" s="3" t="s">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4023" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4023" s="3" t="s">
+        <v>5596</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4024" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4024" s="3" t="s">
+        <v>5597</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4025" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4025" s="3" t="s">
+        <v>5598</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4026" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4026" s="3" t="s">
+        <v>5599</v>
+      </c>
+    </row>
+    <row r="4027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4027" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4027" s="3" t="s">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="4028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4028" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4028" s="3" t="s">
+        <v>5601</v>
+      </c>
+    </row>
+    <row r="4029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4029" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4029" s="3" t="s">
+        <v>5602</v>
+      </c>
+    </row>
+    <row r="4030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4030" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4030" s="3" t="s">
+        <v>5603</v>
+      </c>
+    </row>
+    <row r="4031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4031" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4031" s="3" t="s">
+        <v>5604</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4032" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4032" s="3" t="s">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="4033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4033" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4033" s="3" t="s">
+        <v>5606</v>
+      </c>
+    </row>
+    <row r="4034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4034" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4034" s="3" t="s">
+        <v>5608</v>
+      </c>
+    </row>
+    <row r="4035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4035" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4035" s="3" t="s">
+        <v>5609</v>
+      </c>
+    </row>
+    <row r="4036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4036" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4036" s="3" t="s">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="4037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4037" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4037" s="3" t="s">
+        <v>5611</v>
+      </c>
+    </row>
+    <row r="4038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4038" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4038" s="3" t="s">
+        <v>5612</v>
+      </c>
+    </row>
+    <row r="4039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4039" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4039" s="3" t="s">
+        <v>5613</v>
+      </c>
+    </row>
+    <row r="4040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4040" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4040" s="3" t="s">
+        <v>5614</v>
+      </c>
+    </row>
+    <row r="4041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4041" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4041" s="3" t="s">
+        <v>5615</v>
+      </c>
+    </row>
+    <row r="4042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4042" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4042" s="3" t="s">
+        <v>5616</v>
+      </c>
+    </row>
+    <row r="4043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4043" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4043" s="3" t="s">
+        <v>5617</v>
+      </c>
+    </row>
+    <row r="4044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4044" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4044" s="3" t="s">
+        <v>5618</v>
+      </c>
+    </row>
+    <row r="4045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4045" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4045" s="3" t="s">
+        <v>5619</v>
+      </c>
+    </row>
+    <row r="4046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4046" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4046" s="3" t="s">
+        <v>5620</v>
+      </c>
+    </row>
+    <row r="4047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4047" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4047" s="3" t="s">
+        <v>5621</v>
+      </c>
+    </row>
+    <row r="4048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4048" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4048" s="3" t="s">
+        <v>5623</v>
+      </c>
+    </row>
+    <row r="4049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4049" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4049" s="3" t="s">
+        <v>5624</v>
+      </c>
+    </row>
+    <row r="4050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4050" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4050" s="3" t="s">
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="4051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4051" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4051" s="3" t="s">
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="4052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4052" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4052" s="3" t="s">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="4053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4053" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4053" s="3" t="s">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="4054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4054" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4054" s="3" t="s">
+        <v>5629</v>
+      </c>
+    </row>
+    <row r="4055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4055" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4055" s="3" t="s">
+        <v>5631</v>
+      </c>
+    </row>
+    <row r="4056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4056" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4056" s="3" t="s">
+        <v>5632</v>
+      </c>
+    </row>
+    <row r="4057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4057" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4057" s="3" t="s">
+        <v>5633</v>
+      </c>
+    </row>
+    <row r="4058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4058" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4058" s="3" t="s">
+        <v>5634</v>
+      </c>
+    </row>
+    <row r="4059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4059" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4059" s="3" t="s">
+        <v>5635</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4060" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4060" s="3" t="s">
+        <v>5636</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4061" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4061" s="3" t="s">
+        <v>5637</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4062" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4062" s="3" t="s">
+        <v>5639</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4063" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4063" s="3" t="s">
+        <v>5641</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4064" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4064" s="3" t="s">
+        <v>5642</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4065" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4065" s="3" t="s">
+        <v>5643</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4066" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4066" s="3" t="s">
+        <v>5644</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4067" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4067" s="3" t="s">
+        <v>5645</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4068" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4068" s="3" t="s">
+        <v>5646</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4069" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4069" s="3" t="s">
+        <v>5647</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4070" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4070" s="3" t="s">
+        <v>5648</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4071" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4071" s="3" t="s">
+        <v>5649</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4072" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4072" s="3" t="s">
+        <v>5651</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4073" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4073" s="3" t="s">
+        <v>5652</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4074" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4074" s="3" t="s">
+        <v>5653</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4075" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4075" s="3" t="s">
+        <v>5654</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4076" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4076" s="3" t="s">
+        <v>5656</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4077" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4077" s="3" t="s">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4078" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4078" s="3" t="s">
+        <v>5658</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4079" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4079" s="3" t="s">
+        <v>5659</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4080" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4080" s="3" t="s">
+        <v>5661</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4081" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4081" s="3" t="s">
+        <v>5662</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4082" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4082" s="3" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4083" s="3">
+        <v>5800</v>
+      </c>
+      <c r="C4083" s="3" t="s">
+        <v>5664</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4084" s="4">
+        <v>5900</v>
+      </c>
+      <c r="C4084" s="3" t="s">
+        <v>5665</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4085" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4086" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4087" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4088" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4089" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4090" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4091" s="3">
+        <v>5900</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1E771-7D41-4E6C-B917-1A5C055BAF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1466149D-13B2-44BD-9FFE-B74FD7681F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5686" uniqueCount="5666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5786" uniqueCount="5766">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -22685,6 +22685,406 @@
   </si>
   <si>
     <t>tentatively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brightness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">regeneration </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiwi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hummingbird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ridiculous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsuitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydroponic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>currier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Semitic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>randomly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sparrowhawks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intergalactic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diffuses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synonymous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discoloration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backdrop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refractory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soilless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nebular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>someday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circuit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complementary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nectar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>package</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adornment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imperative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lesley</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ppm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assortment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>astound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>one-quarter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>germinate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nitric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luncheon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viscosity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>muddy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incomprehensible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evidently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>label</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symmetrical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theropod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supporter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precarious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wispy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artificially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exempt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rehabilitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persuade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intoxication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genuine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whereby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alteration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>longtime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>customary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>validate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sulfide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ether</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whittle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supersede</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dehydrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amino</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subjective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>milky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fertilization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celestial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>victory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>petrifaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regolith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ptarmigan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydroxyapatite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -23157,7 +23557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4091"/>
+  <dimension ref="A1:N4182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -59640,6 +60040,9 @@
       <c r="A4084" s="4">
         <v>5900</v>
       </c>
+      <c r="B4084" s="3" t="s">
+        <v>5666</v>
+      </c>
       <c r="C4084" s="3" t="s">
         <v>5665</v>
       </c>
@@ -59648,35 +60051,787 @@
       <c r="A4085" s="3">
         <v>5900</v>
       </c>
+      <c r="B4085" s="3" t="s">
+        <v>5692</v>
+      </c>
+      <c r="C4085" s="3" t="s">
+        <v>5667</v>
+      </c>
     </row>
     <row r="4086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4086" s="3">
         <v>5900</v>
       </c>
+      <c r="B4086" s="3" t="s">
+        <v>5695</v>
+      </c>
+      <c r="C4086" s="3" t="s">
+        <v>5668</v>
+      </c>
     </row>
     <row r="4087" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4087" s="3">
         <v>5900</v>
       </c>
+      <c r="B4087" s="3" t="s">
+        <v>5700</v>
+      </c>
+      <c r="C4087" s="3" t="s">
+        <v>5669</v>
+      </c>
     </row>
     <row r="4088" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4088" s="3">
         <v>5900</v>
       </c>
+      <c r="B4088" s="3" t="s">
+        <v>5701</v>
+      </c>
+      <c r="C4088" s="3" t="s">
+        <v>5670</v>
+      </c>
     </row>
     <row r="4089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4089" s="3">
         <v>5900</v>
       </c>
+      <c r="B4089" s="3" t="s">
+        <v>5703</v>
+      </c>
+      <c r="C4089" s="3" t="s">
+        <v>5671</v>
+      </c>
     </row>
     <row r="4090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4090" s="3">
         <v>5900</v>
       </c>
+      <c r="B4090" s="3" t="s">
+        <v>5712</v>
+      </c>
+      <c r="C4090" s="3" t="s">
+        <v>5672</v>
+      </c>
     </row>
     <row r="4091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4091" s="3">
         <v>5900</v>
+      </c>
+      <c r="B4091" s="3" t="s">
+        <v>5718</v>
+      </c>
+      <c r="C4091" s="3" t="s">
+        <v>5673</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4092" s="3">
+        <v>5900</v>
+      </c>
+      <c r="B4092" s="3" t="s">
+        <v>5723</v>
+      </c>
+      <c r="C4092" s="3" t="s">
+        <v>5674</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4093" s="3">
+        <v>5900</v>
+      </c>
+      <c r="B4093" s="3" t="s">
+        <v>5727</v>
+      </c>
+      <c r="C4093" s="3" t="s">
+        <v>5675</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4094" s="3">
+        <v>5900</v>
+      </c>
+      <c r="B4094" s="3" t="s">
+        <v>5735</v>
+      </c>
+      <c r="C4094" s="3" t="s">
+        <v>5676</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4095" s="3">
+        <v>5900</v>
+      </c>
+      <c r="B4095" s="3" t="s">
+        <v>5741</v>
+      </c>
+      <c r="C4095" s="3" t="s">
+        <v>5677</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4096" s="3">
+        <v>5900</v>
+      </c>
+      <c r="B4096" s="3" t="s">
+        <v>5758</v>
+      </c>
+      <c r="C4096" s="3" t="s">
+        <v>5678</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4097" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4097" s="3" t="s">
+        <v>5679</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4098" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4098" s="3" t="s">
+        <v>5680</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4099" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4099" s="3" t="s">
+        <v>5681</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4100" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4100" s="3" t="s">
+        <v>5682</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4101" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4101" s="3" t="s">
+        <v>5683</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4102" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4102" s="3" t="s">
+        <v>5684</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4103" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4103" s="3" t="s">
+        <v>5685</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4104" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4104" s="3" t="s">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4105" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4105" s="3" t="s">
+        <v>5687</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4106" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4106" s="3" t="s">
+        <v>5688</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4107" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4107" s="3" t="s">
+        <v>5689</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4108" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4108" s="3" t="s">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4109" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4109" s="3" t="s">
+        <v>5691</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4110" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4110" s="3" t="s">
+        <v>5693</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4111" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4111" s="3" t="s">
+        <v>5694</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4112" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4112" s="3" t="s">
+        <v>5696</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4113" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4113" s="3" t="s">
+        <v>5697</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4114" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4114" s="3" t="s">
+        <v>5698</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4115" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4115" s="3" t="s">
+        <v>5699</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4116" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4116" s="3" t="s">
+        <v>5702</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4117" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4117" s="3" t="s">
+        <v>5704</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4118" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4118" s="3" t="s">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4119" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4119" s="3" t="s">
+        <v>5706</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4120" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4120" s="3" t="s">
+        <v>5707</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4121" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4121" s="3" t="s">
+        <v>5708</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4122" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4122" s="3" t="s">
+        <v>5709</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4123" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4123" s="3" t="s">
+        <v>5710</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4124" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4124" s="3" t="s">
+        <v>5711</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4125" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4125" s="3" t="s">
+        <v>5713</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4126" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4126" s="3" t="s">
+        <v>5714</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4127" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4127" s="3" t="s">
+        <v>5715</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4128" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4128" s="3" t="s">
+        <v>5716</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4129" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4129" s="3" t="s">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4130" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4130" s="3" t="s">
+        <v>5719</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4131" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4131" s="3" t="s">
+        <v>5720</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4132" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4132" s="3" t="s">
+        <v>5721</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4133" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4133" s="3" t="s">
+        <v>5722</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4134" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4134" s="3" t="s">
+        <v>5724</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4135" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4135" s="3" t="s">
+        <v>5725</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4136" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4136" s="3" t="s">
+        <v>5726</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4137" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4137" s="3" t="s">
+        <v>5728</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4138" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4138" s="3" t="s">
+        <v>5729</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4139" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4139" s="3" t="s">
+        <v>5730</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4140" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4140" s="3" t="s">
+        <v>5731</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4141" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4141" s="3" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4142" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4142" s="3" t="s">
+        <v>5733</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4143" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4143" s="3" t="s">
+        <v>5734</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4144" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4144" s="3" t="s">
+        <v>5736</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4145" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4145" s="3" t="s">
+        <v>5737</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4146" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4146" s="3" t="s">
+        <v>5738</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4147" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4147" s="3" t="s">
+        <v>5739</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4148" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4148" s="3" t="s">
+        <v>5740</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4149" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4149" s="3" t="s">
+        <v>5742</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4150" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4150" s="3" t="s">
+        <v>5743</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4151" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4151" s="3" t="s">
+        <v>5744</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4152" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4152" s="3" t="s">
+        <v>5745</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4153" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4153" s="3" t="s">
+        <v>5746</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4154" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4154" s="3" t="s">
+        <v>5747</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4155" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4155" s="3" t="s">
+        <v>5748</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4156" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4156" s="3" t="s">
+        <v>5749</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4157" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4157" s="3" t="s">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4158" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4158" s="3" t="s">
+        <v>5751</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4159" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4159" s="3" t="s">
+        <v>5752</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4160" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4160" s="3" t="s">
+        <v>5753</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4161" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4161" s="3" t="s">
+        <v>5754</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4162" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4162" s="3" t="s">
+        <v>5755</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4163" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4163" s="3" t="s">
+        <v>5756</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4164" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4164" s="3" t="s">
+        <v>5757</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4165" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4165" s="3" t="s">
+        <v>5759</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4166" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4166" s="3" t="s">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4167" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4167" s="3" t="s">
+        <v>5761</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4168" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4168" s="3" t="s">
+        <v>5762</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4169" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4169" s="3" t="s">
+        <v>5763</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4170" s="3">
+        <v>5900</v>
+      </c>
+      <c r="C4170" s="3" t="s">
+        <v>5764</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4171" s="4">
+        <v>6000</v>
+      </c>
+      <c r="C4171" s="3" t="s">
+        <v>5765</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4172" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4173" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4174" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4175" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4176" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4177" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4178" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4179" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4180" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4181" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4182" s="3">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1466149D-13B2-44BD-9FFE-B74FD7681F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E8AF28-9FBF-40D6-A191-B69BE8413BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5786" uniqueCount="5766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5986" uniqueCount="5965">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -23085,6 +23085,802 @@
   </si>
   <si>
     <t>hydroxyapatite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>percolate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rapidity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mudflats</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mineralize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calcareous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tailor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eyebrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bedcover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pillow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vaguely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hundredfold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agriculturally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immersion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>founding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indispensable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scuba</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frustrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunlit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsatisfactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>separately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collectible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shade-tolerant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orchestral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landslide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counteract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relaxation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remediation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unincorporated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spurge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calotype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fringe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>molasses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>torque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battlefield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needlefish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discriminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>improvisation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommendation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprehensible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>my</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingoing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>realistically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artistry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knowledgeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cannon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recede</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>organically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unintentionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geomagnetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnetize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bonito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hatchling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specialist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vocal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hilly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elongate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linoleum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>customarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprehensive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>franklin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lathe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inherent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inconspicuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utterance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>treasury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apparatus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heartbeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unexplored</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playground</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woodpecker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friendliness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sympathy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wingspan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>campus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flicker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>approve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proximity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excellence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loggerhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pertain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>demonstration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ineffective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explosive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rooftop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interplanetary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lovely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caput</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receptiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>punish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>militaristic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acreage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impersonation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reabsorb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overturn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squarely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Henderson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pronoun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prisoner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>October</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rawhide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonagricultural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devastation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fletcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paradoxically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>automate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pedagogy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pregnant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autonomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exuberant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cast-iron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reaper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anxiously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elephant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plague</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unreal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>child-oriented</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receptive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unplanned</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>longevity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mongolia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sexually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifeway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>façade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>torrid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kindergarten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neuron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transmission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eukaryote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commensal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>living</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inadvertently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roadbed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encompass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outnumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sacr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metabolize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>administer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fasten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diversify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grumble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>degradation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neurospora</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsidy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonsense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>destination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mosquito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paucity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -23557,7 +24353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4182"/>
+  <dimension ref="A1:N4354"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -60775,6 +61571,9 @@
       <c r="A4171" s="4">
         <v>6000</v>
       </c>
+      <c r="B4171" s="3" t="s">
+        <v>5782</v>
+      </c>
       <c r="C4171" s="3" t="s">
         <v>5765</v>
       </c>
@@ -60783,55 +61582,1512 @@
       <c r="A4172" s="3">
         <v>6000</v>
       </c>
+      <c r="B4172" s="3" t="s">
+        <v>5794</v>
+      </c>
+      <c r="C4172" s="3" t="s">
+        <v>5766</v>
+      </c>
     </row>
     <row r="4173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4173" s="3">
         <v>6000</v>
       </c>
+      <c r="B4173" s="3" t="s">
+        <v>5795</v>
+      </c>
+      <c r="C4173" s="3" t="s">
+        <v>5767</v>
+      </c>
     </row>
     <row r="4174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4174" s="3">
         <v>6000</v>
       </c>
+      <c r="B4174" s="3" t="s">
+        <v>5803</v>
+      </c>
+      <c r="C4174" s="3" t="s">
+        <v>5768</v>
+      </c>
     </row>
     <row r="4175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4175" s="3">
         <v>6000</v>
       </c>
+      <c r="B4175" s="3" t="s">
+        <v>5805</v>
+      </c>
+      <c r="C4175" s="3" t="s">
+        <v>5769</v>
+      </c>
     </row>
     <row r="4176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4176" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4176" s="3" t="s">
+        <v>5814</v>
+      </c>
+      <c r="C4176" s="3" t="s">
+        <v>5770</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4177" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4177" s="3" t="s">
+        <v>5820</v>
+      </c>
+      <c r="C4177" s="3" t="s">
+        <v>5771</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4178" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4178" s="3" t="s">
+        <v>5772</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4179" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4179" s="3" t="s">
+        <v>5773</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4180" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4180" s="3" t="s">
+        <v>5774</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4181" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4181" s="3" t="s">
+        <v>5775</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4182" s="3">
         <v>6000</v>
+      </c>
+      <c r="C4182" s="3" t="s">
+        <v>5776</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4183" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4183" s="3" t="s">
+        <v>5777</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4184" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4184" s="3" t="s">
+        <v>5778</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4185" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4185" s="3" t="s">
+        <v>5779</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4186" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4186" s="3" t="s">
+        <v>5780</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4187" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4187" s="3" t="s">
+        <v>5781</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4188" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4188" s="3" t="s">
+        <v>5783</v>
+      </c>
+    </row>
+    <row r="4189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4189" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4189" s="3" t="s">
+        <v>5784</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4190" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4190" s="3" t="s">
+        <v>5785</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4191" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4191" s="3" t="s">
+        <v>5786</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4192" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4192" s="3" t="s">
+        <v>5787</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4193" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4193" s="3" t="s">
+        <v>5788</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4194" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4194" s="3" t="s">
+        <v>5789</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4195" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4195" s="3" t="s">
+        <v>5790</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4196" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4196" s="3" t="s">
+        <v>5791</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4197" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4197" s="3" t="s">
+        <v>5792</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4198" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4198" s="3" t="s">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4199" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4199" s="3" t="s">
+        <v>5796</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4200" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4200" s="3" t="s">
+        <v>5797</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4201" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4201" s="3" t="s">
+        <v>5798</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4202" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4202" s="3" t="s">
+        <v>5799</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4203" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4203" s="3" t="s">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4204" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4204" s="3" t="s">
+        <v>5801</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4205" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4205" s="3" t="s">
+        <v>5802</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4206" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4206" s="3" t="s">
+        <v>5804</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4207" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4207" s="3" t="s">
+        <v>5806</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4208" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4208" s="3" t="s">
+        <v>5807</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4209" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4209" s="3" t="s">
+        <v>5808</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4210" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4210" s="3" t="s">
+        <v>5809</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4211" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4211" s="3" t="s">
+        <v>5810</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4212" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4212" s="3" t="s">
+        <v>5811</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4213" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4213" s="3" t="s">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4214" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4214" s="3" t="s">
+        <v>5813</v>
+      </c>
+    </row>
+    <row r="4215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4215" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4215" s="3" t="s">
+        <v>5815</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4216" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4216" s="3" t="s">
+        <v>5816</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4217" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4217" s="3" t="s">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4218" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4218" s="3" t="s">
+        <v>5818</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4219" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4219" s="3" t="s">
+        <v>5819</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4220" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4220" s="3" t="s">
+        <v>5821</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4221" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4221" s="3" t="s">
+        <v>5822</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4222" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4222" s="3" t="s">
+        <v>5823</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4223" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4223" s="3" t="s">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4224" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4224" s="3" t="s">
+        <v>5825</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4225" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4225" s="3" t="s">
+        <v>5826</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4226" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4226" s="3" t="s">
+        <v>5827</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4227" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4227" s="3" t="s">
+        <v>5828</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4228" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4228" s="3" t="s">
+        <v>5829</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4229" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4229" s="3" t="s">
+        <v>5830</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4230" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4230" s="3" t="s">
+        <v>5831</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4231" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4231" s="3" t="s">
+        <v>5832</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4232" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4232" s="3" t="s">
+        <v>5833</v>
+      </c>
+    </row>
+    <row r="4233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4233" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4233" s="3" t="s">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4234" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4234" s="3" t="s">
+        <v>5835</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4235" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4235" s="3" t="s">
+        <v>5836</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4236" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4236" s="3" t="s">
+        <v>5837</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4237" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4237" s="3" t="s">
+        <v>5838</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4238" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4238" s="3" t="s">
+        <v>5839</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4239" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4239" s="3" t="s">
+        <v>5840</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4240" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4240" s="3" t="s">
+        <v>5841</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4241" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4241" s="3" t="s">
+        <v>5842</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4242" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4242" s="3" t="s">
+        <v>5843</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4243" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4243" s="3" t="s">
+        <v>5844</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4244" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4244" s="3" t="s">
+        <v>5845</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4245" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4245" s="3" t="s">
+        <v>5846</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4246" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4246" s="3" t="s">
+        <v>5847</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4247" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4247" s="3" t="s">
+        <v>5848</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4248" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4248" s="3" t="s">
+        <v>5849</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4249" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4249" s="3" t="s">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4250" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4250" s="4" t="s">
+        <v>5851</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4251" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4251" s="3" t="s">
+        <v>5852</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4252" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4252" s="3" t="s">
+        <v>5853</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4253" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4253" s="3" t="s">
+        <v>5854</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4254" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4254" s="3" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4255" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4255" s="3" t="s">
+        <v>5856</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4256" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4256" s="3" t="s">
+        <v>5857</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4257" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4257" s="3" t="s">
+        <v>5858</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4258" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4258" s="3" t="s">
+        <v>5859</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4259" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4259" s="3" t="s">
+        <v>5860</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4260" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4260" s="3" t="s">
+        <v>5861</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4261" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4261" s="3" t="s">
+        <v>5862</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4262" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4262" s="3" t="s">
+        <v>5863</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4263" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C4263" s="3" t="s">
+        <v>5864</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4264" s="4">
+        <v>6100</v>
+      </c>
+      <c r="B4264" s="3" t="s">
+        <v>5867</v>
+      </c>
+      <c r="C4264" s="3" t="s">
+        <v>5865</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4265" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4265" s="3" t="s">
+        <v>5873</v>
+      </c>
+      <c r="C4265" s="3" t="s">
+        <v>5866</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4266" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4266" s="3" t="s">
+        <v>5882</v>
+      </c>
+      <c r="C4266" s="3" t="s">
+        <v>5868</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4267" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4267" s="3" t="s">
+        <v>5883</v>
+      </c>
+      <c r="C4267" s="3" t="s">
+        <v>5869</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4268" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4268" s="3" t="s">
+        <v>5900</v>
+      </c>
+      <c r="C4268" s="3" t="s">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4269" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4269" s="3" t="s">
+        <v>5907</v>
+      </c>
+      <c r="C4269" s="3" t="s">
+        <v>5871</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4270" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4270" s="3" t="s">
+        <v>5909</v>
+      </c>
+      <c r="C4270" s="3" t="s">
+        <v>5872</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4271" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4271" s="3" t="s">
+        <v>5915</v>
+      </c>
+      <c r="C4271" s="3" t="s">
+        <v>5874</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4272" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4272" s="3" t="s">
+        <v>5918</v>
+      </c>
+      <c r="C4272" s="3" t="s">
+        <v>5875</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4273" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4273" s="3" t="s">
+        <v>5919</v>
+      </c>
+      <c r="C4273" s="3" t="s">
+        <v>5876</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4274" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4274" s="3" t="s">
+        <v>5922</v>
+      </c>
+      <c r="C4274" s="3" t="s">
+        <v>5877</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4275" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4275" s="3" t="s">
+        <v>5923</v>
+      </c>
+      <c r="C4275" s="3" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4276" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4276" s="3" t="s">
+        <v>5928</v>
+      </c>
+      <c r="C4276" s="3" t="s">
+        <v>5879</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4277" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4277" s="3" t="s">
+        <v>5932</v>
+      </c>
+      <c r="C4277" s="3" t="s">
+        <v>5880</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4278" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4278" s="3" t="s">
+        <v>5935</v>
+      </c>
+      <c r="C4278" s="3" t="s">
+        <v>5881</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4279" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4279" s="3" t="s">
+        <v>5937</v>
+      </c>
+      <c r="C4279" s="3" t="s">
+        <v>5884</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4280" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4280" s="3" t="s">
+        <v>5945</v>
+      </c>
+      <c r="C4280" s="3" t="s">
+        <v>5885</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4281" s="3">
+        <v>6100</v>
+      </c>
+      <c r="B4281" s="3" t="s">
+        <v>5953</v>
+      </c>
+      <c r="C4281" s="3" t="s">
+        <v>5886</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4282" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4282" s="3" t="s">
+        <v>5887</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4283" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4283" s="3" t="s">
+        <v>5888</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4284" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4284" s="3" t="s">
+        <v>5889</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4285" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4285" s="3" t="s">
+        <v>5890</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4286" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4286" s="3" t="s">
+        <v>5891</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4287" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4287" s="3" t="s">
+        <v>5892</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4288" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4288" s="3" t="s">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4289" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4289" s="3" t="s">
+        <v>5894</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4290" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4290" s="3" t="s">
+        <v>5895</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4291" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4291" s="3" t="s">
+        <v>5896</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4292" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4292" s="3" t="s">
+        <v>5897</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4293" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4293" s="3" t="s">
+        <v>5898</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4294" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4294" s="3" t="s">
+        <v>5899</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4295" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4295" s="3" t="s">
+        <v>5901</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4296" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4296" s="3" t="s">
+        <v>5902</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4297" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4297" s="3" t="s">
+        <v>5903</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4298" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4298" s="3" t="s">
+        <v>5904</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4299" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4299" s="3" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4300" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4300" s="3" t="s">
+        <v>5906</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4301" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4301" s="3" t="s">
+        <v>5908</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4302" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4302" s="3" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4303" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4303" s="3" t="s">
+        <v>5910</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4304" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4304" s="3" t="s">
+        <v>5911</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4305" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4305" s="3" t="s">
+        <v>5912</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4306" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4306" s="3" t="s">
+        <v>5913</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4307" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4307" s="3" t="s">
+        <v>5914</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4308" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4308" s="3" t="s">
+        <v>5916</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4309" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4309" s="3" t="s">
+        <v>5917</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4310" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4310" s="3" t="s">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4311" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4311" s="3" t="s">
+        <v>5921</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4312" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4312" s="3" t="s">
+        <v>5924</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4313" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4313" s="3" t="s">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4314" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4314" s="3" t="s">
+        <v>5926</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4315" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4315" s="3" t="s">
+        <v>5927</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4316" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4316" s="3" t="s">
+        <v>5929</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4317" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4317" s="3" t="s">
+        <v>5930</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4318" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4318" s="3" t="s">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4319" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4319" s="3" t="s">
+        <v>5933</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4320" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4320" s="3" t="s">
+        <v>5934</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4321" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4321" s="3" t="s">
+        <v>5936</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4322" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4322" s="3" t="s">
+        <v>5938</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4323" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4323" s="3" t="s">
+        <v>5939</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4324" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4324" s="3" t="s">
+        <v>5940</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4325" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4325" s="3" t="s">
+        <v>5941</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4326" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4326" s="3" t="s">
+        <v>5942</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4327" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4327" s="3" t="s">
+        <v>5943</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4328" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4328" s="3" t="s">
+        <v>5944</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4329" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4329" s="3" t="s">
+        <v>5946</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4330" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4330" s="3" t="s">
+        <v>5947</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4331" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4331" s="3" t="s">
+        <v>5948</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4332" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4332" s="3" t="s">
+        <v>5949</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4333" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4333" s="3" t="s">
+        <v>5950</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4334" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4334" s="3" t="s">
+        <v>5951</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4335" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4335" s="3" t="s">
+        <v>5952</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4336" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4336" s="3" t="s">
+        <v>5954</v>
+      </c>
+    </row>
+    <row r="4337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4337" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4337" s="3" t="s">
+        <v>5955</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4338" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4338" s="3" t="s">
+        <v>5956</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4339" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4339" s="3" t="s">
+        <v>5957</v>
+      </c>
+    </row>
+    <row r="4340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4340" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4340" s="3" t="s">
+        <v>5958</v>
+      </c>
+    </row>
+    <row r="4341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4341" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4341" s="3" t="s">
+        <v>5959</v>
+      </c>
+    </row>
+    <row r="4342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4342" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4342" s="3" t="s">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="4343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4343" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4343" s="3" t="s">
+        <v>5961</v>
+      </c>
+    </row>
+    <row r="4344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4344" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4344" s="3" t="s">
+        <v>5962</v>
+      </c>
+    </row>
+    <row r="4345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4345" s="3">
+        <v>6100</v>
+      </c>
+      <c r="C4345" s="3" t="s">
+        <v>5963</v>
+      </c>
+    </row>
+    <row r="4346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4346" s="4">
+        <v>6200</v>
+      </c>
+      <c r="C4346" s="3" t="s">
+        <v>5964</v>
+      </c>
+    </row>
+    <row r="4347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4347" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4348" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4349" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4350" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4351" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4352" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4353" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4354" s="3">
+        <v>6200</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E8AF28-9FBF-40D6-A191-B69BE8413BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64170FE-2DE7-4924-8E3D-E08A2B04ECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5986" uniqueCount="5965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6086" uniqueCount="6065">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -23881,6 +23881,406 @@
   </si>
   <si>
     <t>paucity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>make-up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walrus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deserve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incubator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poorhouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsidize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amniotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>porpoise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emanate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noxious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deviate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>individually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggregation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erectus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleepiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oneness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remainder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>namely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>button</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workforce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analyst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gradient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regulator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toolmaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>essay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morphology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiccup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>platypus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nurse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>halite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>straighten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>July</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-resolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>balloon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteorologist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undeveloped</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conestoga</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unexpectedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappearance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nowcasting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>readership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pencil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wharf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>individuality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>squander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mesopotamia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>birdlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>somerset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appetite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dampen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>textural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ribbon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>derrick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phoenix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impersonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imaginary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coal-fired</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kinetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commitment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pluto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chicopee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seaport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patchy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sacred</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clinical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verbalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uphold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cellulose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Patricia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sharper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>candlelight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allocation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vantage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flowerbed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debatable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -24353,7 +24753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4354"/>
+  <dimension ref="A1:N4454"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -63046,6 +63446,9 @@
       <c r="A4346" s="4">
         <v>6200</v>
       </c>
+      <c r="B4346" s="3" t="s">
+        <v>5969</v>
+      </c>
       <c r="C4346" s="3" t="s">
         <v>5964</v>
       </c>
@@ -63054,40 +63457,837 @@
       <c r="A4347" s="3">
         <v>6200</v>
       </c>
+      <c r="B4347" s="3" t="s">
+        <v>5973</v>
+      </c>
+      <c r="C4347" s="3" t="s">
+        <v>5965</v>
+      </c>
     </row>
     <row r="4348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4348" s="3">
         <v>6200</v>
       </c>
+      <c r="B4348" s="3" t="s">
+        <v>5987</v>
+      </c>
+      <c r="C4348" s="3" t="s">
+        <v>5966</v>
+      </c>
     </row>
     <row r="4349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4349" s="3">
         <v>6200</v>
       </c>
+      <c r="B4349" s="3" t="s">
+        <v>5994</v>
+      </c>
+      <c r="C4349" s="3" t="s">
+        <v>5967</v>
+      </c>
     </row>
     <row r="4350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4350" s="3">
         <v>6200</v>
       </c>
+      <c r="B4350" s="3" t="s">
+        <v>6005</v>
+      </c>
+      <c r="C4350" s="3" t="s">
+        <v>5968</v>
+      </c>
     </row>
     <row r="4351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4351" s="3">
         <v>6200</v>
       </c>
+      <c r="B4351" s="3" t="s">
+        <v>6010</v>
+      </c>
+      <c r="C4351" s="3" t="s">
+        <v>5970</v>
+      </c>
     </row>
     <row r="4352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4352" s="3">
         <v>6200</v>
       </c>
-    </row>
-    <row r="4353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4352" s="3" t="s">
+        <v>6023</v>
+      </c>
+      <c r="C4352" s="3" t="s">
+        <v>5971</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4353" s="3">
         <v>6200</v>
       </c>
-    </row>
-    <row r="4354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4353" s="3" t="s">
+        <v>6027</v>
+      </c>
+      <c r="C4353" s="3" t="s">
+        <v>5972</v>
+      </c>
+    </row>
+    <row r="4354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4354" s="3">
         <v>6200</v>
+      </c>
+      <c r="C4354" s="3" t="s">
+        <v>5974</v>
+      </c>
+    </row>
+    <row r="4355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4355" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4355" s="3" t="s">
+        <v>5975</v>
+      </c>
+    </row>
+    <row r="4356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4356" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4356" s="3" t="s">
+        <v>5976</v>
+      </c>
+    </row>
+    <row r="4357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4357" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4357" s="3" t="s">
+        <v>5977</v>
+      </c>
+    </row>
+    <row r="4358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4358" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4358" s="3" t="s">
+        <v>5978</v>
+      </c>
+    </row>
+    <row r="4359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4359" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4359" s="3" t="s">
+        <v>5979</v>
+      </c>
+    </row>
+    <row r="4360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4360" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4360" s="3" t="s">
+        <v>5980</v>
+      </c>
+    </row>
+    <row r="4361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4361" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4361" s="3" t="s">
+        <v>5981</v>
+      </c>
+    </row>
+    <row r="4362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4362" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4362" s="3" t="s">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="4363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4363" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4363" s="3" t="s">
+        <v>5983</v>
+      </c>
+    </row>
+    <row r="4364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4364" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4364" s="3" t="s">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="4365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4365" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4365" s="3" t="s">
+        <v>5985</v>
+      </c>
+    </row>
+    <row r="4366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4366" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4366" s="3" t="s">
+        <v>5986</v>
+      </c>
+    </row>
+    <row r="4367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4367" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4367" s="3" t="s">
+        <v>5988</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4368" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4368" s="3" t="s">
+        <v>5989</v>
+      </c>
+    </row>
+    <row r="4369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4369" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4369" s="3" t="s">
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4370" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4370" s="3" t="s">
+        <v>5991</v>
+      </c>
+    </row>
+    <row r="4371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4371" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4371" s="3" t="s">
+        <v>5992</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4372" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4372" s="3" t="s">
+        <v>5993</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4373" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4373" s="3" t="s">
+        <v>5995</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4374" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4374" s="3" t="s">
+        <v>5996</v>
+      </c>
+    </row>
+    <row r="4375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4375" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4375" s="3" t="s">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4376" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4376" s="3" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="4377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4377" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4377" s="3" t="s">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="4378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4378" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4378" s="3" t="s">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4379" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4379" s="3" t="s">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="4380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4380" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4380" s="3" t="s">
+        <v>6002</v>
+      </c>
+    </row>
+    <row r="4381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4381" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4381" s="3" t="s">
+        <v>6003</v>
+      </c>
+    </row>
+    <row r="4382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4382" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4382" s="3" t="s">
+        <v>6004</v>
+      </c>
+    </row>
+    <row r="4383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4383" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4383" s="3" t="s">
+        <v>6006</v>
+      </c>
+    </row>
+    <row r="4384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4384" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4384" s="3" t="s">
+        <v>6007</v>
+      </c>
+    </row>
+    <row r="4385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4385" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4385" s="3" t="s">
+        <v>6008</v>
+      </c>
+    </row>
+    <row r="4386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4386" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4386" s="3" t="s">
+        <v>6009</v>
+      </c>
+    </row>
+    <row r="4387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4387" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4387" s="3" t="s">
+        <v>6011</v>
+      </c>
+    </row>
+    <row r="4388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4388" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4388" s="3" t="s">
+        <v>6012</v>
+      </c>
+    </row>
+    <row r="4389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4389" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4389" s="3" t="s">
+        <v>6013</v>
+      </c>
+    </row>
+    <row r="4390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4390" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4390" s="3" t="s">
+        <v>6014</v>
+      </c>
+    </row>
+    <row r="4391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4391" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4391" s="3" t="s">
+        <v>6015</v>
+      </c>
+    </row>
+    <row r="4392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4392" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4392" s="3" t="s">
+        <v>6016</v>
+      </c>
+    </row>
+    <row r="4393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4393" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4393" s="3" t="s">
+        <v>6017</v>
+      </c>
+    </row>
+    <row r="4394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4394" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4394" s="3" t="s">
+        <v>6018</v>
+      </c>
+    </row>
+    <row r="4395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4395" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4395" s="3" t="s">
+        <v>6019</v>
+      </c>
+    </row>
+    <row r="4396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4396" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4396" s="3" t="s">
+        <v>6020</v>
+      </c>
+    </row>
+    <row r="4397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4397" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4397" s="3" t="s">
+        <v>6021</v>
+      </c>
+    </row>
+    <row r="4398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4398" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4398" s="3" t="s">
+        <v>6022</v>
+      </c>
+    </row>
+    <row r="4399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4399" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4399" s="3" t="s">
+        <v>6024</v>
+      </c>
+    </row>
+    <row r="4400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4400" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4400" s="3" t="s">
+        <v>6025</v>
+      </c>
+    </row>
+    <row r="4401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4401" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4401" s="3" t="s">
+        <v>6026</v>
+      </c>
+    </row>
+    <row r="4402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4402" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4402" s="3" t="s">
+        <v>6028</v>
+      </c>
+    </row>
+    <row r="4403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4403" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4403" s="3" t="s">
+        <v>6029</v>
+      </c>
+    </row>
+    <row r="4404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4404" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4404" s="3" t="s">
+        <v>6030</v>
+      </c>
+    </row>
+    <row r="4405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4405" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4405" s="3" t="s">
+        <v>6031</v>
+      </c>
+    </row>
+    <row r="4406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4406" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4406" s="3" t="s">
+        <v>6032</v>
+      </c>
+    </row>
+    <row r="4407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4407" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4407" s="3" t="s">
+        <v>6033</v>
+      </c>
+    </row>
+    <row r="4408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4408" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4408" s="3" t="s">
+        <v>6034</v>
+      </c>
+    </row>
+    <row r="4409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4409" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4409" s="3" t="s">
+        <v>6035</v>
+      </c>
+    </row>
+    <row r="4410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4410" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4410" s="3" t="s">
+        <v>6036</v>
+      </c>
+    </row>
+    <row r="4411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4411" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4411" s="3" t="s">
+        <v>6037</v>
+      </c>
+    </row>
+    <row r="4412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4412" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4412" s="3" t="s">
+        <v>6038</v>
+      </c>
+    </row>
+    <row r="4413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4413" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4413" s="3" t="s">
+        <v>6039</v>
+      </c>
+    </row>
+    <row r="4414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4414" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4414" s="3" t="s">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="4415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4415" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4415" s="3" t="s">
+        <v>6041</v>
+      </c>
+    </row>
+    <row r="4416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4416" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4416" s="3" t="s">
+        <v>6042</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4417" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4417" s="3" t="s">
+        <v>6043</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4418" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4418" s="3" t="s">
+        <v>6044</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4419" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4419" s="3" t="s">
+        <v>6045</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4420" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4420" s="3" t="s">
+        <v>6046</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4421" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4421" s="3" t="s">
+        <v>6047</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4422" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4422" s="3" t="s">
+        <v>6048</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4423" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4423" s="3" t="s">
+        <v>6049</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4424" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4424" s="3" t="s">
+        <v>6050</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4425" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4425" s="3" t="s">
+        <v>6051</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4426" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4426" s="3" t="s">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4427" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4427" s="3" t="s">
+        <v>6053</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4428" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4428" s="3" t="s">
+        <v>6054</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4429" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4429" s="3" t="s">
+        <v>6055</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4430" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4430" s="3" t="s">
+        <v>6056</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4431" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4431" s="3" t="s">
+        <v>6057</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4432" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4432" s="3" t="s">
+        <v>6058</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4433" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4433" s="3" t="s">
+        <v>6059</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4434" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4434" s="3" t="s">
+        <v>6060</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4435" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4435" s="3" t="s">
+        <v>6061</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4436" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4436" s="3" t="s">
+        <v>6062</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4437" s="3">
+        <v>6200</v>
+      </c>
+      <c r="C4437" s="3" t="s">
+        <v>6063</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4438" s="4">
+        <v>6300</v>
+      </c>
+      <c r="C4438" s="3" t="s">
+        <v>6064</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4439" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4440" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4441" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4442" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4443" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4444" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4445" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4446" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4447" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4448" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4449" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4450" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4451" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4452" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4453" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4454" s="3">
+        <v>6300</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64170FE-2DE7-4924-8E3D-E08A2B04ECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF335A-9D81-4F06-A483-9A48F21280A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6086" uniqueCount="6065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6186" uniqueCount="6165">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -24281,6 +24281,406 @@
   </si>
   <si>
     <t>debatable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>petrochemical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>life-form</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>objectify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alternatively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intelligible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deviation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtropic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scenic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tusk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meaty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resilient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indigestible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prolifically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elevator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rigidity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dismantle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refinery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>working-class</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>riverbank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landslip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ephemeral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clerk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low-intensity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monotonous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aquatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vibration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unionization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aboveground</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encroachment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>semicircular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handsome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weightlessness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggestive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rougher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mystique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lengthwise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Victorian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>human-related</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ninety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alpha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pumped-storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prevalence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cousin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negligible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>west-side</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleeper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colonizer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unmatched</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nutritive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shade-grown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morris</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonfiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>straightforward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brilliantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eighty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flexibly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sandal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cumulative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wisdom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rigor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grotto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prostrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>club</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blaze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indecipherable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substantiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ghost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peru</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diva</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonstop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bifocal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cougar</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -24377,74 +24777,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -24464,7 +24796,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -24753,7 +25085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4454"/>
+  <dimension ref="A1:N4545"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -64206,6 +64538,9 @@
       <c r="A4438" s="4">
         <v>6300</v>
       </c>
+      <c r="B4438" s="3" t="s">
+        <v>6082</v>
+      </c>
       <c r="C4438" s="3" t="s">
         <v>6064</v>
       </c>
@@ -64214,80 +64549,832 @@
       <c r="A4439" s="3">
         <v>6300</v>
       </c>
+      <c r="B4439" s="3" t="s">
+        <v>6116</v>
+      </c>
+      <c r="C4439" s="3" t="s">
+        <v>6065</v>
+      </c>
     </row>
     <row r="4440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4440" s="3">
         <v>6300</v>
       </c>
+      <c r="B4440" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="C4440" s="3" t="s">
+        <v>6066</v>
+      </c>
     </row>
     <row r="4441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4441" s="3">
         <v>6300</v>
       </c>
+      <c r="B4441" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="C4441" s="3" t="s">
+        <v>6067</v>
+      </c>
     </row>
     <row r="4442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4442" s="3">
         <v>6300</v>
       </c>
+      <c r="B4442" s="3" t="s">
+        <v>6149</v>
+      </c>
+      <c r="C4442" s="3" t="s">
+        <v>6068</v>
+      </c>
     </row>
     <row r="4443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4443" s="3">
         <v>6300</v>
       </c>
+      <c r="B4443" s="3" t="s">
+        <v>6153</v>
+      </c>
+      <c r="C4443" s="3" t="s">
+        <v>6069</v>
+      </c>
     </row>
     <row r="4444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4444" s="3">
         <v>6300</v>
       </c>
+      <c r="C4444" s="3" t="s">
+        <v>6070</v>
+      </c>
     </row>
     <row r="4445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4445" s="3">
         <v>6300</v>
       </c>
+      <c r="C4445" s="3" t="s">
+        <v>6071</v>
+      </c>
     </row>
     <row r="4446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4446" s="3">
         <v>6300</v>
       </c>
+      <c r="C4446" s="3" t="s">
+        <v>6072</v>
+      </c>
     </row>
     <row r="4447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4447" s="3">
         <v>6300</v>
       </c>
+      <c r="C4447" s="3" t="s">
+        <v>6073</v>
+      </c>
     </row>
     <row r="4448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4448" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4448" s="3" t="s">
+        <v>6074</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4449" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4449" s="3" t="s">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4450" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4450" s="3" t="s">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4451" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4451" s="3" t="s">
+        <v>6077</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4452" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4452" s="3" t="s">
+        <v>6078</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4453" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="4454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4453" s="3" t="s">
+        <v>6079</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4454" s="3">
         <v>6300</v>
+      </c>
+      <c r="C4454" s="3" t="s">
+        <v>6080</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4455" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4455" s="3" t="s">
+        <v>6081</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4456" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4456" s="3" t="s">
+        <v>6083</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4457" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4457" s="3" t="s">
+        <v>6084</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4458" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4458" s="3" t="s">
+        <v>6085</v>
+      </c>
+    </row>
+    <row r="4459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4459" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4459" s="3" t="s">
+        <v>6086</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4460" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4460" s="3" t="s">
+        <v>6087</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4461" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4461" s="3" t="s">
+        <v>6088</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4462" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4462" s="3" t="s">
+        <v>6089</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4463" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4463" s="3" t="s">
+        <v>6090</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4464" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4464" s="3" t="s">
+        <v>6091</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4465" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4465" s="3" t="s">
+        <v>6092</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4466" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4466" s="3" t="s">
+        <v>6093</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4467" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4467" s="3" t="s">
+        <v>6094</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4468" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4468" s="3" t="s">
+        <v>6095</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4469" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4469" s="3" t="s">
+        <v>6096</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4470" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4470" s="3" t="s">
+        <v>6097</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4471" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4471" s="3" t="s">
+        <v>6098</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4472" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4472" s="3" t="s">
+        <v>6099</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4473" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4473" s="3" t="s">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4474" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4474" s="3" t="s">
+        <v>6101</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4475" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4475" s="3" t="s">
+        <v>6102</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4476" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4476" s="3" t="s">
+        <v>6103</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4477" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4477" s="3" t="s">
+        <v>6104</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4478" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4478" s="3" t="s">
+        <v>6105</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4479" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4479" s="3" t="s">
+        <v>6106</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4480" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4480" s="3" t="s">
+        <v>6107</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4481" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4481" s="3" t="s">
+        <v>6108</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4482" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4482" s="3" t="s">
+        <v>6109</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4483" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4483" s="3" t="s">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4484" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4484" s="3" t="s">
+        <v>6111</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4485" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4485" s="3" t="s">
+        <v>6112</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4486" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4486" s="3" t="s">
+        <v>6113</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4487" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4487" s="3" t="s">
+        <v>6114</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4488" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4488" s="3" t="s">
+        <v>6115</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4489" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4489" s="3" t="s">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4490" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4490" s="3" t="s">
+        <v>6119</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4491" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4491" s="3" t="s">
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4492" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4492" s="3" t="s">
+        <v>6121</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4493" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4493" s="3" t="s">
+        <v>6122</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4494" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4494" s="3" t="s">
+        <v>6123</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4495" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4495" s="3" t="s">
+        <v>6124</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4496" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4496" s="3" t="s">
+        <v>6125</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4497" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4497" s="3" t="s">
+        <v>6126</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4498" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4498" s="3" t="s">
+        <v>6127</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4499" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4499" s="3" t="s">
+        <v>6128</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4500" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4500" s="3" t="s">
+        <v>6129</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4501" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4501" s="3" t="s">
+        <v>6130</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4502" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4502" s="3" t="s">
+        <v>6131</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4503" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4503" s="3" t="s">
+        <v>6132</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4504" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4504" s="3" t="s">
+        <v>6133</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4505" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4505" s="3" t="s">
+        <v>6134</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4506" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4506" s="3" t="s">
+        <v>6135</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4507" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4507" s="3" t="s">
+        <v>6136</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4508" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4508" s="3" t="s">
+        <v>6137</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4509" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4509" s="3" t="s">
+        <v>6138</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4510" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4510" s="3" t="s">
+        <v>6139</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4511" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4511" s="3" t="s">
+        <v>6141</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4512" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4512" s="3" t="s">
+        <v>6142</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4513" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4513" s="3" t="s">
+        <v>6143</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4514" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4514" s="3" t="s">
+        <v>6144</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4515" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4515" s="3" t="s">
+        <v>6145</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4516" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4516" s="3" t="s">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4517" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4517" s="3" t="s">
+        <v>6147</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4518" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4518" s="3" t="s">
+        <v>6148</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4519" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4519" s="3" t="s">
+        <v>6150</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4520" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4520" s="3" t="s">
+        <v>6151</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4521" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4521" s="3" t="s">
+        <v>6152</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4522" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4522" s="3" t="s">
+        <v>6154</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4523" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4523" s="3" t="s">
+        <v>6155</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4524" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4524" s="3" t="s">
+        <v>6156</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4525" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4525" s="3" t="s">
+        <v>6157</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4526" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4526" s="3" t="s">
+        <v>6158</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4527" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4527" s="3" t="s">
+        <v>6159</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4528" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4528" s="3" t="s">
+        <v>6160</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4529" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4529" s="3" t="s">
+        <v>6161</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4530" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4530" s="3" t="s">
+        <v>6162</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4531" s="3">
+        <v>6300</v>
+      </c>
+      <c r="C4531" s="3" t="s">
+        <v>6163</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4532" s="4">
+        <v>6400</v>
+      </c>
+      <c r="C4532" s="3" t="s">
+        <v>6164</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4533" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4534" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4535" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4536" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4537" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4538" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4539" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4540" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4541" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4542" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4543" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4544" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4545" s="3">
+        <v>6400</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\GitEnglish\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF335A-9D81-4F06-A483-9A48F21280A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA28CC8-84AA-457B-BD6C-2A03AC458149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6186" uniqueCount="6165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="6264">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -24681,6 +24678,402 @@
   </si>
   <si>
     <t>cougar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>versatile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ocher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-quality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mentally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obliterate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspiration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conceivable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>internationally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greenish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">succinct </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">short-range </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">midway </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsung</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fungicide </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">popularize </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>changeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>responsive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amplify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notebook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pertinent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decision-making</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utilization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theoretical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>determinant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overtax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>youth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>custodial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">academician </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flatter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressionistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortuitously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thriller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plentifully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monopolize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadbasket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>annihilate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sectional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jealousy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garbage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>routinely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predicament</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thermometer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divergence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oceanography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outbuilding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forbes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grama</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhyolite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decisive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comparably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transmitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coarse-grained</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exponential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gesso</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attendant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capitalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">deference </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cumbersome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pendant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basketmaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kennel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postmaster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interestingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perfume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concomitant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reckless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regidly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>renounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overhang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>observatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forward-looking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urbanism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refrigeration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harshly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chitin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jules</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reviewer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triassic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjunct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glasswork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplorable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instructor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>midday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loneliness</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -24761,7 +25154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -24769,8 +25162,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -24789,9 +25180,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -24829,7 +25220,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -24935,7 +25326,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -25077,7 +25468,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -25085,7 +25476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4545"/>
+  <dimension ref="A1:N4642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -29073,7 +29464,7 @@
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A539" s="5">
+      <c r="A539" s="3">
         <v>900</v>
       </c>
       <c r="B539" s="3" t="s">
@@ -29095,7 +29486,7 @@
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A541" s="5">
+      <c r="A541" s="3">
         <v>900</v>
       </c>
       <c r="B541" s="3" t="s">
@@ -29117,7 +29508,7 @@
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A543" s="5">
+      <c r="A543" s="3">
         <v>900</v>
       </c>
       <c r="B543" s="3" t="s">
@@ -29139,7 +29530,7 @@
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A545" s="5">
+      <c r="A545" s="3">
         <v>900</v>
       </c>
       <c r="B545" s="3" t="s">
@@ -29161,7 +29552,7 @@
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A547" s="5">
+      <c r="A547" s="3">
         <v>900</v>
       </c>
       <c r="B547" s="3" t="s">
@@ -29183,7 +29574,7 @@
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A549" s="5">
+      <c r="A549" s="3">
         <v>900</v>
       </c>
       <c r="B549" s="3" t="s">
@@ -29205,7 +29596,7 @@
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A551" s="5">
+      <c r="A551" s="3">
         <v>900</v>
       </c>
       <c r="B551" s="3" t="s">
@@ -29227,7 +29618,7 @@
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A553" s="5">
+      <c r="A553" s="3">
         <v>900</v>
       </c>
       <c r="B553" s="3" t="s">
@@ -29249,7 +29640,7 @@
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A555" s="5">
+      <c r="A555" s="3">
         <v>900</v>
       </c>
       <c r="B555" s="3" t="s">
@@ -29271,7 +29662,7 @@
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A557" s="5">
+      <c r="A557" s="3">
         <v>900</v>
       </c>
       <c r="B557" s="3" t="s">
@@ -29293,7 +29684,7 @@
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A559" s="5">
+      <c r="A559" s="3">
         <v>900</v>
       </c>
       <c r="B559" s="3" t="s">
@@ -29315,7 +29706,7 @@
       </c>
     </row>
     <row r="561" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A561" s="5">
+      <c r="A561" s="3">
         <v>900</v>
       </c>
       <c r="B561" s="3" t="s">
@@ -29337,7 +29728,7 @@
       </c>
     </row>
     <row r="563" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A563" s="5">
+      <c r="A563" s="3">
         <v>900</v>
       </c>
       <c r="B563" s="3" t="s">
@@ -29359,7 +29750,7 @@
       </c>
     </row>
     <row r="565" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A565" s="5">
+      <c r="A565" s="3">
         <v>900</v>
       </c>
       <c r="B565" s="3" t="s">
@@ -29381,7 +29772,7 @@
       </c>
     </row>
     <row r="567" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A567" s="5">
+      <c r="A567" s="3">
         <v>900</v>
       </c>
       <c r="B567" s="3" t="s">
@@ -29403,7 +29794,7 @@
       </c>
     </row>
     <row r="569" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A569" s="5">
+      <c r="A569" s="3">
         <v>900</v>
       </c>
       <c r="B569" s="3" t="s">
@@ -29428,7 +29819,7 @@
       </c>
     </row>
     <row r="571" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A571" s="5">
+      <c r="A571" s="3">
         <v>900</v>
       </c>
       <c r="B571" s="3" t="s">
@@ -29450,7 +29841,7 @@
       </c>
     </row>
     <row r="573" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A573" s="5">
+      <c r="A573" s="3">
         <v>900</v>
       </c>
       <c r="B573" s="3" t="s">
@@ -29472,7 +29863,7 @@
       </c>
     </row>
     <row r="575" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A575" s="5">
+      <c r="A575" s="3">
         <v>900</v>
       </c>
       <c r="B575" s="3" t="s">
@@ -29493,8 +29884,8 @@
         <v>840</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A577" s="5">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A577" s="3">
         <v>900</v>
       </c>
       <c r="B577" s="3" t="s">
@@ -29504,7 +29895,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A578" s="3">
         <v>900</v>
       </c>
@@ -29514,10 +29905,9 @@
       <c r="C578" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="G578" s="6"/>
-    </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A579" s="5">
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A579" s="3">
         <v>900</v>
       </c>
       <c r="B579" s="3" t="s">
@@ -29527,7 +29917,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A580" s="3">
         <v>900</v>
       </c>
@@ -29538,8 +29928,8 @@
         <v>848</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A581" s="5">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A581" s="3">
         <v>900</v>
       </c>
       <c r="B581" s="3" t="s">
@@ -29549,7 +29939,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A582" s="3">
         <v>900</v>
       </c>
@@ -29560,8 +29950,8 @@
         <v>852</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A583" s="5">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A583" s="3">
         <v>900</v>
       </c>
       <c r="B583" s="3" t="s">
@@ -29571,7 +29961,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A584" s="3">
         <v>900</v>
       </c>
@@ -29582,8 +29972,8 @@
         <v>855</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A585" s="5">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A585" s="3">
         <v>900</v>
       </c>
       <c r="B585" s="3" t="s">
@@ -29593,7 +29983,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A586" s="3">
         <v>900</v>
       </c>
@@ -29601,15 +29991,15 @@
         <v>857</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A587" s="5">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A587" s="3">
         <v>900</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A588" s="3">
         <v>900</v>
       </c>
@@ -29617,15 +30007,15 @@
         <v>860</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A589" s="5">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A589" s="3">
         <v>900</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A590" s="4">
         <v>1000</v>
       </c>
@@ -29636,7 +30026,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A591" s="3">
         <v>1000</v>
       </c>
@@ -29647,7 +30037,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A592" s="3">
         <v>1000</v>
       </c>
@@ -65308,6 +65698,9 @@
       <c r="A4532" s="4">
         <v>6400</v>
       </c>
+      <c r="B4532" s="3" t="s">
+        <v>6168</v>
+      </c>
       <c r="C4532" s="3" t="s">
         <v>6164</v>
       </c>
@@ -65316,65 +65709,847 @@
       <c r="A4533" s="3">
         <v>6400</v>
       </c>
+      <c r="B4533" s="3" t="s">
+        <v>6173</v>
+      </c>
+      <c r="C4533" s="3" t="s">
+        <v>6165</v>
+      </c>
     </row>
     <row r="4534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4534" s="3">
         <v>6400</v>
       </c>
+      <c r="B4534" s="3" t="s">
+        <v>6176</v>
+      </c>
+      <c r="C4534" s="3" t="s">
+        <v>6166</v>
+      </c>
     </row>
     <row r="4535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4535" s="3">
         <v>6400</v>
       </c>
+      <c r="B4535" s="3" t="s">
+        <v>6181</v>
+      </c>
+      <c r="C4535" s="3" t="s">
+        <v>6167</v>
+      </c>
     </row>
     <row r="4536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4536" s="3">
         <v>6400</v>
       </c>
+      <c r="B4536" s="3" t="s">
+        <v>6182</v>
+      </c>
+      <c r="C4536" s="3" t="s">
+        <v>6169</v>
+      </c>
     </row>
     <row r="4537" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4537" s="3">
         <v>6400</v>
       </c>
+      <c r="B4537" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="C4537" s="3" t="s">
+        <v>6170</v>
+      </c>
     </row>
     <row r="4538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4538" s="3">
         <v>6400</v>
       </c>
+      <c r="B4538" s="3" t="s">
+        <v>6186</v>
+      </c>
+      <c r="C4538" s="3" t="s">
+        <v>6171</v>
+      </c>
     </row>
     <row r="4539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4539" s="3">
         <v>6400</v>
       </c>
+      <c r="B4539" s="3" t="s">
+        <v>6192</v>
+      </c>
+      <c r="C4539" s="3" t="s">
+        <v>6172</v>
+      </c>
     </row>
     <row r="4540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4540" s="3">
         <v>6400</v>
       </c>
+      <c r="B4540" s="3" t="s">
+        <v>6193</v>
+      </c>
+      <c r="C4540" s="3" t="s">
+        <v>6174</v>
+      </c>
     </row>
     <row r="4541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4541" s="3">
         <v>6400</v>
       </c>
+      <c r="B4541" s="3" t="s">
+        <v>6199</v>
+      </c>
+      <c r="C4541" s="3" t="s">
+        <v>6175</v>
+      </c>
     </row>
     <row r="4542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4542" s="3">
         <v>6400</v>
       </c>
+      <c r="B4542" s="3" t="s">
+        <v>6207</v>
+      </c>
+      <c r="C4542" s="3" t="s">
+        <v>6177</v>
+      </c>
     </row>
     <row r="4543" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4543" s="3">
         <v>6400</v>
       </c>
+      <c r="B4543" s="3" t="s">
+        <v>6209</v>
+      </c>
+      <c r="C4543" s="3" t="s">
+        <v>6178</v>
+      </c>
     </row>
     <row r="4544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4544" s="3">
         <v>6400</v>
       </c>
-    </row>
-    <row r="4545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4544" s="3" t="s">
+        <v>6215</v>
+      </c>
+      <c r="C4544" s="3" t="s">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4545" s="3">
         <v>6400</v>
+      </c>
+      <c r="B4545" s="3" t="s">
+        <v>6219</v>
+      </c>
+      <c r="C4545" s="3" t="s">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4546" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4546" s="3" t="s">
+        <v>6232</v>
+      </c>
+      <c r="C4546" s="3" t="s">
+        <v>6183</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4547" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4547" s="3" t="s">
+        <v>6236</v>
+      </c>
+      <c r="C4547" s="3" t="s">
+        <v>6185</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4548" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4548" s="3" t="s">
+        <v>6239</v>
+      </c>
+      <c r="C4548" s="3" t="s">
+        <v>6187</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4549" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4549" s="3" t="s">
+        <v>6245</v>
+      </c>
+      <c r="C4549" s="3" t="s">
+        <v>6188</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4550" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4550" s="3" t="s">
+        <v>6253</v>
+      </c>
+      <c r="C4550" s="3" t="s">
+        <v>6189</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4551" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4551" s="3" t="s">
+        <v>6256</v>
+      </c>
+      <c r="C4551" s="3" t="s">
+        <v>6190</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4552" s="3">
+        <v>6400</v>
+      </c>
+      <c r="B4552" s="3" t="s">
+        <v>6262</v>
+      </c>
+      <c r="C4552" s="3" t="s">
+        <v>6191</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4553" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4553" s="3" t="s">
+        <v>6194</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4554" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4554" s="3" t="s">
+        <v>6195</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4555" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4555" s="3" t="s">
+        <v>6196</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4556" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4556" s="3" t="s">
+        <v>6197</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4557" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4557" s="3" t="s">
+        <v>6198</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4558" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4558" s="3" t="s">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4559" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4559" s="3" t="s">
+        <v>6201</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4560" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4560" s="3" t="s">
+        <v>6202</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4561" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4561" s="3" t="s">
+        <v>6203</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4562" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4562" s="3" t="s">
+        <v>6204</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4563" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4563" s="3" t="s">
+        <v>6205</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4564" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4564" s="3" t="s">
+        <v>6206</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4565" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4565" s="3" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4566" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4566" s="3" t="s">
+        <v>6208</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4567" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4567" s="3" t="s">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4568" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4568" s="3" t="s">
+        <v>6211</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4569" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4569" s="3" t="s">
+        <v>6212</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4570" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4570" s="3" t="s">
+        <v>6213</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4571" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4571" s="3" t="s">
+        <v>6214</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4572" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4572" s="3" t="s">
+        <v>6216</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4573" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4573" s="3" t="s">
+        <v>6217</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4574" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4574" s="3" t="s">
+        <v>6218</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4575" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4575" s="3" t="s">
+        <v>6220</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4576" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4576" s="3" t="s">
+        <v>6221</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4577" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4577" s="3" t="s">
+        <v>6222</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4578" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4578" s="3" t="s">
+        <v>6223</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4579" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4579" s="3" t="s">
+        <v>6224</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4580" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4580" s="3" t="s">
+        <v>6225</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4581" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4581" s="3" t="s">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4582" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4582" s="3" t="s">
+        <v>6227</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4583" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4583" s="3" t="s">
+        <v>6228</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4584" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4584" s="3" t="s">
+        <v>6229</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4585" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4585" s="3" t="s">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4586" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4586" s="3" t="s">
+        <v>6231</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4587" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4587" s="3" t="s">
+        <v>6233</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4588" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4588" s="3" t="s">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4589" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4589" s="3" t="s">
+        <v>6235</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4590" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4590" s="3" t="s">
+        <v>6237</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4591" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4591" s="3" t="s">
+        <v>6238</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4592" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4592" s="3" t="s">
+        <v>6240</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4593" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4593" s="3" t="s">
+        <v>6241</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4594" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4594" s="3" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4595" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4595" s="3" t="s">
+        <v>6243</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4596" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4596" s="3" t="s">
+        <v>6244</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4597" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4597" s="3" t="s">
+        <v>6246</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4598" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4598" s="3" t="s">
+        <v>6247</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4599" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4599" s="3" t="s">
+        <v>6248</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4600" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4600" s="3" t="s">
+        <v>6249</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4601" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4601" s="3" t="s">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4602" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4602" s="3" t="s">
+        <v>6251</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4603" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4603" s="3" t="s">
+        <v>6252</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4604" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4604" s="3" t="s">
+        <v>6254</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4605" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4605" s="3" t="s">
+        <v>6255</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4606" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4606" s="3" t="s">
+        <v>6257</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4607" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4607" s="3" t="s">
+        <v>6258</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4608" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4608" s="3" t="s">
+        <v>6259</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4609" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4609" s="3" t="s">
+        <v>6260</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4610" s="3">
+        <v>6400</v>
+      </c>
+      <c r="C4610" s="3" t="s">
+        <v>6261</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4611" s="4">
+        <v>6500</v>
+      </c>
+      <c r="B4611" s="3" t="s">
+        <v>6263</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4612" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4613" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4614" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4615" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4616" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4617" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4618" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4619" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4620" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4621" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4622" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4623" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4624" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4625" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4626" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4627" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4628" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4629" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4630" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4631" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4632" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4633" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4634" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4635" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4636" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4637" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4638" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4639" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4640" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4641" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4642" s="3">
+        <v>6500</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA28CC8-84AA-457B-BD6C-2A03AC458149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044009D3-2554-4C91-BE32-A0E8038EEA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="6264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6386" uniqueCount="6364">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -25074,6 +25074,406 @@
   </si>
   <si>
     <t>loneliness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hopeless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interchangeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bizarre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laundry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>definitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puncture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glandular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glycoside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interactive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unusable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inducible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sepal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snippet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>correlate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beetle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glycoprotein</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cardiac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autonomic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ending</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preoccupation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coyote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endowment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puddle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proboscis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crimson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhaustion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>winner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthropological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter-clockwise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sticky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>structurally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wholesome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polyphony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cornet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chivalry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unadorned</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compatible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelkeeper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paraphrase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unselfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonself</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ragtime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-tensile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unrestricted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quasar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concertina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bedroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bolster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>halt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angstrom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microscopy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narcotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narcosis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embolism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rupture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abrasion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proportionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virgo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freighter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thinly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Andromeda</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yardstick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exalt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monoxide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>owe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>premature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grievance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conjectural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oystercatcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shorebird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photogrammetry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mandible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corrosion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upright</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unravel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glassmaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Katherine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>malleability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>robust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baedeker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microfossil</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -25476,7 +25876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4642"/>
+  <dimension ref="A1:N4729"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -66396,160 +66796,895 @@
       <c r="B4611" s="3" t="s">
         <v>6263</v>
       </c>
+      <c r="C4611" s="3" t="s">
+        <v>6265</v>
+      </c>
     </row>
     <row r="4612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4612" s="3">
         <v>6500</v>
       </c>
+      <c r="B4612" s="3" t="s">
+        <v>6264</v>
+      </c>
+      <c r="C4612" s="3" t="s">
+        <v>6266</v>
+      </c>
     </row>
     <row r="4613" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4613" s="3">
         <v>6500</v>
       </c>
+      <c r="B4613" s="3" t="s">
+        <v>6267</v>
+      </c>
+      <c r="C4613" s="3" t="s">
+        <v>6268</v>
+      </c>
     </row>
     <row r="4614" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4614" s="3">
         <v>6500</v>
       </c>
+      <c r="B4614" s="3" t="s">
+        <v>6273</v>
+      </c>
+      <c r="C4614" s="3" t="s">
+        <v>6269</v>
+      </c>
     </row>
     <row r="4615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4615" s="3">
         <v>6500</v>
       </c>
+      <c r="B4615" s="3" t="s">
+        <v>6274</v>
+      </c>
+      <c r="C4615" s="3" t="s">
+        <v>6270</v>
+      </c>
     </row>
     <row r="4616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4616" s="3">
         <v>6500</v>
       </c>
+      <c r="B4616" s="3" t="s">
+        <v>6283</v>
+      </c>
+      <c r="C4616" s="3" t="s">
+        <v>6271</v>
+      </c>
     </row>
     <row r="4617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4617" s="3">
         <v>6500</v>
       </c>
+      <c r="B4617" s="3" t="s">
+        <v>6284</v>
+      </c>
+      <c r="C4617" s="3" t="s">
+        <v>6272</v>
+      </c>
     </row>
     <row r="4618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4618" s="3">
         <v>6500</v>
       </c>
+      <c r="B4618" s="3" t="s">
+        <v>6293</v>
+      </c>
+      <c r="C4618" s="3" t="s">
+        <v>6275</v>
+      </c>
     </row>
     <row r="4619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4619" s="3">
         <v>6500</v>
       </c>
+      <c r="B4619" s="3" t="s">
+        <v>6306</v>
+      </c>
+      <c r="C4619" s="3" t="s">
+        <v>6276</v>
+      </c>
     </row>
     <row r="4620" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4620" s="3">
         <v>6500</v>
       </c>
+      <c r="B4620" s="3" t="s">
+        <v>6311</v>
+      </c>
+      <c r="C4620" s="3" t="s">
+        <v>6277</v>
+      </c>
     </row>
     <row r="4621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4621" s="3">
         <v>6500</v>
       </c>
+      <c r="B4621" s="3" t="s">
+        <v>6318</v>
+      </c>
+      <c r="C4621" s="3" t="s">
+        <v>6278</v>
+      </c>
     </row>
     <row r="4622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4622" s="3">
         <v>6500</v>
       </c>
+      <c r="C4622" s="3" t="s">
+        <v>6279</v>
+      </c>
     </row>
     <row r="4623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4623" s="3">
         <v>6500</v>
       </c>
+      <c r="C4623" s="3" t="s">
+        <v>6280</v>
+      </c>
     </row>
     <row r="4624" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4624" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4624" s="3" t="s">
+        <v>6281</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4625" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4625" s="3" t="s">
+        <v>6282</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4626" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4626" s="3" t="s">
+        <v>6285</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4627" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4627" s="3" t="s">
+        <v>6286</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4628" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4628" s="3" t="s">
+        <v>6287</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4629" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4629" s="3" t="s">
+        <v>6288</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4630" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4630" s="3" t="s">
+        <v>6289</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4631" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4631" s="3" t="s">
+        <v>6290</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4632" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4632" s="3" t="s">
+        <v>6291</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4633" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4633" s="3" t="s">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4634" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4634" s="3" t="s">
+        <v>6294</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4635" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4635" s="3" t="s">
+        <v>6295</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4636" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4636" s="3" t="s">
+        <v>6296</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4637" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4637" s="3" t="s">
+        <v>6297</v>
+      </c>
+    </row>
+    <row r="4638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4638" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4638" s="3" t="s">
+        <v>6298</v>
+      </c>
+    </row>
+    <row r="4639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4639" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4639" s="3" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="4640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4640" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4640" s="3" t="s">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="4641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4641" s="3">
         <v>6500</v>
       </c>
-    </row>
-    <row r="4642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4641" s="3" t="s">
+        <v>6301</v>
+      </c>
+    </row>
+    <row r="4642" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4642" s="3">
         <v>6500</v>
+      </c>
+      <c r="C4642" s="3" t="s">
+        <v>6302</v>
+      </c>
+    </row>
+    <row r="4643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4643" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4643" s="3" t="s">
+        <v>6303</v>
+      </c>
+    </row>
+    <row r="4644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4644" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4644" s="3" t="s">
+        <v>6304</v>
+      </c>
+    </row>
+    <row r="4645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4645" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4645" s="3" t="s">
+        <v>6305</v>
+      </c>
+    </row>
+    <row r="4646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4646" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4646" s="3" t="s">
+        <v>6307</v>
+      </c>
+    </row>
+    <row r="4647" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4647" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4647" s="3" t="s">
+        <v>6308</v>
+      </c>
+    </row>
+    <row r="4648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4648" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4648" s="3" t="s">
+        <v>6309</v>
+      </c>
+    </row>
+    <row r="4649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4649" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4649" s="3" t="s">
+        <v>6310</v>
+      </c>
+    </row>
+    <row r="4650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4650" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4650" s="3" t="s">
+        <v>6312</v>
+      </c>
+    </row>
+    <row r="4651" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4651" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4651" s="3" t="s">
+        <v>6313</v>
+      </c>
+    </row>
+    <row r="4652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4652" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4652" s="3" t="s">
+        <v>6314</v>
+      </c>
+    </row>
+    <row r="4653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4653" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4653" s="3" t="s">
+        <v>6315</v>
+      </c>
+    </row>
+    <row r="4654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4654" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4654" s="3" t="s">
+        <v>6316</v>
+      </c>
+    </row>
+    <row r="4655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4655" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4655" s="3" t="s">
+        <v>6317</v>
+      </c>
+    </row>
+    <row r="4656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4656" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4656" s="3" t="s">
+        <v>6319</v>
+      </c>
+    </row>
+    <row r="4657" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4657" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4657" s="3" t="s">
+        <v>6320</v>
+      </c>
+    </row>
+    <row r="4658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4658" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4658" s="3" t="s">
+        <v>6321</v>
+      </c>
+    </row>
+    <row r="4659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4659" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4659" s="3" t="s">
+        <v>6322</v>
+      </c>
+    </row>
+    <row r="4660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4660" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4660" s="3" t="s">
+        <v>6323</v>
+      </c>
+    </row>
+    <row r="4661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4661" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4661" s="3" t="s">
+        <v>6324</v>
+      </c>
+    </row>
+    <row r="4662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4662" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4662" s="3" t="s">
+        <v>6325</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4663" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4663" s="3" t="s">
+        <v>6326</v>
+      </c>
+    </row>
+    <row r="4664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4664" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4664" s="3" t="s">
+        <v>6327</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4665" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4665" s="3" t="s">
+        <v>6328</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4666" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4666" s="3" t="s">
+        <v>6329</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4667" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4667" s="3" t="s">
+        <v>6330</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4668" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4668" s="3" t="s">
+        <v>6331</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4669" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4669" s="3" t="s">
+        <v>6332</v>
+      </c>
+    </row>
+    <row r="4670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4670" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4670" s="3" t="s">
+        <v>6333</v>
+      </c>
+    </row>
+    <row r="4671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4671" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4671" s="3" t="s">
+        <v>6334</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4672" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4672" s="3" t="s">
+        <v>6335</v>
+      </c>
+    </row>
+    <row r="4673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4673" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4673" s="3" t="s">
+        <v>6336</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4674" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4674" s="3" t="s">
+        <v>6337</v>
+      </c>
+    </row>
+    <row r="4675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4675" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4675" s="3" t="s">
+        <v>6338</v>
+      </c>
+    </row>
+    <row r="4676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4676" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4676" s="3" t="s">
+        <v>6339</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4677" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4677" s="3" t="s">
+        <v>6340</v>
+      </c>
+    </row>
+    <row r="4678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4678" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4678" s="3" t="s">
+        <v>6341</v>
+      </c>
+    </row>
+    <row r="4679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4679" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4679" s="3" t="s">
+        <v>6342</v>
+      </c>
+    </row>
+    <row r="4680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4680" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4680" s="3" t="s">
+        <v>6343</v>
+      </c>
+    </row>
+    <row r="4681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4681" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4681" s="3" t="s">
+        <v>6344</v>
+      </c>
+    </row>
+    <row r="4682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4682" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4682" s="3" t="s">
+        <v>6345</v>
+      </c>
+    </row>
+    <row r="4683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4683" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4683" s="3" t="s">
+        <v>6346</v>
+      </c>
+    </row>
+    <row r="4684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4684" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4684" s="3" t="s">
+        <v>6347</v>
+      </c>
+    </row>
+    <row r="4685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4685" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4685" s="3" t="s">
+        <v>6348</v>
+      </c>
+    </row>
+    <row r="4686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4686" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4686" s="3" t="s">
+        <v>6349</v>
+      </c>
+    </row>
+    <row r="4687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4687" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4687" s="3" t="s">
+        <v>6350</v>
+      </c>
+    </row>
+    <row r="4688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4688" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4688" s="3" t="s">
+        <v>6351</v>
+      </c>
+    </row>
+    <row r="4689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4689" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4689" s="3" t="s">
+        <v>6352</v>
+      </c>
+    </row>
+    <row r="4690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4690" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4690" s="3" t="s">
+        <v>6353</v>
+      </c>
+    </row>
+    <row r="4691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4691" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4691" s="3" t="s">
+        <v>6354</v>
+      </c>
+    </row>
+    <row r="4692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4692" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4692" s="3" t="s">
+        <v>6355</v>
+      </c>
+    </row>
+    <row r="4693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4693" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4693" s="3" t="s">
+        <v>6356</v>
+      </c>
+    </row>
+    <row r="4694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4694" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4694" s="3" t="s">
+        <v>6357</v>
+      </c>
+    </row>
+    <row r="4695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4695" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4695" s="3" t="s">
+        <v>6358</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4696" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4696" s="3" t="s">
+        <v>6359</v>
+      </c>
+    </row>
+    <row r="4697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4697" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4697" s="3" t="s">
+        <v>6360</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4698" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4698" s="3" t="s">
+        <v>6361</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4699" s="3">
+        <v>6500</v>
+      </c>
+      <c r="C4699" s="3" t="s">
+        <v>6362</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4700" s="4">
+        <v>6600</v>
+      </c>
+      <c r="C4700" s="3" t="s">
+        <v>6363</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4701" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4702" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4703" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4704" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4705" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4706" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4707" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4708" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4709" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4710" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4711" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4712" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4713" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4714" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4715" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4715" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4716" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4717" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4718" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4719" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4720" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4721" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4722" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4723" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4724" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4725" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4726" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4727" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4728" s="3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4729" s="3">
+        <v>6600</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044009D3-2554-4C91-BE32-A0E8038EEA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F28C4E-B91D-4692-B218-4A22838B976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6386" uniqueCount="6364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6486" uniqueCount="6464">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -25474,6 +25474,406 @@
   </si>
   <si>
     <t>microfossil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entomb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burgher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puffin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insoluble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reliability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unemployed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immobility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spacious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydrographic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portraiture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talented</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>filmmaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>understate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gannet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underswing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exorbitant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gondwanaland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gunpowper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wren</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kinglet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniformity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>screw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>priestess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neoclassical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thousandfold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enjoyment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forester</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoilage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonthreatening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tumble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harshness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collagen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surgeon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sumptuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synchrotron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landlord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>government-subsidized</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stringent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>signature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cabinetmaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervisory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resentment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purposely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irresponsibly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grapple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>haunt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revealingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obedience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rearrange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-disciplined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>armory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tuck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slippery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>courtship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleek</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corselet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secrecy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lira</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>livelihood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impediment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nurture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silhouette</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misinterpret</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marketable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mudstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carcass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subdivide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteoritic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offshoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inborn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storeotypical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifelike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bipedal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antiquate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chondritic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>painful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weldon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scorch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stonework</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -25876,7 +26276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4729"/>
+  <dimension ref="A1:N4813"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -67538,6 +67938,9 @@
       <c r="A4700" s="4">
         <v>6600</v>
       </c>
+      <c r="B4700" s="3" t="s">
+        <v>6375</v>
+      </c>
       <c r="C4700" s="3" t="s">
         <v>6363</v>
       </c>
@@ -67546,145 +67949,862 @@
       <c r="A4701" s="3">
         <v>6600</v>
       </c>
+      <c r="B4701" s="3" t="s">
+        <v>6376</v>
+      </c>
+      <c r="C4701" s="3" t="s">
+        <v>6364</v>
+      </c>
     </row>
     <row r="4702" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4702" s="3">
         <v>6600</v>
       </c>
+      <c r="B4702" s="3" t="s">
+        <v>6377</v>
+      </c>
+      <c r="C4702" s="3" t="s">
+        <v>6365</v>
+      </c>
     </row>
     <row r="4703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4703" s="3">
         <v>6600</v>
       </c>
+      <c r="B4703" s="3" t="s">
+        <v>6398</v>
+      </c>
+      <c r="C4703" s="3" t="s">
+        <v>6366</v>
+      </c>
     </row>
     <row r="4704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4704" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4705" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4704" s="3" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C4704" s="3" t="s">
+        <v>6367</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4705" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4706" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4705" s="3" t="s">
+        <v>6368</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4706" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4707" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4706" s="3" t="s">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4707" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4708" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4707" s="3" t="s">
+        <v>6370</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4708" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4709" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4708" s="3" t="s">
+        <v>6371</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4709" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4710" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4709" s="3" t="s">
+        <v>6372</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4710" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4711" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4710" s="3" t="s">
+        <v>6373</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4711" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4712" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4711" s="3" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4712" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4713" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4712" s="3" t="s">
+        <v>6378</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4713" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4714" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4713" s="3" t="s">
+        <v>6379</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4714" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4715" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4714" s="3" t="s">
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="4715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4715" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4716" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4715" s="3" t="s">
+        <v>6381</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4716" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4717" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4716" s="3" t="s">
+        <v>6382</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4717" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4718" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4717" s="3" t="s">
+        <v>6383</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4718" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4719" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4718" s="3" t="s">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4719" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4720" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4719" s="3" t="s">
+        <v>6385</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4720" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4721" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4720" s="3" t="s">
+        <v>6386</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4721" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4722" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4721" s="3" t="s">
+        <v>6387</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4722" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4723" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4722" s="3" t="s">
+        <v>6388</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4723" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4724" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4723" s="3" t="s">
+        <v>6389</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4724" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4725" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4724" s="3" t="s">
+        <v>6390</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4725" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4726" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4725" s="3" t="s">
+        <v>6391</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4726" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4727" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4726" s="3" t="s">
+        <v>6392</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4727" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4728" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4727" s="3" t="s">
+        <v>6393</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4728" s="3">
         <v>6600</v>
       </c>
-    </row>
-    <row r="4729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4728" s="3" t="s">
+        <v>6394</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4729" s="3">
         <v>6600</v>
+      </c>
+      <c r="C4729" s="3" t="s">
+        <v>6395</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4730" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4730" s="3" t="s">
+        <v>6396</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4731" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4731" s="3" t="s">
+        <v>6397</v>
+      </c>
+    </row>
+    <row r="4732" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4732" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4732" s="3" t="s">
+        <v>6399</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4733" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4733" s="3" t="s">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4734" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4734" s="3" t="s">
+        <v>6401</v>
+      </c>
+    </row>
+    <row r="4735" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4735" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4735" s="3" t="s">
+        <v>6402</v>
+      </c>
+    </row>
+    <row r="4736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4736" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4736" s="3" t="s">
+        <v>6403</v>
+      </c>
+    </row>
+    <row r="4737" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4737" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4737" s="3" t="s">
+        <v>6404</v>
+      </c>
+    </row>
+    <row r="4738" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4738" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4738" s="3" t="s">
+        <v>6405</v>
+      </c>
+    </row>
+    <row r="4739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4739" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4739" s="3" t="s">
+        <v>6406</v>
+      </c>
+    </row>
+    <row r="4740" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4740" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4740" s="3" t="s">
+        <v>6407</v>
+      </c>
+    </row>
+    <row r="4741" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4741" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4741" s="3" t="s">
+        <v>6408</v>
+      </c>
+    </row>
+    <row r="4742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4742" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4742" s="3" t="s">
+        <v>6409</v>
+      </c>
+    </row>
+    <row r="4743" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4743" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4743" s="3" t="s">
+        <v>6410</v>
+      </c>
+    </row>
+    <row r="4744" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4744" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4744" s="3" t="s">
+        <v>6411</v>
+      </c>
+    </row>
+    <row r="4745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4745" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4745" s="3" t="s">
+        <v>6412</v>
+      </c>
+    </row>
+    <row r="4746" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4746" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4746" s="3" t="s">
+        <v>6413</v>
+      </c>
+    </row>
+    <row r="4747" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4747" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4747" s="3" t="s">
+        <v>6414</v>
+      </c>
+    </row>
+    <row r="4748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4748" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4748" s="3" t="s">
+        <v>6415</v>
+      </c>
+    </row>
+    <row r="4749" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4749" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4749" s="3" t="s">
+        <v>6416</v>
+      </c>
+    </row>
+    <row r="4750" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4750" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4750" s="3" t="s">
+        <v>6417</v>
+      </c>
+    </row>
+    <row r="4751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4751" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4751" s="3" t="s">
+        <v>6418</v>
+      </c>
+    </row>
+    <row r="4752" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4752" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4752" s="3" t="s">
+        <v>6419</v>
+      </c>
+    </row>
+    <row r="4753" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4753" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4753" s="3" t="s">
+        <v>6420</v>
+      </c>
+    </row>
+    <row r="4754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4754" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4754" s="3" t="s">
+        <v>6421</v>
+      </c>
+    </row>
+    <row r="4755" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4755" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4755" s="3" t="s">
+        <v>6422</v>
+      </c>
+    </row>
+    <row r="4756" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4756" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4756" s="3" t="s">
+        <v>6423</v>
+      </c>
+    </row>
+    <row r="4757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4757" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4757" s="3" t="s">
+        <v>6424</v>
+      </c>
+    </row>
+    <row r="4758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4758" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4758" s="3" t="s">
+        <v>6425</v>
+      </c>
+    </row>
+    <row r="4759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4759" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4759" s="3" t="s">
+        <v>6426</v>
+      </c>
+    </row>
+    <row r="4760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4760" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4760" s="3" t="s">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="4761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4761" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4761" s="3" t="s">
+        <v>6428</v>
+      </c>
+    </row>
+    <row r="4762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4762" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4762" s="3" t="s">
+        <v>6429</v>
+      </c>
+    </row>
+    <row r="4763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4763" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4763" s="3" t="s">
+        <v>6430</v>
+      </c>
+    </row>
+    <row r="4764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4764" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4764" s="3" t="s">
+        <v>6431</v>
+      </c>
+    </row>
+    <row r="4765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4765" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4765" s="3" t="s">
+        <v>6432</v>
+      </c>
+    </row>
+    <row r="4766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4766" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4766" s="3" t="s">
+        <v>6433</v>
+      </c>
+    </row>
+    <row r="4767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4767" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4767" s="3" t="s">
+        <v>6434</v>
+      </c>
+    </row>
+    <row r="4768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4768" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4768" s="3" t="s">
+        <v>6435</v>
+      </c>
+    </row>
+    <row r="4769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4769" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4769" s="3" t="s">
+        <v>6436</v>
+      </c>
+    </row>
+    <row r="4770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4770" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4770" s="3" t="s">
+        <v>6437</v>
+      </c>
+    </row>
+    <row r="4771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4771" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4771" s="3" t="s">
+        <v>6438</v>
+      </c>
+    </row>
+    <row r="4772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4772" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4772" s="3" t="s">
+        <v>6439</v>
+      </c>
+    </row>
+    <row r="4773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4773" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4773" s="3" t="s">
+        <v>6440</v>
+      </c>
+    </row>
+    <row r="4774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4774" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4774" s="3" t="s">
+        <v>6441</v>
+      </c>
+    </row>
+    <row r="4775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4775" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4775" s="3" t="s">
+        <v>6442</v>
+      </c>
+    </row>
+    <row r="4776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4776" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4776" s="3" t="s">
+        <v>6443</v>
+      </c>
+    </row>
+    <row r="4777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4777" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4777" s="3" t="s">
+        <v>6444</v>
+      </c>
+    </row>
+    <row r="4778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4778" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4778" s="3" t="s">
+        <v>6445</v>
+      </c>
+    </row>
+    <row r="4779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4779" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4779" s="3" t="s">
+        <v>6446</v>
+      </c>
+    </row>
+    <row r="4780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4780" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4780" s="3" t="s">
+        <v>6447</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4781" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4781" s="3" t="s">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="4782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4782" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4782" s="3" t="s">
+        <v>6449</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4783" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4783" s="3" t="s">
+        <v>6450</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4784" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4784" s="3" t="s">
+        <v>6451</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4785" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4785" s="3" t="s">
+        <v>6452</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4786" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4786" s="3" t="s">
+        <v>6453</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4787" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4787" s="3" t="s">
+        <v>6454</v>
+      </c>
+    </row>
+    <row r="4788" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4788" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4788" s="3" t="s">
+        <v>6455</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4789" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4789" s="3" t="s">
+        <v>6456</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4790" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4790" s="3" t="s">
+        <v>6457</v>
+      </c>
+    </row>
+    <row r="4791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4791" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4791" s="3" t="s">
+        <v>6458</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4792" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4792" s="3" t="s">
+        <v>6459</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4793" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4793" s="3" t="s">
+        <v>6461</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4794" s="3">
+        <v>6600</v>
+      </c>
+      <c r="C4794" s="3" t="s">
+        <v>6462</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4795" s="4">
+        <v>6700</v>
+      </c>
+      <c r="C4795" s="3" t="s">
+        <v>6463</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4796" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4797" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4798" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4799" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4800" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4801" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4802" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4803" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4804" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4805" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4806" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4807" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4808" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4809" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4810" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4811" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4812" s="3">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4813" s="3">
+        <v>6700</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F28C4E-B91D-4692-B218-4A22838B976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57520AE4-A41D-431E-ADA8-8142E9BD45E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6486" uniqueCount="6464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="6564">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -25874,6 +25874,406 @@
   </si>
   <si>
     <t>stonework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shipwreck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unanswered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misfortune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mantel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desalination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydraulic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reappear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elegance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horsepower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quiver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eternal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duchenne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reopen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immutable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permeability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterwards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consolidation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterfowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>efficacious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fanwise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>riverbed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>destine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expertly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stipulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sandbar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contingent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>congenial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faucet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alienate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-regulated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implicit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preponderance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imperfect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeotherm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>envy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jewel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>practicality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pictorial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mortal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unschooled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burgeon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ashcan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>literalness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flyspeck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rennin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hormonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angiotensin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprivation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aldosterone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-taught</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mandate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>henceforth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mammalian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfairly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irrelevant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burdensome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confederate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pardon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authorization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gymnastic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peacetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>readjust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pre-modern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rivalry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steam-powered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-preserved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nobility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ponderous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thresher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cohesion-tension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utensil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intentional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrifty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enactment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proclaim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seafood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>besiege</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsubstantiated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-binding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unaware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>semimolten</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -26276,7 +26676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4813"/>
+  <dimension ref="A1:N4933"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -68713,6 +69113,9 @@
       <c r="A4795" s="4">
         <v>6700</v>
       </c>
+      <c r="B4795" s="3" t="s">
+        <v>6465</v>
+      </c>
       <c r="C4795" s="3" t="s">
         <v>6463</v>
       </c>
@@ -68721,90 +69124,987 @@
       <c r="A4796" s="3">
         <v>6700</v>
       </c>
+      <c r="B4796" s="3" t="s">
+        <v>6466</v>
+      </c>
+      <c r="C4796" s="3" t="s">
+        <v>6464</v>
+      </c>
     </row>
     <row r="4797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4797" s="3">
         <v>6700</v>
       </c>
+      <c r="B4797" s="3" t="s">
+        <v>6481</v>
+      </c>
+      <c r="C4797" s="3" t="s">
+        <v>6467</v>
+      </c>
     </row>
     <row r="4798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4798" s="3">
         <v>6700</v>
       </c>
+      <c r="B4798" s="3" t="s">
+        <v>6484</v>
+      </c>
+      <c r="C4798" s="3" t="s">
+        <v>6468</v>
+      </c>
     </row>
     <row r="4799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4799" s="3">
         <v>6700</v>
       </c>
+      <c r="B4799" s="3" t="s">
+        <v>6494</v>
+      </c>
+      <c r="C4799" s="3" t="s">
+        <v>6469</v>
+      </c>
     </row>
     <row r="4800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4800" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4801" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4800" s="3" t="s">
+        <v>6517</v>
+      </c>
+      <c r="C4800" s="3" t="s">
+        <v>6470</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4801" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4802" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4801" s="3" t="s">
+        <v>6531</v>
+      </c>
+      <c r="C4801" s="3" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4802" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4803" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4802" s="3" t="s">
+        <v>6541</v>
+      </c>
+      <c r="C4802" s="3" t="s">
+        <v>6472</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4803" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4804" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4803" s="3" t="s">
+        <v>6473</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4804" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4805" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4804" s="3" t="s">
+        <v>6474</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4805" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4806" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4805" s="3" t="s">
+        <v>6475</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4806" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4807" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4806" s="3" t="s">
+        <v>6476</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4807" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4808" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4807" s="3" t="s">
+        <v>6477</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4808" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4809" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4808" s="3" t="s">
+        <v>6478</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4809" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4810" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4809" s="3" t="s">
+        <v>6479</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4810" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4811" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4810" s="3" t="s">
+        <v>6480</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4811" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4812" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4811" s="3" t="s">
+        <v>6482</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4812" s="3">
         <v>6700</v>
       </c>
-    </row>
-    <row r="4813" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4812" s="3" t="s">
+        <v>6483</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4813" s="3">
         <v>6700</v>
+      </c>
+      <c r="C4813" s="3" t="s">
+        <v>6485</v>
+      </c>
+    </row>
+    <row r="4814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4814" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4814" s="3" t="s">
+        <v>6486</v>
+      </c>
+    </row>
+    <row r="4815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4815" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4815" s="3" t="s">
+        <v>6487</v>
+      </c>
+    </row>
+    <row r="4816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4816" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4816" s="3" t="s">
+        <v>6488</v>
+      </c>
+    </row>
+    <row r="4817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4817" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4817" s="3" t="s">
+        <v>6489</v>
+      </c>
+    </row>
+    <row r="4818" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4818" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4818" s="3" t="s">
+        <v>6490</v>
+      </c>
+    </row>
+    <row r="4819" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4819" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4819" s="3" t="s">
+        <v>6491</v>
+      </c>
+    </row>
+    <row r="4820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4820" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4820" s="3" t="s">
+        <v>6492</v>
+      </c>
+    </row>
+    <row r="4821" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4821" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4821" s="3" t="s">
+        <v>6493</v>
+      </c>
+    </row>
+    <row r="4822" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4822" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4822" s="3" t="s">
+        <v>6495</v>
+      </c>
+    </row>
+    <row r="4823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4823" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4823" s="3" t="s">
+        <v>6496</v>
+      </c>
+    </row>
+    <row r="4824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4824" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4824" s="3" t="s">
+        <v>6497</v>
+      </c>
+    </row>
+    <row r="4825" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4825" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4825" s="3" t="s">
+        <v>6498</v>
+      </c>
+    </row>
+    <row r="4826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4826" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4826" s="3" t="s">
+        <v>6499</v>
+      </c>
+    </row>
+    <row r="4827" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4827" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4827" s="3" t="s">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4828" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4828" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4828" s="3" t="s">
+        <v>6501</v>
+      </c>
+    </row>
+    <row r="4829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4829" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4829" s="3" t="s">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="4830" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4830" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4830" s="3" t="s">
+        <v>6503</v>
+      </c>
+    </row>
+    <row r="4831" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4831" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4831" s="3" t="s">
+        <v>6504</v>
+      </c>
+    </row>
+    <row r="4832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4832" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4832" s="3" t="s">
+        <v>6505</v>
+      </c>
+    </row>
+    <row r="4833" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4833" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4833" s="3" t="s">
+        <v>6506</v>
+      </c>
+    </row>
+    <row r="4834" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4834" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4834" s="3" t="s">
+        <v>6507</v>
+      </c>
+    </row>
+    <row r="4835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4835" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4835" s="3" t="s">
+        <v>6508</v>
+      </c>
+    </row>
+    <row r="4836" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4836" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4836" s="3" t="s">
+        <v>6509</v>
+      </c>
+    </row>
+    <row r="4837" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4837" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4837" s="3" t="s">
+        <v>6510</v>
+      </c>
+    </row>
+    <row r="4838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4838" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4838" s="3" t="s">
+        <v>6511</v>
+      </c>
+    </row>
+    <row r="4839" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4839" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4839" s="3" t="s">
+        <v>6512</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4840" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4840" s="3" t="s">
+        <v>6513</v>
+      </c>
+    </row>
+    <row r="4841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4841" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4841" s="3" t="s">
+        <v>6514</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4842" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4842" s="3" t="s">
+        <v>6515</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4843" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4843" s="3" t="s">
+        <v>6516</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4844" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4844" s="3" t="s">
+        <v>6518</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4845" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4845" s="3" t="s">
+        <v>6519</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4846" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4846" s="3" t="s">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4847" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4847" s="3" t="s">
+        <v>6521</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4848" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4848" s="3" t="s">
+        <v>6522</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4849" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4849" s="3" t="s">
+        <v>6523</v>
+      </c>
+    </row>
+    <row r="4850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4850" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4850" s="3" t="s">
+        <v>6524</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4851" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4851" s="3" t="s">
+        <v>6525</v>
+      </c>
+    </row>
+    <row r="4852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4852" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4852" s="3" t="s">
+        <v>6526</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4853" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4853" s="3" t="s">
+        <v>6527</v>
+      </c>
+    </row>
+    <row r="4854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4854" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4854" s="3" t="s">
+        <v>6528</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4855" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4855" s="3" t="s">
+        <v>6529</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4856" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4856" s="3" t="s">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="4857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4857" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4857" s="3" t="s">
+        <v>6532</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4858" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4858" s="3" t="s">
+        <v>6533</v>
+      </c>
+    </row>
+    <row r="4859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4859" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4859" s="3" t="s">
+        <v>6534</v>
+      </c>
+    </row>
+    <row r="4860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4860" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4860" s="3" t="s">
+        <v>6535</v>
+      </c>
+    </row>
+    <row r="4861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4861" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4861" s="3" t="s">
+        <v>6536</v>
+      </c>
+    </row>
+    <row r="4862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4862" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4862" s="3" t="s">
+        <v>6537</v>
+      </c>
+    </row>
+    <row r="4863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4863" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4863" s="3" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="4864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4864" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4864" s="3" t="s">
+        <v>6539</v>
+      </c>
+    </row>
+    <row r="4865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4865" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4865" s="3" t="s">
+        <v>6540</v>
+      </c>
+    </row>
+    <row r="4866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4866" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4866" s="3" t="s">
+        <v>6542</v>
+      </c>
+    </row>
+    <row r="4867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4867" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4867" s="3" t="s">
+        <v>6543</v>
+      </c>
+    </row>
+    <row r="4868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4868" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4868" s="3" t="s">
+        <v>6544</v>
+      </c>
+    </row>
+    <row r="4869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4869" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4869" s="3" t="s">
+        <v>6545</v>
+      </c>
+    </row>
+    <row r="4870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4870" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4870" s="3" t="s">
+        <v>6546</v>
+      </c>
+    </row>
+    <row r="4871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4871" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4871" s="3" t="s">
+        <v>6547</v>
+      </c>
+    </row>
+    <row r="4872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4872" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4872" s="3" t="s">
+        <v>6548</v>
+      </c>
+    </row>
+    <row r="4873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4873" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4873" s="3" t="s">
+        <v>6549</v>
+      </c>
+    </row>
+    <row r="4874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4874" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4874" s="3" t="s">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="4875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4875" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4875" s="3" t="s">
+        <v>6551</v>
+      </c>
+    </row>
+    <row r="4876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4876" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4876" s="3" t="s">
+        <v>6552</v>
+      </c>
+    </row>
+    <row r="4877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4877" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4877" s="3" t="s">
+        <v>6553</v>
+      </c>
+    </row>
+    <row r="4878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4878" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4878" s="3" t="s">
+        <v>6554</v>
+      </c>
+    </row>
+    <row r="4879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4879" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4879" s="3" t="s">
+        <v>6555</v>
+      </c>
+    </row>
+    <row r="4880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4880" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4880" s="3" t="s">
+        <v>6556</v>
+      </c>
+    </row>
+    <row r="4881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4881" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4881" s="3" t="s">
+        <v>6557</v>
+      </c>
+    </row>
+    <row r="4882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4882" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4882" s="3" t="s">
+        <v>6558</v>
+      </c>
+    </row>
+    <row r="4883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4883" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4883" s="3" t="s">
+        <v>6559</v>
+      </c>
+    </row>
+    <row r="4884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4884" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4884" s="3" t="s">
+        <v>6560</v>
+      </c>
+    </row>
+    <row r="4885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4885" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4885" s="3" t="s">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="4886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4886" s="3">
+        <v>6700</v>
+      </c>
+      <c r="C4886" s="3" t="s">
+        <v>6562</v>
+      </c>
+    </row>
+    <row r="4887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4887" s="4">
+        <v>6800</v>
+      </c>
+      <c r="C4887" s="3" t="s">
+        <v>6563</v>
+      </c>
+    </row>
+    <row r="4888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4888" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4889" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4890" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4891" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4892" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4893" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4894" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4895" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4896" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4897" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4897" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4898" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4898" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4899" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4900" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4900" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4901" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4902" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4903" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4904" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4905" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4906" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4907" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4908" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4909" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4909" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4910" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4911" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4912" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4913" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4914" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4915" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4915" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4916" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4917" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4918" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4919" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4920" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4920" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4921" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4922" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4922" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4923" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4923" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4924" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4924" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4925" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4925" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4926" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4926" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4927" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4927" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4928" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4928" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4929" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4929" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4930" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4930" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4931" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4931" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4932" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4932" s="3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4933" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4933" s="3">
+        <v>6800</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57520AE4-A41D-431E-ADA8-8142E9BD45E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB02B9F-B347-43E3-8881-ED10D023FF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="6564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6687" uniqueCount="6664">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -26274,6 +26274,406 @@
   </si>
   <si>
     <t>semimolten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incinerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>topographical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>festival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canyon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>falconer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lien</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prejudice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>starfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extraordinarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dismember</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twenty-odd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unquestionably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phylum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spinet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supremacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rumor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passageway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gothic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bluff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>versatility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tonal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pedal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inconvenient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contributor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overcultivation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penetration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtrcat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hearth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saguaro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transcend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taproot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distributor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>signify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seminar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flavor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissatisfy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adequacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninteresting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minstrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irreversible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phosphate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apiece</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distinctly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deteriorate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stretcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hoof</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discolor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foreleg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buckskin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buckle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chafe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tourniquet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bandanna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vestigial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonfunctional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>land-dwelling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>computer-assisted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monroe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flesh-eating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concede</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jawbone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Irap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grande</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>facelift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>donation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>massif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atlas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wireless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sterilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reenter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bowl-shaped</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>satisfaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rappoet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elevate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gripe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gossip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attendance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>socialization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Irish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eyewitness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conglomerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gang</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -26676,7 +27076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4933"/>
+  <dimension ref="A1:N4990"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -69873,6 +70273,9 @@
       <c r="A4887" s="4">
         <v>6800</v>
       </c>
+      <c r="B4887" s="3" t="s">
+        <v>6566</v>
+      </c>
       <c r="C4887" s="3" t="s">
         <v>6563</v>
       </c>
@@ -69881,230 +70284,815 @@
       <c r="A4888" s="3">
         <v>6800</v>
       </c>
+      <c r="B4888" s="3" t="s">
+        <v>6604</v>
+      </c>
+      <c r="C4888" s="3" t="s">
+        <v>6564</v>
+      </c>
     </row>
     <row r="4889" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4889" s="3">
         <v>6800</v>
       </c>
+      <c r="B4889" s="3" t="s">
+        <v>6611</v>
+      </c>
+      <c r="C4889" s="3" t="s">
+        <v>6565</v>
+      </c>
     </row>
     <row r="4890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4890" s="3">
         <v>6800</v>
       </c>
+      <c r="B4890" s="3" t="s">
+        <v>6646</v>
+      </c>
+      <c r="C4890" s="3" t="s">
+        <v>6567</v>
+      </c>
     </row>
     <row r="4891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4891" s="3">
         <v>6800</v>
       </c>
+      <c r="B4891" s="3" t="s">
+        <v>6650</v>
+      </c>
+      <c r="C4891" s="3" t="s">
+        <v>6568</v>
+      </c>
     </row>
     <row r="4892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4892" s="3">
         <v>6800</v>
       </c>
+      <c r="B4892" s="3" t="s">
+        <v>6658</v>
+      </c>
+      <c r="C4892" s="3" t="s">
+        <v>6569</v>
+      </c>
     </row>
     <row r="4893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4893" s="3">
         <v>6800</v>
       </c>
+      <c r="C4893" s="3" t="s">
+        <v>6570</v>
+      </c>
     </row>
     <row r="4894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4894" s="3">
         <v>6800</v>
       </c>
+      <c r="C4894" s="3" t="s">
+        <v>6571</v>
+      </c>
     </row>
     <row r="4895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4895" s="3">
         <v>6800</v>
       </c>
+      <c r="C4895" s="3" t="s">
+        <v>6572</v>
+      </c>
     </row>
     <row r="4896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4896" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4897" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4896" s="3" t="s">
+        <v>6573</v>
+      </c>
+    </row>
+    <row r="4897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4897" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4898" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4897" s="3" t="s">
+        <v>6574</v>
+      </c>
+    </row>
+    <row r="4898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4898" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4899" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4898" s="3" t="s">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4899" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4900" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4899" s="3" t="s">
+        <v>6576</v>
+      </c>
+    </row>
+    <row r="4900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4900" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4901" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4900" s="3" t="s">
+        <v>6577</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4901" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4902" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4901" s="3" t="s">
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4902" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4903" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4902" s="3" t="s">
+        <v>6579</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4903" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4904" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4903" s="3" t="s">
+        <v>6580</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4904" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4905" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4904" s="3" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4905" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4906" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4905" s="3" t="s">
+        <v>6581</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4906" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4907" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4906" s="3" t="s">
+        <v>6582</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4907" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4908" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4907" s="3" t="s">
+        <v>6583</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4908" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4909" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4908" s="3" t="s">
+        <v>6584</v>
+      </c>
+    </row>
+    <row r="4909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4909" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4910" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4909" s="3" t="s">
+        <v>6585</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4910" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4911" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4910" s="3" t="s">
+        <v>6586</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4911" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4912" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4911" s="3" t="s">
+        <v>6587</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4912" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4913" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4912" s="3" t="s">
+        <v>6588</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4913" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4914" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4913" s="3" t="s">
+        <v>6589</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4914" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4915" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4914" s="3" t="s">
+        <v>6590</v>
+      </c>
+    </row>
+    <row r="4915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4915" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4916" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4915" s="3" t="s">
+        <v>6591</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4916" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4917" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4916" s="3" t="s">
+        <v>6592</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4917" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4918" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4917" s="3" t="s">
+        <v>6593</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4918" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4919" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4918" s="3" t="s">
+        <v>6594</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4919" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4920" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4919" s="3" t="s">
+        <v>6595</v>
+      </c>
+    </row>
+    <row r="4920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4920" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4921" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4920" s="3" t="s">
+        <v>6596</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4921" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4922" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4921" s="3" t="s">
+        <v>6597</v>
+      </c>
+    </row>
+    <row r="4922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4922" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4923" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4922" s="3" t="s">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="4923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4923" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4924" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4923" s="3" t="s">
+        <v>6599</v>
+      </c>
+    </row>
+    <row r="4924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4924" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4925" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4924" s="3" t="s">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4925" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4926" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4925" s="3" t="s">
+        <v>6601</v>
+      </c>
+    </row>
+    <row r="4926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4926" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4927" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4926" s="3" t="s">
+        <v>6602</v>
+      </c>
+    </row>
+    <row r="4927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4927" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4928" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4927" s="3" t="s">
+        <v>6603</v>
+      </c>
+    </row>
+    <row r="4928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4928" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4929" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4928" s="3" t="s">
+        <v>6605</v>
+      </c>
+    </row>
+    <row r="4929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4929" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4930" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4929" s="3" t="s">
+        <v>6606</v>
+      </c>
+    </row>
+    <row r="4930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4930" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4931" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4930" s="3" t="s">
+        <v>6607</v>
+      </c>
+    </row>
+    <row r="4931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4931" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4932" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4931" s="3" t="s">
+        <v>6608</v>
+      </c>
+    </row>
+    <row r="4932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4932" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="4933" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C4932" s="3" t="s">
+        <v>6609</v>
+      </c>
+    </row>
+    <row r="4933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4933" s="3">
         <v>6800</v>
+      </c>
+      <c r="C4933" s="3" t="s">
+        <v>6610</v>
+      </c>
+    </row>
+    <row r="4934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4934" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4934" s="3" t="s">
+        <v>6612</v>
+      </c>
+    </row>
+    <row r="4935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4935" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4935" s="3" t="s">
+        <v>6613</v>
+      </c>
+    </row>
+    <row r="4936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4936" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4936" s="3" t="s">
+        <v>6614</v>
+      </c>
+    </row>
+    <row r="4937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4937" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4937" s="3" t="s">
+        <v>6615</v>
+      </c>
+    </row>
+    <row r="4938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4938" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4938" s="3" t="s">
+        <v>6616</v>
+      </c>
+    </row>
+    <row r="4939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4939" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4939" s="3" t="s">
+        <v>6617</v>
+      </c>
+    </row>
+    <row r="4940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4940" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4940" s="3" t="s">
+        <v>6618</v>
+      </c>
+    </row>
+    <row r="4941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4941" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4941" s="3" t="s">
+        <v>6619</v>
+      </c>
+    </row>
+    <row r="4942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4942" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4942" s="3" t="s">
+        <v>6620</v>
+      </c>
+    </row>
+    <row r="4943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4943" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4943" s="3" t="s">
+        <v>6621</v>
+      </c>
+    </row>
+    <row r="4944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4944" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4944" s="3" t="s">
+        <v>6622</v>
+      </c>
+    </row>
+    <row r="4945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4945" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4945" s="3" t="s">
+        <v>6623</v>
+      </c>
+    </row>
+    <row r="4946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4946" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4946" s="3" t="s">
+        <v>6624</v>
+      </c>
+    </row>
+    <row r="4947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4947" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4947" s="3" t="s">
+        <v>6625</v>
+      </c>
+    </row>
+    <row r="4948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4948" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4948" s="3" t="s">
+        <v>6626</v>
+      </c>
+    </row>
+    <row r="4949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4949" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4949" s="3" t="s">
+        <v>6627</v>
+      </c>
+    </row>
+    <row r="4950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4950" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4950" s="3" t="s">
+        <v>6628</v>
+      </c>
+    </row>
+    <row r="4951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4951" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4951" s="3" t="s">
+        <v>6629</v>
+      </c>
+    </row>
+    <row r="4952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4952" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4952" s="3" t="s">
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="4953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4953" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4953" s="3" t="s">
+        <v>6631</v>
+      </c>
+    </row>
+    <row r="4954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4954" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4954" s="3" t="s">
+        <v>6632</v>
+      </c>
+    </row>
+    <row r="4955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4955" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4955" s="3" t="s">
+        <v>6633</v>
+      </c>
+    </row>
+    <row r="4956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4956" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4956" s="3" t="s">
+        <v>6634</v>
+      </c>
+    </row>
+    <row r="4957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4957" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4957" s="3" t="s">
+        <v>6635</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4958" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4958" s="3" t="s">
+        <v>6636</v>
+      </c>
+    </row>
+    <row r="4959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4959" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4959" s="3" t="s">
+        <v>6637</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4960" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4960" s="3" t="s">
+        <v>6638</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4961" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4961" s="3" t="s">
+        <v>6639</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4962" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4962" s="3" t="s">
+        <v>6640</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4963" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4963" s="3" t="s">
+        <v>6641</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4964" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4964" s="3" t="s">
+        <v>6642</v>
+      </c>
+    </row>
+    <row r="4965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4965" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4965" s="3" t="s">
+        <v>6643</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4966" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4966" s="3" t="s">
+        <v>6644</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4967" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4967" s="3" t="s">
+        <v>6645</v>
+      </c>
+    </row>
+    <row r="4968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4968" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4968" s="3" t="s">
+        <v>6647</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4969" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4969" s="3" t="s">
+        <v>6648</v>
+      </c>
+    </row>
+    <row r="4970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4970" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4970" s="3" t="s">
+        <v>6649</v>
+      </c>
+    </row>
+    <row r="4971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4971" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4971" s="3" t="s">
+        <v>6651</v>
+      </c>
+    </row>
+    <row r="4972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4972" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4972" s="3" t="s">
+        <v>6652</v>
+      </c>
+    </row>
+    <row r="4973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4973" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4973" s="3" t="s">
+        <v>6653</v>
+      </c>
+    </row>
+    <row r="4974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4974" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4974" s="3" t="s">
+        <v>6654</v>
+      </c>
+    </row>
+    <row r="4975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4975" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4975" s="3" t="s">
+        <v>6655</v>
+      </c>
+    </row>
+    <row r="4976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4976" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4976" s="3" t="s">
+        <v>6656</v>
+      </c>
+    </row>
+    <row r="4977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4977" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4977" s="3" t="s">
+        <v>6657</v>
+      </c>
+    </row>
+    <row r="4978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4978" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4978" s="3" t="s">
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="4979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4979" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4979" s="3" t="s">
+        <v>6660</v>
+      </c>
+    </row>
+    <row r="4980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4980" s="3">
+        <v>6800</v>
+      </c>
+      <c r="C4980" s="3" t="s">
+        <v>6661</v>
+      </c>
+    </row>
+    <row r="4981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4981" s="4">
+        <v>6900</v>
+      </c>
+      <c r="C4981" s="3" t="s">
+        <v>6662</v>
+      </c>
+    </row>
+    <row r="4982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4982" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4982" s="3" t="s">
+        <v>6663</v>
+      </c>
+    </row>
+    <row r="4983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4983" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4984" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4985" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4986" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4987" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4988" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4989" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="4990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4990" s="3">
+        <v>6900</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB02B9F-B347-43E3-8881-ED10D023FF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF566032-315D-4DD7-9A26-42963E7AECE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6687" uniqueCount="6664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6787" uniqueCount="6764">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -26674,6 +26674,406 @@
   </si>
   <si>
     <t>gang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>punch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>railhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preferential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cerebral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kenya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alphabet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleanly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unresolved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>non-western</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhilarate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choreography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>teem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scarcity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>premiere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>screening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exemplary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Austrian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watershed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>periodization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homemaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chronicle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sustenance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tremendously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perceptive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>painstaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ill-equipped</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reflectivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dishabituate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roughness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>responsiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>partition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutrality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alkaline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ballad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conflate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cardboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catechism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rewrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterbalance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creditor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regionalization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescopic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crayfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geophysical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ample</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synchronize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluffy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>militarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clause</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enforcer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ostracize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extracurricular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>habitual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chronobiology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thinker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>songwriter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spotlight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earth-based</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inducement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overgeneralize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keplerian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grinder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Galilean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>align</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diffusely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caucasian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crescent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dodge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surrender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impatient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gosple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thirst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ductless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ridicule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admiration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recreate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncritical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resonator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jewett</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chaotic</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -27076,7 +27476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N4990"/>
+  <dimension ref="A1:N5093"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -71043,6 +71443,9 @@
       <c r="A4981" s="4">
         <v>6900</v>
       </c>
+      <c r="B4981" s="3" t="s">
+        <v>6671</v>
+      </c>
       <c r="C4981" s="3" t="s">
         <v>6662</v>
       </c>
@@ -71051,6 +71454,9 @@
       <c r="A4982" s="3">
         <v>6900</v>
       </c>
+      <c r="B4982" s="3" t="s">
+        <v>6674</v>
+      </c>
       <c r="C4982" s="3" t="s">
         <v>6663</v>
       </c>
@@ -71059,40 +71465,849 @@
       <c r="A4983" s="3">
         <v>6900</v>
       </c>
+      <c r="B4983" s="3" t="s">
+        <v>6679</v>
+      </c>
+      <c r="C4983" s="3" t="s">
+        <v>6664</v>
+      </c>
     </row>
     <row r="4984" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4984" s="3">
         <v>6900</v>
       </c>
+      <c r="B4984" s="3" t="s">
+        <v>6687</v>
+      </c>
+      <c r="C4984" s="3" t="s">
+        <v>6665</v>
+      </c>
     </row>
     <row r="4985" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4985" s="3">
         <v>6900</v>
       </c>
+      <c r="B4985" s="3" t="s">
+        <v>6693</v>
+      </c>
+      <c r="C4985" s="3" t="s">
+        <v>6666</v>
+      </c>
     </row>
     <row r="4986" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4986" s="3">
         <v>6900</v>
       </c>
+      <c r="B4986" s="3" t="s">
+        <v>6697</v>
+      </c>
+      <c r="C4986" s="3" t="s">
+        <v>6667</v>
+      </c>
     </row>
     <row r="4987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4987" s="3">
         <v>6900</v>
       </c>
+      <c r="B4987" s="3" t="s">
+        <v>6714</v>
+      </c>
+      <c r="C4987" s="3" t="s">
+        <v>6668</v>
+      </c>
     </row>
     <row r="4988" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4988" s="3">
         <v>6900</v>
       </c>
+      <c r="B4988" s="3" t="s">
+        <v>6733</v>
+      </c>
+      <c r="C4988" s="3" t="s">
+        <v>6669</v>
+      </c>
     </row>
     <row r="4989" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4989" s="3">
         <v>6900</v>
       </c>
+      <c r="B4989" s="3" t="s">
+        <v>6734</v>
+      </c>
+      <c r="C4989" s="3" t="s">
+        <v>6670</v>
+      </c>
     </row>
     <row r="4990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4990" s="3">
         <v>6900</v>
+      </c>
+      <c r="C4990" s="3" t="s">
+        <v>6672</v>
+      </c>
+    </row>
+    <row r="4991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4991" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4991" s="3" t="s">
+        <v>6673</v>
+      </c>
+    </row>
+    <row r="4992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4992" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4992" s="3" t="s">
+        <v>6675</v>
+      </c>
+    </row>
+    <row r="4993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4993" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4993" s="3" t="s">
+        <v>6676</v>
+      </c>
+    </row>
+    <row r="4994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4994" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4994" s="3" t="s">
+        <v>6677</v>
+      </c>
+    </row>
+    <row r="4995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4995" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4995" s="3" t="s">
+        <v>6678</v>
+      </c>
+    </row>
+    <row r="4996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4996" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4996" s="3" t="s">
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="4997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4997" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4997" s="3" t="s">
+        <v>6681</v>
+      </c>
+    </row>
+    <row r="4998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4998" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4998" s="3" t="s">
+        <v>6682</v>
+      </c>
+    </row>
+    <row r="4999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4999" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C4999" s="3" t="s">
+        <v>6683</v>
+      </c>
+    </row>
+    <row r="5000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5000" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5000" s="3" t="s">
+        <v>6684</v>
+      </c>
+    </row>
+    <row r="5001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5001" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5001" s="3" t="s">
+        <v>6685</v>
+      </c>
+    </row>
+    <row r="5002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5002" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5002" s="3" t="s">
+        <v>6686</v>
+      </c>
+    </row>
+    <row r="5003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5003" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5003" s="3" t="s">
+        <v>6688</v>
+      </c>
+    </row>
+    <row r="5004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5004" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5004" s="3" t="s">
+        <v>6689</v>
+      </c>
+    </row>
+    <row r="5005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5005" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5005" s="3" t="s">
+        <v>6690</v>
+      </c>
+    </row>
+    <row r="5006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5006" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5006" s="3" t="s">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="5007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5007" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5007" s="3" t="s">
+        <v>6692</v>
+      </c>
+    </row>
+    <row r="5008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5008" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5008" s="3" t="s">
+        <v>6694</v>
+      </c>
+    </row>
+    <row r="5009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5009" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5009" s="3" t="s">
+        <v>6695</v>
+      </c>
+    </row>
+    <row r="5010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5010" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5010" s="3" t="s">
+        <v>6696</v>
+      </c>
+    </row>
+    <row r="5011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5011" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5011" s="3" t="s">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="5012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5012" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5012" s="3" t="s">
+        <v>6699</v>
+      </c>
+    </row>
+    <row r="5013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5013" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5013" s="3" t="s">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="5014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5014" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5014" s="3" t="s">
+        <v>6701</v>
+      </c>
+    </row>
+    <row r="5015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5015" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5015" s="3" t="s">
+        <v>6702</v>
+      </c>
+    </row>
+    <row r="5016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5016" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5016" s="3" t="s">
+        <v>6703</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5017" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5017" s="3" t="s">
+        <v>6704</v>
+      </c>
+    </row>
+    <row r="5018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5018" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5018" s="3" t="s">
+        <v>6705</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5019" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5019" s="3" t="s">
+        <v>6706</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5020" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5020" s="3" t="s">
+        <v>6707</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5021" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5021" s="3" t="s">
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="5022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5022" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5022" s="3" t="s">
+        <v>6709</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5023" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5023" s="3" t="s">
+        <v>6710</v>
+      </c>
+    </row>
+    <row r="5024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5024" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5024" s="3" t="s">
+        <v>6711</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5025" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5025" s="3" t="s">
+        <v>6712</v>
+      </c>
+    </row>
+    <row r="5026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5026" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5026" s="3" t="s">
+        <v>6713</v>
+      </c>
+    </row>
+    <row r="5027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5027" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5027" s="3" t="s">
+        <v>6715</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5028" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5028" s="3" t="s">
+        <v>6716</v>
+      </c>
+    </row>
+    <row r="5029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5029" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5029" s="3" t="s">
+        <v>6717</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5030" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5030" s="3" t="s">
+        <v>6718</v>
+      </c>
+    </row>
+    <row r="5031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5031" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5031" s="3" t="s">
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="5032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5032" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5032" s="3" t="s">
+        <v>6720</v>
+      </c>
+    </row>
+    <row r="5033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5033" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5033" s="3" t="s">
+        <v>6721</v>
+      </c>
+    </row>
+    <row r="5034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5034" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5034" s="3" t="s">
+        <v>6722</v>
+      </c>
+    </row>
+    <row r="5035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5035" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5035" s="3" t="s">
+        <v>6723</v>
+      </c>
+    </row>
+    <row r="5036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5036" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5036" s="3" t="s">
+        <v>6724</v>
+      </c>
+    </row>
+    <row r="5037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5037" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5037" s="3" t="s">
+        <v>6725</v>
+      </c>
+    </row>
+    <row r="5038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5038" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5038" s="3" t="s">
+        <v>6726</v>
+      </c>
+    </row>
+    <row r="5039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5039" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5039" s="3" t="s">
+        <v>6727</v>
+      </c>
+    </row>
+    <row r="5040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5040" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5040" s="3" t="s">
+        <v>6728</v>
+      </c>
+    </row>
+    <row r="5041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5041" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5041" s="3" t="s">
+        <v>6729</v>
+      </c>
+    </row>
+    <row r="5042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5042" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5042" s="3" t="s">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="5043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5043" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5043" s="3" t="s">
+        <v>6731</v>
+      </c>
+    </row>
+    <row r="5044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5044" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5044" s="3" t="s">
+        <v>6732</v>
+      </c>
+    </row>
+    <row r="5045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5045" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5045" s="3" t="s">
+        <v>6735</v>
+      </c>
+    </row>
+    <row r="5046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5046" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5046" s="3" t="s">
+        <v>6736</v>
+      </c>
+    </row>
+    <row r="5047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5047" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5047" s="3" t="s">
+        <v>6737</v>
+      </c>
+    </row>
+    <row r="5048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5048" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5048" s="3" t="s">
+        <v>6738</v>
+      </c>
+    </row>
+    <row r="5049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5049" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5049" s="3" t="s">
+        <v>6739</v>
+      </c>
+    </row>
+    <row r="5050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5050" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5050" s="3" t="s">
+        <v>6740</v>
+      </c>
+    </row>
+    <row r="5051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5051" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5051" s="3" t="s">
+        <v>6741</v>
+      </c>
+    </row>
+    <row r="5052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5052" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5052" s="3" t="s">
+        <v>6742</v>
+      </c>
+    </row>
+    <row r="5053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5053" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5053" s="3" t="s">
+        <v>6743</v>
+      </c>
+    </row>
+    <row r="5054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5054" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5054" s="3" t="s">
+        <v>6744</v>
+      </c>
+    </row>
+    <row r="5055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5055" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5055" s="3" t="s">
+        <v>6745</v>
+      </c>
+    </row>
+    <row r="5056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5056" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5056" s="3" t="s">
+        <v>6746</v>
+      </c>
+    </row>
+    <row r="5057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5057" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5057" s="3" t="s">
+        <v>6747</v>
+      </c>
+    </row>
+    <row r="5058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5058" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5058" s="3" t="s">
+        <v>6748</v>
+      </c>
+    </row>
+    <row r="5059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5059" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5059" s="3" t="s">
+        <v>6749</v>
+      </c>
+    </row>
+    <row r="5060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5060" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5060" s="3" t="s">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="5061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5061" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5061" s="3" t="s">
+        <v>6751</v>
+      </c>
+    </row>
+    <row r="5062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5062" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5062" s="3" t="s">
+        <v>6752</v>
+      </c>
+    </row>
+    <row r="5063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5063" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5063" s="3" t="s">
+        <v>6753</v>
+      </c>
+    </row>
+    <row r="5064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5064" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5064" s="3" t="s">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="5065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5065" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5065" s="3" t="s">
+        <v>6755</v>
+      </c>
+    </row>
+    <row r="5066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5066" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5066" s="3" t="s">
+        <v>6756</v>
+      </c>
+    </row>
+    <row r="5067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5067" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5067" s="3" t="s">
+        <v>6757</v>
+      </c>
+    </row>
+    <row r="5068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5068" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5068" s="3" t="s">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="5069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5069" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5069" s="3" t="s">
+        <v>6759</v>
+      </c>
+    </row>
+    <row r="5070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5070" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5070" s="3" t="s">
+        <v>6760</v>
+      </c>
+    </row>
+    <row r="5071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5071" s="3">
+        <v>6900</v>
+      </c>
+      <c r="C5071" s="3" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="5072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5072" s="4">
+        <v>7000</v>
+      </c>
+      <c r="C5072" s="3" t="s">
+        <v>6762</v>
+      </c>
+    </row>
+    <row r="5073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5073" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5073" s="3" t="s">
+        <v>6763</v>
+      </c>
+    </row>
+    <row r="5074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5074" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5075" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5076" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5077" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5078" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5079" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5080" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5081" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5082" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5083" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5084" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5085" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5086" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5087" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5088" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5089" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5090" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5091" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5092" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5092" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5093" s="3">
+        <v>7000</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF566032-315D-4DD7-9A26-42963E7AECE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54540C1D-6422-4CDD-BBA4-799BEB838824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6787" uniqueCount="6764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6887" uniqueCount="6864">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -27074,6 +27074,406 @@
   </si>
   <si>
     <t>chaotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remuneration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expressiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pancreatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pancreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>juice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebratory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>digestion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endocrinology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intestinal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secretin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hamlin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crustacean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dragon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consultant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lobster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bliss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pomegranate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misunderstand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spatter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refurbish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mottle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indifferent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doubtful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idealization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fidelity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exceedingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immensely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interdependent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>understandably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misunderstanding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emblem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lyrical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>module</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yuan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>victimize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uppermost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beggar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siliceous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grassy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suburban</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>edible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scramble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discontent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tressed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rib</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bongo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recital</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restaurant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>out-of-date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nursery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dizzy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woodwind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsuccessful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seeker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfavorably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spatial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symphony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chronological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pylon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquaintance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colonel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marshal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dilemma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>validity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Militant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dismiss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superficial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>federalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biographical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnetism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sonar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perennial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infiltration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herbicide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compactness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pluck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>springboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>localization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airborne</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -27476,7 +27876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5093"/>
+  <dimension ref="A1:N5184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -72198,6 +72598,9 @@
       <c r="A5072" s="4">
         <v>7000</v>
       </c>
+      <c r="B5072" s="3" t="s">
+        <v>6773</v>
+      </c>
       <c r="C5072" s="3" t="s">
         <v>6762</v>
       </c>
@@ -72206,6 +72609,9 @@
       <c r="A5073" s="3">
         <v>7000</v>
       </c>
+      <c r="B5073" s="3" t="s">
+        <v>6774</v>
+      </c>
       <c r="C5073" s="3" t="s">
         <v>6763</v>
       </c>
@@ -72214,100 +72620,849 @@
       <c r="A5074" s="3">
         <v>7000</v>
       </c>
+      <c r="B5074" s="3" t="s">
+        <v>6803</v>
+      </c>
+      <c r="C5074" s="3" t="s">
+        <v>6764</v>
+      </c>
     </row>
     <row r="5075" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5075" s="3">
         <v>7000</v>
       </c>
+      <c r="B5075" s="3" t="s">
+        <v>6804</v>
+      </c>
+      <c r="C5075" s="3" t="s">
+        <v>6765</v>
+      </c>
     </row>
     <row r="5076" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5076" s="3">
         <v>7000</v>
       </c>
+      <c r="C5076" s="3" t="s">
+        <v>6766</v>
+      </c>
     </row>
     <row r="5077" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5077" s="3">
         <v>7000</v>
       </c>
+      <c r="C5077" s="3" t="s">
+        <v>6767</v>
+      </c>
     </row>
     <row r="5078" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5078" s="3">
         <v>7000</v>
       </c>
+      <c r="C5078" s="3" t="s">
+        <v>6768</v>
+      </c>
     </row>
     <row r="5079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5079" s="3">
         <v>7000</v>
       </c>
+      <c r="C5079" s="3" t="s">
+        <v>6769</v>
+      </c>
     </row>
     <row r="5080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5080" s="3">
         <v>7000</v>
       </c>
+      <c r="C5080" s="3" t="s">
+        <v>6770</v>
+      </c>
     </row>
     <row r="5081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5081" s="3">
         <v>7000</v>
       </c>
+      <c r="C5081" s="3" t="s">
+        <v>6771</v>
+      </c>
     </row>
     <row r="5082" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5082" s="3">
         <v>7000</v>
       </c>
+      <c r="C5082" s="3" t="s">
+        <v>6772</v>
+      </c>
     </row>
     <row r="5083" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5083" s="3">
         <v>7000</v>
       </c>
+      <c r="C5083" s="3" t="s">
+        <v>6775</v>
+      </c>
     </row>
     <row r="5084" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5084" s="3">
         <v>7000</v>
       </c>
+      <c r="C5084" s="3" t="s">
+        <v>6776</v>
+      </c>
     </row>
     <row r="5085" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5085" s="3">
         <v>7000</v>
       </c>
+      <c r="C5085" s="3" t="s">
+        <v>6777</v>
+      </c>
     </row>
     <row r="5086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5086" s="3">
         <v>7000</v>
       </c>
+      <c r="C5086" s="3" t="s">
+        <v>6778</v>
+      </c>
     </row>
     <row r="5087" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5087" s="3">
         <v>7000</v>
       </c>
+      <c r="C5087" s="3" t="s">
+        <v>6779</v>
+      </c>
     </row>
     <row r="5088" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5088" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="5089" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5088" s="3" t="s">
+        <v>6780</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5089" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="5090" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5089" s="3" t="s">
+        <v>6781</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5090" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="5091" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5090" s="3" t="s">
+        <v>6782</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5091" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="5092" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5091" s="3" t="s">
+        <v>6783</v>
+      </c>
+    </row>
+    <row r="5092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5092" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="5093" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5092" s="3" t="s">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5093" s="3">
         <v>7000</v>
+      </c>
+      <c r="C5093" s="3" t="s">
+        <v>6785</v>
+      </c>
+    </row>
+    <row r="5094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5094" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5094" s="3" t="s">
+        <v>6786</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5095" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5095" s="3" t="s">
+        <v>6787</v>
+      </c>
+    </row>
+    <row r="5096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5096" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5096" s="3" t="s">
+        <v>6788</v>
+      </c>
+    </row>
+    <row r="5097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5097" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5097" s="3" t="s">
+        <v>6789</v>
+      </c>
+    </row>
+    <row r="5098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5098" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5098" s="3" t="s">
+        <v>6790</v>
+      </c>
+    </row>
+    <row r="5099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5099" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5099" s="3" t="s">
+        <v>6791</v>
+      </c>
+    </row>
+    <row r="5100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5100" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5100" s="3" t="s">
+        <v>6792</v>
+      </c>
+    </row>
+    <row r="5101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5101" s="3" t="s">
+        <v>6793</v>
+      </c>
+    </row>
+    <row r="5102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5102" s="3" t="s">
+        <v>6794</v>
+      </c>
+    </row>
+    <row r="5103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5103" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5103" s="3" t="s">
+        <v>6795</v>
+      </c>
+    </row>
+    <row r="5104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5104" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5104" s="3" t="s">
+        <v>6796</v>
+      </c>
+    </row>
+    <row r="5105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5105" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5105" s="3" t="s">
+        <v>6797</v>
+      </c>
+    </row>
+    <row r="5106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5106" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5106" s="3" t="s">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="5107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5107" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5107" s="3" t="s">
+        <v>6799</v>
+      </c>
+    </row>
+    <row r="5108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5108" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5108" s="3" t="s">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="5109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5109" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5109" s="3" t="s">
+        <v>6801</v>
+      </c>
+    </row>
+    <row r="5110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5110" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5110" s="3" t="s">
+        <v>6802</v>
+      </c>
+    </row>
+    <row r="5111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5111" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5111" s="3" t="s">
+        <v>6805</v>
+      </c>
+    </row>
+    <row r="5112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5112" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5112" s="3" t="s">
+        <v>6806</v>
+      </c>
+    </row>
+    <row r="5113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5113" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5113" s="3" t="s">
+        <v>6807</v>
+      </c>
+    </row>
+    <row r="5114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5114" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5114" s="3" t="s">
+        <v>6808</v>
+      </c>
+    </row>
+    <row r="5115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5115" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5115" s="3" t="s">
+        <v>6809</v>
+      </c>
+    </row>
+    <row r="5116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5116" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5116" s="3" t="s">
+        <v>6810</v>
+      </c>
+    </row>
+    <row r="5117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5117" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5117" s="3" t="s">
+        <v>6811</v>
+      </c>
+    </row>
+    <row r="5118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5118" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5118" s="3" t="s">
+        <v>6812</v>
+      </c>
+    </row>
+    <row r="5119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5119" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5119" s="3" t="s">
+        <v>6813</v>
+      </c>
+    </row>
+    <row r="5120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5120" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5120" s="3" t="s">
+        <v>6814</v>
+      </c>
+    </row>
+    <row r="5121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5121" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5121" s="3" t="s">
+        <v>6815</v>
+      </c>
+    </row>
+    <row r="5122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5122" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5122" s="3" t="s">
+        <v>6816</v>
+      </c>
+    </row>
+    <row r="5123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5123" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5123" s="3" t="s">
+        <v>6817</v>
+      </c>
+    </row>
+    <row r="5124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5124" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5124" s="3" t="s">
+        <v>6818</v>
+      </c>
+    </row>
+    <row r="5125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5125" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5125" s="3" t="s">
+        <v>6819</v>
+      </c>
+    </row>
+    <row r="5126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5126" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5126" s="3" t="s">
+        <v>6820</v>
+      </c>
+    </row>
+    <row r="5127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5127" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5127" s="3" t="s">
+        <v>6821</v>
+      </c>
+    </row>
+    <row r="5128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5128" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5128" s="3" t="s">
+        <v>6822</v>
+      </c>
+    </row>
+    <row r="5129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5129" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5129" s="3" t="s">
+        <v>6823</v>
+      </c>
+    </row>
+    <row r="5130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5130" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5130" s="3" t="s">
+        <v>6824</v>
+      </c>
+    </row>
+    <row r="5131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5131" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5131" s="3" t="s">
+        <v>6825</v>
+      </c>
+    </row>
+    <row r="5132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5132" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5132" s="3" t="s">
+        <v>6826</v>
+      </c>
+    </row>
+    <row r="5133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5133" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5133" s="3" t="s">
+        <v>6827</v>
+      </c>
+    </row>
+    <row r="5134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5134" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5134" s="3" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5135" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5135" s="3" t="s">
+        <v>6829</v>
+      </c>
+    </row>
+    <row r="5136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5136" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5136" s="3" t="s">
+        <v>6830</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5137" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5137" s="3" t="s">
+        <v>6831</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5138" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5138" s="3" t="s">
+        <v>6832</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5139" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5139" s="3" t="s">
+        <v>6833</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5140" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5140" s="3" t="s">
+        <v>6834</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5141" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5141" s="3" t="s">
+        <v>6835</v>
+      </c>
+    </row>
+    <row r="5142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5142" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5142" s="3" t="s">
+        <v>6836</v>
+      </c>
+    </row>
+    <row r="5143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5143" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5143" s="3" t="s">
+        <v>6837</v>
+      </c>
+    </row>
+    <row r="5144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5144" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5144" s="3" t="s">
+        <v>6838</v>
+      </c>
+    </row>
+    <row r="5145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5145" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5145" s="3" t="s">
+        <v>6839</v>
+      </c>
+    </row>
+    <row r="5146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5146" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5146" s="3" t="s">
+        <v>6840</v>
+      </c>
+    </row>
+    <row r="5147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5147" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5147" s="3" t="s">
+        <v>6841</v>
+      </c>
+    </row>
+    <row r="5148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5148" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5148" s="3" t="s">
+        <v>6842</v>
+      </c>
+    </row>
+    <row r="5149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5149" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5149" s="3" t="s">
+        <v>6843</v>
+      </c>
+    </row>
+    <row r="5150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5150" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5150" s="3" t="s">
+        <v>6844</v>
+      </c>
+    </row>
+    <row r="5151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5151" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5151" s="3" t="s">
+        <v>6845</v>
+      </c>
+    </row>
+    <row r="5152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5152" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5152" s="3" t="s">
+        <v>6846</v>
+      </c>
+    </row>
+    <row r="5153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5153" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5153" s="3" t="s">
+        <v>6847</v>
+      </c>
+    </row>
+    <row r="5154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5154" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5154" s="3" t="s">
+        <v>6848</v>
+      </c>
+    </row>
+    <row r="5155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5155" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5155" s="3" t="s">
+        <v>6849</v>
+      </c>
+    </row>
+    <row r="5156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5156" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5156" s="3" t="s">
+        <v>6850</v>
+      </c>
+    </row>
+    <row r="5157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5157" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5157" s="3" t="s">
+        <v>6851</v>
+      </c>
+    </row>
+    <row r="5158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5158" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5158" s="3" t="s">
+        <v>6852</v>
+      </c>
+    </row>
+    <row r="5159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5159" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5159" s="3" t="s">
+        <v>6853</v>
+      </c>
+    </row>
+    <row r="5160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5160" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5160" s="3" t="s">
+        <v>6854</v>
+      </c>
+    </row>
+    <row r="5161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5161" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5161" s="3" t="s">
+        <v>6855</v>
+      </c>
+    </row>
+    <row r="5162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5162" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5162" s="3" t="s">
+        <v>6856</v>
+      </c>
+    </row>
+    <row r="5163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5163" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5163" s="3" t="s">
+        <v>6857</v>
+      </c>
+    </row>
+    <row r="5164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5164" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5164" s="3" t="s">
+        <v>6858</v>
+      </c>
+    </row>
+    <row r="5165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5165" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5165" s="3" t="s">
+        <v>6859</v>
+      </c>
+    </row>
+    <row r="5166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5166" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5166" s="3" t="s">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="5167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5167" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C5167" s="3" t="s">
+        <v>6861</v>
+      </c>
+    </row>
+    <row r="5168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5168" s="4">
+        <v>7100</v>
+      </c>
+      <c r="C5168" s="3" t="s">
+        <v>6862</v>
+      </c>
+    </row>
+    <row r="5169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5169" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5169" s="3" t="s">
+        <v>6863</v>
+      </c>
+    </row>
+    <row r="5170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5170" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5171" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5172" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5173" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5174" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5175" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5176" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5177" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5178" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5179" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5180" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5181" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5182" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5183" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5184" s="3">
+        <v>7100</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54540C1D-6422-4CDD-BBA4-799BEB838824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F538D410-F747-46A9-978E-0FC6D280401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6887" uniqueCount="6864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6987" uniqueCount="6963">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -27474,6 +27474,402 @@
   </si>
   <si>
     <t>airborne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalyst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beneficiary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaflet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cross-hatching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>good-quality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affordable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>myxoma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>importation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intaglio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elaboration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>congenital</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photodissociation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>survivor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninhabited</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aphid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weekend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miami</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weekday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paralyze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>articulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>airway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outgassing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overrun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loosen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Netherland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incorrectly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Athens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tollgate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bravely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Athenian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outskirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>milligram</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supplier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>closeness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stately</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infinitesimally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lyric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uranus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insulator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keelboat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manageable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metaphor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disaffection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>requisition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reprint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheerful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entwine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>untie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impermeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condenses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>looseness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anchor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>governmental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romanize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permeate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>teacup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>characterization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earthen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insistence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonporous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turnover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southernmost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enhancement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>memorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indeterminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unbalance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conclusively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortuitous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hieroglyph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admirable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>democratization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peacefully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upheaval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inflection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stocking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radiometric</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -27876,7 +28272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5184"/>
+  <dimension ref="A1:N5287"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -73378,6 +73774,9 @@
       <c r="A5168" s="4">
         <v>7100</v>
       </c>
+      <c r="B5168" s="3" t="s">
+        <v>6871</v>
+      </c>
       <c r="C5168" s="3" t="s">
         <v>6862</v>
       </c>
@@ -73386,6 +73785,9 @@
       <c r="A5169" s="3">
         <v>7100</v>
       </c>
+      <c r="B5169" s="3" t="s">
+        <v>6875</v>
+      </c>
       <c r="C5169" s="3" t="s">
         <v>6863</v>
       </c>
@@ -73394,75 +73796,884 @@
       <c r="A5170" s="3">
         <v>7100</v>
       </c>
+      <c r="B5170" s="3" t="s">
+        <v>6885</v>
+      </c>
+      <c r="C5170" s="3" t="s">
+        <v>6864</v>
+      </c>
     </row>
     <row r="5171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5171" s="3">
         <v>7100</v>
       </c>
+      <c r="B5171" s="3" t="s">
+        <v>6887</v>
+      </c>
+      <c r="C5171" s="3" t="s">
+        <v>6865</v>
+      </c>
     </row>
     <row r="5172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5172" s="3">
         <v>7100</v>
       </c>
+      <c r="B5172" s="3" t="s">
+        <v>6890</v>
+      </c>
+      <c r="C5172" s="3" t="s">
+        <v>6866</v>
+      </c>
     </row>
     <row r="5173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5173" s="3">
         <v>7100</v>
       </c>
+      <c r="B5173" s="3" t="s">
+        <v>6914</v>
+      </c>
+      <c r="C5173" s="3" t="s">
+        <v>6867</v>
+      </c>
     </row>
     <row r="5174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5174" s="3">
         <v>7100</v>
       </c>
+      <c r="B5174" s="3" t="s">
+        <v>6922</v>
+      </c>
+      <c r="C5174" s="3" t="s">
+        <v>6868</v>
+      </c>
     </row>
     <row r="5175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5175" s="3">
         <v>7100</v>
       </c>
+      <c r="B5175" s="3" t="s">
+        <v>6927</v>
+      </c>
+      <c r="C5175" s="3" t="s">
+        <v>6869</v>
+      </c>
     </row>
     <row r="5176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5176" s="3">
         <v>7100</v>
       </c>
+      <c r="B5176" s="3" t="s">
+        <v>6930</v>
+      </c>
+      <c r="C5176" s="3" t="s">
+        <v>6870</v>
+      </c>
     </row>
     <row r="5177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5177" s="3">
         <v>7100</v>
       </c>
+      <c r="B5177" s="3" t="s">
+        <v>6936</v>
+      </c>
+      <c r="C5177" s="3" t="s">
+        <v>6872</v>
+      </c>
     </row>
     <row r="5178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5178" s="3">
         <v>7100</v>
       </c>
+      <c r="B5178" s="3" t="s">
+        <v>6940</v>
+      </c>
+      <c r="C5178" s="3" t="s">
+        <v>6873</v>
+      </c>
     </row>
     <row r="5179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5179" s="3">
         <v>7100</v>
       </c>
+      <c r="B5179" s="3" t="s">
+        <v>6944</v>
+      </c>
+      <c r="C5179" s="3" t="s">
+        <v>6874</v>
+      </c>
     </row>
     <row r="5180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5180" s="3">
         <v>7100</v>
       </c>
+      <c r="B5180" s="3" t="s">
+        <v>6945</v>
+      </c>
+      <c r="C5180" s="3" t="s">
+        <v>6876</v>
+      </c>
     </row>
     <row r="5181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5181" s="3">
         <v>7100</v>
       </c>
+      <c r="B5181" s="3" t="s">
+        <v>6949</v>
+      </c>
+      <c r="C5181" s="3" t="s">
+        <v>6877</v>
+      </c>
     </row>
     <row r="5182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5182" s="3">
         <v>7100</v>
       </c>
+      <c r="B5182" s="3" t="s">
+        <v>6950</v>
+      </c>
+      <c r="C5182" s="3" t="s">
+        <v>6878</v>
+      </c>
     </row>
     <row r="5183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5183" s="3">
         <v>7100</v>
       </c>
+      <c r="B5183" s="3" t="s">
+        <v>6952</v>
+      </c>
+      <c r="C5183" s="3" t="s">
+        <v>6879</v>
+      </c>
     </row>
     <row r="5184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5184" s="3">
         <v>7100</v>
+      </c>
+      <c r="B5184" s="3" t="s">
+        <v>6958</v>
+      </c>
+      <c r="C5184" s="3" t="s">
+        <v>6880</v>
+      </c>
+    </row>
+    <row r="5185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5185" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5185" s="3" t="s">
+        <v>6881</v>
+      </c>
+    </row>
+    <row r="5186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5186" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5186" s="3" t="s">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="5187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5187" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5187" s="3" t="s">
+        <v>6883</v>
+      </c>
+    </row>
+    <row r="5188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5188" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5188" s="3" t="s">
+        <v>6884</v>
+      </c>
+    </row>
+    <row r="5189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5189" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5189" s="3" t="s">
+        <v>6886</v>
+      </c>
+    </row>
+    <row r="5190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5190" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5190" s="3" t="s">
+        <v>6888</v>
+      </c>
+    </row>
+    <row r="5191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5191" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5191" s="3" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="5192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5192" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5192" s="3" t="s">
+        <v>6891</v>
+      </c>
+    </row>
+    <row r="5193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5193" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5193" s="3" t="s">
+        <v>6892</v>
+      </c>
+    </row>
+    <row r="5194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5194" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5194" s="3" t="s">
+        <v>6893</v>
+      </c>
+    </row>
+    <row r="5195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5195" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5195" s="3" t="s">
+        <v>6894</v>
+      </c>
+    </row>
+    <row r="5196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5196" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5196" s="3" t="s">
+        <v>6895</v>
+      </c>
+    </row>
+    <row r="5197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5197" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5197" s="3" t="s">
+        <v>6896</v>
+      </c>
+    </row>
+    <row r="5198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5198" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5198" s="3" t="s">
+        <v>6897</v>
+      </c>
+    </row>
+    <row r="5199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5199" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5199" s="3" t="s">
+        <v>6898</v>
+      </c>
+    </row>
+    <row r="5200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5200" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5200" s="3" t="s">
+        <v>6899</v>
+      </c>
+    </row>
+    <row r="5201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5201" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5201" s="3" t="s">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="5202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5202" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5202" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="5203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5203" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5203" s="3" t="s">
+        <v>6901</v>
+      </c>
+    </row>
+    <row r="5204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5204" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5204" s="3" t="s">
+        <v>6902</v>
+      </c>
+    </row>
+    <row r="5205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5205" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5205" s="3" t="s">
+        <v>6903</v>
+      </c>
+    </row>
+    <row r="5206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5206" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5206" s="3" t="s">
+        <v>6904</v>
+      </c>
+    </row>
+    <row r="5207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5207" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5207" s="3" t="s">
+        <v>6905</v>
+      </c>
+    </row>
+    <row r="5208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5208" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5208" s="3" t="s">
+        <v>6906</v>
+      </c>
+    </row>
+    <row r="5209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5209" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5209" s="3" t="s">
+        <v>6907</v>
+      </c>
+    </row>
+    <row r="5210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5210" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5210" s="3" t="s">
+        <v>6908</v>
+      </c>
+    </row>
+    <row r="5211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5211" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5211" s="3" t="s">
+        <v>6909</v>
+      </c>
+    </row>
+    <row r="5212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5212" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5212" s="3" t="s">
+        <v>6910</v>
+      </c>
+    </row>
+    <row r="5213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5213" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5213" s="3" t="s">
+        <v>6911</v>
+      </c>
+    </row>
+    <row r="5214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5214" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5214" s="3" t="s">
+        <v>6912</v>
+      </c>
+    </row>
+    <row r="5215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5215" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5215" s="3" t="s">
+        <v>6913</v>
+      </c>
+    </row>
+    <row r="5216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5216" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5216" s="3" t="s">
+        <v>6915</v>
+      </c>
+    </row>
+    <row r="5217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5217" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5217" s="3" t="s">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="5218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5218" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5218" s="3" t="s">
+        <v>6917</v>
+      </c>
+    </row>
+    <row r="5219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5219" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5219" s="3" t="s">
+        <v>6918</v>
+      </c>
+    </row>
+    <row r="5220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5220" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5220" s="3" t="s">
+        <v>6919</v>
+      </c>
+    </row>
+    <row r="5221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5221" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5221" s="3" t="s">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="5222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5222" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5222" s="3" t="s">
+        <v>6921</v>
+      </c>
+    </row>
+    <row r="5223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5223" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5223" s="3" t="s">
+        <v>6923</v>
+      </c>
+    </row>
+    <row r="5224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5224" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5224" s="3" t="s">
+        <v>6924</v>
+      </c>
+    </row>
+    <row r="5225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5225" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5225" s="3" t="s">
+        <v>6925</v>
+      </c>
+    </row>
+    <row r="5226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5226" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5226" s="3" t="s">
+        <v>6926</v>
+      </c>
+    </row>
+    <row r="5227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5227" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5227" s="3" t="s">
+        <v>6928</v>
+      </c>
+    </row>
+    <row r="5228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5228" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5228" s="3" t="s">
+        <v>6929</v>
+      </c>
+    </row>
+    <row r="5229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5229" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5229" s="3" t="s">
+        <v>6931</v>
+      </c>
+    </row>
+    <row r="5230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5230" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5230" s="3" t="s">
+        <v>6932</v>
+      </c>
+    </row>
+    <row r="5231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5231" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5231" s="3" t="s">
+        <v>6933</v>
+      </c>
+    </row>
+    <row r="5232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5232" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5232" s="3" t="s">
+        <v>6934</v>
+      </c>
+    </row>
+    <row r="5233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5233" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5233" s="3" t="s">
+        <v>6935</v>
+      </c>
+    </row>
+    <row r="5234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5234" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5234" s="3" t="s">
+        <v>6937</v>
+      </c>
+    </row>
+    <row r="5235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5235" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5235" s="3" t="s">
+        <v>6938</v>
+      </c>
+    </row>
+    <row r="5236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5236" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5236" s="3" t="s">
+        <v>6939</v>
+      </c>
+    </row>
+    <row r="5237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5237" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5237" s="3" t="s">
+        <v>6941</v>
+      </c>
+    </row>
+    <row r="5238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5238" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5238" s="3" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="5239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5239" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5239" s="3" t="s">
+        <v>6943</v>
+      </c>
+    </row>
+    <row r="5240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5240" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5240" s="3" t="s">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="5241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5241" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5241" s="3" t="s">
+        <v>6947</v>
+      </c>
+    </row>
+    <row r="5242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5242" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5242" s="3" t="s">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="5243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5243" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5243" s="3" t="s">
+        <v>6951</v>
+      </c>
+    </row>
+    <row r="5244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5244" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5244" s="3" t="s">
+        <v>6953</v>
+      </c>
+    </row>
+    <row r="5245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5245" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5245" s="3" t="s">
+        <v>6954</v>
+      </c>
+    </row>
+    <row r="5246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5246" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5246" s="3" t="s">
+        <v>6955</v>
+      </c>
+    </row>
+    <row r="5247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5247" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5247" s="3" t="s">
+        <v>6956</v>
+      </c>
+    </row>
+    <row r="5248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5248" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5248" s="3" t="s">
+        <v>6957</v>
+      </c>
+    </row>
+    <row r="5249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5249" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5249" s="3" t="s">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="5250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5250" s="3">
+        <v>7100</v>
+      </c>
+      <c r="C5250" s="3" t="s">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="5251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5251" s="4">
+        <v>7200</v>
+      </c>
+      <c r="C5251" s="3" t="s">
+        <v>6961</v>
+      </c>
+    </row>
+    <row r="5252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5252" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5252" s="3" t="s">
+        <v>6962</v>
+      </c>
+    </row>
+    <row r="5253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5253" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5254" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5255" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5256" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5257" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5258" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5259" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5260" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5261" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5262" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5263" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5264" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5265" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5266" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5267" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5268" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5269" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5270" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5271" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5272" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5273" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5274" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5275" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5276" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5277" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5278" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5279" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5280" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5281" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5282" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5283" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5284" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5285" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5286" s="3">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5287" s="3">
+        <v>7200</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F538D410-F747-46A9-978E-0FC6D280401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CEF696-0174-4575-B5D5-435C702E434A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6987" uniqueCount="6963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7087" uniqueCount="7061">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -27870,6 +27870,398 @@
   </si>
   <si>
     <t>radiometric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>balkan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thwart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hieratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intonation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>composite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fibrous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pedagogic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>floe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synonym</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listener</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conductivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physiology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miocene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eletricity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nowhere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>groom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prickly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recurrent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monoid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affront</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deflect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discernible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>watery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secretary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catchment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underscore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tambourine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluidity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ongoing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unhindered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fleet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>almanac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breathtaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coniferous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loyalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incoming</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpredictably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scraping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reorganize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turkic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accuracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>momentarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overconfident</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expansionist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crowbar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interdependence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broaden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>till</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inappropriate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>residue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enterprising</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moisten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medicinal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tribespeople</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unattractive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>envelope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crucible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unbreakable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thumb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intermittently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flotation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>healthful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mesh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leafcutter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zagros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arabian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bypass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>segregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>willingness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marketplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revenue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unconsciously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forebear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>topography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clergyman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Haiti</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -28272,7 +28664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5287"/>
+  <dimension ref="A1:N5380"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -74489,6 +74881,9 @@
       <c r="A5251" s="4">
         <v>7200</v>
       </c>
+      <c r="B5251" s="3" t="s">
+        <v>6974</v>
+      </c>
       <c r="C5251" s="3" t="s">
         <v>6961</v>
       </c>
@@ -74497,6 +74892,9 @@
       <c r="A5252" s="3">
         <v>7200</v>
       </c>
+      <c r="B5252" s="3" t="s">
+        <v>6981</v>
+      </c>
       <c r="C5252" s="3" t="s">
         <v>6962</v>
       </c>
@@ -74505,175 +74903,934 @@
       <c r="A5253" s="3">
         <v>7200</v>
       </c>
+      <c r="B5253" s="3" t="s">
+        <v>6983</v>
+      </c>
+      <c r="C5253" s="3" t="s">
+        <v>6963</v>
+      </c>
     </row>
     <row r="5254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5254" s="3">
         <v>7200</v>
       </c>
+      <c r="B5254" s="3" t="s">
+        <v>6986</v>
+      </c>
+      <c r="C5254" s="3" t="s">
+        <v>6964</v>
+      </c>
     </row>
     <row r="5255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5255" s="3">
         <v>7200</v>
       </c>
+      <c r="B5255" s="3" t="s">
+        <v>6997</v>
+      </c>
+      <c r="C5255" s="3" t="s">
+        <v>6965</v>
+      </c>
     </row>
     <row r="5256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5256" s="3">
         <v>7200</v>
       </c>
+      <c r="B5256" s="3" t="s">
+        <v>7021</v>
+      </c>
+      <c r="C5256" s="3" t="s">
+        <v>6966</v>
+      </c>
     </row>
     <row r="5257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5257" s="3">
         <v>7200</v>
       </c>
+      <c r="B5257" s="3" t="s">
+        <v>5937</v>
+      </c>
+      <c r="C5257" s="3" t="s">
+        <v>6967</v>
+      </c>
     </row>
     <row r="5258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5258" s="3">
         <v>7200</v>
       </c>
+      <c r="B5258" s="3" t="s">
+        <v>7026</v>
+      </c>
+      <c r="C5258" s="3" t="s">
+        <v>6968</v>
+      </c>
     </row>
     <row r="5259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5259" s="3">
         <v>7200</v>
       </c>
+      <c r="B5259" s="3" t="s">
+        <v>7043</v>
+      </c>
+      <c r="C5259" s="3" t="s">
+        <v>6969</v>
+      </c>
     </row>
     <row r="5260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5260" s="3">
         <v>7200</v>
       </c>
+      <c r="C5260" s="3" t="s">
+        <v>6970</v>
+      </c>
     </row>
     <row r="5261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5261" s="3">
         <v>7200</v>
       </c>
+      <c r="C5261" s="3" t="s">
+        <v>6971</v>
+      </c>
     </row>
     <row r="5262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5262" s="3">
         <v>7200</v>
       </c>
+      <c r="C5262" s="3" t="s">
+        <v>6972</v>
+      </c>
     </row>
     <row r="5263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5263" s="3">
         <v>7200</v>
       </c>
+      <c r="C5263" s="3" t="s">
+        <v>6973</v>
+      </c>
     </row>
     <row r="5264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5264" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5264" s="3" t="s">
+        <v>6975</v>
+      </c>
+    </row>
+    <row r="5265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5265" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5265" s="3" t="s">
+        <v>6976</v>
+      </c>
+    </row>
+    <row r="5266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5266" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5266" s="3" t="s">
+        <v>6977</v>
+      </c>
+    </row>
+    <row r="5267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5267" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5267" s="3" t="s">
+        <v>6978</v>
+      </c>
+    </row>
+    <row r="5268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5268" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5268" s="3" t="s">
+        <v>6979</v>
+      </c>
+    </row>
+    <row r="5269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5269" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5269" s="3" t="s">
+        <v>6980</v>
+      </c>
+    </row>
+    <row r="5270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5270" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5270" s="3" t="s">
+        <v>6982</v>
+      </c>
+    </row>
+    <row r="5271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5271" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5271" s="3" t="s">
+        <v>6984</v>
+      </c>
+    </row>
+    <row r="5272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5272" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5272" s="3" t="s">
+        <v>6985</v>
+      </c>
+    </row>
+    <row r="5273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5273" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5273" s="3" t="s">
+        <v>6987</v>
+      </c>
+    </row>
+    <row r="5274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5274" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5274" s="3" t="s">
+        <v>6988</v>
+      </c>
+    </row>
+    <row r="5275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5275" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5275" s="3" t="s">
+        <v>6989</v>
+      </c>
+    </row>
+    <row r="5276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5276" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5276" s="3" t="s">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="5277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5277" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5277" s="3" t="s">
+        <v>6991</v>
+      </c>
+    </row>
+    <row r="5278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5278" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5278" s="3" t="s">
+        <v>6992</v>
+      </c>
+    </row>
+    <row r="5279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5279" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5279" s="3" t="s">
+        <v>6993</v>
+      </c>
+    </row>
+    <row r="5280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5280" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5280" s="3" t="s">
+        <v>6994</v>
+      </c>
+    </row>
+    <row r="5281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5281" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5281" s="3" t="s">
+        <v>6995</v>
+      </c>
+    </row>
+    <row r="5282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5282" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5282" s="3" t="s">
+        <v>6996</v>
+      </c>
+    </row>
+    <row r="5283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5283" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5283" s="3" t="s">
+        <v>6998</v>
+      </c>
+    </row>
+    <row r="5284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5284" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5284" s="3" t="s">
+        <v>6999</v>
+      </c>
+    </row>
+    <row r="5285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5285" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5285" s="3" t="s">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5286" s="3">
         <v>7200</v>
       </c>
-    </row>
-    <row r="5287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5286" s="3" t="s">
+        <v>7001</v>
+      </c>
+    </row>
+    <row r="5287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5287" s="3">
         <v>7200</v>
+      </c>
+      <c r="C5287" s="3" t="s">
+        <v>7002</v>
+      </c>
+    </row>
+    <row r="5288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5288" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5288" s="3" t="s">
+        <v>7003</v>
+      </c>
+    </row>
+    <row r="5289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5289" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5289" s="3" t="s">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="5290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5290" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5290" s="3" t="s">
+        <v>7005</v>
+      </c>
+    </row>
+    <row r="5291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5291" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5291" s="3" t="s">
+        <v>7006</v>
+      </c>
+    </row>
+    <row r="5292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5292" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5292" s="3" t="s">
+        <v>7007</v>
+      </c>
+    </row>
+    <row r="5293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5293" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5293" s="3" t="s">
+        <v>7008</v>
+      </c>
+    </row>
+    <row r="5294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5294" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5294" s="3" t="s">
+        <v>7009</v>
+      </c>
+    </row>
+    <row r="5295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5295" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5295" s="3" t="s">
+        <v>7010</v>
+      </c>
+    </row>
+    <row r="5296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5296" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5296" s="3" t="s">
+        <v>7011</v>
+      </c>
+    </row>
+    <row r="5297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5297" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5297" s="3" t="s">
+        <v>7012</v>
+      </c>
+    </row>
+    <row r="5298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5298" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5298" s="3" t="s">
+        <v>7013</v>
+      </c>
+    </row>
+    <row r="5299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5299" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5299" s="3" t="s">
+        <v>7014</v>
+      </c>
+    </row>
+    <row r="5300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5300" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5300" s="3" t="s">
+        <v>7015</v>
+      </c>
+    </row>
+    <row r="5301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5301" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5301" s="3" t="s">
+        <v>7016</v>
+      </c>
+    </row>
+    <row r="5302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5302" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5302" s="3" t="s">
+        <v>7017</v>
+      </c>
+    </row>
+    <row r="5303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5303" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5303" s="3" t="s">
+        <v>7018</v>
+      </c>
+    </row>
+    <row r="5304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5304" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5304" s="3" t="s">
+        <v>7019</v>
+      </c>
+    </row>
+    <row r="5305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5305" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5305" s="3" t="s">
+        <v>7020</v>
+      </c>
+    </row>
+    <row r="5306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5306" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5306" s="3" t="s">
+        <v>7022</v>
+      </c>
+    </row>
+    <row r="5307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5307" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5307" s="3" t="s">
+        <v>7023</v>
+      </c>
+    </row>
+    <row r="5308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5308" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5308" s="3" t="s">
+        <v>7024</v>
+      </c>
+    </row>
+    <row r="5309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5309" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5309" s="3" t="s">
+        <v>7025</v>
+      </c>
+    </row>
+    <row r="5310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5310" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5310" s="3" t="s">
+        <v>7027</v>
+      </c>
+    </row>
+    <row r="5311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5311" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5311" s="3" t="s">
+        <v>7028</v>
+      </c>
+    </row>
+    <row r="5312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5312" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5312" s="3" t="s">
+        <v>7029</v>
+      </c>
+    </row>
+    <row r="5313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5313" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5313" s="3" t="s">
+        <v>7030</v>
+      </c>
+    </row>
+    <row r="5314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5314" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5314" s="3" t="s">
+        <v>7031</v>
+      </c>
+    </row>
+    <row r="5315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5315" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5315" s="3" t="s">
+        <v>7032</v>
+      </c>
+    </row>
+    <row r="5316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5316" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5316" s="3" t="s">
+        <v>7033</v>
+      </c>
+    </row>
+    <row r="5317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5317" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5317" s="3" t="s">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="5318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5318" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5318" s="3" t="s">
+        <v>7035</v>
+      </c>
+    </row>
+    <row r="5319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5319" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5319" s="3" t="s">
+        <v>7036</v>
+      </c>
+    </row>
+    <row r="5320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5320" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5320" s="3" t="s">
+        <v>7037</v>
+      </c>
+    </row>
+    <row r="5321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5321" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5321" s="3" t="s">
+        <v>7038</v>
+      </c>
+    </row>
+    <row r="5322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5322" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5322" s="3" t="s">
+        <v>7039</v>
+      </c>
+    </row>
+    <row r="5323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5323" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5323" s="3" t="s">
+        <v>7040</v>
+      </c>
+    </row>
+    <row r="5324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5324" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5324" s="3" t="s">
+        <v>7041</v>
+      </c>
+    </row>
+    <row r="5325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5325" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5325" s="3" t="s">
+        <v>7042</v>
+      </c>
+    </row>
+    <row r="5326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5326" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5326" s="3" t="s">
+        <v>7044</v>
+      </c>
+    </row>
+    <row r="5327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5327" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5327" s="3" t="s">
+        <v>7045</v>
+      </c>
+    </row>
+    <row r="5328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5328" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5328" s="3" t="s">
+        <v>7046</v>
+      </c>
+    </row>
+    <row r="5329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5329" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5329" s="3" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="5330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5330" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5330" s="3" t="s">
+        <v>7047</v>
+      </c>
+    </row>
+    <row r="5331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5331" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5331" s="3" t="s">
+        <v>7048</v>
+      </c>
+    </row>
+    <row r="5332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5332" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5332" s="3" t="s">
+        <v>7049</v>
+      </c>
+    </row>
+    <row r="5333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5333" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5333" s="3" t="s">
+        <v>7050</v>
+      </c>
+    </row>
+    <row r="5334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5334" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5334" s="3" t="s">
+        <v>7051</v>
+      </c>
+    </row>
+    <row r="5335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5335" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5335" s="3" t="s">
+        <v>7052</v>
+      </c>
+    </row>
+    <row r="5336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5336" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5336" s="3" t="s">
+        <v>7053</v>
+      </c>
+    </row>
+    <row r="5337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5337" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5337" s="3" t="s">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="5338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5338" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5338" s="3" t="s">
+        <v>7055</v>
+      </c>
+    </row>
+    <row r="5339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5339" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5339" s="3" t="s">
+        <v>7056</v>
+      </c>
+    </row>
+    <row r="5340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5340" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5340" s="3" t="s">
+        <v>7057</v>
+      </c>
+    </row>
+    <row r="5341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5341" s="3">
+        <v>7200</v>
+      </c>
+      <c r="C5341" s="3" t="s">
+        <v>7058</v>
+      </c>
+    </row>
+    <row r="5342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5342" s="4">
+        <v>7300</v>
+      </c>
+      <c r="C5342" s="3" t="s">
+        <v>7059</v>
+      </c>
+    </row>
+    <row r="5343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5343" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5343" s="3" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="5344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5344" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5345" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5346" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5347" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5348" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5349" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5350" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5351" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5352" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5353" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5354" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5355" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5356" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5357" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5358" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5359" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5360" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5361" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5362" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5363" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5364" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5365" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5366" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5367" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5368" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5369" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5370" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5371" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5372" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5373" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5374" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5375" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5376" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5377" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5378" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5379" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5380" s="3">
+        <v>7300</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CEF696-0174-4575-B5D5-435C702E434A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7018CBF5-81CF-4A4D-9F2D-6C7103D5EB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7087" uniqueCount="7061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7187" uniqueCount="7159">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -28262,6 +28262,398 @@
   </si>
   <si>
     <t>Haiti</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fatigue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wreck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disintegrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faithful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awesome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydroelectric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>favorably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unemployment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preferably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>driveway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spacecraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hermit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pathway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guideline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>November</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lvory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deluge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deep-sea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minutely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landlocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monolithic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cohesiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peculiarly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cruise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oceanographic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vicious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turnip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>congestion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meticulous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impermanence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impenetrable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expendable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high-powered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undeniable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conqueror</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>land-based</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backbreaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commercialize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landsman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>albedo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verbalizable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imcompatibilitty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forefront</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classicism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foresight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infertile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horticultural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parcel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hospitalize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scanty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verbally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>juicy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physiologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viewpoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chipmunk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>birthday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kernel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stereotype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trivial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distortion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumstantially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grizzly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Americanism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shortwave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fleshy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fallout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pluralism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alumnus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heritage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geochemical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cloudlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vegetative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quickest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -28664,7 +29056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5380"/>
+  <dimension ref="A1:N5459"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -75636,6 +76028,9 @@
       <c r="A5342" s="4">
         <v>7300</v>
       </c>
+      <c r="B5342" s="3" t="s">
+        <v>7070</v>
+      </c>
       <c r="C5342" s="3" t="s">
         <v>7059</v>
       </c>
@@ -75644,6 +76039,9 @@
       <c r="A5343" s="3">
         <v>7300</v>
       </c>
+      <c r="B5343" s="3" t="s">
+        <v>7073</v>
+      </c>
       <c r="C5343" s="3" t="s">
         <v>7060</v>
       </c>
@@ -75652,185 +76050,874 @@
       <c r="A5344" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5344" s="3" t="s">
+        <v>7074</v>
+      </c>
+      <c r="C5344" s="3" t="s">
+        <v>7061</v>
+      </c>
+    </row>
+    <row r="5345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5345" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5345" s="3" t="s">
+        <v>7076</v>
+      </c>
+      <c r="C5345" s="3" t="s">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="5346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5346" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5346" s="3" t="s">
+        <v>7080</v>
+      </c>
+      <c r="C5346" s="3" t="s">
+        <v>7063</v>
+      </c>
+    </row>
+    <row r="5347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5347" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5347" s="3" t="s">
+        <v>7083</v>
+      </c>
+      <c r="C5347" s="3" t="s">
+        <v>7064</v>
+      </c>
+    </row>
+    <row r="5348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5348" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5348" s="3" t="s">
+        <v>7097</v>
+      </c>
+      <c r="C5348" s="3" t="s">
+        <v>7065</v>
+      </c>
+    </row>
+    <row r="5349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5349" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5349" s="3" t="s">
+        <v>7115</v>
+      </c>
+      <c r="C5349" s="3" t="s">
+        <v>7066</v>
+      </c>
+    </row>
+    <row r="5350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5350" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5350" s="3" t="s">
+        <v>7125</v>
+      </c>
+      <c r="C5350" s="3" t="s">
+        <v>7067</v>
+      </c>
+    </row>
+    <row r="5351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5351" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5351" s="3" t="s">
+        <v>7130</v>
+      </c>
+      <c r="C5351" s="3" t="s">
+        <v>7068</v>
+      </c>
+    </row>
+    <row r="5352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5352" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5352" s="3" t="s">
+        <v>7133</v>
+      </c>
+      <c r="C5352" s="3" t="s">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="5353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5353" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B5353" s="3" t="s">
+        <v>7142</v>
+      </c>
+      <c r="C5353" s="3" t="s">
+        <v>7071</v>
+      </c>
+    </row>
+    <row r="5354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5354" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5354" s="3" t="s">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="5355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5355" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5355" s="3" t="s">
+        <v>5574</v>
+      </c>
+    </row>
+    <row r="5356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5356" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5356" s="3" t="s">
+        <v>7075</v>
+      </c>
+    </row>
+    <row r="5357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5357" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5357" s="3" t="s">
+        <v>7077</v>
+      </c>
+    </row>
+    <row r="5358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5358" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5358" s="3" t="s">
+        <v>7078</v>
+      </c>
+    </row>
+    <row r="5359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5359" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5359" s="3" t="s">
+        <v>7079</v>
+      </c>
+    </row>
+    <row r="5360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5360" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5360" s="3" t="s">
+        <v>7081</v>
+      </c>
+    </row>
+    <row r="5361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5361" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5361" s="3" t="s">
+        <v>7082</v>
+      </c>
+    </row>
+    <row r="5362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5362" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5362" s="3" t="s">
+        <v>7084</v>
+      </c>
+    </row>
+    <row r="5363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5363" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5363" s="3" t="s">
+        <v>7085</v>
+      </c>
+    </row>
+    <row r="5364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5364" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5364" s="3" t="s">
+        <v>7086</v>
+      </c>
+    </row>
+    <row r="5365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5365" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5365" s="3" t="s">
+        <v>7087</v>
+      </c>
+    </row>
+    <row r="5366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5366" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5366" s="3" t="s">
+        <v>7088</v>
+      </c>
+    </row>
+    <row r="5367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5367" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5367" s="3" t="s">
+        <v>7089</v>
+      </c>
+    </row>
+    <row r="5368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5368" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5368" s="3" t="s">
+        <v>7090</v>
+      </c>
+    </row>
+    <row r="5369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5369" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5369" s="3" t="s">
+        <v>7091</v>
+      </c>
+    </row>
+    <row r="5370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5370" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5370" s="3" t="s">
+        <v>7092</v>
+      </c>
+    </row>
+    <row r="5371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5371" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5371" s="3" t="s">
+        <v>7093</v>
+      </c>
+    </row>
+    <row r="5372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5372" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5372" s="3" t="s">
+        <v>7094</v>
+      </c>
+    </row>
+    <row r="5373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5373" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5373" s="3" t="s">
+        <v>7095</v>
+      </c>
+    </row>
+    <row r="5374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5374" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5374" s="3" t="s">
+        <v>7096</v>
+      </c>
+    </row>
+    <row r="5375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5375" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5375" s="3" t="s">
+        <v>7098</v>
+      </c>
+    </row>
+    <row r="5376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5376" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5376" s="3" t="s">
+        <v>7099</v>
+      </c>
+    </row>
+    <row r="5377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5377" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5377" s="3" t="s">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="5378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5378" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5378" s="3" t="s">
+        <v>7101</v>
+      </c>
+    </row>
+    <row r="5379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5379" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="5380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5379" s="3" t="s">
+        <v>7102</v>
+      </c>
+    </row>
+    <row r="5380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5380" s="3">
         <v>7300</v>
+      </c>
+      <c r="C5380" s="3" t="s">
+        <v>7103</v>
+      </c>
+    </row>
+    <row r="5381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5381" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5381" s="3" t="s">
+        <v>7104</v>
+      </c>
+    </row>
+    <row r="5382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5382" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5382" s="3" t="s">
+        <v>7105</v>
+      </c>
+    </row>
+    <row r="5383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5383" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5383" s="3" t="s">
+        <v>7106</v>
+      </c>
+    </row>
+    <row r="5384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5384" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5384" s="3" t="s">
+        <v>7107</v>
+      </c>
+    </row>
+    <row r="5385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5385" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5385" s="3" t="s">
+        <v>7108</v>
+      </c>
+    </row>
+    <row r="5386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5386" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5386" s="3" t="s">
+        <v>7109</v>
+      </c>
+    </row>
+    <row r="5387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5387" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5387" s="3" t="s">
+        <v>7110</v>
+      </c>
+    </row>
+    <row r="5388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5388" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5388" s="3" t="s">
+        <v>7111</v>
+      </c>
+    </row>
+    <row r="5389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5389" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5389" s="3" t="s">
+        <v>7112</v>
+      </c>
+    </row>
+    <row r="5390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5390" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5390" s="3" t="s">
+        <v>7113</v>
+      </c>
+    </row>
+    <row r="5391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5391" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5391" s="3" t="s">
+        <v>7114</v>
+      </c>
+    </row>
+    <row r="5392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5392" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5392" s="3" t="s">
+        <v>7116</v>
+      </c>
+    </row>
+    <row r="5393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5393" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5393" s="3" t="s">
+        <v>7117</v>
+      </c>
+    </row>
+    <row r="5394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5394" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5394" s="3" t="s">
+        <v>7118</v>
+      </c>
+    </row>
+    <row r="5395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5395" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5395" s="3" t="s">
+        <v>7119</v>
+      </c>
+    </row>
+    <row r="5396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5396" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5396" s="3" t="s">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="5397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5397" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5397" s="3" t="s">
+        <v>7121</v>
+      </c>
+    </row>
+    <row r="5398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5398" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5398" s="3" t="s">
+        <v>7122</v>
+      </c>
+    </row>
+    <row r="5399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5399" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5399" s="3" t="s">
+        <v>7123</v>
+      </c>
+    </row>
+    <row r="5400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5400" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5400" s="3" t="s">
+        <v>7124</v>
+      </c>
+    </row>
+    <row r="5401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5401" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5401" s="3" t="s">
+        <v>7126</v>
+      </c>
+    </row>
+    <row r="5402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5402" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5402" s="3" t="s">
+        <v>7127</v>
+      </c>
+    </row>
+    <row r="5403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5403" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5403" s="3" t="s">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="5404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5404" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5404" s="3" t="s">
+        <v>7129</v>
+      </c>
+    </row>
+    <row r="5405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5405" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5405" s="3" t="s">
+        <v>7131</v>
+      </c>
+    </row>
+    <row r="5406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5406" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5406" s="3" t="s">
+        <v>7132</v>
+      </c>
+    </row>
+    <row r="5407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5407" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5407" s="3" t="s">
+        <v>7134</v>
+      </c>
+    </row>
+    <row r="5408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5408" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5408" s="3" t="s">
+        <v>7135</v>
+      </c>
+    </row>
+    <row r="5409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5409" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5409" s="3" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="5410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5410" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5410" s="3" t="s">
+        <v>7136</v>
+      </c>
+    </row>
+    <row r="5411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5411" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5411" s="3" t="s">
+        <v>7137</v>
+      </c>
+    </row>
+    <row r="5412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5412" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5412" s="3" t="s">
+        <v>7138</v>
+      </c>
+    </row>
+    <row r="5413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5413" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5413" s="3" t="s">
+        <v>7139</v>
+      </c>
+    </row>
+    <row r="5414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5414" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5414" s="3" t="s">
+        <v>7140</v>
+      </c>
+    </row>
+    <row r="5415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5415" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5415" s="3" t="s">
+        <v>7141</v>
+      </c>
+    </row>
+    <row r="5416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5416" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5416" s="3" t="s">
+        <v>7143</v>
+      </c>
+    </row>
+    <row r="5417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5417" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5417" s="3" t="s">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="5418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5418" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5418" s="3" t="s">
+        <v>7145</v>
+      </c>
+    </row>
+    <row r="5419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5419" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5419" s="3" t="s">
+        <v>7146</v>
+      </c>
+    </row>
+    <row r="5420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5420" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5420" s="3" t="s">
+        <v>7147</v>
+      </c>
+    </row>
+    <row r="5421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5421" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5421" s="3" t="s">
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="5422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5422" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5422" s="3" t="s">
+        <v>7149</v>
+      </c>
+    </row>
+    <row r="5423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5423" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5423" s="3" t="s">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="5424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5424" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5424" s="3" t="s">
+        <v>7151</v>
+      </c>
+    </row>
+    <row r="5425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5425" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5425" s="3" t="s">
+        <v>7152</v>
+      </c>
+    </row>
+    <row r="5426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5426" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5426" s="3" t="s">
+        <v>7153</v>
+      </c>
+    </row>
+    <row r="5427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5427" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5427" s="3" t="s">
+        <v>7154</v>
+      </c>
+    </row>
+    <row r="5428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5428" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5428" s="3" t="s">
+        <v>7155</v>
+      </c>
+    </row>
+    <row r="5429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5429" s="3">
+        <v>7300</v>
+      </c>
+      <c r="C5429" s="3" t="s">
+        <v>7156</v>
+      </c>
+    </row>
+    <row r="5430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5430" s="4">
+        <v>7400</v>
+      </c>
+      <c r="B5430" s="3" t="s">
+        <v>7158</v>
+      </c>
+      <c r="C5430" s="3" t="s">
+        <v>7157</v>
+      </c>
+    </row>
+    <row r="5431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5431" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5432" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5433" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5434" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5435" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5436" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5437" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5438" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5439" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5440" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5441" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5441" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5442" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5442" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5443" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5443" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5444" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5444" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5445" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5445" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5446" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5446" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5447" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5447" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5448" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5448" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5449" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5450" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5451" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5452" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5453" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5454" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5455" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5455" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5456" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5456" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5457" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5457" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5458" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5458" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5459" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5459" s="3">
+        <v>7400</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7018CBF5-81CF-4A4D-9F2D-6C7103D5EB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99714EB-FCE6-4E5C-A98F-230E79C7DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7187" uniqueCount="7159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7287" uniqueCount="7259">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -28654,6 +28654,406 @@
   </si>
   <si>
     <t>quickest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overgrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enlargement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>downhill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idiomatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reckon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chromosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonproductive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grammar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caliber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>junior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>millet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intimacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coalescence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tantamount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inorganic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marvelously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavalry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unacceptable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unprofitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reradiate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weld</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fanners</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attractiveness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unparalleled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saddle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contamination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dyestuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disadvantageous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southerner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vicinity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourcefulness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>micronesian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outrigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>narration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmonious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ironically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marginal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sago</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadfruit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sugarcane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predetermine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nobody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazardous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsuspected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>missionary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underestimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nitrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exportation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extremity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>converse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grounding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spillage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curiously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ashore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redesign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>citizenry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scenario</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duplicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smelter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diamond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pennycress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydroponically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>petiole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mobilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conveniently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paramount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shoshone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salmon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oxfordshire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gaslit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>londoner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microbe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tepee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pawnee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>experimenter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -29056,7 +29456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5459"/>
+  <dimension ref="A1:N5579"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -76779,145 +77179,1045 @@
       <c r="A5431" s="3">
         <v>7400</v>
       </c>
+      <c r="B5431" s="3" t="s">
+        <v>7177</v>
+      </c>
+      <c r="C5431" s="3" t="s">
+        <v>7159</v>
+      </c>
     </row>
     <row r="5432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5432" s="3">
         <v>7400</v>
       </c>
+      <c r="B5432" s="3" t="s">
+        <v>7179</v>
+      </c>
+      <c r="C5432" s="3" t="s">
+        <v>7160</v>
+      </c>
     </row>
     <row r="5433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5433" s="3">
         <v>7400</v>
       </c>
+      <c r="C5433" s="3" t="s">
+        <v>7161</v>
+      </c>
     </row>
     <row r="5434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5434" s="3">
         <v>7400</v>
       </c>
+      <c r="C5434" s="3" t="s">
+        <v>7162</v>
+      </c>
     </row>
     <row r="5435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5435" s="3">
         <v>7400</v>
       </c>
+      <c r="C5435" s="3" t="s">
+        <v>7163</v>
+      </c>
     </row>
     <row r="5436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5436" s="3">
         <v>7400</v>
       </c>
+      <c r="C5436" s="3" t="s">
+        <v>7164</v>
+      </c>
     </row>
     <row r="5437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5437" s="3">
         <v>7400</v>
       </c>
+      <c r="C5437" s="3" t="s">
+        <v>7165</v>
+      </c>
     </row>
     <row r="5438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5438" s="3">
         <v>7400</v>
       </c>
+      <c r="C5438" s="3" t="s">
+        <v>7166</v>
+      </c>
     </row>
     <row r="5439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5439" s="3">
         <v>7400</v>
       </c>
+      <c r="C5439" s="3" t="s">
+        <v>7167</v>
+      </c>
     </row>
     <row r="5440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5440" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5441" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5440" s="3" t="s">
+        <v>7168</v>
+      </c>
+    </row>
+    <row r="5441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5441" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5442" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5441" s="3" t="s">
+        <v>7169</v>
+      </c>
+    </row>
+    <row r="5442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5442" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5443" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5442" s="3" t="s">
+        <v>7170</v>
+      </c>
+    </row>
+    <row r="5443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5443" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5444" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5443" s="3" t="s">
+        <v>7171</v>
+      </c>
+    </row>
+    <row r="5444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5444" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5445" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5444" s="3" t="s">
+        <v>7172</v>
+      </c>
+    </row>
+    <row r="5445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5445" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5446" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5445" s="3" t="s">
+        <v>7173</v>
+      </c>
+    </row>
+    <row r="5446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5446" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5447" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5446" s="3" t="s">
+        <v>7174</v>
+      </c>
+    </row>
+    <row r="5447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5447" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5448" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5447" s="3" t="s">
+        <v>7175</v>
+      </c>
+    </row>
+    <row r="5448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5448" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5448" s="3" t="s">
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="5449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5449" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5449" s="3" t="s">
+        <v>7178</v>
+      </c>
+    </row>
+    <row r="5450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5450" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5450" s="3" t="s">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="5451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5451" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5451" s="3" t="s">
+        <v>7181</v>
+      </c>
+    </row>
+    <row r="5452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5452" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5452" s="3" t="s">
+        <v>7182</v>
+      </c>
+    </row>
+    <row r="5453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5453" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5453" s="3" t="s">
+        <v>7183</v>
+      </c>
+    </row>
+    <row r="5454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5454" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5455" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5454" s="3" t="s">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="5455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5455" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5456" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5455" s="3" t="s">
+        <v>7185</v>
+      </c>
+    </row>
+    <row r="5456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5456" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5457" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5456" s="3" t="s">
+        <v>7186</v>
+      </c>
+    </row>
+    <row r="5457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5457" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5458" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5457" s="3" t="s">
+        <v>7187</v>
+      </c>
+    </row>
+    <row r="5458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5458" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5459" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5458" s="3" t="s">
+        <v>7188</v>
+      </c>
+    </row>
+    <row r="5459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5459" s="3">
         <v>7400</v>
+      </c>
+      <c r="C5459" s="3" t="s">
+        <v>7189</v>
+      </c>
+    </row>
+    <row r="5460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5460" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5460" s="3" t="s">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="5461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5461" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5461" s="3" t="s">
+        <v>7191</v>
+      </c>
+    </row>
+    <row r="5462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5462" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5462" s="3" t="s">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="5463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5463" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5463" s="3" t="s">
+        <v>7193</v>
+      </c>
+    </row>
+    <row r="5464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5464" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5464" s="3" t="s">
+        <v>7194</v>
+      </c>
+    </row>
+    <row r="5465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5465" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5465" s="3" t="s">
+        <v>7195</v>
+      </c>
+    </row>
+    <row r="5466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5466" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5466" s="3" t="s">
+        <v>7196</v>
+      </c>
+    </row>
+    <row r="5467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5467" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5467" s="3" t="s">
+        <v>7197</v>
+      </c>
+    </row>
+    <row r="5468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5468" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5468" s="3" t="s">
+        <v>7198</v>
+      </c>
+    </row>
+    <row r="5469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5469" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5469" s="3" t="s">
+        <v>7199</v>
+      </c>
+    </row>
+    <row r="5470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5470" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5470" s="3" t="s">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="5471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5471" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5471" s="3" t="s">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="5472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5472" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5472" s="3" t="s">
+        <v>7202</v>
+      </c>
+    </row>
+    <row r="5473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5473" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5473" s="3" t="s">
+        <v>7203</v>
+      </c>
+    </row>
+    <row r="5474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5474" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5474" s="3" t="s">
+        <v>7204</v>
+      </c>
+    </row>
+    <row r="5475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5475" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5475" s="3" t="s">
+        <v>7205</v>
+      </c>
+    </row>
+    <row r="5476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5476" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5476" s="3" t="s">
+        <v>7206</v>
+      </c>
+    </row>
+    <row r="5477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5477" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5477" s="3" t="s">
+        <v>7207</v>
+      </c>
+    </row>
+    <row r="5478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5478" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5478" s="3" t="s">
+        <v>7208</v>
+      </c>
+    </row>
+    <row r="5479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5479" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5479" s="3" t="s">
+        <v>7209</v>
+      </c>
+    </row>
+    <row r="5480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5480" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5480" s="3" t="s">
+        <v>7210</v>
+      </c>
+    </row>
+    <row r="5481" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5481" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5481" s="3" t="s">
+        <v>7211</v>
+      </c>
+    </row>
+    <row r="5482" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5482" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5482" s="3" t="s">
+        <v>7212</v>
+      </c>
+    </row>
+    <row r="5483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5483" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5483" s="3" t="s">
+        <v>7213</v>
+      </c>
+    </row>
+    <row r="5484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5484" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5484" s="3" t="s">
+        <v>7214</v>
+      </c>
+    </row>
+    <row r="5485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5485" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5485" s="3" t="s">
+        <v>7215</v>
+      </c>
+    </row>
+    <row r="5486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5486" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5486" s="3" t="s">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="5487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5487" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5487" s="3" t="s">
+        <v>7217</v>
+      </c>
+    </row>
+    <row r="5488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5488" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5488" s="3" t="s">
+        <v>7218</v>
+      </c>
+    </row>
+    <row r="5489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5489" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5489" s="3" t="s">
+        <v>7219</v>
+      </c>
+    </row>
+    <row r="5490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5490" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5490" s="3" t="s">
+        <v>7220</v>
+      </c>
+    </row>
+    <row r="5491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5491" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5491" s="3" t="s">
+        <v>7221</v>
+      </c>
+    </row>
+    <row r="5492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5492" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5492" s="3" t="s">
+        <v>7222</v>
+      </c>
+    </row>
+    <row r="5493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5493" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5493" s="3" t="s">
+        <v>7223</v>
+      </c>
+    </row>
+    <row r="5494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5494" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5494" s="3" t="s">
+        <v>7224</v>
+      </c>
+    </row>
+    <row r="5495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5495" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5495" s="3" t="s">
+        <v>7225</v>
+      </c>
+    </row>
+    <row r="5496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5496" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5496" s="3" t="s">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="5497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5497" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5497" s="3" t="s">
+        <v>7227</v>
+      </c>
+    </row>
+    <row r="5498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5498" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5498" s="3" t="s">
+        <v>7228</v>
+      </c>
+    </row>
+    <row r="5499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5499" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5499" s="3" t="s">
+        <v>7229</v>
+      </c>
+    </row>
+    <row r="5500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5500" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5500" s="3" t="s">
+        <v>7230</v>
+      </c>
+    </row>
+    <row r="5501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5501" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5501" s="3" t="s">
+        <v>7231</v>
+      </c>
+    </row>
+    <row r="5502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5502" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5502" s="3" t="s">
+        <v>7232</v>
+      </c>
+    </row>
+    <row r="5503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5503" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5503" s="3" t="s">
+        <v>7233</v>
+      </c>
+    </row>
+    <row r="5504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5504" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5504" s="3" t="s">
+        <v>7234</v>
+      </c>
+    </row>
+    <row r="5505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5505" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5505" s="3" t="s">
+        <v>7235</v>
+      </c>
+    </row>
+    <row r="5506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5506" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5506" s="3" t="s">
+        <v>7236</v>
+      </c>
+    </row>
+    <row r="5507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5507" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5507" s="3" t="s">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="5508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5508" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5508" s="3" t="s">
+        <v>7238</v>
+      </c>
+    </row>
+    <row r="5509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5509" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5509" s="3" t="s">
+        <v>7239</v>
+      </c>
+    </row>
+    <row r="5510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5510" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5510" s="3" t="s">
+        <v>7240</v>
+      </c>
+    </row>
+    <row r="5511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5511" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5511" s="3" t="s">
+        <v>7241</v>
+      </c>
+    </row>
+    <row r="5512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5512" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5512" s="3" t="s">
+        <v>7242</v>
+      </c>
+    </row>
+    <row r="5513" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5513" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5513" s="3" t="s">
+        <v>7243</v>
+      </c>
+    </row>
+    <row r="5514" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5514" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5514" s="3" t="s">
+        <v>7244</v>
+      </c>
+    </row>
+    <row r="5515" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5515" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5515" s="3" t="s">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="5516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5516" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5516" s="3" t="s">
+        <v>7246</v>
+      </c>
+    </row>
+    <row r="5517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5517" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5517" s="3" t="s">
+        <v>7247</v>
+      </c>
+    </row>
+    <row r="5518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5518" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5518" s="3" t="s">
+        <v>7248</v>
+      </c>
+    </row>
+    <row r="5519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5519" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5519" s="3" t="s">
+        <v>7249</v>
+      </c>
+    </row>
+    <row r="5520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5520" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5520" s="3" t="s">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="5521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5521" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5521" s="3" t="s">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="5522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5522" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5522" s="3" t="s">
+        <v>7252</v>
+      </c>
+    </row>
+    <row r="5523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5523" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5523" s="3" t="s">
+        <v>7253</v>
+      </c>
+    </row>
+    <row r="5524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5524" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5524" s="3" t="s">
+        <v>7254</v>
+      </c>
+    </row>
+    <row r="5525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5525" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5525" s="3" t="s">
+        <v>7255</v>
+      </c>
+    </row>
+    <row r="5526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5526" s="3">
+        <v>7400</v>
+      </c>
+      <c r="C5526" s="3" t="s">
+        <v>7256</v>
+      </c>
+    </row>
+    <row r="5527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5527" s="4">
+        <v>7500</v>
+      </c>
+      <c r="C5527" s="3" t="s">
+        <v>7257</v>
+      </c>
+    </row>
+    <row r="5528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5528" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5528" s="3" t="s">
+        <v>7258</v>
+      </c>
+    </row>
+    <row r="5529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5529" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5530" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5531" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5532" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5533" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5534" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5535" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5536" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5537" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5537" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5538" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5538" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5539" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5539" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5540" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5540" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5541" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5541" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5542" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5542" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5543" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5544" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5544" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5545" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5546" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5546" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5547" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5547" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5548" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5548" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5549" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5549" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5550" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5550" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5551" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5551" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5552" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5552" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5553" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5553" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5554" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5554" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5555" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5556" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5557" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5558" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5559" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5560" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5561" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5562" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5563" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5564" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5565" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5566" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5567" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5568" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5569" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5570" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5571" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5572" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5573" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5574" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5575" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5576" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5577" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5578" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5579" s="3">
+        <v>7500</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99714EB-FCE6-4E5C-A98F-230E79C7DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA1A1E4-13B5-43BE-8358-C85E5BAB8794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7287" uniqueCount="7259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7387" uniqueCount="7358">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -29054,6 +29054,402 @@
   </si>
   <si>
     <t>experimenter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virtual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inanimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>halve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handsomely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outcrop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nucleic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pavement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ascribe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innumerable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>totality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emigration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patriarch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grandeur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everlasting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detritus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>completion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lipid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smoky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primeval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subtraction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concentric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indigenous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remnant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>graceful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toehold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>planetary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cuspidor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>activist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>identification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weakly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doorknob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incessant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>widow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preliminary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tieback</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loyal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afloat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mistrust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interviewer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affectional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>southerly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>covering</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abnormal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shopper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>correspondingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varicolored</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>psychoanalyst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagecraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifeblood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>autobiography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bedpan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>streak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>daughter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentimentalized</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rentable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voluminous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inhibition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innocent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chomp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>civic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inconsistency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perceivable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>posit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incompletely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subjugate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniformitarianism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contributory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -29456,7 +29852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5579"/>
+  <dimension ref="A1:N5679"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -77953,6 +78349,9 @@
       <c r="A5527" s="4">
         <v>7500</v>
       </c>
+      <c r="B5527" s="3" t="s">
+        <v>7259</v>
+      </c>
       <c r="C5527" s="3" t="s">
         <v>7257</v>
       </c>
@@ -77961,6 +78360,9 @@
       <c r="A5528" s="3">
         <v>7500</v>
       </c>
+      <c r="B5528" s="3" t="s">
+        <v>7283</v>
+      </c>
       <c r="C5528" s="3" t="s">
         <v>7258</v>
       </c>
@@ -77969,255 +78371,1049 @@
       <c r="A5529" s="3">
         <v>7500</v>
       </c>
+      <c r="B5529" s="3" t="s">
+        <v>7307</v>
+      </c>
+      <c r="C5529" s="3" t="s">
+        <v>7260</v>
+      </c>
     </row>
     <row r="5530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5530" s="3">
         <v>7500</v>
       </c>
+      <c r="B5530" s="3" t="s">
+        <v>7314</v>
+      </c>
+      <c r="C5530" s="3" t="s">
+        <v>7261</v>
+      </c>
     </row>
     <row r="5531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5531" s="3">
         <v>7500</v>
       </c>
+      <c r="B5531" s="3" t="s">
+        <v>7333</v>
+      </c>
+      <c r="C5531" s="3" t="s">
+        <v>7262</v>
+      </c>
     </row>
     <row r="5532" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5532" s="3">
         <v>7500</v>
       </c>
+      <c r="C5532" s="3" t="s">
+        <v>7263</v>
+      </c>
     </row>
     <row r="5533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5533" s="3">
         <v>7500</v>
       </c>
+      <c r="C5533" s="3" t="s">
+        <v>7264</v>
+      </c>
     </row>
     <row r="5534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5534" s="3">
         <v>7500</v>
       </c>
+      <c r="C5534" s="3" t="s">
+        <v>7265</v>
+      </c>
     </row>
     <row r="5535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5535" s="3">
         <v>7500</v>
       </c>
+      <c r="C5535" s="3" t="s">
+        <v>7266</v>
+      </c>
     </row>
     <row r="5536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5536" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5537" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5536" s="3" t="s">
+        <v>7267</v>
+      </c>
+    </row>
+    <row r="5537" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5537" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5538" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5537" s="3" t="s">
+        <v>7268</v>
+      </c>
+    </row>
+    <row r="5538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5538" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5539" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5538" s="3" t="s">
+        <v>7269</v>
+      </c>
+    </row>
+    <row r="5539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5539" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5540" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5539" s="3" t="s">
+        <v>7270</v>
+      </c>
+    </row>
+    <row r="5540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5540" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5541" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5540" s="3" t="s">
+        <v>7271</v>
+      </c>
+    </row>
+    <row r="5541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5541" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5542" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5541" s="3" t="s">
+        <v>7272</v>
+      </c>
+    </row>
+    <row r="5542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5542" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5542" s="3" t="s">
+        <v>7273</v>
+      </c>
+    </row>
+    <row r="5543" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5543" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5544" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5543" s="3" t="s">
+        <v>7274</v>
+      </c>
+    </row>
+    <row r="5544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5544" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5544" s="3" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="5545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5545" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5546" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5545" s="3" t="s">
+        <v>7275</v>
+      </c>
+    </row>
+    <row r="5546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5546" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5547" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5546" s="3" t="s">
+        <v>7276</v>
+      </c>
+    </row>
+    <row r="5547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5547" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5548" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5547" s="3" t="s">
+        <v>7277</v>
+      </c>
+    </row>
+    <row r="5548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5548" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5549" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5548" s="3" t="s">
+        <v>7278</v>
+      </c>
+    </row>
+    <row r="5549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5549" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5550" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5549" s="3" t="s">
+        <v>7279</v>
+      </c>
+    </row>
+    <row r="5550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5550" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5551" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5550" s="3" t="s">
+        <v>7280</v>
+      </c>
+    </row>
+    <row r="5551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5551" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5552" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5551" s="3" t="s">
+        <v>7281</v>
+      </c>
+    </row>
+    <row r="5552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5552" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5553" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5552" s="3" t="s">
+        <v>7282</v>
+      </c>
+    </row>
+    <row r="5553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5553" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5554" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5553" s="3" t="s">
+        <v>7284</v>
+      </c>
+    </row>
+    <row r="5554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5554" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5554" s="3" t="s">
+        <v>7285</v>
+      </c>
+    </row>
+    <row r="5555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5555" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5555" s="3" t="s">
+        <v>7286</v>
+      </c>
+    </row>
+    <row r="5556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5556" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5556" s="3" t="s">
+        <v>7287</v>
+      </c>
+    </row>
+    <row r="5557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5557" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5557" s="3" t="s">
+        <v>7288</v>
+      </c>
+    </row>
+    <row r="5558" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5558" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5558" s="3" t="s">
+        <v>7289</v>
+      </c>
+    </row>
+    <row r="5559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5559" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5559" s="3" t="s">
+        <v>7290</v>
+      </c>
+    </row>
+    <row r="5560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5560" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5560" s="3" t="s">
+        <v>7291</v>
+      </c>
+    </row>
+    <row r="5561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5561" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5561" s="3" t="s">
+        <v>7292</v>
+      </c>
+    </row>
+    <row r="5562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5562" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5562" s="3" t="s">
+        <v>7293</v>
+      </c>
+    </row>
+    <row r="5563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5563" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5563" s="3" t="s">
+        <v>7294</v>
+      </c>
+    </row>
+    <row r="5564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5564" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5564" s="3" t="s">
+        <v>7295</v>
+      </c>
+    </row>
+    <row r="5565" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5565" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5565" s="3" t="s">
+        <v>7296</v>
+      </c>
+    </row>
+    <row r="5566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5566" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5566" s="3" t="s">
+        <v>7297</v>
+      </c>
+    </row>
+    <row r="5567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5567" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5567" s="3" t="s">
+        <v>7298</v>
+      </c>
+    </row>
+    <row r="5568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5568" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5568" s="3" t="s">
+        <v>7299</v>
+      </c>
+    </row>
+    <row r="5569" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5569" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5569" s="3" t="s">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="5570" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5570" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5570" s="3" t="s">
+        <v>7301</v>
+      </c>
+    </row>
+    <row r="5571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5571" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5571" s="3" t="s">
+        <v>7302</v>
+      </c>
+    </row>
+    <row r="5572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5572" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5572" s="3" t="s">
+        <v>7303</v>
+      </c>
+    </row>
+    <row r="5573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5573" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5573" s="3" t="s">
+        <v>7304</v>
+      </c>
+    </row>
+    <row r="5574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5574" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5574" s="3" t="s">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="5575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5575" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5575" s="3" t="s">
+        <v>7306</v>
+      </c>
+    </row>
+    <row r="5576" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5576" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5576" s="3" t="s">
+        <v>7308</v>
+      </c>
+    </row>
+    <row r="5577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5577" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5577" s="3" t="s">
+        <v>7309</v>
+      </c>
+    </row>
+    <row r="5578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5578" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="5579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5578" s="3" t="s">
+        <v>7310</v>
+      </c>
+    </row>
+    <row r="5579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5579" s="3">
         <v>7500</v>
+      </c>
+      <c r="C5579" s="3" t="s">
+        <v>7311</v>
+      </c>
+    </row>
+    <row r="5580" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5580" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5580" s="3" t="s">
+        <v>7312</v>
+      </c>
+    </row>
+    <row r="5581" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5581" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5581" s="3" t="s">
+        <v>7313</v>
+      </c>
+    </row>
+    <row r="5582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5582" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5582" s="3" t="s">
+        <v>7315</v>
+      </c>
+    </row>
+    <row r="5583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5583" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5583" s="3" t="s">
+        <v>7316</v>
+      </c>
+    </row>
+    <row r="5584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5584" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5584" s="3" t="s">
+        <v>7317</v>
+      </c>
+    </row>
+    <row r="5585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5585" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5585" s="3" t="s">
+        <v>7318</v>
+      </c>
+    </row>
+    <row r="5586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5586" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5586" s="3" t="s">
+        <v>7319</v>
+      </c>
+    </row>
+    <row r="5587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5587" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5587" s="3" t="s">
+        <v>7320</v>
+      </c>
+    </row>
+    <row r="5588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5588" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5588" s="3" t="s">
+        <v>7321</v>
+      </c>
+    </row>
+    <row r="5589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5589" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5589" s="3" t="s">
+        <v>7322</v>
+      </c>
+    </row>
+    <row r="5590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5590" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5590" s="3" t="s">
+        <v>7323</v>
+      </c>
+    </row>
+    <row r="5591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5591" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5591" s="3" t="s">
+        <v>7324</v>
+      </c>
+    </row>
+    <row r="5592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5592" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5592" s="3" t="s">
+        <v>7325</v>
+      </c>
+    </row>
+    <row r="5593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5593" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5593" s="3" t="s">
+        <v>7326</v>
+      </c>
+    </row>
+    <row r="5594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5594" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5594" s="3" t="s">
+        <v>7327</v>
+      </c>
+    </row>
+    <row r="5595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5595" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5595" s="3" t="s">
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="5596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5596" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5596" s="3" t="s">
+        <v>7329</v>
+      </c>
+    </row>
+    <row r="5597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5597" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5597" s="3" t="s">
+        <v>7330</v>
+      </c>
+    </row>
+    <row r="5598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5598" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5598" s="3" t="s">
+        <v>7331</v>
+      </c>
+    </row>
+    <row r="5599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5599" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5599" s="3" t="s">
+        <v>7332</v>
+      </c>
+    </row>
+    <row r="5600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5600" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5600" s="3" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="5601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5601" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5601" s="3" t="s">
+        <v>7335</v>
+      </c>
+    </row>
+    <row r="5602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5602" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5602" s="3" t="s">
+        <v>7336</v>
+      </c>
+    </row>
+    <row r="5603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5603" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5603" s="3" t="s">
+        <v>7337</v>
+      </c>
+    </row>
+    <row r="5604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5604" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5604" s="3" t="s">
+        <v>7338</v>
+      </c>
+    </row>
+    <row r="5605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5605" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5605" s="3" t="s">
+        <v>7339</v>
+      </c>
+    </row>
+    <row r="5606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5606" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5606" s="3" t="s">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="5607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5607" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5607" s="3" t="s">
+        <v>7341</v>
+      </c>
+    </row>
+    <row r="5608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5608" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5608" s="3" t="s">
+        <v>7342</v>
+      </c>
+    </row>
+    <row r="5609" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5609" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5609" s="3" t="s">
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="5610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5610" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5610" s="3" t="s">
+        <v>7344</v>
+      </c>
+    </row>
+    <row r="5611" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5611" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5611" s="3" t="s">
+        <v>7345</v>
+      </c>
+    </row>
+    <row r="5612" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5612" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5612" s="3" t="s">
+        <v>7346</v>
+      </c>
+    </row>
+    <row r="5613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5613" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5613" s="3" t="s">
+        <v>7347</v>
+      </c>
+    </row>
+    <row r="5614" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5614" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5614" s="3" t="s">
+        <v>7348</v>
+      </c>
+    </row>
+    <row r="5615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5615" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5615" s="3" t="s">
+        <v>7349</v>
+      </c>
+    </row>
+    <row r="5616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5616" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5616" s="3" t="s">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="5617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5617" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5617" s="3" t="s">
+        <v>7351</v>
+      </c>
+    </row>
+    <row r="5618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5618" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5618" s="3" t="s">
+        <v>7352</v>
+      </c>
+    </row>
+    <row r="5619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5619" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5619" s="3" t="s">
+        <v>7353</v>
+      </c>
+    </row>
+    <row r="5620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5620" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5620" s="3" t="s">
+        <v>7354</v>
+      </c>
+    </row>
+    <row r="5621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5621" s="3">
+        <v>7500</v>
+      </c>
+      <c r="C5621" s="3" t="s">
+        <v>7355</v>
+      </c>
+    </row>
+    <row r="5622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5622" s="4">
+        <v>7600</v>
+      </c>
+      <c r="C5622" s="3" t="s">
+        <v>7356</v>
+      </c>
+    </row>
+    <row r="5623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5623" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5623" s="3" t="s">
+        <v>7357</v>
+      </c>
+    </row>
+    <row r="5624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5624" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5625" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5626" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5627" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5628" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5629" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5630" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5631" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5632" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5633" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5634" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5635" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5636" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5637" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5638" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5639" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5640" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5641" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5642" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5643" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5644" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5645" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5646" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5647" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5648" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5649" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5650" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5651" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5652" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5653" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5654" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5655" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5656" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5657" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5658" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5659" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5660" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5661" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5662" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5663" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5663" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5664" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5664" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5665" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5665" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5666" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5666" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5667" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5667" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5668" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5668" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5669" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5669" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5670" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5670" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5671" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5671" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5672" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5672" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5673" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5673" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5674" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5674" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5675" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5675" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5676" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5676" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5677" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5677" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5678" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5678" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5679" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5679" s="3">
+        <v>7600</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA1A1E4-13B5-43BE-8358-C85E5BAB8794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67B56DD-EB9C-4BB0-A9EC-F656D14FF09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7387" uniqueCount="7358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7487" uniqueCount="7458">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -29450,6 +29450,406 @@
   </si>
   <si>
     <t>contributory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beloved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunshine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exponent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intellectually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concoct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>darling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seclusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vulnerability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>candid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puritan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regurgitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flatten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>milkweed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divergent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unproven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permafrost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stocky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convergence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conceivably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statistical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Venice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiffany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uproot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refuge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unnatural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>powerfully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nursing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enamel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gossamer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unnecessarily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cube</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monogamous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwieldy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coloration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>butler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caribbean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anatomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pulse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genuinely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bomb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vicissitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantitative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suitably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colorless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flatboat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleanliness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>professionalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monochrome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incessantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightweight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polychrome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coriander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tedium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foothill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>momentous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chateau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provincialism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>husk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seashell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emigrant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsettle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feasibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unending</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eradication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disapproval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>junction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upriver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reorient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neatness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nonnative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intercommunity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>townspeople</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utopian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biogeochemical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homespun</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -29852,7 +30252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5679"/>
+  <dimension ref="A1:N5753"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -79124,6 +79524,9 @@
       <c r="A5622" s="4">
         <v>7600</v>
       </c>
+      <c r="B5622" s="3" t="s">
+        <v>7360</v>
+      </c>
       <c r="C5622" s="3" t="s">
         <v>7356</v>
       </c>
@@ -79132,6 +79535,9 @@
       <c r="A5623" s="3">
         <v>7600</v>
       </c>
+      <c r="B5623" s="3" t="s">
+        <v>7364</v>
+      </c>
       <c r="C5623" s="3" t="s">
         <v>7357</v>
       </c>
@@ -79140,280 +79546,944 @@
       <c r="A5624" s="3">
         <v>7600</v>
       </c>
+      <c r="B5624" s="3" t="s">
+        <v>7385</v>
+      </c>
+      <c r="C5624" s="3" t="s">
+        <v>7358</v>
+      </c>
     </row>
     <row r="5625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5625" s="3">
         <v>7600</v>
       </c>
+      <c r="B5625" s="3" t="s">
+        <v>7441</v>
+      </c>
+      <c r="C5625" s="3" t="s">
+        <v>7359</v>
+      </c>
     </row>
     <row r="5626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5626" s="3">
         <v>7600</v>
       </c>
+      <c r="B5626" s="3" t="s">
+        <v>7442</v>
+      </c>
+      <c r="C5626" s="3" t="s">
+        <v>7361</v>
+      </c>
     </row>
     <row r="5627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5627" s="3">
         <v>7600</v>
       </c>
+      <c r="C5627" s="3" t="s">
+        <v>7362</v>
+      </c>
     </row>
     <row r="5628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5628" s="3">
         <v>7600</v>
       </c>
+      <c r="C5628" s="3" t="s">
+        <v>7363</v>
+      </c>
     </row>
     <row r="5629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5629" s="3">
         <v>7600</v>
       </c>
+      <c r="C5629" s="3" t="s">
+        <v>7365</v>
+      </c>
     </row>
     <row r="5630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5630" s="3">
         <v>7600</v>
       </c>
+      <c r="C5630" s="3" t="s">
+        <v>7366</v>
+      </c>
     </row>
     <row r="5631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5631" s="3">
         <v>7600</v>
       </c>
+      <c r="C5631" s="3" t="s">
+        <v>7367</v>
+      </c>
     </row>
     <row r="5632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5632" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5632" s="3" t="s">
+        <v>7368</v>
+      </c>
+    </row>
+    <row r="5633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5633" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5633" s="3" t="s">
+        <v>7369</v>
+      </c>
+    </row>
+    <row r="5634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5634" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5634" s="3" t="s">
+        <v>7370</v>
+      </c>
+    </row>
+    <row r="5635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5635" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5635" s="3" t="s">
+        <v>7371</v>
+      </c>
+    </row>
+    <row r="5636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5636" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5636" s="3" t="s">
+        <v>7372</v>
+      </c>
+    </row>
+    <row r="5637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5637" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5637" s="3" t="s">
+        <v>7373</v>
+      </c>
+    </row>
+    <row r="5638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5638" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5638" s="3" t="s">
+        <v>7374</v>
+      </c>
+    </row>
+    <row r="5639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5639" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5639" s="3" t="s">
+        <v>7375</v>
+      </c>
+    </row>
+    <row r="5640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5640" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5640" s="3" t="s">
+        <v>7376</v>
+      </c>
+    </row>
+    <row r="5641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5641" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5641" s="3" t="s">
+        <v>7377</v>
+      </c>
+    </row>
+    <row r="5642" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5642" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5642" s="3" t="s">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="5643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5643" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5643" s="3" t="s">
+        <v>7379</v>
+      </c>
+    </row>
+    <row r="5644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5644" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5644" s="3" t="s">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="5645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5645" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5645" s="3" t="s">
+        <v>7381</v>
+      </c>
+    </row>
+    <row r="5646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5646" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5646" s="3" t="s">
+        <v>7382</v>
+      </c>
+    </row>
+    <row r="5647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5647" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5647" s="3" t="s">
+        <v>7383</v>
+      </c>
+    </row>
+    <row r="5648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5648" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5648" s="3" t="s">
+        <v>7384</v>
+      </c>
+    </row>
+    <row r="5649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5649" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5649" s="3" t="s">
+        <v>7386</v>
+      </c>
+    </row>
+    <row r="5650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5650" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5650" s="3" t="s">
+        <v>7387</v>
+      </c>
+    </row>
+    <row r="5651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5651" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5651" s="3" t="s">
+        <v>7388</v>
+      </c>
+    </row>
+    <row r="5652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5652" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5652" s="3" t="s">
+        <v>7389</v>
+      </c>
+    </row>
+    <row r="5653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5653" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5653" s="3" t="s">
+        <v>7390</v>
+      </c>
+    </row>
+    <row r="5654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5654" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5654" s="3" t="s">
+        <v>7391</v>
+      </c>
+    </row>
+    <row r="5655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5655" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5655" s="3" t="s">
+        <v>7392</v>
+      </c>
+    </row>
+    <row r="5656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5656" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5656" s="3" t="s">
+        <v>7393</v>
+      </c>
+    </row>
+    <row r="5657" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5657" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5657" s="3" t="s">
+        <v>7394</v>
+      </c>
+    </row>
+    <row r="5658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5658" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5658" s="3" t="s">
+        <v>7395</v>
+      </c>
+    </row>
+    <row r="5659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5659" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5659" s="3" t="s">
+        <v>7396</v>
+      </c>
+    </row>
+    <row r="5660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5660" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5660" s="3" t="s">
+        <v>7397</v>
+      </c>
+    </row>
+    <row r="5661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5661" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5661" s="3" t="s">
+        <v>7398</v>
+      </c>
+    </row>
+    <row r="5662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5662" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5663" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5662" s="3" t="s">
+        <v>7399</v>
+      </c>
+    </row>
+    <row r="5663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5663" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5664" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5663" s="3" t="s">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="5664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5664" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5665" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5664" s="3" t="s">
+        <v>7401</v>
+      </c>
+    </row>
+    <row r="5665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5665" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5666" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5665" s="3" t="s">
+        <v>7402</v>
+      </c>
+    </row>
+    <row r="5666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5666" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5667" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5666" s="3" t="s">
+        <v>7403</v>
+      </c>
+    </row>
+    <row r="5667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5667" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5668" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5667" s="3" t="s">
+        <v>7404</v>
+      </c>
+    </row>
+    <row r="5668" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5668" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5669" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5668" s="3" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="5669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5669" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5670" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5669" s="3" t="s">
+        <v>7406</v>
+      </c>
+    </row>
+    <row r="5670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5670" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5671" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5670" s="3" t="s">
+        <v>7407</v>
+      </c>
+    </row>
+    <row r="5671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5671" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5672" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5671" s="3" t="s">
+        <v>7408</v>
+      </c>
+    </row>
+    <row r="5672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5672" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5673" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5672" s="3" t="s">
+        <v>7409</v>
+      </c>
+    </row>
+    <row r="5673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5673" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5674" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5673" s="3" t="s">
+        <v>7410</v>
+      </c>
+    </row>
+    <row r="5674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5674" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5675" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5674" s="3" t="s">
+        <v>7411</v>
+      </c>
+    </row>
+    <row r="5675" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5675" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5676" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5675" s="3" t="s">
+        <v>7412</v>
+      </c>
+    </row>
+    <row r="5676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5676" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5677" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5676" s="3" t="s">
+        <v>7413</v>
+      </c>
+    </row>
+    <row r="5677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5677" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5678" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5677" s="3" t="s">
+        <v>7414</v>
+      </c>
+    </row>
+    <row r="5678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5678" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="5679" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5678" s="3" t="s">
+        <v>7415</v>
+      </c>
+    </row>
+    <row r="5679" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5679" s="3">
         <v>7600</v>
+      </c>
+      <c r="C5679" s="3" t="s">
+        <v>7416</v>
+      </c>
+    </row>
+    <row r="5680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5680" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5680" s="3" t="s">
+        <v>7417</v>
+      </c>
+    </row>
+    <row r="5681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5681" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5681" s="3" t="s">
+        <v>7418</v>
+      </c>
+    </row>
+    <row r="5682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5682" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5682" s="3" t="s">
+        <v>7419</v>
+      </c>
+    </row>
+    <row r="5683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5683" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5683" s="3" t="s">
+        <v>7420</v>
+      </c>
+    </row>
+    <row r="5684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5684" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5684" s="3" t="s">
+        <v>7421</v>
+      </c>
+    </row>
+    <row r="5685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5685" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5685" s="3" t="s">
+        <v>7422</v>
+      </c>
+    </row>
+    <row r="5686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5686" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5686" s="3" t="s">
+        <v>7423</v>
+      </c>
+    </row>
+    <row r="5687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5687" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5687" s="3" t="s">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="5688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5688" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5688" s="3" t="s">
+        <v>7425</v>
+      </c>
+    </row>
+    <row r="5689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5689" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5689" s="3" t="s">
+        <v>7426</v>
+      </c>
+    </row>
+    <row r="5690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5690" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5690" s="3" t="s">
+        <v>7427</v>
+      </c>
+    </row>
+    <row r="5691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5691" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5691" s="3" t="s">
+        <v>7428</v>
+      </c>
+    </row>
+    <row r="5692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5692" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5692" s="3" t="s">
+        <v>7429</v>
+      </c>
+    </row>
+    <row r="5693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5693" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5693" s="3" t="s">
+        <v>7430</v>
+      </c>
+    </row>
+    <row r="5694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5694" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5694" s="3" t="s">
+        <v>7431</v>
+      </c>
+    </row>
+    <row r="5695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5695" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5695" s="3" t="s">
+        <v>7432</v>
+      </c>
+    </row>
+    <row r="5696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5696" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5696" s="3" t="s">
+        <v>7433</v>
+      </c>
+    </row>
+    <row r="5697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5697" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5697" s="3" t="s">
+        <v>7434</v>
+      </c>
+    </row>
+    <row r="5698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5698" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5698" s="3" t="s">
+        <v>7435</v>
+      </c>
+    </row>
+    <row r="5699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5699" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5699" s="3" t="s">
+        <v>7436</v>
+      </c>
+    </row>
+    <row r="5700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5700" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5700" s="3" t="s">
+        <v>7437</v>
+      </c>
+    </row>
+    <row r="5701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5701" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5701" s="3" t="s">
+        <v>7438</v>
+      </c>
+    </row>
+    <row r="5702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5702" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5702" s="3" t="s">
+        <v>7439</v>
+      </c>
+    </row>
+    <row r="5703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5703" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5703" s="3" t="s">
+        <v>7440</v>
+      </c>
+    </row>
+    <row r="5704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5704" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5704" s="3" t="s">
+        <v>7443</v>
+      </c>
+    </row>
+    <row r="5705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5705" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5705" s="3" t="s">
+        <v>7444</v>
+      </c>
+    </row>
+    <row r="5706" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5706" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5706" s="3" t="s">
+        <v>7445</v>
+      </c>
+    </row>
+    <row r="5707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5707" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5707" s="3" t="s">
+        <v>7446</v>
+      </c>
+    </row>
+    <row r="5708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5708" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5708" s="3" t="s">
+        <v>7447</v>
+      </c>
+    </row>
+    <row r="5709" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5709" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5709" s="3" t="s">
+        <v>7448</v>
+      </c>
+    </row>
+    <row r="5710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5710" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5710" s="3" t="s">
+        <v>7449</v>
+      </c>
+    </row>
+    <row r="5711" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5711" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5711" s="3" t="s">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="5712" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5712" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5712" s="3" t="s">
+        <v>7451</v>
+      </c>
+    </row>
+    <row r="5713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5713" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5713" s="3" t="s">
+        <v>7452</v>
+      </c>
+    </row>
+    <row r="5714" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5714" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5714" s="3" t="s">
+        <v>7453</v>
+      </c>
+    </row>
+    <row r="5715" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5715" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5715" s="3" t="s">
+        <v>7454</v>
+      </c>
+    </row>
+    <row r="5716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5716" s="3">
+        <v>7600</v>
+      </c>
+      <c r="C5716" s="3" t="s">
+        <v>7455</v>
+      </c>
+    </row>
+    <row r="5717" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5717" s="4">
+        <v>7700</v>
+      </c>
+      <c r="C5717" s="3" t="s">
+        <v>7456</v>
+      </c>
+    </row>
+    <row r="5718" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5718" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5718" s="3" t="s">
+        <v>7457</v>
+      </c>
+    </row>
+    <row r="5719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5719" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5720" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5720" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5721" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5721" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5722" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5722" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5723" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5723" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5724" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5724" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5725" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5726" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5726" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5727" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5727" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5728" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5729" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5730" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5730" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5731" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5731" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5732" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5732" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5733" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5733" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5734" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5734" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5735" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5735" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5736" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5736" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5737" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5737" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5738" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5738" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5739" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5739" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5740" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5740" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5741" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5741" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5742" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5742" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5743" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5743" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5744" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5744" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5745" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5745" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5746" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5746" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5747" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5747" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5748" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5748" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5749" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5749" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5750" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5750" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5751" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5751" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5752" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5752" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5753" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5753" s="3">
+        <v>7700</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67B56DD-EB9C-4BB0-A9EC-F656D14FF09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A580D4CD-8E6A-4584-B961-E13437D00DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7487" uniqueCount="7458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7587" uniqueCount="7558">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -29850,6 +29850,406 @@
   </si>
   <si>
     <t>homespun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwelcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avoidable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>referee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predetermined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unselective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensitively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authenticity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discredit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superorganisms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>floodplain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preservative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insightful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misdeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salmonberry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snugly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dripstone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterexample</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dapple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multifaceted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flesh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alluvial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rootless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fecund</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proliferation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>petticoat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reluctant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stratify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basketwork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commercialization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acidity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diligence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>separable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thimble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cyclic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buyer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmfully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boxlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amazingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinhole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admittedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maternal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wintertime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pliable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthropologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bachelor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>literate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>totemism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enigmatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illiterate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inquire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proclivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awkwardly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>escutcheon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horticulturalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reunion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alphabetically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carelessly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supermodel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brusquely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stubble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chihuahua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morphological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reactive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Philippine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geothermally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subfreezing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anthropomorphism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mansion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awkward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constraint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confinement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>centrally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adversity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imaginative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incapacitated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onslaught</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -30252,7 +30652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5753"/>
+  <dimension ref="A1:N5849"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -80299,6 +80699,9 @@
       <c r="A5717" s="4">
         <v>7700</v>
       </c>
+      <c r="B5717" s="3" t="s">
+        <v>7458</v>
+      </c>
       <c r="C5717" s="3" t="s">
         <v>7456</v>
       </c>
@@ -80307,6 +80710,9 @@
       <c r="A5718" s="3">
         <v>7700</v>
       </c>
+      <c r="B5718" s="3" t="s">
+        <v>7503</v>
+      </c>
       <c r="C5718" s="3" t="s">
         <v>7457</v>
       </c>
@@ -80315,175 +80721,949 @@
       <c r="A5719" s="3">
         <v>7700</v>
       </c>
+      <c r="C5719" s="3" t="s">
+        <v>7459</v>
+      </c>
     </row>
     <row r="5720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5720" s="3">
         <v>7700</v>
       </c>
+      <c r="C5720" s="3" t="s">
+        <v>7460</v>
+      </c>
     </row>
     <row r="5721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5721" s="3">
         <v>7700</v>
       </c>
+      <c r="C5721" s="3" t="s">
+        <v>7461</v>
+      </c>
     </row>
     <row r="5722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5722" s="3">
         <v>7700</v>
       </c>
+      <c r="C5722" s="3" t="s">
+        <v>7462</v>
+      </c>
     </row>
     <row r="5723" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5723" s="3">
         <v>7700</v>
       </c>
+      <c r="C5723" s="3" t="s">
+        <v>7463</v>
+      </c>
     </row>
     <row r="5724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5724" s="3">
         <v>7700</v>
       </c>
+      <c r="C5724" s="3" t="s">
+        <v>7464</v>
+      </c>
     </row>
     <row r="5725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5725" s="3">
         <v>7700</v>
       </c>
+      <c r="C5725" s="3" t="s">
+        <v>7465</v>
+      </c>
     </row>
     <row r="5726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5726" s="3">
         <v>7700</v>
       </c>
+      <c r="C5726" s="3" t="s">
+        <v>7466</v>
+      </c>
     </row>
     <row r="5727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5727" s="3">
         <v>7700</v>
       </c>
+      <c r="C5727" s="3" t="s">
+        <v>7467</v>
+      </c>
     </row>
     <row r="5728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5728" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5728" s="3" t="s">
+        <v>7468</v>
+      </c>
+    </row>
+    <row r="5729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5729" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5730" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5729" s="3" t="s">
+        <v>7469</v>
+      </c>
+    </row>
+    <row r="5730" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5730" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5731" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5730" s="3" t="s">
+        <v>7470</v>
+      </c>
+    </row>
+    <row r="5731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5731" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5732" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5731" s="3" t="s">
+        <v>7471</v>
+      </c>
+    </row>
+    <row r="5732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5732" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5733" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5732" s="3" t="s">
+        <v>7472</v>
+      </c>
+    </row>
+    <row r="5733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5733" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5734" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5733" s="3" t="s">
+        <v>7473</v>
+      </c>
+    </row>
+    <row r="5734" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5734" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5735" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5734" s="3" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="5735" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5735" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5736" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5735" s="3" t="s">
+        <v>7475</v>
+      </c>
+    </row>
+    <row r="5736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5736" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5737" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5736" s="3" t="s">
+        <v>7476</v>
+      </c>
+    </row>
+    <row r="5737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5737" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5738" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5737" s="3" t="s">
+        <v>7477</v>
+      </c>
+    </row>
+    <row r="5738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5738" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5739" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5738" s="3" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="5739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5739" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5740" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5739" s="3" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="5740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5740" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5741" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5740" s="3" t="s">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="5741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5741" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5742" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5741" s="3" t="s">
+        <v>7481</v>
+      </c>
+    </row>
+    <row r="5742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5742" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5743" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5742" s="3" t="s">
+        <v>7482</v>
+      </c>
+    </row>
+    <row r="5743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5743" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5744" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5743" s="3" t="s">
+        <v>7483</v>
+      </c>
+    </row>
+    <row r="5744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5744" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5745" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5744" s="3" t="s">
+        <v>7484</v>
+      </c>
+    </row>
+    <row r="5745" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5745" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5746" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5745" s="3" t="s">
+        <v>7485</v>
+      </c>
+    </row>
+    <row r="5746" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5746" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5747" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5746" s="3" t="s">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="5747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5747" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5748" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5747" s="3" t="s">
+        <v>7487</v>
+      </c>
+    </row>
+    <row r="5748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5748" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5749" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5748" s="3" t="s">
+        <v>7488</v>
+      </c>
+    </row>
+    <row r="5749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5749" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5750" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5749" s="3" t="s">
+        <v>7489</v>
+      </c>
+    </row>
+    <row r="5750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5750" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5751" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5750" s="3" t="s">
+        <v>7490</v>
+      </c>
+    </row>
+    <row r="5751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5751" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5752" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5751" s="3" t="s">
+        <v>7491</v>
+      </c>
+    </row>
+    <row r="5752" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5752" s="3">
         <v>7700</v>
       </c>
-    </row>
-    <row r="5753" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5752" s="3" t="s">
+        <v>7492</v>
+      </c>
+    </row>
+    <row r="5753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5753" s="3">
         <v>7700</v>
+      </c>
+      <c r="C5753" s="3" t="s">
+        <v>7493</v>
+      </c>
+    </row>
+    <row r="5754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5754" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5754" s="3" t="s">
+        <v>7494</v>
+      </c>
+    </row>
+    <row r="5755" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5755" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5755" s="3" t="s">
+        <v>7495</v>
+      </c>
+    </row>
+    <row r="5756" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5756" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5756" s="3" t="s">
+        <v>7496</v>
+      </c>
+    </row>
+    <row r="5757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5757" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5757" s="3" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="5758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5758" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5758" s="3" t="s">
+        <v>7498</v>
+      </c>
+    </row>
+    <row r="5759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5759" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5759" s="3" t="s">
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="5760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5760" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5760" s="3" t="s">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5761" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5761" s="3" t="s">
+        <v>7501</v>
+      </c>
+    </row>
+    <row r="5762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5762" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5762" s="3" t="s">
+        <v>7502</v>
+      </c>
+    </row>
+    <row r="5763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5763" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5763" s="3" t="s">
+        <v>7504</v>
+      </c>
+    </row>
+    <row r="5764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5764" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5764" s="3" t="s">
+        <v>7505</v>
+      </c>
+    </row>
+    <row r="5765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5765" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5765" s="3" t="s">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="5766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5766" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5766" s="3" t="s">
+        <v>7507</v>
+      </c>
+    </row>
+    <row r="5767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5767" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5767" s="3" t="s">
+        <v>7508</v>
+      </c>
+    </row>
+    <row r="5768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5768" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5768" s="3" t="s">
+        <v>7509</v>
+      </c>
+    </row>
+    <row r="5769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5769" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5769" s="3" t="s">
+        <v>7510</v>
+      </c>
+    </row>
+    <row r="5770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5770" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5770" s="3" t="s">
+        <v>7511</v>
+      </c>
+    </row>
+    <row r="5771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5771" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5771" s="3" t="s">
+        <v>7512</v>
+      </c>
+    </row>
+    <row r="5772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5772" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5772" s="3" t="s">
+        <v>7513</v>
+      </c>
+    </row>
+    <row r="5773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5773" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5773" s="3" t="s">
+        <v>7514</v>
+      </c>
+    </row>
+    <row r="5774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5774" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5774" s="3" t="s">
+        <v>7515</v>
+      </c>
+    </row>
+    <row r="5775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5775" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5775" s="3" t="s">
+        <v>7516</v>
+      </c>
+    </row>
+    <row r="5776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5776" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5776" s="3" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="5777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5777" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5777" s="3" t="s">
+        <v>7518</v>
+      </c>
+    </row>
+    <row r="5778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5778" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5778" s="3" t="s">
+        <v>7519</v>
+      </c>
+    </row>
+    <row r="5779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5779" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5779" s="3" t="s">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="5780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5780" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5780" s="3" t="s">
+        <v>7521</v>
+      </c>
+    </row>
+    <row r="5781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5781" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5781" s="3" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="5782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5782" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5782" s="3" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="5783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5783" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5783" s="3" t="s">
+        <v>7524</v>
+      </c>
+    </row>
+    <row r="5784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5784" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5784" s="3" t="s">
+        <v>7525</v>
+      </c>
+    </row>
+    <row r="5785" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5785" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5785" s="3" t="s">
+        <v>7526</v>
+      </c>
+    </row>
+    <row r="5786" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5786" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5786" s="3" t="s">
+        <v>7527</v>
+      </c>
+    </row>
+    <row r="5787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5787" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5787" s="3" t="s">
+        <v>7528</v>
+      </c>
+    </row>
+    <row r="5788" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5788" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5788" s="3" t="s">
+        <v>7529</v>
+      </c>
+    </row>
+    <row r="5789" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5789" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5789" s="3" t="s">
+        <v>7530</v>
+      </c>
+    </row>
+    <row r="5790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5790" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5790" s="3" t="s">
+        <v>7531</v>
+      </c>
+    </row>
+    <row r="5791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5791" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5791" s="3" t="s">
+        <v>7532</v>
+      </c>
+    </row>
+    <row r="5792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5792" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5792" s="3" t="s">
+        <v>7533</v>
+      </c>
+    </row>
+    <row r="5793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5793" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5793" s="3" t="s">
+        <v>7534</v>
+      </c>
+    </row>
+    <row r="5794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5794" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5794" s="3" t="s">
+        <v>7535</v>
+      </c>
+    </row>
+    <row r="5795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5795" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5795" s="3" t="s">
+        <v>7536</v>
+      </c>
+    </row>
+    <row r="5796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5796" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5796" s="3" t="s">
+        <v>7537</v>
+      </c>
+    </row>
+    <row r="5797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5797" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5797" s="3" t="s">
+        <v>7538</v>
+      </c>
+    </row>
+    <row r="5798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5798" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5798" s="3" t="s">
+        <v>7539</v>
+      </c>
+    </row>
+    <row r="5799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5799" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5799" s="3" t="s">
+        <v>7540</v>
+      </c>
+    </row>
+    <row r="5800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5800" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5800" s="3" t="s">
+        <v>7541</v>
+      </c>
+    </row>
+    <row r="5801" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5801" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5801" s="3" t="s">
+        <v>7542</v>
+      </c>
+    </row>
+    <row r="5802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5802" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5802" s="3" t="s">
+        <v>7543</v>
+      </c>
+    </row>
+    <row r="5803" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5803" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5803" s="3" t="s">
+        <v>7544</v>
+      </c>
+    </row>
+    <row r="5804" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5804" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5804" s="3" t="s">
+        <v>7545</v>
+      </c>
+    </row>
+    <row r="5805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5805" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5805" s="3" t="s">
+        <v>7546</v>
+      </c>
+    </row>
+    <row r="5806" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5806" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5806" s="3" t="s">
+        <v>7547</v>
+      </c>
+    </row>
+    <row r="5807" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5807" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5807" s="3" t="s">
+        <v>7548</v>
+      </c>
+    </row>
+    <row r="5808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5808" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5808" s="3" t="s">
+        <v>7549</v>
+      </c>
+    </row>
+    <row r="5809" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5809" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5809" s="3" t="s">
+        <v>7550</v>
+      </c>
+    </row>
+    <row r="5810" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5810" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5810" s="3" t="s">
+        <v>7551</v>
+      </c>
+    </row>
+    <row r="5811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5811" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5811" s="3" t="s">
+        <v>7552</v>
+      </c>
+    </row>
+    <row r="5812" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5812" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5812" s="3" t="s">
+        <v>7553</v>
+      </c>
+    </row>
+    <row r="5813" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5813" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5813" s="3" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="5814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5814" s="3">
+        <v>7700</v>
+      </c>
+      <c r="C5814" s="3" t="s">
+        <v>7555</v>
+      </c>
+    </row>
+    <row r="5815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5815" s="4">
+        <v>7800</v>
+      </c>
+      <c r="C5815" s="3" t="s">
+        <v>7556</v>
+      </c>
+    </row>
+    <row r="5816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5816" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5816" s="3" t="s">
+        <v>7557</v>
+      </c>
+    </row>
+    <row r="5817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5817" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5818" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5818" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5819" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5819" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5820" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5821" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5821" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5822" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5822" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5823" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5824" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5825" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5825" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5826" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5826" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5827" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5827" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5828" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5828" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5829" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5829" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5830" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5830" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5831" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5831" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5832" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5832" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5833" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5833" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5834" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5834" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5835" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5835" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5836" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5836" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5837" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5837" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5838" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5838" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5839" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5839" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5840" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5840" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5841" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5841" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5842" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5842" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5843" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5843" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5844" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5844" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5845" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5845" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5846" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5846" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5847" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5847" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5848" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5848" s="3">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5849" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5849" s="3">
+        <v>7800</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A580D4CD-8E6A-4584-B961-E13437D00DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84D0EE5-C5E3-439D-A787-E9BD834442EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7587" uniqueCount="7558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7687" uniqueCount="7657">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -30250,6 +30250,402 @@
   </si>
   <si>
     <t>onslaught</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrialist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soloist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interstitial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intertidal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refreshment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sickness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patrol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intertwine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>morale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incompatible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buddy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pristine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sludge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swiss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hallmark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vibrato</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sparrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blackbird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhythmic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lacuna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enigma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tendon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fiddler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carnival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assemblage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saucer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dedication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualitatively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redwing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vigilance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adventurous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telltale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordinance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tether</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overestimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syrup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gild</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ductile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anonymous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grateful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sewerage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urbanity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avoidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permineralization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amenable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>binge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immerse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quicksand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modernization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cabbage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>malleable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>einkorn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carrot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unanticipated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pistachio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dredge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>propriety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glassware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affluent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>courtyard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>singleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrestle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nationalistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soothe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deteriorates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabilization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>joinery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stride</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windswept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swiftness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radioactivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seabird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reykjavik</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polarize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>degas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>midnight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utah</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trickle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admiral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hydrosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geyser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabilizer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exoskeleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dimply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clamor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enjoyable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -30652,7 +31048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5849"/>
+  <dimension ref="A1:N5939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -81489,6 +81885,9 @@
       <c r="A5815" s="4">
         <v>7800</v>
       </c>
+      <c r="B5815" s="3" t="s">
+        <v>7564</v>
+      </c>
       <c r="C5815" s="3" t="s">
         <v>7556</v>
       </c>
@@ -81497,6 +81896,9 @@
       <c r="A5816" s="3">
         <v>7800</v>
       </c>
+      <c r="B5816" s="3" t="s">
+        <v>7604</v>
+      </c>
       <c r="C5816" s="3" t="s">
         <v>7557</v>
       </c>
@@ -81505,165 +81907,909 @@
       <c r="A5817" s="3">
         <v>7800</v>
       </c>
+      <c r="B5817" s="3" t="s">
+        <v>7644</v>
+      </c>
+      <c r="C5817" s="3" t="s">
+        <v>7558</v>
+      </c>
     </row>
     <row r="5818" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5818" s="3">
         <v>7800</v>
       </c>
+      <c r="C5818" s="3" t="s">
+        <v>7559</v>
+      </c>
     </row>
     <row r="5819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5819" s="3">
         <v>7800</v>
       </c>
+      <c r="C5819" s="3" t="s">
+        <v>7560</v>
+      </c>
     </row>
     <row r="5820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5820" s="3">
         <v>7800</v>
       </c>
+      <c r="C5820" s="3" t="s">
+        <v>7561</v>
+      </c>
     </row>
     <row r="5821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5821" s="3">
         <v>7800</v>
       </c>
+      <c r="C5821" s="3" t="s">
+        <v>7562</v>
+      </c>
     </row>
     <row r="5822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5822" s="3">
         <v>7800</v>
       </c>
+      <c r="C5822" s="3" t="s">
+        <v>7563</v>
+      </c>
     </row>
     <row r="5823" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5823" s="3">
         <v>7800</v>
       </c>
+      <c r="C5823" s="3" t="s">
+        <v>7565</v>
+      </c>
     </row>
     <row r="5824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5824" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5825" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5824" s="3" t="s">
+        <v>7566</v>
+      </c>
+    </row>
+    <row r="5825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5825" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5826" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5825" s="3" t="s">
+        <v>7567</v>
+      </c>
+    </row>
+    <row r="5826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5826" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5827" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5826" s="3" t="s">
+        <v>7568</v>
+      </c>
+    </row>
+    <row r="5827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5827" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5828" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5827" s="3" t="s">
+        <v>7569</v>
+      </c>
+    </row>
+    <row r="5828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5828" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5829" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5828" s="3" t="s">
+        <v>7570</v>
+      </c>
+    </row>
+    <row r="5829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5829" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5830" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5829" s="3" t="s">
+        <v>7571</v>
+      </c>
+    </row>
+    <row r="5830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5830" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5831" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5830" s="3" t="s">
+        <v>7572</v>
+      </c>
+    </row>
+    <row r="5831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5831" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5832" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5831" s="3" t="s">
+        <v>7573</v>
+      </c>
+    </row>
+    <row r="5832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5832" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5833" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5832" s="3" t="s">
+        <v>7574</v>
+      </c>
+    </row>
+    <row r="5833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5833" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5834" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5833" s="3" t="s">
+        <v>7575</v>
+      </c>
+    </row>
+    <row r="5834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5834" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5835" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5834" s="3" t="s">
+        <v>7576</v>
+      </c>
+    </row>
+    <row r="5835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5835" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5836" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5835" s="3" t="s">
+        <v>7577</v>
+      </c>
+    </row>
+    <row r="5836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5836" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5837" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5836" s="3" t="s">
+        <v>7578</v>
+      </c>
+    </row>
+    <row r="5837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5837" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5838" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5837" s="3" t="s">
+        <v>7579</v>
+      </c>
+    </row>
+    <row r="5838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5838" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5839" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5838" s="3" t="s">
+        <v>7580</v>
+      </c>
+    </row>
+    <row r="5839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5839" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5840" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5839" s="3" t="s">
+        <v>7581</v>
+      </c>
+    </row>
+    <row r="5840" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5840" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5841" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5840" s="3" t="s">
+        <v>7582</v>
+      </c>
+    </row>
+    <row r="5841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5841" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5842" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5841" s="3" t="s">
+        <v>7583</v>
+      </c>
+    </row>
+    <row r="5842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5842" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5843" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5842" s="3" t="s">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="5843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5843" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5844" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5843" s="3" t="s">
+        <v>7585</v>
+      </c>
+    </row>
+    <row r="5844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5844" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5845" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5844" s="3" t="s">
+        <v>7586</v>
+      </c>
+    </row>
+    <row r="5845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5845" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5846" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5845" s="3" t="s">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="5846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5846" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5847" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5846" s="3" t="s">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="5847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5847" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5848" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5847" s="3" t="s">
+        <v>7588</v>
+      </c>
+    </row>
+    <row r="5848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5848" s="3">
         <v>7800</v>
       </c>
-    </row>
-    <row r="5849" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5848" s="3" t="s">
+        <v>7589</v>
+      </c>
+    </row>
+    <row r="5849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5849" s="3">
         <v>7800</v>
+      </c>
+      <c r="C5849" s="3" t="s">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="5850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5850" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5850" s="3" t="s">
+        <v>7591</v>
+      </c>
+    </row>
+    <row r="5851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5851" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5851" s="3" t="s">
+        <v>7592</v>
+      </c>
+    </row>
+    <row r="5852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5852" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5852" s="3" t="s">
+        <v>7593</v>
+      </c>
+    </row>
+    <row r="5853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5853" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5853" s="3" t="s">
+        <v>7594</v>
+      </c>
+    </row>
+    <row r="5854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5854" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5854" s="3" t="s">
+        <v>7595</v>
+      </c>
+    </row>
+    <row r="5855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5855" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5855" s="3" t="s">
+        <v>7596</v>
+      </c>
+    </row>
+    <row r="5856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5856" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5856" s="3" t="s">
+        <v>7597</v>
+      </c>
+    </row>
+    <row r="5857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5857" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5857" s="3" t="s">
+        <v>7598</v>
+      </c>
+    </row>
+    <row r="5858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5858" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5858" s="3" t="s">
+        <v>7599</v>
+      </c>
+    </row>
+    <row r="5859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5859" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5859" s="3" t="s">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="5860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5860" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5860" s="3" t="s">
+        <v>7601</v>
+      </c>
+    </row>
+    <row r="5861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5861" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5861" s="3" t="s">
+        <v>7602</v>
+      </c>
+    </row>
+    <row r="5862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5862" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5862" s="3" t="s">
+        <v>7603</v>
+      </c>
+    </row>
+    <row r="5863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5863" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5863" s="3" t="s">
+        <v>7605</v>
+      </c>
+    </row>
+    <row r="5864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5864" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5864" s="3" t="s">
+        <v>7606</v>
+      </c>
+    </row>
+    <row r="5865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5865" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5865" s="3" t="s">
+        <v>7607</v>
+      </c>
+    </row>
+    <row r="5866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5866" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5866" s="3" t="s">
+        <v>7608</v>
+      </c>
+    </row>
+    <row r="5867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5867" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5867" s="3" t="s">
+        <v>7609</v>
+      </c>
+    </row>
+    <row r="5868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5868" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5868" s="3" t="s">
+        <v>7610</v>
+      </c>
+    </row>
+    <row r="5869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5869" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5869" s="3" t="s">
+        <v>7611</v>
+      </c>
+    </row>
+    <row r="5870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5870" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5870" s="3" t="s">
+        <v>7612</v>
+      </c>
+    </row>
+    <row r="5871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5871" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5871" s="3" t="s">
+        <v>7613</v>
+      </c>
+    </row>
+    <row r="5872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5872" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5872" s="3" t="s">
+        <v>7614</v>
+      </c>
+    </row>
+    <row r="5873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5873" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5873" s="3" t="s">
+        <v>7615</v>
+      </c>
+    </row>
+    <row r="5874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5874" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5874" s="3" t="s">
+        <v>7616</v>
+      </c>
+    </row>
+    <row r="5875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5875" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5875" s="3" t="s">
+        <v>7617</v>
+      </c>
+    </row>
+    <row r="5876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5876" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5876" s="3" t="s">
+        <v>7618</v>
+      </c>
+    </row>
+    <row r="5877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5877" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5877" s="3" t="s">
+        <v>7619</v>
+      </c>
+    </row>
+    <row r="5878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5878" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5878" s="3" t="s">
+        <v>7620</v>
+      </c>
+    </row>
+    <row r="5879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5879" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5879" s="3" t="s">
+        <v>7621</v>
+      </c>
+    </row>
+    <row r="5880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5880" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5880" s="3" t="s">
+        <v>7622</v>
+      </c>
+    </row>
+    <row r="5881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5881" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5881" s="3" t="s">
+        <v>7623</v>
+      </c>
+    </row>
+    <row r="5882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5882" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5882" s="3" t="s">
+        <v>7624</v>
+      </c>
+    </row>
+    <row r="5883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5883" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5883" s="3" t="s">
+        <v>7625</v>
+      </c>
+    </row>
+    <row r="5884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5884" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5884" s="3" t="s">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="5885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5885" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5885" s="3" t="s">
+        <v>7627</v>
+      </c>
+    </row>
+    <row r="5886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5886" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5886" s="3" t="s">
+        <v>7628</v>
+      </c>
+    </row>
+    <row r="5887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5887" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5887" s="3" t="s">
+        <v>7629</v>
+      </c>
+    </row>
+    <row r="5888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5888" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5888" s="3" t="s">
+        <v>7630</v>
+      </c>
+    </row>
+    <row r="5889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5889" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5889" s="3" t="s">
+        <v>7631</v>
+      </c>
+    </row>
+    <row r="5890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5890" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5890" s="3" t="s">
+        <v>7632</v>
+      </c>
+    </row>
+    <row r="5891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5891" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5891" s="3" t="s">
+        <v>7633</v>
+      </c>
+    </row>
+    <row r="5892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5892" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5892" s="3" t="s">
+        <v>7634</v>
+      </c>
+    </row>
+    <row r="5893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5893" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5893" s="3" t="s">
+        <v>7635</v>
+      </c>
+    </row>
+    <row r="5894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5894" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5894" s="3" t="s">
+        <v>7636</v>
+      </c>
+    </row>
+    <row r="5895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5895" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5895" s="3" t="s">
+        <v>7637</v>
+      </c>
+    </row>
+    <row r="5896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5896" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5896" s="3" t="s">
+        <v>7638</v>
+      </c>
+    </row>
+    <row r="5897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5897" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5897" s="3" t="s">
+        <v>7639</v>
+      </c>
+    </row>
+    <row r="5898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5898" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5898" s="3" t="s">
+        <v>7640</v>
+      </c>
+    </row>
+    <row r="5899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5899" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5899" s="3" t="s">
+        <v>7641</v>
+      </c>
+    </row>
+    <row r="5900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5900" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5900" s="3" t="s">
+        <v>7642</v>
+      </c>
+    </row>
+    <row r="5901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5901" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5901" s="3" t="s">
+        <v>7643</v>
+      </c>
+    </row>
+    <row r="5902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5902" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5902" s="3" t="s">
+        <v>7645</v>
+      </c>
+    </row>
+    <row r="5903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5903" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5903" s="3" t="s">
+        <v>7646</v>
+      </c>
+    </row>
+    <row r="5904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5904" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5904" s="3" t="s">
+        <v>7647</v>
+      </c>
+    </row>
+    <row r="5905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5905" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5905" s="3" t="s">
+        <v>7648</v>
+      </c>
+    </row>
+    <row r="5906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5906" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5906" s="3" t="s">
+        <v>7649</v>
+      </c>
+    </row>
+    <row r="5907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5907" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5907" s="3" t="s">
+        <v>7650</v>
+      </c>
+    </row>
+    <row r="5908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5908" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5908" s="3" t="s">
+        <v>7651</v>
+      </c>
+    </row>
+    <row r="5909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5909" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5909" s="3" t="s">
+        <v>7652</v>
+      </c>
+    </row>
+    <row r="5910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5910" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5910" s="3" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="5911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5911" s="3">
+        <v>7800</v>
+      </c>
+      <c r="C5911" s="3" t="s">
+        <v>7654</v>
+      </c>
+    </row>
+    <row r="5912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5912" s="4">
+        <v>7900</v>
+      </c>
+      <c r="B5912" s="3" t="s">
+        <v>7656</v>
+      </c>
+      <c r="C5912" s="3" t="s">
+        <v>7655</v>
+      </c>
+    </row>
+    <row r="5913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5913" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5914" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5915" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5916" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5917" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5918" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5919" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5920" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5921" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5921" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5922" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5922" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5923" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5923" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5924" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5924" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5925" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5925" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5926" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5926" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5927" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5927" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5928" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5928" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5929" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5929" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5930" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5930" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5931" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5931" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5932" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5932" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5933" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5933" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5934" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5934" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5935" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5935" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5936" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5936" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5937" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5937" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5938" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5938" s="3">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="5939" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5939" s="3">
+        <v>7900</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84D0EE5-C5E3-439D-A787-E9BD834442EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592A9F19-578B-4940-A0FB-FB6E49EF1E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7687" uniqueCount="7657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7787" uniqueCount="7756">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -30646,6 +30646,402 @@
   </si>
   <si>
     <t>enjoyable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reluctantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overbalance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carbonization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marshland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viscera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superbly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oxygen-deficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shipwright</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ghostly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conservatism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blacken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fiercely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faultfinding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steadfastly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>untold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intolerant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encapsulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evanescent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archipelago</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usefully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encyclopedia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multivolume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supportive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anathema</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>patty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workmanship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>documentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>untraditional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoughtless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>modernist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bergere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mainstream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>photojournalism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>souvenir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regionalist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reportedly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reachable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paradox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stratosphere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Americana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desirability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inflexibly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implausible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convincingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwillingness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stronghold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vitality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restatement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constituency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eclectic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preparedness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrinkle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eyeball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persuasive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoughtfully</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eventually</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unbiased</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>square</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plethora</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>openly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conditioner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dung</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>substantive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>automatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replenishment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fanner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>globally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invigorate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>civet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>untrue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dolphin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rephrase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overproduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replica</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aridity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>therapist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attacker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regrettable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>schist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thai</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loyally</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31048,7 +31444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N5939"/>
+  <dimension ref="A1:N6033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -82681,135 +83077,905 @@
       <c r="A5913" s="3">
         <v>7900</v>
       </c>
+      <c r="B5913" s="3" t="s">
+        <v>7672</v>
+      </c>
+      <c r="C5913" s="3" t="s">
+        <v>7657</v>
+      </c>
     </row>
     <row r="5914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5914" s="3">
         <v>7900</v>
       </c>
+      <c r="B5914" s="3" t="s">
+        <v>7673</v>
+      </c>
+      <c r="C5914" s="3" t="s">
+        <v>7658</v>
+      </c>
     </row>
     <row r="5915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5915" s="3">
         <v>7900</v>
       </c>
+      <c r="B5915" s="3" t="s">
+        <v>7685</v>
+      </c>
+      <c r="C5915" s="3" t="s">
+        <v>7659</v>
+      </c>
     </row>
     <row r="5916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5916" s="3">
         <v>7900</v>
       </c>
+      <c r="B5916" s="3" t="s">
+        <v>7737</v>
+      </c>
+      <c r="C5916" s="3" t="s">
+        <v>7660</v>
+      </c>
     </row>
     <row r="5917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5917" s="3">
         <v>7900</v>
       </c>
+      <c r="B5917" s="3" t="s">
+        <v>7738</v>
+      </c>
+      <c r="C5917" s="3" t="s">
+        <v>7661</v>
+      </c>
     </row>
     <row r="5918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5918" s="3">
         <v>7900</v>
       </c>
+      <c r="B5918" s="3" t="s">
+        <v>7751</v>
+      </c>
+      <c r="C5918" s="3" t="s">
+        <v>7662</v>
+      </c>
     </row>
     <row r="5919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5919" s="3">
         <v>7900</v>
       </c>
+      <c r="C5919" s="3" t="s">
+        <v>7663</v>
+      </c>
     </row>
     <row r="5920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5920" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5921" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5920" s="3" t="s">
+        <v>7664</v>
+      </c>
+    </row>
+    <row r="5921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5921" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5922" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5921" s="3" t="s">
+        <v>7665</v>
+      </c>
+    </row>
+    <row r="5922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5922" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5923" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5922" s="3" t="s">
+        <v>7666</v>
+      </c>
+    </row>
+    <row r="5923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5923" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5924" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5923" s="3" t="s">
+        <v>7667</v>
+      </c>
+    </row>
+    <row r="5924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5924" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5925" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5924" s="3" t="s">
+        <v>7668</v>
+      </c>
+    </row>
+    <row r="5925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5925" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5926" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5925" s="3" t="s">
+        <v>7669</v>
+      </c>
+    </row>
+    <row r="5926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5926" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5927" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5926" s="3" t="s">
+        <v>7670</v>
+      </c>
+    </row>
+    <row r="5927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5927" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5928" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5927" s="3" t="s">
+        <v>7671</v>
+      </c>
+    </row>
+    <row r="5928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5928" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5929" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5928" s="3" t="s">
+        <v>7674</v>
+      </c>
+    </row>
+    <row r="5929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5929" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5930" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5929" s="3" t="s">
+        <v>7675</v>
+      </c>
+    </row>
+    <row r="5930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5930" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5931" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5930" s="3" t="s">
+        <v>7676</v>
+      </c>
+    </row>
+    <row r="5931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5931" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5932" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5931" s="3" t="s">
+        <v>7677</v>
+      </c>
+    </row>
+    <row r="5932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5932" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5933" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5932" s="3" t="s">
+        <v>7678</v>
+      </c>
+    </row>
+    <row r="5933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5933" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5934" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5933" s="3" t="s">
+        <v>7679</v>
+      </c>
+    </row>
+    <row r="5934" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5934" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5935" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5934" s="3" t="s">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="5935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5935" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5936" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5935" s="3" t="s">
+        <v>7681</v>
+      </c>
+    </row>
+    <row r="5936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5936" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5937" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5936" s="3" t="s">
+        <v>7682</v>
+      </c>
+    </row>
+    <row r="5937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5937" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5938" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5937" s="3" t="s">
+        <v>7683</v>
+      </c>
+    </row>
+    <row r="5938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5938" s="3">
         <v>7900</v>
       </c>
-    </row>
-    <row r="5939" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C5938" s="3" t="s">
+        <v>7684</v>
+      </c>
+    </row>
+    <row r="5939" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5939" s="3">
         <v>7900</v>
+      </c>
+      <c r="C5939" s="3" t="s">
+        <v>7686</v>
+      </c>
+    </row>
+    <row r="5940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5940" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5940" s="3" t="s">
+        <v>7687</v>
+      </c>
+    </row>
+    <row r="5941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5941" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5941" s="3" t="s">
+        <v>7688</v>
+      </c>
+    </row>
+    <row r="5942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5942" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5942" s="3" t="s">
+        <v>7689</v>
+      </c>
+    </row>
+    <row r="5943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5943" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5943" s="3" t="s">
+        <v>7690</v>
+      </c>
+    </row>
+    <row r="5944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5944" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5944" s="3" t="s">
+        <v>7691</v>
+      </c>
+    </row>
+    <row r="5945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5945" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5945" s="3" t="s">
+        <v>7692</v>
+      </c>
+    </row>
+    <row r="5946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5946" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5946" s="3" t="s">
+        <v>7693</v>
+      </c>
+    </row>
+    <row r="5947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5947" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5947" s="3" t="s">
+        <v>7694</v>
+      </c>
+    </row>
+    <row r="5948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5948" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5948" s="3" t="s">
+        <v>7695</v>
+      </c>
+    </row>
+    <row r="5949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5949" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5949" s="3" t="s">
+        <v>7696</v>
+      </c>
+    </row>
+    <row r="5950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5950" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5950" s="3" t="s">
+        <v>7697</v>
+      </c>
+    </row>
+    <row r="5951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5951" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5951" s="3" t="s">
+        <v>7698</v>
+      </c>
+    </row>
+    <row r="5952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5952" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5952" s="3" t="s">
+        <v>7699</v>
+      </c>
+    </row>
+    <row r="5953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5953" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5953" s="3" t="s">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="5954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5954" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5954" s="3" t="s">
+        <v>7701</v>
+      </c>
+    </row>
+    <row r="5955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5955" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5955" s="3" t="s">
+        <v>7702</v>
+      </c>
+    </row>
+    <row r="5956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5956" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5956" s="3" t="s">
+        <v>7703</v>
+      </c>
+    </row>
+    <row r="5957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5957" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5957" s="3" t="s">
+        <v>7704</v>
+      </c>
+    </row>
+    <row r="5958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5958" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5958" s="3" t="s">
+        <v>7705</v>
+      </c>
+    </row>
+    <row r="5959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5959" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5959" s="3" t="s">
+        <v>7706</v>
+      </c>
+    </row>
+    <row r="5960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5960" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5960" s="3" t="s">
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="5961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5961" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5961" s="3" t="s">
+        <v>7708</v>
+      </c>
+    </row>
+    <row r="5962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5962" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5962" s="3" t="s">
+        <v>7709</v>
+      </c>
+    </row>
+    <row r="5963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5963" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5963" s="3" t="s">
+        <v>7710</v>
+      </c>
+    </row>
+    <row r="5964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5964" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5964" s="3" t="s">
+        <v>7711</v>
+      </c>
+    </row>
+    <row r="5965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5965" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5965" s="3" t="s">
+        <v>7712</v>
+      </c>
+    </row>
+    <row r="5966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5966" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5966" s="3" t="s">
+        <v>7713</v>
+      </c>
+    </row>
+    <row r="5967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5967" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5967" s="3" t="s">
+        <v>7714</v>
+      </c>
+    </row>
+    <row r="5968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5968" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5968" s="3" t="s">
+        <v>7715</v>
+      </c>
+    </row>
+    <row r="5969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5969" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5969" s="3" t="s">
+        <v>7716</v>
+      </c>
+    </row>
+    <row r="5970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5970" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5970" s="3" t="s">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="5971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5971" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5971" s="3" t="s">
+        <v>7718</v>
+      </c>
+    </row>
+    <row r="5972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5972" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5972" s="3" t="s">
+        <v>7719</v>
+      </c>
+    </row>
+    <row r="5973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5973" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5973" s="3" t="s">
+        <v>7720</v>
+      </c>
+    </row>
+    <row r="5974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5974" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5974" s="3" t="s">
+        <v>7721</v>
+      </c>
+    </row>
+    <row r="5975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5975" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5975" s="3" t="s">
+        <v>7722</v>
+      </c>
+    </row>
+    <row r="5976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5976" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5976" s="3" t="s">
+        <v>7723</v>
+      </c>
+    </row>
+    <row r="5977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5977" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5977" s="3" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="5978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5978" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5978" s="3" t="s">
+        <v>7725</v>
+      </c>
+    </row>
+    <row r="5979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5979" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5979" s="3" t="s">
+        <v>7726</v>
+      </c>
+    </row>
+    <row r="5980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5980" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5980" s="3" t="s">
+        <v>7727</v>
+      </c>
+    </row>
+    <row r="5981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5981" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5981" s="3" t="s">
+        <v>7728</v>
+      </c>
+    </row>
+    <row r="5982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5982" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5982" s="3" t="s">
+        <v>7729</v>
+      </c>
+    </row>
+    <row r="5983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5983" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5983" s="3" t="s">
+        <v>7730</v>
+      </c>
+    </row>
+    <row r="5984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5984" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5984" s="3" t="s">
+        <v>7731</v>
+      </c>
+    </row>
+    <row r="5985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5985" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5985" s="3" t="s">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="5986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5986" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5986" s="3" t="s">
+        <v>7733</v>
+      </c>
+    </row>
+    <row r="5987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5987" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5987" s="3" t="s">
+        <v>7734</v>
+      </c>
+    </row>
+    <row r="5988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5988" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5988" s="3" t="s">
+        <v>7735</v>
+      </c>
+    </row>
+    <row r="5989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5989" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5989" s="3" t="s">
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="5990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5990" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5990" s="3" t="s">
+        <v>7739</v>
+      </c>
+    </row>
+    <row r="5991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5991" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5991" s="3" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="5992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5992" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5992" s="3" t="s">
+        <v>7741</v>
+      </c>
+    </row>
+    <row r="5993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5993" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5993" s="3" t="s">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="5994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5994" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5994" s="3" t="s">
+        <v>7743</v>
+      </c>
+    </row>
+    <row r="5995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5995" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5995" s="3" t="s">
+        <v>7744</v>
+      </c>
+    </row>
+    <row r="5996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5996" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5996" s="3" t="s">
+        <v>7745</v>
+      </c>
+    </row>
+    <row r="5997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5997" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5997" s="3" t="s">
+        <v>7746</v>
+      </c>
+    </row>
+    <row r="5998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5998" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5998" s="3" t="s">
+        <v>7747</v>
+      </c>
+    </row>
+    <row r="5999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5999" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C5999" s="3" t="s">
+        <v>7748</v>
+      </c>
+    </row>
+    <row r="6000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6000" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C6000" s="3" t="s">
+        <v>7749</v>
+      </c>
+    </row>
+    <row r="6001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6001" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C6001" s="3" t="s">
+        <v>7750</v>
+      </c>
+    </row>
+    <row r="6002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6002" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C6002" s="3" t="s">
+        <v>7752</v>
+      </c>
+    </row>
+    <row r="6003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6003" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C6003" s="3" t="s">
+        <v>7753</v>
+      </c>
+    </row>
+    <row r="6004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6004" s="3">
+        <v>7900</v>
+      </c>
+      <c r="C6004" s="3" t="s">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="6005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6005" s="4">
+        <v>8000</v>
+      </c>
+      <c r="B6005" s="3" t="s">
+        <v>7755</v>
+      </c>
+      <c r="C6005" s="3" t="s">
+        <v>7697</v>
+      </c>
+    </row>
+    <row r="6006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6006" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6007" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6008" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6009" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6010" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6011" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6012" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6013" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6014" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6015" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6016" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6017" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6017" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6018" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6018" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6019" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6019" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6020" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6021" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6021" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6022" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6023" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6024" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6025" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6026" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6027" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6027" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6028" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6029" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6030" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6030" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6031" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6032" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6033" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6033" s="3">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592A9F19-578B-4940-A0FB-FB6E49EF1E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6751F22E-9C08-418F-84FB-4F3E50158235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7787" uniqueCount="7756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7887" uniqueCount="7856">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31042,6 +31042,406 @@
   </si>
   <si>
     <t>loyally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artiste</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symbolically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misinterprete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>controllable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>categorically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outwit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intelligently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>problematic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restlessness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bearing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clutch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncarved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>macaque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>villager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fallacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vitascope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfocused</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anyplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stealthy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>douse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>silvery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>healer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diviner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>panhandle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>belter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>terylene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humorously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nylon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elimination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nowadays</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rayon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>olive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indigo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needlelike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abnormality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hugely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acetate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>micronutrient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>turmeric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>christian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saffron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overprint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>religiously</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storyteller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ritualize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>teller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abruptness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pantomimic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subglacial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhythmically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sincerity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleverness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bombardment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lounger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>northward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dugout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moccasin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chronologically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>activate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>episodic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fiord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>esteem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>colosseum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>achievable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fixation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acknowledge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncooperative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteoroid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>threadlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pulp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physician</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supplementation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disrepute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syndrome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rectify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>herein</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>denial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sugarlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>survivability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theological</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31444,7 +31844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N6033"/>
+  <dimension ref="A1:N6134"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -83842,140 +84242,945 @@
       <c r="A6006" s="3">
         <v>8000</v>
       </c>
+      <c r="B6006" s="3" t="s">
+        <v>7773</v>
+      </c>
+      <c r="C6006" s="3" t="s">
+        <v>7756</v>
+      </c>
     </row>
     <row r="6007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6007" s="3">
         <v>8000</v>
       </c>
+      <c r="B6007" s="3" t="s">
+        <v>7816</v>
+      </c>
+      <c r="C6007" s="3" t="s">
+        <v>7757</v>
+      </c>
     </row>
     <row r="6008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6008" s="3">
         <v>8000</v>
       </c>
+      <c r="B6008" s="3" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C6008" s="3" t="s">
+        <v>7758</v>
+      </c>
     </row>
     <row r="6009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6009" s="3">
         <v>8000</v>
       </c>
+      <c r="C6009" s="3" t="s">
+        <v>7759</v>
+      </c>
     </row>
     <row r="6010" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6010" s="3">
         <v>8000</v>
       </c>
+      <c r="C6010" s="3" t="s">
+        <v>7760</v>
+      </c>
     </row>
     <row r="6011" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6011" s="3">
         <v>8000</v>
       </c>
+      <c r="C6011" s="3" t="s">
+        <v>7761</v>
+      </c>
     </row>
     <row r="6012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6012" s="3">
         <v>8000</v>
       </c>
+      <c r="C6012" s="3" t="s">
+        <v>7762</v>
+      </c>
     </row>
     <row r="6013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6013" s="3">
         <v>8000</v>
       </c>
+      <c r="C6013" s="3" t="s">
+        <v>7763</v>
+      </c>
     </row>
     <row r="6014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6014" s="3">
         <v>8000</v>
       </c>
+      <c r="C6014" s="3" t="s">
+        <v>7764</v>
+      </c>
     </row>
     <row r="6015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6015" s="3">
         <v>8000</v>
       </c>
+      <c r="C6015" s="3" t="s">
+        <v>7765</v>
+      </c>
     </row>
     <row r="6016" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6016" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6017" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6016" s="3" t="s">
+        <v>7766</v>
+      </c>
+    </row>
+    <row r="6017" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6017" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6018" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6017" s="3" t="s">
+        <v>7767</v>
+      </c>
+    </row>
+    <row r="6018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6018" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6019" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6018" s="3" t="s">
+        <v>7768</v>
+      </c>
+    </row>
+    <row r="6019" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6019" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6020" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6019" s="3" t="s">
+        <v>7769</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6020" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6021" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6020" s="3" t="s">
+        <v>7770</v>
+      </c>
+    </row>
+    <row r="6021" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6021" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6022" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6021" s="3" t="s">
+        <v>7771</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6022" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6023" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6022" s="3" t="s">
+        <v>7772</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6023" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6024" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6023" s="3" t="s">
+        <v>7774</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6024" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6025" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6024" s="3" t="s">
+        <v>7775</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6025" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6026" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6025" s="3" t="s">
+        <v>7776</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6026" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6027" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6026" s="3" t="s">
+        <v>7777</v>
+      </c>
+    </row>
+    <row r="6027" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6027" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6028" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6027" s="3" t="s">
+        <v>7778</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6028" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6029" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6028" s="3" t="s">
+        <v>7779</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6029" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6030" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6029" s="3" t="s">
+        <v>7780</v>
+      </c>
+    </row>
+    <row r="6030" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6030" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6031" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6030" s="3" t="s">
+        <v>7781</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6031" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6032" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6031" s="3" t="s">
+        <v>7782</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6032" s="3">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6033" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6032" s="3" t="s">
+        <v>7783</v>
+      </c>
+    </row>
+    <row r="6033" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6033" s="3">
         <v>8000</v>
+      </c>
+      <c r="C6033" s="3" t="s">
+        <v>7784</v>
+      </c>
+    </row>
+    <row r="6034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6034" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6034" s="3" t="s">
+        <v>7785</v>
+      </c>
+    </row>
+    <row r="6035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6035" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6035" s="3" t="s">
+        <v>7786</v>
+      </c>
+    </row>
+    <row r="6036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6036" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6036" s="3" t="s">
+        <v>7787</v>
+      </c>
+    </row>
+    <row r="6037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6037" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6037" s="3" t="s">
+        <v>7788</v>
+      </c>
+    </row>
+    <row r="6038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6038" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6038" s="3" t="s">
+        <v>7789</v>
+      </c>
+    </row>
+    <row r="6039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6039" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6039" s="3" t="s">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="6040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6040" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6040" s="3" t="s">
+        <v>7791</v>
+      </c>
+    </row>
+    <row r="6041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6041" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6041" s="3" t="s">
+        <v>7792</v>
+      </c>
+    </row>
+    <row r="6042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6042" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6042" s="3" t="s">
+        <v>7793</v>
+      </c>
+    </row>
+    <row r="6043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6043" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6043" s="3" t="s">
+        <v>7794</v>
+      </c>
+    </row>
+    <row r="6044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6044" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6044" s="3" t="s">
+        <v>7795</v>
+      </c>
+    </row>
+    <row r="6045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6045" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6045" s="3" t="s">
+        <v>7796</v>
+      </c>
+    </row>
+    <row r="6046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6046" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6046" s="3" t="s">
+        <v>7797</v>
+      </c>
+    </row>
+    <row r="6047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6047" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6047" s="3" t="s">
+        <v>7798</v>
+      </c>
+    </row>
+    <row r="6048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6048" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6048" s="3" t="s">
+        <v>7799</v>
+      </c>
+    </row>
+    <row r="6049" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6049" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6049" s="3" t="s">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="6050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6050" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6050" s="3" t="s">
+        <v>7801</v>
+      </c>
+    </row>
+    <row r="6051" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6051" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6051" s="3" t="s">
+        <v>7802</v>
+      </c>
+    </row>
+    <row r="6052" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6052" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6052" s="3" t="s">
+        <v>7803</v>
+      </c>
+    </row>
+    <row r="6053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6053" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6053" s="3" t="s">
+        <v>7804</v>
+      </c>
+    </row>
+    <row r="6054" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6054" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6054" s="3" t="s">
+        <v>7805</v>
+      </c>
+    </row>
+    <row r="6055" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6055" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6055" s="3" t="s">
+        <v>7806</v>
+      </c>
+    </row>
+    <row r="6056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6056" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6056" s="3" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="6057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6057" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6057" s="3" t="s">
+        <v>7808</v>
+      </c>
+    </row>
+    <row r="6058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6058" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6058" s="3" t="s">
+        <v>7809</v>
+      </c>
+    </row>
+    <row r="6059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6059" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6059" s="3" t="s">
+        <v>7810</v>
+      </c>
+    </row>
+    <row r="6060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6060" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6060" s="3" t="s">
+        <v>7811</v>
+      </c>
+    </row>
+    <row r="6061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6061" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6061" s="3" t="s">
+        <v>7812</v>
+      </c>
+    </row>
+    <row r="6062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6062" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6062" s="3" t="s">
+        <v>7813</v>
+      </c>
+    </row>
+    <row r="6063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6063" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6063" s="3" t="s">
+        <v>7814</v>
+      </c>
+    </row>
+    <row r="6064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6064" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6064" s="3" t="s">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="6065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6065" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6065" s="3" t="s">
+        <v>7817</v>
+      </c>
+    </row>
+    <row r="6066" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6066" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6066" s="3" t="s">
+        <v>7818</v>
+      </c>
+    </row>
+    <row r="6067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6067" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6067" s="3" t="s">
+        <v>7819</v>
+      </c>
+    </row>
+    <row r="6068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6068" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6068" s="3" t="s">
+        <v>7820</v>
+      </c>
+    </row>
+    <row r="6069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6069" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6069" s="3" t="s">
+        <v>7821</v>
+      </c>
+    </row>
+    <row r="6070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6070" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6070" s="3" t="s">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="6071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6071" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6071" s="3" t="s">
+        <v>7823</v>
+      </c>
+    </row>
+    <row r="6072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6072" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6072" s="3" t="s">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="6073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6073" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6073" s="3" t="s">
+        <v>7825</v>
+      </c>
+    </row>
+    <row r="6074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6074" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6074" s="3" t="s">
+        <v>7826</v>
+      </c>
+    </row>
+    <row r="6075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6075" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6075" s="3" t="s">
+        <v>7827</v>
+      </c>
+    </row>
+    <row r="6076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6076" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6076" s="3" t="s">
+        <v>7828</v>
+      </c>
+    </row>
+    <row r="6077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6077" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6077" s="3" t="s">
+        <v>7829</v>
+      </c>
+    </row>
+    <row r="6078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6078" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6078" s="3" t="s">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="6079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6079" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6079" s="3" t="s">
+        <v>7831</v>
+      </c>
+    </row>
+    <row r="6080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6080" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6080" s="3" t="s">
+        <v>7832</v>
+      </c>
+    </row>
+    <row r="6081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6081" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6081" s="3" t="s">
+        <v>7834</v>
+      </c>
+    </row>
+    <row r="6082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6082" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6082" s="3" t="s">
+        <v>7835</v>
+      </c>
+    </row>
+    <row r="6083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6083" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6083" s="3" t="s">
+        <v>7836</v>
+      </c>
+    </row>
+    <row r="6084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6084" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6084" s="3" t="s">
+        <v>7837</v>
+      </c>
+    </row>
+    <row r="6085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6085" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6085" s="3" t="s">
+        <v>7838</v>
+      </c>
+    </row>
+    <row r="6086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6086" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6086" s="3" t="s">
+        <v>7839</v>
+      </c>
+    </row>
+    <row r="6087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6087" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6087" s="3" t="s">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="6088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6088" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6088" s="3" t="s">
+        <v>7841</v>
+      </c>
+    </row>
+    <row r="6089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6089" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6089" s="3" t="s">
+        <v>7842</v>
+      </c>
+    </row>
+    <row r="6090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6090" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6090" s="3" t="s">
+        <v>7843</v>
+      </c>
+    </row>
+    <row r="6091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6091" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6091" s="3" t="s">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="6092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6092" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6092" s="3" t="s">
+        <v>7845</v>
+      </c>
+    </row>
+    <row r="6093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6093" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6093" s="3" t="s">
+        <v>7846</v>
+      </c>
+    </row>
+    <row r="6094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6094" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6094" s="3" t="s">
+        <v>7847</v>
+      </c>
+    </row>
+    <row r="6095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6095" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6095" s="3" t="s">
+        <v>7848</v>
+      </c>
+    </row>
+    <row r="6096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6096" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6096" s="3" t="s">
+        <v>7849</v>
+      </c>
+    </row>
+    <row r="6097" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6097" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6097" s="3" t="s">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="6098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6098" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6098" s="3" t="s">
+        <v>7851</v>
+      </c>
+    </row>
+    <row r="6099" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6099" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6099" s="3" t="s">
+        <v>7852</v>
+      </c>
+    </row>
+    <row r="6100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6100" s="3">
+        <v>8000</v>
+      </c>
+      <c r="C6100" s="3" t="s">
+        <v>7853</v>
+      </c>
+    </row>
+    <row r="6101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6101" s="4">
+        <v>8100</v>
+      </c>
+      <c r="C6101" s="3" t="s">
+        <v>7854</v>
+      </c>
+    </row>
+    <row r="6102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6102" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6102" s="3" t="s">
+        <v>7855</v>
+      </c>
+    </row>
+    <row r="6103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6103" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6104" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6105" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6106" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6107" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6108" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6109" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6110" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6111" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6112" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6113" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6114" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6115" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6116" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6117" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6118" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6119" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6120" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6121" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6122" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6123" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6124" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6125" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6126" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6127" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6128" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6129" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6130" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6131" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6132" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6133" s="3">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="6134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6134" s="3">
+        <v>8100</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6751F22E-9C08-418F-84FB-4F3E50158235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751AAA25-4863-4641-A9EC-7A4F585CAF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7887" uniqueCount="7856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7987" uniqueCount="7953">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31442,6 +31442,394 @@
   </si>
   <si>
     <t>theological</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dorsal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irritability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neurilemmal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neuroglia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mushroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakdown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yeast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concurrent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stratification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microcosm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unsureness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fright</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>belie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hesitant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sewer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anytime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intuitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undernutrition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hohokam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irresponsible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>health-crisis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retrospect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chronic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flatfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sundial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>butte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low-cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uneducated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>securely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncorrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landscapist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scenery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complimentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incorporation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sobriquet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>socialize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rename</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awaken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afflict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>governance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>methodically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feverishly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personnel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antifungal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>senior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dimly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earthward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>justice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overwhelmingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assembly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stressful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exertion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deformity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disruptive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>girder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bustle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unforeseen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conversational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>governor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abbreviate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broadcaster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adviser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clarification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speechwriter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>televisual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electrify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legislative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melodic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predictably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>climatically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethargic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pathology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>helper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triangular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counsel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>programme</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curvature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endpoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vocational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>datebase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compulsory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shyness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethargy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31844,7 +32232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N6134"/>
+  <dimension ref="A1:N6218"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -85011,6 +85399,9 @@
       <c r="A6101" s="4">
         <v>8100</v>
       </c>
+      <c r="B6101" s="3" t="s">
+        <v>7874</v>
+      </c>
       <c r="C6101" s="3" t="s">
         <v>7854</v>
       </c>
@@ -85019,6 +85410,9 @@
       <c r="A6102" s="3">
         <v>8100</v>
       </c>
+      <c r="B6102" s="3" t="s">
+        <v>7883</v>
+      </c>
       <c r="C6102" s="3" t="s">
         <v>7855</v>
       </c>
@@ -85027,160 +85421,874 @@
       <c r="A6103" s="3">
         <v>8100</v>
       </c>
+      <c r="B6103" s="3" t="s">
+        <v>7899</v>
+      </c>
+      <c r="C6103" s="3" t="s">
+        <v>7856</v>
+      </c>
     </row>
     <row r="6104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6104" s="3">
         <v>8100</v>
       </c>
+      <c r="B6104" s="3" t="s">
+        <v>7911</v>
+      </c>
+      <c r="C6104" s="3" t="s">
+        <v>7857</v>
+      </c>
     </row>
     <row r="6105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6105" s="3">
         <v>8100</v>
       </c>
+      <c r="B6105" s="3" t="s">
+        <v>7937</v>
+      </c>
+      <c r="C6105" s="3" t="s">
+        <v>7858</v>
+      </c>
     </row>
     <row r="6106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6106" s="3">
         <v>8100</v>
       </c>
+      <c r="B6106" s="3" t="s">
+        <v>7941</v>
+      </c>
+      <c r="C6106" s="3" t="s">
+        <v>7859</v>
+      </c>
     </row>
     <row r="6107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6107" s="3">
         <v>8100</v>
       </c>
+      <c r="C6107" s="3" t="s">
+        <v>7860</v>
+      </c>
     </row>
     <row r="6108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6108" s="3">
         <v>8100</v>
       </c>
+      <c r="C6108" s="3" t="s">
+        <v>7861</v>
+      </c>
     </row>
     <row r="6109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6109" s="3">
         <v>8100</v>
       </c>
+      <c r="C6109" s="3" t="s">
+        <v>7862</v>
+      </c>
     </row>
     <row r="6110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6110" s="3">
         <v>8100</v>
       </c>
+      <c r="C6110" s="3" t="s">
+        <v>7863</v>
+      </c>
     </row>
     <row r="6111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6111" s="3">
         <v>8100</v>
       </c>
+      <c r="C6111" s="3" t="s">
+        <v>7864</v>
+      </c>
     </row>
     <row r="6112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6112" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6112" s="3" t="s">
+        <v>7865</v>
+      </c>
+    </row>
+    <row r="6113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6113" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6113" s="3" t="s">
+        <v>7866</v>
+      </c>
+    </row>
+    <row r="6114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6114" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6114" s="3" t="s">
+        <v>7867</v>
+      </c>
+    </row>
+    <row r="6115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6115" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6115" s="3" t="s">
+        <v>7868</v>
+      </c>
+    </row>
+    <row r="6116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6116" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6116" s="3" t="s">
+        <v>7869</v>
+      </c>
+    </row>
+    <row r="6117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6117" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6117" s="3" t="s">
+        <v>7870</v>
+      </c>
+    </row>
+    <row r="6118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6118" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6118" s="3" t="s">
+        <v>7871</v>
+      </c>
+    </row>
+    <row r="6119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6119" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6119" s="3" t="s">
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="6120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6120" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6120" s="3" t="s">
+        <v>7872</v>
+      </c>
+    </row>
+    <row r="6121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6121" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6121" s="3" t="s">
+        <v>7873</v>
+      </c>
+    </row>
+    <row r="6122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6122" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6122" s="3" t="s">
+        <v>7875</v>
+      </c>
+    </row>
+    <row r="6123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6123" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6123" s="3" t="s">
+        <v>7876</v>
+      </c>
+    </row>
+    <row r="6124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6124" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6124" s="3" t="s">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="6125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6125" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6125" s="3" t="s">
+        <v>7878</v>
+      </c>
+    </row>
+    <row r="6126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6126" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6126" s="3" t="s">
+        <v>7879</v>
+      </c>
+    </row>
+    <row r="6127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6127" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6127" s="3" t="s">
+        <v>7880</v>
+      </c>
+    </row>
+    <row r="6128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6128" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6128" s="3" t="s">
+        <v>7881</v>
+      </c>
+    </row>
+    <row r="6129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6129" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6129" s="3" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="6130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6130" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6130" s="3" t="s">
+        <v>7884</v>
+      </c>
+    </row>
+    <row r="6131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6131" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6131" s="3" t="s">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="6132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6132" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6132" s="3" t="s">
+        <v>7886</v>
+      </c>
+    </row>
+    <row r="6133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6133" s="3">
         <v>8100</v>
       </c>
-    </row>
-    <row r="6134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6133" s="3" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="6134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6134" s="3">
         <v>8100</v>
+      </c>
+      <c r="C6134" s="3" t="s">
+        <v>7888</v>
+      </c>
+    </row>
+    <row r="6135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6135" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6135" s="3" t="s">
+        <v>7889</v>
+      </c>
+    </row>
+    <row r="6136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6136" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6136" s="3" t="s">
+        <v>7890</v>
+      </c>
+    </row>
+    <row r="6137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6137" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6137" s="3" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="6138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6138" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6138" s="3" t="s">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="6139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6139" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6139" s="3" t="s">
+        <v>7893</v>
+      </c>
+    </row>
+    <row r="6140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6140" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6140" s="3" t="s">
+        <v>7894</v>
+      </c>
+    </row>
+    <row r="6141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6141" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6141" s="3" t="s">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="6142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6142" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6142" s="3" t="s">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="6143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6143" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6143" s="3" t="s">
+        <v>7897</v>
+      </c>
+    </row>
+    <row r="6144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6144" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6144" s="3" t="s">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="6145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6145" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6145" s="3" t="s">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="6146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6146" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6146" s="3" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="6147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6147" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6147" s="3" t="s">
+        <v>7902</v>
+      </c>
+    </row>
+    <row r="6148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6148" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6148" s="3" t="s">
+        <v>7903</v>
+      </c>
+    </row>
+    <row r="6149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6149" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6149" s="3" t="s">
+        <v>7904</v>
+      </c>
+    </row>
+    <row r="6150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6150" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6150" s="3" t="s">
+        <v>7905</v>
+      </c>
+    </row>
+    <row r="6151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6151" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6151" s="3" t="s">
+        <v>7906</v>
+      </c>
+    </row>
+    <row r="6152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6152" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6152" s="3" t="s">
+        <v>7907</v>
+      </c>
+    </row>
+    <row r="6153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6153" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6153" s="3" t="s">
+        <v>7908</v>
+      </c>
+    </row>
+    <row r="6154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6154" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6154" s="3" t="s">
+        <v>7909</v>
+      </c>
+    </row>
+    <row r="6155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6155" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6155" s="3" t="s">
+        <v>7910</v>
+      </c>
+    </row>
+    <row r="6156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6156" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6156" s="3" t="s">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="6157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6157" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6157" s="3" t="s">
+        <v>7913</v>
+      </c>
+    </row>
+    <row r="6158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6158" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6158" s="3" t="s">
+        <v>7914</v>
+      </c>
+    </row>
+    <row r="6159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6159" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6159" s="3" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="6160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6160" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6160" s="3" t="s">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="6161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6161" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6161" s="3" t="s">
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="6162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6162" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6162" s="3" t="s">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="6163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6163" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6163" s="3" t="s">
+        <v>7919</v>
+      </c>
+    </row>
+    <row r="6164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6164" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6164" s="3" t="s">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="6165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6165" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6165" s="3" t="s">
+        <v>7921</v>
+      </c>
+    </row>
+    <row r="6166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6166" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6166" s="3" t="s">
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="6167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6167" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6167" s="3" t="s">
+        <v>7923</v>
+      </c>
+    </row>
+    <row r="6168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6168" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6168" s="3" t="s">
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="6169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6169" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6169" s="3" t="s">
+        <v>7925</v>
+      </c>
+    </row>
+    <row r="6170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6170" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6170" s="3" t="s">
+        <v>7926</v>
+      </c>
+    </row>
+    <row r="6171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6171" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6171" s="3" t="s">
+        <v>7927</v>
+      </c>
+    </row>
+    <row r="6172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6172" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6172" s="3" t="s">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="6173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6173" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6173" s="3" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="6174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6174" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6174" s="3" t="s">
+        <v>7930</v>
+      </c>
+    </row>
+    <row r="6175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6175" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6175" s="3" t="s">
+        <v>7931</v>
+      </c>
+    </row>
+    <row r="6176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6176" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6176" s="3" t="s">
+        <v>7932</v>
+      </c>
+    </row>
+    <row r="6177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6177" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6177" s="3" t="s">
+        <v>7933</v>
+      </c>
+    </row>
+    <row r="6178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6178" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6178" s="3" t="s">
+        <v>7934</v>
+      </c>
+    </row>
+    <row r="6179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6179" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6179" s="3" t="s">
+        <v>7935</v>
+      </c>
+    </row>
+    <row r="6180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6180" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6180" s="3" t="s">
+        <v>7936</v>
+      </c>
+    </row>
+    <row r="6181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6181" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6181" s="3" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="6182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6182" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6182" s="3" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="6183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6183" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6183" s="3" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="6184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6184" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6184" s="3" t="s">
+        <v>7939</v>
+      </c>
+    </row>
+    <row r="6185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6185" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6185" s="3" t="s">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="6186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6186" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6186" s="3" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="6187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6187" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6187" s="3" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="6188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6188" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6188" s="3" t="s">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="6189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6189" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6189" s="3" t="s">
+        <v>7945</v>
+      </c>
+    </row>
+    <row r="6190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6190" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6190" s="3" t="s">
+        <v>7946</v>
+      </c>
+    </row>
+    <row r="6191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6191" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6191" s="3" t="s">
+        <v>7947</v>
+      </c>
+    </row>
+    <row r="6192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6192" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6192" s="3" t="s">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="6193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6193" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6193" s="3" t="s">
+        <v>7949</v>
+      </c>
+    </row>
+    <row r="6194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6194" s="3">
+        <v>8100</v>
+      </c>
+      <c r="C6194" s="3" t="s">
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="6195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6195" s="4">
+        <v>8200</v>
+      </c>
+      <c r="C6195" s="3" t="s">
+        <v>7951</v>
+      </c>
+    </row>
+    <row r="6196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6196" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6196" s="3" t="s">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="6197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6197" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6198" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6199" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6200" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6201" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6202" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6203" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6204" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6205" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6206" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6207" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6208" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6209" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6210" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6211" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6212" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6213" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6214" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6215" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6216" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6217" s="3">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6218" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6218" s="3">
+        <v>8200</v>
       </c>
     </row>
   </sheetData>

--- a/笔记鲨.xlsx
+++ b/笔记鲨.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\GitEnglish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751AAA25-4863-4641-A9EC-7A4F585CAF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F53F28-8144-4A57-B870-0CB21F778C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C2220A45-7711-40BA-B31A-D0627F4FC2C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7987" uniqueCount="7953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8087" uniqueCount="8052">
   <si>
     <t>熟悉</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31830,6 +31830,402 @@
   </si>
   <si>
     <t>lethargy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hostility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disorientation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>additionally</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninterrupted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bureaucratization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excursion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embryonic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>necklace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bylaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>republish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>publicly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distantly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fierce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>categorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>severity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>definitively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lineage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flaming</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>internet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>newscast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fateful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antipathy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurtly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glisten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>predate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Finnish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cenote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empathy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardwood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prohibit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gesture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretentious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heredity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dining</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amenity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>changeover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skylight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palatable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invariable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depreciation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unspecified</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>helplessness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retentive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amplifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfailingly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undiscovered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>helplessly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overnight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dentist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optometrist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merciless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strenuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emancipate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protagonist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cruel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grimly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apportion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commentator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bankruptcy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subjugation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncontrollably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lazily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>radioactive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consortium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preventive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supplementary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multidirectional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>booklet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chandler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encircle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heading</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Californian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reaumur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mycology</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -32232,7 +32628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2850273-5095-4D8E-A475-3AA86365ECB2}">
-  <dimension ref="A1:N6218"/>
+  <dimension ref="A1:N6322"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -86169,6 +86565,9 @@
       <c r="A6195" s="4">
         <v>8200</v>
       </c>
+      <c r="B6195" s="3" t="s">
+        <v>7978</v>
+      </c>
       <c r="C6195" s="3" t="s">
         <v>7951</v>
       </c>
@@ -86177,6 +86576,9 @@
       <c r="A6196" s="3">
         <v>8200</v>
       </c>
+      <c r="B6196" s="3" t="s">
+        <v>5409</v>
+      </c>
       <c r="C6196" s="3" t="s">
         <v>7952</v>
       </c>
@@ -86185,110 +86587,924 @@
       <c r="A6197" s="3">
         <v>8200</v>
       </c>
+      <c r="B6197" s="3" t="s">
+        <v>8010</v>
+      </c>
+      <c r="C6197" s="3" t="s">
+        <v>7953</v>
+      </c>
     </row>
     <row r="6198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6198" s="3">
         <v>8200</v>
       </c>
+      <c r="C6198" s="3" t="s">
+        <v>7954</v>
+      </c>
     </row>
     <row r="6199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6199" s="3">
         <v>8200</v>
       </c>
+      <c r="C6199" s="3" t="s">
+        <v>7955</v>
+      </c>
     </row>
     <row r="6200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6200" s="3">
         <v>8200</v>
       </c>
+      <c r="C6200" s="3" t="s">
+        <v>7956</v>
+      </c>
     </row>
     <row r="6201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6201" s="3">
         <v>8200</v>
       </c>
+      <c r="C6201" s="3" t="s">
+        <v>7957</v>
+      </c>
     </row>
     <row r="6202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6202" s="3">
         <v>8200</v>
       </c>
+      <c r="C6202" s="3" t="s">
+        <v>7958</v>
+      </c>
     </row>
     <row r="6203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6203" s="3">
         <v>8200</v>
       </c>
+      <c r="C6203" s="3" t="s">
+        <v>7959</v>
+      </c>
     </row>
     <row r="6204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6204" s="3">
         <v>8200</v>
       </c>
+      <c r="C6204" s="3" t="s">
+        <v>7960</v>
+      </c>
     </row>
     <row r="6205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6205" s="3">
         <v>8200</v>
       </c>
+      <c r="C6205" s="3" t="s">
+        <v>7961</v>
+      </c>
     </row>
     <row r="6206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6206" s="3">
         <v>8200</v>
       </c>
+      <c r="C6206" s="3" t="s">
+        <v>7962</v>
+      </c>
     </row>
     <row r="6207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6207" s="3">
         <v>8200</v>
       </c>
+      <c r="C6207" s="3" t="s">
+        <v>7963</v>
+      </c>
     </row>
     <row r="6208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6208" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6209" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6208" s="3" t="s">
+        <v>7964</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6209" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6210" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6209" s="3" t="s">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6210" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6211" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6210" s="3" t="s">
+        <v>7966</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6211" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6212" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6211" s="3" t="s">
+        <v>7967</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6212" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6213" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6212" s="3" t="s">
+        <v>7968</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6213" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6213" s="3" t="s">
+        <v>7969</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6214" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6214" s="3" t="s">
+        <v>7970</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6215" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6215" s="3" t="s">
+        <v>7971</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6216" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6216" s="3" t="s">
+        <v>7972</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6217" s="3">
         <v>8200</v>
       </c>
-    </row>
-    <row r="6218" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C6217" s="3" t="s">
+        <v>7973</v>
+      </c>
+    </row>
+    <row r="6218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6218" s="3">
         <v>8200</v>
+      </c>
+      <c r="C6218" s="3" t="s">
+        <v>7974</v>
+      </c>
+    </row>
+    <row r="6219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6219" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6219" s="3" t="s">
+        <v>7975</v>
+      </c>
+    </row>
+    <row r="6220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6220" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6220" s="3" t="s">
+        <v>7976</v>
+      </c>
+    </row>
+    <row r="6221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6221" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6221" s="3" t="s">
+        <v>7977</v>
+      </c>
+    </row>
+    <row r="6222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6222" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6222" s="3" t="s">
+        <v>7979</v>
+      </c>
+    </row>
+    <row r="6223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6223" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6223" s="3" t="s">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="6224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6224" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6224" s="3" t="s">
+        <v>7981</v>
+      </c>
+    </row>
+    <row r="6225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6225" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6225" s="3" t="s">
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="6226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6226" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6226" s="3" t="s">
+        <v>7983</v>
+      </c>
+    </row>
+    <row r="6227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6227" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6227" s="3" t="s">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="6228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6228" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6228" s="3" t="s">
+        <v>7985</v>
+      </c>
+    </row>
+    <row r="6229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6229" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6229" s="3" t="s">
+        <v>7986</v>
+      </c>
+    </row>
+    <row r="6230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6230" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6230" s="3" t="s">
+        <v>7987</v>
+      </c>
+    </row>
+    <row r="6231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6231" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6231" s="3" t="s">
+        <v>7988</v>
+      </c>
+    </row>
+    <row r="6232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6232" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6232" s="3" t="s">
+        <v>7989</v>
+      </c>
+    </row>
+    <row r="6233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6233" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6233" s="3" t="s">
+        <v>7990</v>
+      </c>
+    </row>
+    <row r="6234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6234" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6234" s="3" t="s">
+        <v>7991</v>
+      </c>
+    </row>
+    <row r="6235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6235" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6235" s="3" t="s">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="6236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6236" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6236" s="3" t="s">
+        <v>7993</v>
+      </c>
+    </row>
+    <row r="6237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6237" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6237" s="3" t="s">
+        <v>7994</v>
+      </c>
+    </row>
+    <row r="6238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6238" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6238" s="3" t="s">
+        <v>7995</v>
+      </c>
+    </row>
+    <row r="6239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6239" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6239" s="3" t="s">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="6240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6240" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6240" s="3" t="s">
+        <v>7997</v>
+      </c>
+    </row>
+    <row r="6241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6241" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6241" s="3" t="s">
+        <v>7998</v>
+      </c>
+    </row>
+    <row r="6242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6242" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6242" s="3" t="s">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="6243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6243" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6243" s="3" t="s">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6244" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6244" s="3" t="s">
+        <v>8001</v>
+      </c>
+    </row>
+    <row r="6245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6245" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6245" s="3" t="s">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="6246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6246" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6246" s="3" t="s">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="6247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6247" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6247" s="3" t="s">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="6248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6248" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6248" s="3" t="s">
+        <v>8005</v>
+      </c>
+    </row>
+    <row r="6249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6249" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6249" s="3" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="6250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6250" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6250" s="3" t="s">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="6251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6251" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6251" s="3" t="s">
+        <v>8008</v>
+      </c>
+    </row>
+    <row r="6252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6252" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6252" s="3" t="s">
+        <v>8009</v>
+      </c>
+    </row>
+    <row r="6253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6253" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6253" s="3" t="s">
+        <v>8011</v>
+      </c>
+    </row>
+    <row r="6254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6254" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6254" s="3" t="s">
+        <v>8012</v>
+      </c>
+    </row>
+    <row r="6255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6255" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6255" s="3" t="s">
+        <v>8013</v>
+      </c>
+    </row>
+    <row r="6256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6256" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6256" s="3" t="s">
+        <v>8014</v>
+      </c>
+    </row>
+    <row r="6257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6257" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6257" s="3" t="s">
+        <v>8015</v>
+      </c>
+    </row>
+    <row r="6258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6258" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6258" s="3" t="s">
+        <v>8016</v>
+      </c>
+    </row>
+    <row r="6259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6259" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6259" s="3" t="s">
+        <v>8017</v>
+      </c>
+    </row>
+    <row r="6260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6260" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6260" s="3" t="s">
+        <v>8018</v>
+      </c>
+    </row>
+    <row r="6261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6261" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6261" s="3" t="s">
+        <v>8019</v>
+      </c>
+    </row>
+    <row r="6262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6262" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6262" s="3" t="s">
+        <v>8020</v>
+      </c>
+    </row>
+    <row r="6263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6263" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6263" s="3" t="s">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="6264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6264" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6264" s="3" t="s">
+        <v>8022</v>
+      </c>
+    </row>
+    <row r="6265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6265" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6265" s="3" t="s">
+        <v>8023</v>
+      </c>
+    </row>
+    <row r="6266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6266" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6266" s="3" t="s">
+        <v>8024</v>
+      </c>
+    </row>
+    <row r="6267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6267" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6267" s="3" t="s">
+        <v>8025</v>
+      </c>
+    </row>
+    <row r="6268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6268" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6268" s="3" t="s">
+        <v>8026</v>
+      </c>
+    </row>
+    <row r="6269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6269" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6269" s="3" t="s">
+        <v>8027</v>
+      </c>
+    </row>
+    <row r="6270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6270" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6270" s="3" t="s">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="6271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6271" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6271" s="3" t="s">
+        <v>8029</v>
+      </c>
+    </row>
+    <row r="6272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6272" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6272" s="3" t="s">
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="6273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6273" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6273" s="3" t="s">
+        <v>8031</v>
+      </c>
+    </row>
+    <row r="6274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6274" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6274" s="3" t="s">
+        <v>8032</v>
+      </c>
+    </row>
+    <row r="6275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6275" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6275" s="3" t="s">
+        <v>8033</v>
+      </c>
+    </row>
+    <row r="6276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6276" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6276" s="3" t="s">
+        <v>8034</v>
+      </c>
+    </row>
+    <row r="6277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6277" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6277" s="3" t="s">
+        <v>8035</v>
+      </c>
+    </row>
+    <row r="6278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6278" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6278" s="3" t="s">
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="6279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6279" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6279" s="3" t="s">
+        <v>8037</v>
+      </c>
+    </row>
+    <row r="6280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6280" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6280" s="3" t="s">
+        <v>8038</v>
+      </c>
+    </row>
+    <row r="6281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6281" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6281" s="3" t="s">
+        <v>8039</v>
+      </c>
+    </row>
+    <row r="6282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6282" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6282" s="3" t="s">
+        <v>8040</v>
+      </c>
+    </row>
+    <row r="6283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6283" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6283" s="3" t="s">
+        <v>8041</v>
+      </c>
+    </row>
+    <row r="6284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6284" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6284" s="3" t="s">
+        <v>8042</v>
+      </c>
+    </row>
+    <row r="6285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6285" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6285" s="3" t="s">
+        <v>8043</v>
+      </c>
+    </row>
+    <row r="6286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6286" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6286" s="3" t="s">
+        <v>8044</v>
+      </c>
+    </row>
+    <row r="6287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6287" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6287" s="3" t="s">
+        <v>8045</v>
+      </c>
+    </row>
+    <row r="6288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6288" s="3">
+        <v>8200</v>
+      </c>
+      <c r="C6288" s="3" t="s">
+        <v>8046</v>
+      </c>
+    </row>
+    <row r="6289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r=